--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H107"/>
+  <dimension ref="A1:H112"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,126 +492,130 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29000</v>
+        <v>14970</v>
       </c>
       <c r="F2" t="n">
-        <v>353</v>
+        <v>983</v>
       </c>
       <c r="G2" t="n">
-        <v>10237000</v>
+        <v>14715510</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1853000</v>
+        <v>114100</v>
       </c>
       <c r="F3" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="G3" t="n">
-        <v>20383000</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>19054700</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.31</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>269000</v>
+        <v>24600</v>
       </c>
       <c r="F4" t="n">
-        <v>76</v>
+        <v>407</v>
       </c>
       <c r="G4" t="n">
-        <v>20444000</v>
+        <v>10012200</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>106300</v>
+        <v>44700</v>
       </c>
       <c r="F5" t="n">
-        <v>194</v>
+        <v>488</v>
       </c>
       <c r="G5" t="n">
-        <v>20622200</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>21813600</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5.67</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,30 +624,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>123100</v>
+        <v>167600</v>
       </c>
       <c r="F6" t="n">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="G6" t="n">
-        <v>20557700</v>
+        <v>20112000</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,30 +656,30 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1856000</v>
+        <v>29000</v>
       </c>
       <c r="F7" t="n">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="G7" t="n">
-        <v>42688000</v>
+        <v>10237000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -684,30 +688,30 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>49000</v>
+        <v>1853000</v>
       </c>
       <c r="F8" t="n">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>8183000</v>
+        <v>20383000</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,77 +720,77 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>13340</v>
+        <v>269000</v>
       </c>
       <c r="F9" t="n">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="G9" t="n">
-        <v>3148240</v>
+        <v>20444000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>29800</v>
+        <v>106300</v>
       </c>
       <c r="F10" t="n">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="G10" t="n">
-        <v>1966800</v>
+        <v>20622200</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>269500</v>
+        <v>123100</v>
       </c>
       <c r="F11" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G11" t="n">
-        <v>31801000</v>
+        <v>20557700</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +802,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +816,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>330000</v>
+        <v>1856000</v>
       </c>
       <c r="F12" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G12" t="n">
-        <v>7920000</v>
+        <v>42688000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,27 +834,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>35550</v>
+        <v>49000</v>
       </c>
       <c r="F13" t="n">
-        <v>581</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
-        <v>20654550</v>
+        <v>8183000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -876,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>574000</v>
+        <v>13340</v>
       </c>
       <c r="F14" t="n">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="G14" t="n">
-        <v>12628000</v>
+        <v>3148240</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>165900</v>
+        <v>29800</v>
       </c>
       <c r="F15" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G15" t="n">
-        <v>3981600</v>
+        <v>1966800</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,27 +930,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>91300</v>
+        <v>269500</v>
       </c>
       <c r="F16" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G16" t="n">
-        <v>4108500</v>
+        <v>31801000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,27 +962,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>224500</v>
+        <v>330000</v>
       </c>
       <c r="F17" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="G17" t="n">
-        <v>20654000</v>
+        <v>7920000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,12 +994,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1004,13 +1008,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6010</v>
+        <v>35550</v>
       </c>
       <c r="F18" t="n">
-        <v>3435</v>
+        <v>581</v>
       </c>
       <c r="G18" t="n">
-        <v>20644350</v>
+        <v>20654550</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,12 +1026,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1036,13 +1040,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>25800</v>
+        <v>574000</v>
       </c>
       <c r="F19" t="n">
-        <v>351</v>
+        <v>22</v>
       </c>
       <c r="G19" t="n">
-        <v>9055800</v>
+        <v>12628000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,27 +1058,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>49150</v>
+        <v>165900</v>
       </c>
       <c r="F20" t="n">
-        <v>420</v>
+        <v>24</v>
       </c>
       <c r="G20" t="n">
-        <v>20643000</v>
+        <v>3981600</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,27 +1090,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>19280</v>
+        <v>91300</v>
       </c>
       <c r="F21" t="n">
-        <v>1071</v>
+        <v>45</v>
       </c>
       <c r="G21" t="n">
-        <v>20648880</v>
+        <v>4108500</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,27 +1122,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>19740</v>
+        <v>224500</v>
       </c>
       <c r="F22" t="n">
-        <v>523</v>
+        <v>92</v>
       </c>
       <c r="G22" t="n">
-        <v>10324020</v>
+        <v>20654000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,12 +1154,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1164,13 +1168,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>25150</v>
+        <v>6010</v>
       </c>
       <c r="F23" t="n">
-        <v>821</v>
+        <v>3435</v>
       </c>
       <c r="G23" t="n">
-        <v>20648150</v>
+        <v>20644350</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,12 +1186,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1196,13 +1200,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>153500</v>
+        <v>25800</v>
       </c>
       <c r="F24" t="n">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="G24" t="n">
-        <v>3684000</v>
+        <v>9055800</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,12 +1218,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1228,13 +1232,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6240</v>
+        <v>49150</v>
       </c>
       <c r="F25" t="n">
-        <v>3308</v>
+        <v>420</v>
       </c>
       <c r="G25" t="n">
-        <v>20641920</v>
+        <v>20643000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1246,12 +1250,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1260,13 +1264,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15520</v>
+        <v>19280</v>
       </c>
       <c r="F26" t="n">
-        <v>1330</v>
+        <v>1071</v>
       </c>
       <c r="G26" t="n">
-        <v>20641600</v>
+        <v>20648880</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1278,12 +1282,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1292,13 +1296,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>24200</v>
+        <v>19740</v>
       </c>
       <c r="F27" t="n">
-        <v>210</v>
+        <v>523</v>
       </c>
       <c r="G27" t="n">
-        <v>5082000</v>
+        <v>10324020</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1310,12 +1314,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1324,13 +1328,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>36300</v>
+        <v>25150</v>
       </c>
       <c r="F28" t="n">
-        <v>569</v>
+        <v>821</v>
       </c>
       <c r="G28" t="n">
-        <v>20654700</v>
+        <v>20648150</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1342,12 +1346,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1356,13 +1360,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>279500</v>
+        <v>153500</v>
       </c>
       <c r="F29" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G29" t="n">
-        <v>12018500</v>
+        <v>3684000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1374,27 +1378,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>132600</v>
+        <v>6240</v>
       </c>
       <c r="F30" t="n">
-        <v>90</v>
+        <v>3308</v>
       </c>
       <c r="G30" t="n">
-        <v>11934000</v>
+        <v>20641920</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1406,27 +1410,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>44600</v>
+        <v>15520</v>
       </c>
       <c r="F31" t="n">
-        <v>139</v>
+        <v>1330</v>
       </c>
       <c r="G31" t="n">
-        <v>6199400</v>
+        <v>20641600</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1438,12 +1442,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1452,13 +1456,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>147100</v>
+        <v>24200</v>
       </c>
       <c r="F32" t="n">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="G32" t="n">
-        <v>882600</v>
+        <v>5082000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1470,27 +1474,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>33500</v>
+        <v>36300</v>
       </c>
       <c r="F33" t="n">
-        <v>8</v>
+        <v>569</v>
       </c>
       <c r="G33" t="n">
-        <v>268000</v>
+        <v>20654700</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1502,12 +1506,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1516,13 +1520,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>143100</v>
+        <v>279500</v>
       </c>
       <c r="F34" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="G34" t="n">
-        <v>13594500</v>
+        <v>12018500</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1534,12 +1538,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1548,13 +1552,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>83800</v>
+        <v>132600</v>
       </c>
       <c r="F35" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G35" t="n">
-        <v>8882800</v>
+        <v>11934000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1566,27 +1570,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>42300</v>
+        <v>44600</v>
       </c>
       <c r="F36" t="n">
-        <v>488</v>
+        <v>139</v>
       </c>
       <c r="G36" t="n">
-        <v>20642400</v>
+        <v>6199400</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1598,12 +1602,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1612,62 +1616,62 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>81200</v>
+        <v>147100</v>
       </c>
       <c r="F37" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="G37" t="n">
-        <v>10962000</v>
+        <v>882600</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>78600</v>
+        <v>33500</v>
       </c>
       <c r="F38" t="n">
-        <v>389</v>
+        <v>8</v>
       </c>
       <c r="G38" t="n">
-        <v>30575400</v>
+        <v>268000</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1676,196 +1680,190 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>92500</v>
+        <v>143100</v>
       </c>
       <c r="F39" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G39" t="n">
-        <v>9805000</v>
+        <v>13594500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>25550</v>
+        <v>83800</v>
       </c>
       <c r="F40" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G40" t="n">
-        <v>29408050</v>
+        <v>8882800</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>21800</v>
+        <v>42300</v>
       </c>
       <c r="F41" t="n">
-        <v>832</v>
+        <v>488</v>
       </c>
       <c r="G41" t="n">
-        <v>18137600</v>
+        <v>20642400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>32250</v>
+        <v>81200</v>
       </c>
       <c r="F42" t="n">
-        <v>878</v>
+        <v>135</v>
       </c>
       <c r="G42" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H42" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>10962000</v>
+      </c>
+      <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>105800</v>
+        <v>78600</v>
       </c>
       <c r="F43" t="n">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="G43" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H43" t="n">
-        <v>17.17</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>33750</v>
+        <v>92500</v>
       </c>
       <c r="F44" t="n">
-        <v>791</v>
+        <v>106</v>
       </c>
       <c r="G44" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H44" t="n">
-        <v>0.29</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1874,194 +1872,196 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>86300</v>
+        <v>25550</v>
       </c>
       <c r="F45" t="n">
-        <v>352</v>
+        <v>1151</v>
       </c>
       <c r="G45" t="n">
-        <v>30377600</v>
+        <v>29408050</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21000</v>
+        <v>21800</v>
       </c>
       <c r="F46" t="n">
-        <v>1517</v>
+        <v>832</v>
       </c>
       <c r="G46" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H46" t="n">
-        <v>3.96</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>21900</v>
+        <v>32250</v>
       </c>
       <c r="F47" t="n">
-        <v>906</v>
+        <v>878</v>
       </c>
       <c r="G47" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>135300</v>
+        <v>105800</v>
       </c>
       <c r="F48" t="n">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="G48" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H48" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>22250</v>
+        <v>33750</v>
       </c>
       <c r="F49" t="n">
-        <v>1399</v>
+        <v>791</v>
       </c>
       <c r="G49" t="n">
-        <v>31127750</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>33500</v>
+        <v>86300</v>
       </c>
       <c r="F50" t="n">
-        <v>848</v>
+        <v>352</v>
       </c>
       <c r="G50" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H50" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2070,307 +2070,311 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>300000</v>
+        <v>21000</v>
       </c>
       <c r="F51" t="n">
-        <v>104</v>
+        <v>1517</v>
       </c>
       <c r="G51" t="n">
-        <v>31200000</v>
+        <v>31857000</v>
       </c>
       <c r="H51" t="n">
-        <v>20.95</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>28200</v>
+        <v>21900</v>
       </c>
       <c r="F52" t="n">
-        <v>1105</v>
+        <v>906</v>
       </c>
       <c r="G52" t="n">
-        <v>31161000</v>
+        <v>19841400</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>398000</v>
+        <v>135300</v>
       </c>
       <c r="F53" t="n">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="G53" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>30577800</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>5620</v>
+        <v>22250</v>
       </c>
       <c r="F54" t="n">
-        <v>4707</v>
+        <v>1399</v>
       </c>
       <c r="G54" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>126900</v>
+        <v>33500</v>
       </c>
       <c r="F55" t="n">
-        <v>246</v>
+        <v>848</v>
       </c>
       <c r="G55" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>28408000</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1671000</v>
+        <v>300000</v>
       </c>
       <c r="F56" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="G56" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H56" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>50600</v>
+        <v>28200</v>
       </c>
       <c r="F57" t="n">
-        <v>186</v>
+        <v>1105</v>
       </c>
       <c r="G57" t="n">
-        <v>9411600</v>
+        <v>31161000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>11720</v>
+        <v>398000</v>
       </c>
       <c r="F58" t="n">
-        <v>665</v>
+        <v>72</v>
       </c>
       <c r="G58" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H58" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>414000</v>
+        <v>5620</v>
       </c>
       <c r="F59" t="n">
-        <v>26</v>
+        <v>4707</v>
       </c>
       <c r="G59" t="n">
-        <v>10764000</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>257000</v>
+        <v>126900</v>
       </c>
       <c r="F60" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G60" t="n">
-        <v>61423000</v>
+        <v>31217400</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2382,27 +2386,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>33900</v>
+        <v>1671000</v>
       </c>
       <c r="F61" t="n">
-        <v>292</v>
+        <v>44</v>
       </c>
       <c r="G61" t="n">
-        <v>9898800</v>
+        <v>73524000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2414,12 +2418,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,13 +2432,13 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>515000</v>
+        <v>50600</v>
       </c>
       <c r="F62" t="n">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="G62" t="n">
-        <v>8755000</v>
+        <v>9411600</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2446,12 +2450,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2460,13 +2464,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>141200</v>
+        <v>11720</v>
       </c>
       <c r="F63" t="n">
-        <v>81</v>
+        <v>665</v>
       </c>
       <c r="G63" t="n">
-        <v>11437200</v>
+        <v>7793800</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2478,12 +2482,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2492,13 +2496,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6320</v>
+        <v>414000</v>
       </c>
       <c r="F64" t="n">
-        <v>1396</v>
+        <v>26</v>
       </c>
       <c r="G64" t="n">
-        <v>8822720</v>
+        <v>10764000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2510,27 +2514,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>90300</v>
+        <v>257000</v>
       </c>
       <c r="F65" t="n">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="G65" t="n">
-        <v>29979600</v>
+        <v>61423000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2542,31 +2546,29 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>163100</v>
+        <v>33900</v>
       </c>
       <c r="F66" t="n">
-        <v>119</v>
+        <v>292</v>
       </c>
       <c r="G66" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>9898800</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2576,12 +2578,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2590,13 +2592,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>37900</v>
+        <v>515000</v>
       </c>
       <c r="F67" t="n">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="G67" t="n">
-        <v>6177700</v>
+        <v>8755000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2608,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2622,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>19990</v>
+        <v>141200</v>
       </c>
       <c r="F68" t="n">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="G68" t="n">
-        <v>12293850</v>
+        <v>11437200</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2640,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2654,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35100</v>
+        <v>6320</v>
       </c>
       <c r="F69" t="n">
-        <v>320</v>
+        <v>1396</v>
       </c>
       <c r="G69" t="n">
-        <v>11232000</v>
+        <v>8822720</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2672,27 +2674,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>286000</v>
+        <v>90300</v>
       </c>
       <c r="F70" t="n">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="G70" t="n">
-        <v>5720000</v>
+        <v>29979600</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2704,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2718,16 +2720,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>416000</v>
+        <v>163100</v>
       </c>
       <c r="F71" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="G71" t="n">
-        <v>21216000</v>
+        <v>19408900</v>
       </c>
       <c r="H71" t="n">
-        <v>5.85</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="72">
@@ -2738,12 +2740,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2754,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>49450</v>
+        <v>37900</v>
       </c>
       <c r="F72" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G72" t="n">
-        <v>7565850</v>
+        <v>6177700</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2772,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2786,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>138000</v>
+        <v>19990</v>
       </c>
       <c r="F73" t="n">
-        <v>68</v>
+        <v>615</v>
       </c>
       <c r="G73" t="n">
-        <v>9384000</v>
+        <v>12293850</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2804,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2818,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>31950</v>
+        <v>35100</v>
       </c>
       <c r="F74" t="n">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="G74" t="n">
-        <v>10831050</v>
+        <v>11232000</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,12 +2836,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2848,128 +2850,128 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>124800</v>
+        <v>286000</v>
       </c>
       <c r="F75" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="G75" t="n">
-        <v>9734400</v>
+        <v>5720000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10800</v>
+        <v>416000</v>
       </c>
       <c r="F76" t="n">
-        <v>1892</v>
+        <v>51</v>
       </c>
       <c r="G76" t="n">
-        <v>20433600</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H76" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>11880</v>
+        <v>49450</v>
       </c>
       <c r="F77" t="n">
-        <v>1474</v>
+        <v>153</v>
       </c>
       <c r="G77" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>7565850</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>20200</v>
+        <v>138000</v>
       </c>
       <c r="F78" t="n">
-        <v>1517</v>
+        <v>68</v>
       </c>
       <c r="G78" t="n">
-        <v>30643400</v>
+        <v>9384000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2978,49 +2980,47 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>102200</v>
+        <v>31950</v>
       </c>
       <c r="F79" t="n">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="G79" t="n">
-        <v>20440000</v>
+        <v>10831050</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>23450</v>
+        <v>124800</v>
       </c>
       <c r="F80" t="n">
-        <v>762</v>
+        <v>78</v>
       </c>
       <c r="G80" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H80" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>9734400</v>
+      </c>
+      <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3030,31 +3030,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>22050</v>
+        <v>10800</v>
       </c>
       <c r="F81" t="n">
-        <v>875</v>
+        <v>1892</v>
       </c>
       <c r="G81" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3064,29 +3062,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>32550</v>
+        <v>11880</v>
       </c>
       <c r="F82" t="n">
-        <v>628</v>
+        <v>1474</v>
       </c>
       <c r="G82" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3096,142 +3096,144 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>99700</v>
+        <v>20200</v>
       </c>
       <c r="F83" t="n">
-        <v>180</v>
+        <v>1517</v>
       </c>
       <c r="G83" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>30643400</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1662000</v>
+        <v>102200</v>
       </c>
       <c r="F84" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G84" t="n">
-        <v>249300000</v>
+        <v>20440000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>49700</v>
+        <v>23450</v>
       </c>
       <c r="F85" t="n">
-        <v>402</v>
+        <v>762</v>
       </c>
       <c r="G85" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H85" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H85" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>435000</v>
+        <v>22050</v>
       </c>
       <c r="F86" t="n">
-        <v>46</v>
+        <v>875</v>
       </c>
       <c r="G86" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3240,47 +3242,49 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>268500</v>
+        <v>32550</v>
       </c>
       <c r="F87" t="n">
-        <v>931</v>
+        <v>628</v>
       </c>
       <c r="G87" t="n">
-        <v>249973500</v>
+        <v>20441400</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>13570</v>
+        <v>99700</v>
       </c>
       <c r="F88" t="n">
-        <v>1474</v>
+        <v>180</v>
       </c>
       <c r="G88" t="n">
-        <v>20002180</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3290,12 +3294,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3304,13 +3308,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>343500</v>
+        <v>1662000</v>
       </c>
       <c r="F89" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="G89" t="n">
-        <v>29884500</v>
+        <v>249300000</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3322,12 +3326,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3336,13 +3340,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>34150</v>
+        <v>49700</v>
       </c>
       <c r="F90" t="n">
-        <v>586</v>
+        <v>402</v>
       </c>
       <c r="G90" t="n">
-        <v>20011900</v>
+        <v>19979400</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3354,12 +3358,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3368,13 +3372,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>488000</v>
+        <v>435000</v>
       </c>
       <c r="F91" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G91" t="n">
-        <v>20008000</v>
+        <v>20010000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3386,12 +3390,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3400,13 +3404,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>153600</v>
+        <v>268500</v>
       </c>
       <c r="F92" t="n">
-        <v>130</v>
+        <v>931</v>
       </c>
       <c r="G92" t="n">
-        <v>19968000</v>
+        <v>249973500</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3418,12 +3422,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3432,13 +3436,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>99800</v>
+        <v>13570</v>
       </c>
       <c r="F93" t="n">
-        <v>200</v>
+        <v>1474</v>
       </c>
       <c r="G93" t="n">
-        <v>19960000</v>
+        <v>20002180</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3450,12 +3454,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3464,13 +3468,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6040</v>
+        <v>343500</v>
       </c>
       <c r="F94" t="n">
-        <v>3311</v>
+        <v>87</v>
       </c>
       <c r="G94" t="n">
-        <v>19998440</v>
+        <v>29884500</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3482,12 +3486,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3496,13 +3500,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>26250</v>
+        <v>34150</v>
       </c>
       <c r="F95" t="n">
-        <v>762</v>
+        <v>586</v>
       </c>
       <c r="G95" t="n">
-        <v>20002500</v>
+        <v>20011900</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3514,12 +3518,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3528,13 +3532,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>22850</v>
+        <v>488000</v>
       </c>
       <c r="F96" t="n">
-        <v>875</v>
+        <v>41</v>
       </c>
       <c r="G96" t="n">
-        <v>19993750</v>
+        <v>20008000</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3546,12 +3550,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>S-OIL</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3560,13 +3564,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>168500</v>
+        <v>153600</v>
       </c>
       <c r="F97" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G97" t="n">
-        <v>20051500</v>
+        <v>19968000</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3578,12 +3582,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3592,13 +3596,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>22850</v>
+        <v>99800</v>
       </c>
       <c r="F98" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G98" t="n">
-        <v>19993750</v>
+        <v>19960000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3610,12 +3614,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3624,13 +3628,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>37900</v>
+        <v>6040</v>
       </c>
       <c r="F99" t="n">
-        <v>528</v>
+        <v>3311</v>
       </c>
       <c r="G99" t="n">
-        <v>20011200</v>
+        <v>19998440</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3642,12 +3646,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3656,13 +3660,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>239000</v>
+        <v>26250</v>
       </c>
       <c r="F100" t="n">
-        <v>84</v>
+        <v>762</v>
       </c>
       <c r="G100" t="n">
-        <v>20076000</v>
+        <v>20002500</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3674,12 +3678,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3688,13 +3692,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>298000</v>
+        <v>22850</v>
       </c>
       <c r="F101" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G101" t="n">
-        <v>34866000</v>
+        <v>19993750</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3706,12 +3710,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3720,13 +3724,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>393000</v>
+        <v>168500</v>
       </c>
       <c r="F102" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="G102" t="n">
-        <v>20043000</v>
+        <v>20051500</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3738,12 +3742,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3752,13 +3756,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>110900</v>
+        <v>22850</v>
       </c>
       <c r="F103" t="n">
-        <v>180</v>
+        <v>875</v>
       </c>
       <c r="G103" t="n">
-        <v>19962000</v>
+        <v>19993750</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3770,12 +3774,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3784,13 +3788,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>44500</v>
+        <v>37900</v>
       </c>
       <c r="F104" t="n">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="G104" t="n">
-        <v>19980500</v>
+        <v>20011200</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3802,12 +3806,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3816,13 +3820,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>135000</v>
+        <v>239000</v>
       </c>
       <c r="F105" t="n">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="G105" t="n">
-        <v>19980000</v>
+        <v>20076000</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3834,12 +3838,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3848,13 +3852,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>33750</v>
+        <v>298000</v>
       </c>
       <c r="F106" t="n">
-        <v>593</v>
+        <v>117</v>
       </c>
       <c r="G106" t="n">
-        <v>20013750</v>
+        <v>34866000</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3866,29 +3870,189 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F107" t="n">
+        <v>51</v>
+      </c>
+      <c r="G107" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E108" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F108" t="n">
+        <v>180</v>
+      </c>
+      <c r="G108" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E109" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F109" t="n">
+        <v>449</v>
+      </c>
+      <c r="G109" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F110" t="n">
+        <v>148</v>
+      </c>
+      <c r="G110" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F111" t="n">
+        <v>593</v>
+      </c>
+      <c r="G111" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C107" t="inlineStr">
+      <c r="C112" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E107" t="n">
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
         <v>124600</v>
       </c>
-      <c r="F107" t="n">
+      <c r="F112" t="n">
         <v>161</v>
       </c>
-      <c r="G107" t="n">
+      <c r="G112" t="n">
         <v>20060600</v>
       </c>
-      <c r="H107" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H112"/>
+  <dimension ref="A1:H113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,32 +473,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14970</v>
+        <v>148700</v>
       </c>
       <c r="F2" t="n">
-        <v>983</v>
+        <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>14715510</v>
+        <v>9962900</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>114100</v>
+        <v>14970</v>
       </c>
       <c r="F3" t="n">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="G3" t="n">
-        <v>19054700</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-7.31</v>
-      </c>
+        <v>14715510</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,29 +542,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>24600</v>
+        <v>114100</v>
       </c>
       <c r="F4" t="n">
-        <v>407</v>
+        <v>167</v>
       </c>
       <c r="G4" t="n">
-        <v>10012200</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>19054700</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-7.31</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,31 +576,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>44700</v>
+        <v>24600</v>
       </c>
       <c r="F5" t="n">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G5" t="n">
-        <v>21813600</v>
-      </c>
-      <c r="H5" t="n">
-        <v>5.67</v>
-      </c>
+        <v>10012200</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,76 +608,78 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>167600</v>
+        <v>44700</v>
       </c>
       <c r="F6" t="n">
-        <v>120</v>
+        <v>488</v>
       </c>
       <c r="G6" t="n">
-        <v>20112000</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>21813600</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5.67</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>29000</v>
+        <v>167600</v>
       </c>
       <c r="F7" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>10237000</v>
+        <v>20112000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1853000</v>
+        <v>29000</v>
       </c>
       <c r="F8" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G8" t="n">
-        <v>20383000</v>
+        <v>10237000</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,12 +706,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F9" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -738,27 +738,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F10" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G10" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,45 +784,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F11" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G11" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F12" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G12" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F13" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G13" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F14" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G14" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F15" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G15" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,12 +930,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,13 +944,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F16" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G16" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G17" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +994,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F18" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G18" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,27 +1026,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F19" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G19" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F20" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,27 +1090,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F21" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G21" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,27 +1122,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F22" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G22" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F23" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G23" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,27 +1186,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F24" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G24" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,27 +1218,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F25" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G25" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F26" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G26" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,27 +1282,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F27" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G27" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F28" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G28" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1346,27 +1346,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F29" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G29" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1378,27 +1378,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F30" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1424,13 +1424,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F31" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G31" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1442,27 +1442,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F32" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G32" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F33" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G33" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1506,27 +1506,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F34" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G34" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1538,12 +1538,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1552,13 +1552,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F35" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G35" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1584,13 +1584,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F36" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G36" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F37" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G37" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1634,12 +1634,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1648,13 +1648,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F38" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G38" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F39" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G39" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F40" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G40" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1730,27 +1730,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F41" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G41" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1762,34 +1762,34 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F42" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G42" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -1804,49 +1804,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F43" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G43" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F44" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G44" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1858,95 +1858,93 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F45" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G45" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F46" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G46" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F47" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G47" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1956,12 +1954,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1970,16 +1968,16 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F48" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G48" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H48" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="49">
@@ -1990,12 +1988,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2004,16 +2002,16 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F49" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G49" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H49" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="50">
@@ -2024,63 +2022,63 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F50" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G50" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H50" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F51" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G51" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H51" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2090,29 +2088,31 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F52" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G52" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2122,44 +2122,44 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F53" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G53" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2168,13 +2168,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F54" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G54" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2186,31 +2186,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F55" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G55" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2220,12 +2218,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2234,49 +2232,51 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F56" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G56" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H56" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F57" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G57" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2286,31 +2286,29 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F58" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G58" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2320,12 +2318,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2334,16 +2332,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F59" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G59" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H59" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="60">
@@ -2354,59 +2352,61 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F60" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G60" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H60" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F61" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G61" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2418,27 +2418,27 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F62" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G62" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2450,12 +2450,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2464,13 +2464,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F63" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G63" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2482,12 +2482,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2496,13 +2496,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G64" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2514,27 +2514,27 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F65" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G65" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2546,27 +2546,27 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F66" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G66" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F67" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G67" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F68" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G68" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F69" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G69" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,27 +2674,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F70" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G70" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,31 +2706,29 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F71" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G71" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H71" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2740,29 +2738,31 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F72" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G72" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H72" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2772,12 +2772,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2786,13 +2786,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F73" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G73" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2804,12 +2804,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2818,13 +2818,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F74" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G74" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2836,12 +2836,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2850,13 +2850,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G75" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2868,31 +2868,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F76" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G76" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H76" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2902,29 +2900,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F77" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G77" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H77" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2934,12 +2934,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2948,13 +2948,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F78" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G78" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2966,12 +2966,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2980,13 +2980,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F79" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G79" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2998,12 +2998,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3012,45 +3012,45 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F80" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G80" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F81" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G81" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3062,31 +3062,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F82" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G82" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3096,29 +3094,31 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F83" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G83" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H83" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H83" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3128,27 +3128,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F84" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G84" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3160,31 +3160,29 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F85" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G85" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H85" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3194,12 +3192,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3208,16 +3206,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F86" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G86" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H86" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="87">
@@ -3228,29 +3226,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F87" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G87" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H87" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3260,63 +3260,63 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F88" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G88" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F89" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G89" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H89" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H89" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3326,12 +3326,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3340,13 +3340,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F90" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G90" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3358,12 +3358,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3372,13 +3372,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F91" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G91" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3404,13 +3404,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F92" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G92" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F93" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G93" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F94" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G94" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F95" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G95" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F96" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G96" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>S-OIL</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F97" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G97" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F98" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G98" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F99" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G99" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F100" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G100" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F101" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G101" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3724,13 +3724,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F102" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G102" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F103" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G103" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F104" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G104" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3820,13 +3820,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F105" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G105" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F106" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G106" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3870,12 +3870,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3884,13 +3884,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F107" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G107" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3916,13 +3916,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F108" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G108" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F109" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G109" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F110" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G110" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3998,12 +3998,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F111" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G111" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4030,29 +4030,61 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F112" t="n">
+        <v>593</v>
+      </c>
+      <c r="G112" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C112" t="inlineStr">
+      <c r="C113" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E112" t="n">
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
         <v>124600</v>
       </c>
-      <c r="F112" t="n">
+      <c r="F113" t="n">
         <v>161</v>
       </c>
-      <c r="G112" t="n">
+      <c r="G113" t="n">
         <v>20060600</v>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14970</v>
+        <v>14540</v>
       </c>
       <c r="F3" t="n">
         <v>983</v>
       </c>
       <c r="G3" t="n">
-        <v>14715510</v>
+        <v>14292820</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>114100</v>
+        <v>113400</v>
       </c>
       <c r="F4" t="n">
         <v>167</v>
       </c>
       <c r="G4" t="n">
-        <v>19054700</v>
+        <v>18937800</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.31</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="5">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24600</v>
+        <v>24350</v>
       </c>
       <c r="F5" t="n">
         <v>407</v>
       </c>
       <c r="G5" t="n">
-        <v>10012200</v>
+        <v>9910450</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44700</v>
+        <v>44100</v>
       </c>
       <c r="F6" t="n">
         <v>488</v>
       </c>
       <c r="G6" t="n">
-        <v>21813600</v>
+        <v>21520800</v>
       </c>
       <c r="H6" t="n">
-        <v>5.67</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>167600</v>
+        <v>165700</v>
       </c>
       <c r="F7" t="n">
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>20112000</v>
+        <v>19884000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -688,13 +688,13 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>29000</v>
+        <v>28950</v>
       </c>
       <c r="F8" t="n">
         <v>353</v>
       </c>
       <c r="G8" t="n">
-        <v>10237000</v>
+        <v>10219350</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -492,13 +492,13 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>148700</v>
+        <v>147200</v>
       </c>
       <c r="F2" t="n">
         <v>67</v>
       </c>
       <c r="G2" t="n">
-        <v>9962900</v>
+        <v>9862400</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14540</v>
+        <v>14970</v>
       </c>
       <c r="F3" t="n">
         <v>983</v>
       </c>
       <c r="G3" t="n">
-        <v>14292820</v>
+        <v>14715510</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113400</v>
+        <v>114100</v>
       </c>
       <c r="F4" t="n">
         <v>167</v>
       </c>
       <c r="G4" t="n">
-        <v>18937800</v>
+        <v>19054700</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.88</v>
+        <v>-7.31</v>
       </c>
     </row>
     <row r="5">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24350</v>
+        <v>24600</v>
       </c>
       <c r="F5" t="n">
         <v>407</v>
       </c>
       <c r="G5" t="n">
-        <v>9910450</v>
+        <v>10012200</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44100</v>
+        <v>44700</v>
       </c>
       <c r="F6" t="n">
         <v>488</v>
       </c>
       <c r="G6" t="n">
-        <v>21520800</v>
+        <v>21813600</v>
       </c>
       <c r="H6" t="n">
-        <v>4.26</v>
+        <v>5.67</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>165700</v>
+        <v>167600</v>
       </c>
       <c r="F7" t="n">
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>19884000</v>
+        <v>20112000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -524,13 +524,13 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14970</v>
+        <v>14540</v>
       </c>
       <c r="F3" t="n">
         <v>983</v>
       </c>
       <c r="G3" t="n">
-        <v>14715510</v>
+        <v>14292820</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -556,16 +556,16 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>114100</v>
+        <v>113400</v>
       </c>
       <c r="F4" t="n">
         <v>167</v>
       </c>
       <c r="G4" t="n">
-        <v>19054700</v>
+        <v>18937800</v>
       </c>
       <c r="H4" t="n">
-        <v>-7.31</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="5">
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24600</v>
+        <v>24350</v>
       </c>
       <c r="F5" t="n">
         <v>407</v>
       </c>
       <c r="G5" t="n">
-        <v>10012200</v>
+        <v>9910450</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -622,16 +622,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44700</v>
+        <v>44100</v>
       </c>
       <c r="F6" t="n">
         <v>488</v>
       </c>
       <c r="G6" t="n">
-        <v>21813600</v>
+        <v>21520800</v>
       </c>
       <c r="H6" t="n">
-        <v>5.67</v>
+        <v>4.26</v>
       </c>
     </row>
     <row r="7">
@@ -656,13 +656,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>167600</v>
+        <v>165700</v>
       </c>
       <c r="F7" t="n">
         <v>120</v>
       </c>
       <c r="G7" t="n">
-        <v>20112000</v>
+        <v>19884000</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H113"/>
+  <dimension ref="A1:H117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,115 +473,113 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F2" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G2" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F3" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G3" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F4" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G4" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,49 +588,47 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F5" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G5" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F6" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G6" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H6" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,140 +638,144 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F7" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G7" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F8" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G8" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F9" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G9" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F10" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G10" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H10" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,52 +784,52 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F11" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G11" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F12" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G12" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -848,30 +848,30 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F13" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G13" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,77 +880,77 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F14" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G14" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F15" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G15" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F16" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G16" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,12 +962,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F17" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F18" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G18" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,27 +1026,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F19" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G19" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1058,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1072,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F20" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G20" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,12 +1090,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,13 +1104,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F21" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G21" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,27 +1122,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F22" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G22" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,12 +1154,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1168,13 +1168,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F23" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G23" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,27 +1186,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F24" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G24" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,13 +1232,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F25" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G25" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,27 +1250,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F26" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G26" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1296,13 +1296,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F27" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G27" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,27 +1314,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F28" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G28" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1346,27 +1346,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F29" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G29" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1378,27 +1378,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G30" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1410,12 +1410,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1424,13 +1424,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F31" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G31" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1442,27 +1442,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F32" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G32" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1474,27 +1474,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F33" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G33" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1506,27 +1506,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F34" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G34" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1538,27 +1538,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F35" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G35" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1570,27 +1570,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F36" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G36" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1602,12 +1602,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F37" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G37" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1634,27 +1634,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F38" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G38" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1666,12 +1666,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1680,13 +1680,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F39" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G39" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1698,12 +1698,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1712,13 +1712,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F40" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G40" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1730,12 +1730,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1744,13 +1744,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F41" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G41" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1762,27 +1762,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F42" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G42" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1794,12 +1794,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1808,62 +1808,62 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F43" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G43" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F44" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G44" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1872,30 +1872,30 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F45" t="n">
         <v>106</v>
       </c>
       <c r="G45" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1904,196 +1904,190 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F46" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G46" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F47" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G47" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F48" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G48" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H48" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F49" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G49" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H49" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F50" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G50" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H50" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F51" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G51" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2102,96 +2096,100 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F52" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G52" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H52" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F53" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G53" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H53" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F54" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G54" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2200,30 +2198,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F55" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G55" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2232,66 +2230,64 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F56" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G56" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H56" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F57" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G57" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H57" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,64 +2296,62 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F58" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G58" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F59" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G59" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2366,175 +2360,181 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F60" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G60" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H60" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F61" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G61" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H61" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F62" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G62" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F63" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G63" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F64" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G64" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H64" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F65" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G65" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2560,13 +2560,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F66" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G66" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2578,12 +2578,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2592,13 +2592,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F67" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G67" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F68" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G68" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F69" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G69" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,27 +2674,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F70" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G70" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,27 +2706,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F71" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G71" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,31 +2738,29 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F72" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G72" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H72" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2772,12 +2770,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2786,13 +2784,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F73" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G73" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2804,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2818,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F74" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G74" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2836,27 +2834,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F75" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G75" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2868,29 +2866,31 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G76" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2900,31 +2900,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F77" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G77" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H77" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2934,12 +2932,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2948,13 +2946,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F78" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G78" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2966,12 +2964,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2980,13 +2978,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F79" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G79" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2998,12 +2996,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3012,13 +3010,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F80" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G80" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3030,142 +3028,142 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F81" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G81" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H81" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F82" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G82" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F83" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G83" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H83" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F84" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G84" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3174,13 +3172,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F85" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G85" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3192,31 +3190,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F86" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G86" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3226,12 +3222,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3240,16 +3236,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F87" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G87" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H87" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="88">
@@ -3260,12 +3256,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3274,13 +3270,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F88" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G88" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3292,110 +3288,112 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F89" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G89" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H89" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F90" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G90" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H90" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H90" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F91" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G91" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H91" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3404,47 +3402,49 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F92" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G92" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F93" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G93" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3454,12 +3454,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3468,13 +3468,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F94" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G94" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3486,12 +3486,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3500,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F95" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G95" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,12 +3518,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3532,13 +3532,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F96" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G96" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3550,12 +3550,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F97" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G97" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3582,12 +3582,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F98" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G98" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3614,12 +3614,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3628,13 +3628,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F99" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G99" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3646,12 +3646,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3660,13 +3660,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F100" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G100" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3678,12 +3678,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3692,13 +3692,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F101" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G101" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3710,12 +3710,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3724,13 +3724,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F102" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G102" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3742,12 +3742,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F103" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G103" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3774,12 +3774,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3788,13 +3788,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F104" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G104" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3806,12 +3806,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3820,13 +3820,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F105" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G105" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3838,12 +3838,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3852,13 +3852,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F106" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G106" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3870,12 +3870,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3884,13 +3884,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F107" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G107" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3902,12 +3902,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3916,13 +3916,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F108" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G108" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3934,12 +3934,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3948,13 +3948,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F109" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G109" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3966,12 +3966,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3980,13 +3980,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F110" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G110" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3998,12 +3998,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,13 +4012,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F111" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G111" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4030,12 +4030,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4044,13 +4044,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F112" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G112" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4062,29 +4062,157 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F113" t="n">
+        <v>180</v>
+      </c>
+      <c r="G113" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F114" t="n">
+        <v>449</v>
+      </c>
+      <c r="G114" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F115" t="n">
+        <v>148</v>
+      </c>
+      <c r="G115" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F116" t="n">
+        <v>593</v>
+      </c>
+      <c r="G116" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C113" t="inlineStr">
+      <c r="C117" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E113" t="n">
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
         <v>124600</v>
       </c>
-      <c r="F113" t="n">
+      <c r="F117" t="n">
         <v>161</v>
       </c>
-      <c r="G113" t="n">
+      <c r="G117" t="n">
         <v>20060600</v>
       </c>
-      <c r="H113" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H118"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,29 +478,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>195800</v>
+        <v>14780</v>
       </c>
       <c r="F2" t="n">
-        <v>101.9921</v>
+        <v>1338</v>
       </c>
       <c r="G2" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H2" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -510,12 +512,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,10 +526,10 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>14600</v>
+        <v>195800</v>
       </c>
       <c r="F3" t="n">
-        <v>1367.8125</v>
+        <v>101.9921</v>
       </c>
       <c r="G3" t="n">
         <v>19970062</v>
@@ -542,27 +544,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>36300</v>
+        <v>14600</v>
       </c>
       <c r="F4" t="n">
-        <v>275.0697</v>
+        <v>1367.8125</v>
       </c>
       <c r="G4" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -574,24 +576,24 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>159300</v>
+        <v>36300</v>
       </c>
       <c r="F5" t="n">
-        <v>62.6807</v>
+        <v>275.0697</v>
       </c>
       <c r="G5" t="n">
         <v>9985031</v>
@@ -601,17 +603,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -620,45 +622,45 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>147200</v>
+        <v>159300</v>
       </c>
       <c r="F6" t="n">
-        <v>67</v>
+        <v>62.6807</v>
       </c>
       <c r="G6" t="n">
-        <v>9862400</v>
+        <v>9985031</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14540</v>
+        <v>147200</v>
       </c>
       <c r="F7" t="n">
-        <v>983</v>
+        <v>67</v>
       </c>
       <c r="G7" t="n">
-        <v>14292820</v>
+        <v>9862400</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,31 +672,29 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>113400</v>
+        <v>14540</v>
       </c>
       <c r="F8" t="n">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="G8" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>14292820</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -704,29 +704,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24350</v>
+        <v>113400</v>
       </c>
       <c r="F9" t="n">
-        <v>407</v>
+        <v>167</v>
       </c>
       <c r="G9" t="n">
-        <v>9910450</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H9" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -736,31 +738,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>44100</v>
+        <v>24350</v>
       </c>
       <c r="F10" t="n">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G10" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H10" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9910450</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -770,76 +770,78 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>165700</v>
+        <v>44100</v>
       </c>
       <c r="F11" t="n">
-        <v>120</v>
+        <v>488</v>
       </c>
       <c r="G11" t="n">
-        <v>19884000</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H11" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>28950</v>
+        <v>165700</v>
       </c>
       <c r="F12" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="G12" t="n">
-        <v>10219350</v>
+        <v>19884000</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +850,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1853000</v>
+        <v>28950</v>
       </c>
       <c r="F13" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G13" t="n">
-        <v>20383000</v>
+        <v>10219350</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +868,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +882,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F14" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G14" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,27 +900,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F15" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G15" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -944,45 +946,45 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F16" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G16" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F17" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G17" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,12 +996,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1008,13 +1010,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F18" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G18" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,12 +1028,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1040,13 +1042,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F19" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G19" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,12 +1060,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1072,13 +1074,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F20" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G20" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1090,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1104,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F21" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G21" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F22" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G22" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,27 +1156,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F23" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G23" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,27 +1188,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F24" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G24" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,12 +1220,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1232,13 +1234,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F25" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,27 +1252,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F26" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G26" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,27 +1284,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F27" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G27" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1328,13 +1330,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F28" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G28" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1346,27 +1348,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F29" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G29" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1378,27 +1380,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F30" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G30" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1410,12 +1412,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1424,13 +1426,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F31" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G31" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1442,27 +1444,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F32" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G32" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1474,27 +1476,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F33" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G33" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1506,27 +1508,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F34" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G34" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1538,27 +1540,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F35" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1570,12 +1572,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1584,13 +1586,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F36" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G36" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1602,27 +1604,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F37" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G37" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1634,27 +1636,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F38" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G38" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1666,27 +1668,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F39" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G39" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1698,12 +1700,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1712,13 +1714,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F40" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G40" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1730,12 +1732,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1744,13 +1746,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F41" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G41" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1762,12 +1764,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1776,13 +1778,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F42" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G42" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1794,12 +1796,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1808,13 +1810,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F43" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G43" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1826,12 +1828,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1840,13 +1842,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F44" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G44" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1858,12 +1860,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1872,13 +1874,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F45" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G45" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1890,27 +1892,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F46" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G46" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1922,34 +1924,34 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F47" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G47" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -1964,49 +1966,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F48" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G48" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F49" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G49" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2018,95 +2020,93 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F50" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G50" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F51" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G51" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F52" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G52" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H52" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2130,16 +2130,16 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F53" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G53" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H53" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="54">
@@ -2150,12 +2150,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2164,16 +2164,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F54" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G54" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H54" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="55">
@@ -2184,63 +2184,63 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F55" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G55" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F56" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G56" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H56" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2250,29 +2250,31 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F57" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G57" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H57" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2282,44 +2284,44 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F58" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G58" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2328,13 +2330,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F59" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G59" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2346,31 +2348,29 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F60" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G60" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H60" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2380,12 +2380,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2394,49 +2394,51 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F61" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G61" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H61" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F62" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G62" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2446,31 +2448,29 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F63" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G63" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2480,12 +2480,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2494,16 +2494,16 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F64" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G64" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H64" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="65">
@@ -2514,59 +2514,61 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F65" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G65" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H65" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F66" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G66" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2578,27 +2580,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F67" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G67" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2612,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2626,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F68" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G68" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2644,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2658,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F69" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G69" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,27 +2676,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F70" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G70" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,27 +2708,27 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F71" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G71" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2740,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2754,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F72" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G72" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2772,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2786,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F73" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G73" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2804,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2818,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F74" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G74" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,27 +2836,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F75" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G75" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,31 +2868,29 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F76" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G76" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H76" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2900,29 +2900,31 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F77" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G77" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H77" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H77" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2932,12 +2934,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2946,13 +2948,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F78" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G78" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2964,12 +2966,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2978,13 +2980,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F79" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G79" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2996,12 +2998,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3010,13 +3012,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F80" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G80" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3028,31 +3030,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F81" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G81" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H81" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3062,29 +3062,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F82" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G82" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H82" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3094,12 +3096,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3108,13 +3110,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F83" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G83" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3126,12 +3128,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3140,13 +3142,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F84" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G84" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3158,12 +3160,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3172,45 +3174,45 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F85" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G85" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F86" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G86" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3222,31 +3224,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F87" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G87" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H87" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3256,29 +3256,31 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F88" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G88" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H88" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H88" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3288,27 +3290,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F89" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G89" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3320,31 +3322,29 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F90" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G90" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H90" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3354,12 +3354,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3368,16 +3368,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F91" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G91" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H91" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="92">
@@ -3388,29 +3388,31 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F92" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G92" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3420,63 +3422,63 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F93" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G93" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F94" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G94" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3486,12 +3488,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3502,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F95" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G95" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,12 +3520,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3532,13 +3534,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F96" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G96" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3550,12 +3552,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3564,13 +3566,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F97" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G97" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3582,12 +3584,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3596,13 +3598,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F98" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G98" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3614,12 +3616,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3628,13 +3630,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F99" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G99" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3646,12 +3648,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3660,13 +3662,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F100" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G100" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3678,12 +3680,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3692,13 +3694,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F101" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G101" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3710,12 +3712,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3724,13 +3726,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F102" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G102" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3742,12 +3744,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3756,13 +3758,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F103" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G103" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3774,12 +3776,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3788,13 +3790,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F104" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G104" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3806,12 +3808,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3820,13 +3822,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F105" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G105" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3838,12 +3840,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3852,13 +3854,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F106" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G106" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3870,12 +3872,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3884,13 +3886,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F107" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G107" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3902,12 +3904,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3916,13 +3918,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F108" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G108" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3934,12 +3936,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3948,13 +3950,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F109" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G109" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3966,12 +3968,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3980,13 +3982,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F110" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G110" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -3998,12 +4000,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,13 +4014,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F111" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G111" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4030,12 +4032,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4044,13 +4046,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F112" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G112" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4062,12 +4064,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4076,13 +4078,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F113" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G113" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4094,12 +4096,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4108,13 +4110,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F114" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G114" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4126,12 +4128,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4140,13 +4142,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F115" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G115" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4158,12 +4160,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4172,13 +4174,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F116" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G116" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4190,29 +4192,61 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F117" t="n">
+        <v>593</v>
+      </c>
+      <c r="G117" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C117" t="inlineStr">
+      <c r="C118" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E117" t="n">
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
         <v>124600</v>
       </c>
-      <c r="F117" t="n">
+      <c r="F118" t="n">
         <v>161</v>
       </c>
-      <c r="G117" t="n">
+      <c r="G118" t="n">
         <v>20060600</v>
       </c>
-      <c r="H117" t="inlineStr"/>
+      <c r="H118" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H118"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,132 +473,134 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>14780</v>
+        <v>87800</v>
       </c>
       <c r="F2" t="n">
-        <v>1338</v>
+        <v>115.4542</v>
       </c>
       <c r="G2" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H2" t="n">
-        <v>33.89</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>195800</v>
+        <v>33150</v>
       </c>
       <c r="F3" t="n">
-        <v>101.9921</v>
+        <v>569</v>
       </c>
       <c r="G3" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>14600</v>
+        <v>254500</v>
       </c>
       <c r="F4" t="n">
-        <v>1367.8125</v>
+        <v>39.8306</v>
       </c>
       <c r="G4" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>36300</v>
+        <v>79400</v>
       </c>
       <c r="F5" t="n">
-        <v>275.0697</v>
+        <v>246</v>
       </c>
       <c r="G5" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,142 +610,142 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>159300</v>
+        <v>14780</v>
       </c>
       <c r="F6" t="n">
-        <v>62.6807</v>
+        <v>1338</v>
       </c>
       <c r="G6" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H6" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F7" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G7" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F8" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G8" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F9" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G9" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -752,49 +754,47 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F10" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G10" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F11" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G11" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H11" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -804,140 +804,144 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F12" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G12" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F13" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G13" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G14" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F15" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G15" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H15" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -946,52 +950,52 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F16" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G16" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F17" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G17" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1010,30 +1014,30 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F18" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G18" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1042,77 +1046,77 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F19" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G19" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F20" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G20" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F21" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G21" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1128,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1142,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F22" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G22" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F23" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G23" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,27 +1192,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F24" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G24" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1220,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1234,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F25" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F26" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G26" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,27 +1288,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F27" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G27" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F28" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G28" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,27 +1352,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F29" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G29" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1380,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1394,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F30" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G30" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F31" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G31" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,12 +1448,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1462,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F32" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G32" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,27 +1480,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F33" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G33" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F34" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G34" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1540,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G35" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1572,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1586,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F36" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G36" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1604,27 +1608,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F37" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G37" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1636,27 +1640,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F38" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G38" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1668,27 +1672,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F39" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G39" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1700,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F40" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G40" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1732,27 +1736,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F41" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G41" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1764,12 +1768,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1778,13 +1782,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F42" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G42" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1796,27 +1800,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F43" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G43" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1828,12 +1832,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1842,13 +1846,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F44" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G44" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1860,12 +1864,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1874,13 +1878,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F45" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G45" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1892,12 +1896,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1906,13 +1910,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F46" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G46" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1924,27 +1928,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F47" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G47" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1956,12 +1960,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1970,62 +1974,62 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F48" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G48" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F49" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G49" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2034,30 +2038,30 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F50" t="n">
         <v>106</v>
       </c>
       <c r="G50" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2066,196 +2070,190 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F51" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G51" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F52" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G52" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F53" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G53" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F54" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G54" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H54" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F55" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G55" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H55" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F56" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G56" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2264,96 +2262,100 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F57" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G57" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H57" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F58" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G58" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H58" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F59" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G59" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2362,30 +2364,30 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F60" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G60" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -2394,66 +2396,64 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F61" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G61" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H61" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F62" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G62" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H62" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2462,64 +2462,62 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F63" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G63" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F64" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G64" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H64" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2528,175 +2526,181 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F65" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G65" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H65" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F66" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G66" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H66" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F67" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G67" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F68" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G68" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H68" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F69" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G69" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H69" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F70" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G70" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2708,12 +2712,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2722,13 +2726,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F71" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G71" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2740,12 +2744,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2754,13 +2758,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F72" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G72" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2772,12 +2776,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2786,13 +2790,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F73" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G73" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2804,12 +2808,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2818,13 +2822,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F74" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G74" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2836,27 +2840,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F75" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G75" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2868,27 +2872,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F76" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G76" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2900,31 +2904,29 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F77" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G77" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H77" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2934,12 +2936,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2948,13 +2950,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F78" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G78" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2966,12 +2968,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2980,13 +2982,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F79" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G79" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2998,27 +3000,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F80" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G80" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3030,29 +3032,31 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F81" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G81" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3062,31 +3066,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F82" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G82" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H82" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3096,12 +3098,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3110,13 +3112,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F83" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G83" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3128,12 +3130,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3142,13 +3144,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F84" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G84" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3160,12 +3162,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3174,13 +3176,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F85" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G85" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3192,142 +3194,142 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F86" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G86" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H86" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F87" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G87" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F88" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G88" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H88" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F89" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G89" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3336,13 +3338,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F90" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G90" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3354,31 +3356,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F91" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G91" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3388,12 +3388,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3402,16 +3402,16 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F92" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G92" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H92" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="93">
@@ -3422,12 +3422,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3436,13 +3436,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F93" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G93" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3454,110 +3454,112 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F94" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G94" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F95" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G95" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H95" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F96" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G96" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H96" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3566,47 +3568,49 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F97" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G97" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F98" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G98" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3616,12 +3620,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3630,13 +3634,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F99" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G99" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3648,12 +3652,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3662,13 +3666,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F100" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G100" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3680,12 +3684,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3694,13 +3698,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F101" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G101" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3712,12 +3716,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3726,13 +3730,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F102" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G102" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3744,12 +3748,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3758,13 +3762,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F103" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G103" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3776,12 +3780,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3790,13 +3794,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F104" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G104" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3808,12 +3812,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3822,13 +3826,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F105" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G105" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3840,12 +3844,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3854,13 +3858,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F106" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G106" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3872,12 +3876,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3886,13 +3890,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F107" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G107" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3904,12 +3908,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3918,13 +3922,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F108" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G108" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3936,12 +3940,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3950,13 +3954,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F109" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G109" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3968,12 +3972,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3982,13 +3986,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F110" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G110" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4000,12 +4004,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4014,13 +4018,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F111" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G111" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4032,12 +4036,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4046,13 +4050,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F112" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G112" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4064,12 +4068,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4078,13 +4082,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F113" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G113" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4096,12 +4100,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4110,13 +4114,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F114" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G114" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4128,12 +4132,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4142,13 +4146,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F115" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G115" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4160,12 +4164,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4174,13 +4178,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F116" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G116" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4192,12 +4196,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4206,13 +4210,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F117" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G117" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4224,29 +4228,157 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F118" t="n">
+        <v>180</v>
+      </c>
+      <c r="G118" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F119" t="n">
+        <v>449</v>
+      </c>
+      <c r="G119" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F120" t="n">
+        <v>148</v>
+      </c>
+      <c r="G120" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F121" t="n">
+        <v>593</v>
+      </c>
+      <c r="G121" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C118" t="inlineStr">
+      <c r="C122" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E118" t="n">
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
         <v>124600</v>
       </c>
-      <c r="F118" t="n">
+      <c r="F122" t="n">
         <v>161</v>
       </c>
-      <c r="G118" t="n">
+      <c r="G122" t="n">
         <v>20060600</v>
       </c>
-      <c r="H118" t="inlineStr"/>
+      <c r="H122" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H122"/>
+  <dimension ref="A1:H123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F3" t="n">
-        <v>569</v>
+        <v>891.1538</v>
       </c>
       <c r="G3" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,29 +542,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>254500</v>
+        <v>33150</v>
       </c>
       <c r="F4" t="n">
-        <v>39.8306</v>
+        <v>569</v>
       </c>
       <c r="G4" t="n">
-        <v>10136875</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,46 +576,44 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>79400</v>
+        <v>254500</v>
       </c>
       <c r="F5" t="n">
-        <v>246</v>
+        <v>39.8306</v>
       </c>
       <c r="G5" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -624,16 +622,16 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>14780</v>
+        <v>79400</v>
       </c>
       <c r="F6" t="n">
-        <v>1338</v>
+        <v>246</v>
       </c>
       <c r="G6" t="n">
-        <v>19775640</v>
+        <v>19532400</v>
       </c>
       <c r="H6" t="n">
-        <v>33.89</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="7">
@@ -644,29 +642,31 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>195800</v>
+        <v>14780</v>
       </c>
       <c r="F7" t="n">
-        <v>101.9921</v>
+        <v>1338</v>
       </c>
       <c r="G7" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H7" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>14600</v>
+        <v>195800</v>
       </c>
       <c r="F8" t="n">
-        <v>1367.8125</v>
+        <v>101.9921</v>
       </c>
       <c r="G8" t="n">
         <v>19970062</v>
@@ -708,27 +708,27 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>36300</v>
+        <v>14600</v>
       </c>
       <c r="F9" t="n">
-        <v>275.0697</v>
+        <v>1367.8125</v>
       </c>
       <c r="G9" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -740,24 +740,24 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>159300</v>
+        <v>36300</v>
       </c>
       <c r="F10" t="n">
-        <v>62.6807</v>
+        <v>275.0697</v>
       </c>
       <c r="G10" t="n">
         <v>9985031</v>
@@ -767,17 +767,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,45 +786,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>147200</v>
+        <v>159300</v>
       </c>
       <c r="F11" t="n">
-        <v>67</v>
+        <v>62.6807</v>
       </c>
       <c r="G11" t="n">
-        <v>9862400</v>
+        <v>9985031</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>14540</v>
+        <v>147200</v>
       </c>
       <c r="F12" t="n">
-        <v>983</v>
+        <v>67</v>
       </c>
       <c r="G12" t="n">
-        <v>14292820</v>
+        <v>9862400</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,31 +836,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>113400</v>
+        <v>14540</v>
       </c>
       <c r="F13" t="n">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="G13" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>14292820</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -870,29 +868,31 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>24350</v>
+        <v>113400</v>
       </c>
       <c r="F14" t="n">
-        <v>407</v>
+        <v>167</v>
       </c>
       <c r="G14" t="n">
-        <v>9910450</v>
-      </c>
-      <c r="H14" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H14" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -902,31 +902,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>44100</v>
+        <v>24350</v>
       </c>
       <c r="F15" t="n">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G15" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H15" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9910450</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -936,76 +934,78 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>165700</v>
+        <v>44100</v>
       </c>
       <c r="F16" t="n">
-        <v>120</v>
+        <v>488</v>
       </c>
       <c r="G16" t="n">
-        <v>19884000</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H16" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28950</v>
+        <v>165700</v>
       </c>
       <c r="F17" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="G17" t="n">
-        <v>10219350</v>
+        <v>19884000</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1014,13 +1014,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1853000</v>
+        <v>28950</v>
       </c>
       <c r="F18" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G18" t="n">
-        <v>20383000</v>
+        <v>10219350</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,13 +1046,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F19" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G19" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,27 +1064,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F20" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G20" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,45 +1110,45 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F21" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G21" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F22" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G22" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1174,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F23" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G23" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,12 +1192,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,13 +1206,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F24" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G24" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1238,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F25" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G25" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F26" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G26" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F27" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G27" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,27 +1320,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F28" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G28" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,27 +1352,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F29" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G29" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G30" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,27 +1416,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F31" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G31" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F32" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G32" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F33" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G33" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F34" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G34" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,27 +1544,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F35" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G35" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1576,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,13 +1590,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F36" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G36" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,27 +1608,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F37" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G37" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,27 +1640,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F38" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G38" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,27 +1672,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F39" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G39" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F40" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G40" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F41" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G41" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1768,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F42" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G42" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F43" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G43" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,27 +1832,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F44" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G44" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,13 +1878,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F45" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G45" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1896,12 +1896,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1910,13 +1910,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F46" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G46" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F47" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G47" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1960,12 +1960,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1974,13 +1974,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F48" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G48" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F49" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G49" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F50" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G50" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2056,27 +2056,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F51" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G51" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2088,34 +2088,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F52" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G52" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -2130,49 +2130,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F53" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G53" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F54" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G54" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2184,95 +2184,93 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F55" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G55" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F56" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G56" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F57" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G57" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2282,12 +2280,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2296,16 +2294,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F58" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G58" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H58" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="59">
@@ -2316,12 +2314,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2330,16 +2328,16 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F59" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G59" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H59" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="60">
@@ -2350,63 +2348,63 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F60" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G60" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H60" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F61" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G61" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H61" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2416,29 +2414,31 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F62" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G62" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H62" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H62" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2448,44 +2448,44 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F63" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G63" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2494,13 +2494,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F64" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G64" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2512,31 +2512,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F65" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G65" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2546,12 +2544,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2560,49 +2558,51 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F66" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G66" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H66" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F67" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G67" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H67" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2612,31 +2612,29 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F68" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G68" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H68" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2646,12 +2644,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2660,16 +2658,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F69" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G69" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H69" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="70">
@@ -2680,59 +2678,61 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F70" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G70" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F71" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G71" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2744,27 +2744,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F72" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G72" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2790,13 +2790,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F73" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G73" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2808,12 +2808,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2822,13 +2822,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F74" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G74" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2840,27 +2840,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F75" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G75" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2872,27 +2872,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F76" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G76" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F77" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G77" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F78" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G78" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F79" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G79" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3000,27 +3000,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F80" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G80" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3032,31 +3032,29 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F81" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G81" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3066,29 +3064,31 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F82" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G82" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3112,13 +3112,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F83" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G83" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3130,12 +3130,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3144,13 +3144,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F84" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G84" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3162,12 +3162,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3176,13 +3176,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F85" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G85" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3194,31 +3194,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F86" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G86" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H86" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3228,29 +3226,31 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F87" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G87" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H87" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H87" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3274,13 +3274,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F88" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G88" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3292,12 +3292,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3306,13 +3306,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F89" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G89" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3324,12 +3324,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3338,45 +3338,45 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F90" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G90" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F91" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G91" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3388,31 +3388,29 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F92" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G92" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H92" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3422,29 +3420,31 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F93" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G93" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H93" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H93" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3454,27 +3454,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F94" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G94" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3486,31 +3486,29 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F95" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G95" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H95" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3520,12 +3518,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3534,16 +3532,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F96" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G96" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H96" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="97">
@@ -3554,29 +3552,31 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F97" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G97" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H97" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H97" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3586,63 +3586,63 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F98" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G98" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F99" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G99" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3666,13 +3666,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F100" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G100" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3684,12 +3684,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3698,13 +3698,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F101" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G101" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3716,12 +3716,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3730,13 +3730,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F102" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G102" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3748,12 +3748,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3762,13 +3762,13 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F103" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G103" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F104" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G104" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3826,13 +3826,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F105" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G105" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F106" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G106" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3876,12 +3876,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F107" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G107" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F108" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G108" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F109" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G109" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F110" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G110" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F111" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G111" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F112" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G112" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4082,13 +4082,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F113" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G113" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F114" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G114" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F115" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G115" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4178,13 +4178,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F116" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G116" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F117" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G117" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F118" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G118" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F119" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G119" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4306,13 +4306,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F120" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G120" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F121" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G121" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4356,29 +4356,61 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F122" t="n">
+        <v>593</v>
+      </c>
+      <c r="G122" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C122" t="inlineStr">
+      <c r="C123" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E122" t="n">
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
         <v>124600</v>
       </c>
-      <c r="F122" t="n">
+      <c r="F123" t="n">
         <v>161</v>
       </c>
-      <c r="G122" t="n">
+      <c r="G123" t="n">
         <v>20060600</v>
       </c>
-      <c r="H122" t="inlineStr"/>
+      <c r="H123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H123"/>
+  <dimension ref="A1:H127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,111 +492,109 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>87800</v>
+        <v>1849000</v>
       </c>
       <c r="F2" t="n">
-        <v>115.4542</v>
+        <v>5.5521</v>
       </c>
       <c r="G2" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>22750</v>
+        <v>260000</v>
       </c>
       <c r="F3" t="n">
-        <v>891.1538</v>
+        <v>39.4838</v>
       </c>
       <c r="G3" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>33150</v>
+        <v>24700</v>
       </c>
       <c r="F4" t="n">
-        <v>569</v>
+        <v>415.6194</v>
       </c>
       <c r="G4" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10265800.4</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>254500</v>
+        <v>48650</v>
       </c>
       <c r="F5" t="n">
-        <v>39.8306</v>
+        <v>422.0267</v>
       </c>
       <c r="G5" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
@@ -608,161 +606,161 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>79400</v>
+        <v>87800</v>
       </c>
       <c r="F6" t="n">
-        <v>246</v>
+        <v>115.4542</v>
       </c>
       <c r="G6" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>14780</v>
+        <v>22750</v>
       </c>
       <c r="F7" t="n">
-        <v>1338</v>
+        <v>891.1538</v>
       </c>
       <c r="G7" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H7" t="n">
-        <v>33.89</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>195800</v>
+        <v>33150</v>
       </c>
       <c r="F8" t="n">
-        <v>101.9921</v>
+        <v>569</v>
       </c>
       <c r="G8" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H8" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H8" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>14600</v>
+        <v>254500</v>
       </c>
       <c r="F9" t="n">
-        <v>1367.8125</v>
+        <v>39.8306</v>
       </c>
       <c r="G9" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>36300</v>
+        <v>79400</v>
       </c>
       <c r="F10" t="n">
-        <v>275.0697</v>
+        <v>246</v>
       </c>
       <c r="G10" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -772,142 +770,142 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>159300</v>
+        <v>14780</v>
       </c>
       <c r="F11" t="n">
-        <v>62.6807</v>
+        <v>1338</v>
       </c>
       <c r="G11" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H11" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F12" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G12" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F13" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G13" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F14" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G14" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H14" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -916,49 +914,47 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F15" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G15" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F16" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G16" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H16" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -968,140 +964,144 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F17" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G17" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F18" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G18" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F19" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G19" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F20" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G20" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H20" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,52 +1110,52 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F21" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G21" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F22" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G22" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1174,30 +1174,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F23" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G23" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1206,77 +1206,77 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F24" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G24" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F25" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G25" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F26" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G26" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F27" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G27" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,13 +1334,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F28" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G28" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1352,27 +1352,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F29" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G29" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1398,13 +1398,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F30" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G30" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1416,12 +1416,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1430,13 +1430,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F31" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G31" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,27 +1448,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F32" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G32" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,12 +1480,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1494,13 +1494,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F33" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G33" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F34" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G34" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F35" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G35" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F36" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G36" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F37" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G37" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,27 +1640,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F38" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G38" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,27 +1672,27 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F39" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G39" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1704,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G40" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1736,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1750,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F41" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G41" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1768,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F42" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G42" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,27 +1800,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F43" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G43" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,27 +1832,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F44" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G44" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1864,27 +1864,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F45" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G45" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1896,27 +1896,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F46" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G46" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,12 +1928,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,13 +1942,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F47" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G47" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1960,27 +1960,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F48" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G48" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1992,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,13 +2006,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F49" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G49" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2024,12 +2024,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2038,13 +2038,13 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F50" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G50" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2056,12 +2056,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2070,13 +2070,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F51" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G51" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2088,27 +2088,27 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F52" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G52" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2120,12 +2120,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2134,62 +2134,62 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F53" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G53" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F54" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G54" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2198,30 +2198,30 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F55" t="n">
         <v>106</v>
       </c>
       <c r="G55" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2230,196 +2230,190 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F56" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G56" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F57" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G57" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F58" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G58" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F59" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G59" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H59" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F60" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G60" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H60" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F61" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G61" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,96 +2422,100 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F62" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G62" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H62" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F63" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G63" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H63" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F64" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G64" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H64" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2526,30 +2524,30 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F65" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G65" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2558,66 +2556,64 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F66" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G66" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H66" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F67" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G67" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H67" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2626,64 +2622,62 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F68" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G68" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F69" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G69" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H69" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2692,175 +2686,181 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F70" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G70" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H70" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F71" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G71" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H71" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H71" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F72" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G72" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F73" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G73" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H73" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H73" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F74" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G74" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H74" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F75" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G75" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F76" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G76" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F77" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G77" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F78" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G78" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F79" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G79" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3000,27 +3000,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F80" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G80" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F81" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G81" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3064,31 +3064,29 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F82" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G82" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3098,12 +3096,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3112,13 +3110,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F83" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G83" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3130,12 +3128,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3144,13 +3142,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F84" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G84" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3162,27 +3160,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F85" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G85" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3194,29 +3192,31 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F86" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G86" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H86" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H86" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3226,31 +3226,29 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F87" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G87" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H87" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3260,12 +3258,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3274,13 +3272,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F88" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G88" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3292,12 +3290,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3306,13 +3304,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F89" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G89" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3324,12 +3322,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3338,13 +3336,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F90" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G90" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3356,142 +3354,142 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F91" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G91" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H91" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H91" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F92" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G92" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F93" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G93" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H93" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F94" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G94" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3500,13 +3498,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F95" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G95" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3518,31 +3516,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F96" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G96" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H96" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3552,12 +3548,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3566,16 +3562,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F97" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G97" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H97" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="98">
@@ -3586,12 +3582,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3600,13 +3596,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F98" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G98" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3618,110 +3614,112 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F99" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G99" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F100" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G100" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H100" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F101" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G101" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H101" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3730,47 +3728,49 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F102" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G102" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F103" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G103" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H103" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3780,12 +3780,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F104" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G104" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3812,12 +3812,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3826,13 +3826,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F105" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G105" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3844,12 +3844,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3858,13 +3858,13 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F106" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G106" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3876,12 +3876,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3890,13 +3890,13 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F107" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G107" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3908,12 +3908,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3922,13 +3922,13 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F108" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G108" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
@@ -3940,12 +3940,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3954,13 +3954,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F109" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G109" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3972,12 +3972,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3986,13 +3986,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F110" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G110" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4004,12 +4004,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4018,13 +4018,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F111" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G111" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4050,13 +4050,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F112" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G112" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4068,12 +4068,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4082,13 +4082,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F113" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G113" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4100,12 +4100,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4114,13 +4114,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F114" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G114" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4132,12 +4132,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4146,13 +4146,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F115" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G115" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4164,12 +4164,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4178,13 +4178,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F116" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G116" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4196,12 +4196,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4210,13 +4210,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F117" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G117" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4228,12 +4228,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4242,13 +4242,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F118" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G118" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4260,12 +4260,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4274,13 +4274,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F119" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G119" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4292,12 +4292,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4306,13 +4306,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F120" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G120" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4324,12 +4324,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4338,13 +4338,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F121" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G121" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4356,12 +4356,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4370,13 +4370,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F122" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G122" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4388,29 +4388,157 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F123" t="n">
+        <v>180</v>
+      </c>
+      <c r="G123" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F124" t="n">
+        <v>449</v>
+      </c>
+      <c r="G124" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F125" t="n">
+        <v>148</v>
+      </c>
+      <c r="G125" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F126" t="n">
+        <v>593</v>
+      </c>
+      <c r="G126" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C123" t="inlineStr">
+      <c r="C127" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E123" t="n">
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
         <v>124600</v>
       </c>
-      <c r="F123" t="n">
+      <c r="F127" t="n">
         <v>161</v>
       </c>
-      <c r="G123" t="n">
+      <c r="G127" t="n">
         <v>20060600</v>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H127"/>
+  <dimension ref="A1:H132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,243 +473,247 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1849000</v>
+        <v>29050</v>
       </c>
       <c r="F2" t="n">
-        <v>5.5521</v>
+        <v>686</v>
       </c>
       <c r="G2" t="n">
-        <v>10265800.4</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H2" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>260000</v>
+        <v>19430</v>
       </c>
       <c r="F3" t="n">
-        <v>39.4838</v>
+        <v>1071</v>
       </c>
       <c r="G3" t="n">
-        <v>10265800.4</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>24700</v>
+        <v>21200</v>
       </c>
       <c r="F4" t="n">
-        <v>415.6194</v>
+        <v>1475.6547</v>
       </c>
       <c r="G4" t="n">
-        <v>10265800.4</v>
+        <v>31283879.4</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>48650</v>
+        <v>256000</v>
       </c>
       <c r="F5" t="n">
-        <v>422.0267</v>
+        <v>113.8306</v>
       </c>
       <c r="G5" t="n">
-        <v>20531600.8</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>87800</v>
+        <v>183500</v>
       </c>
       <c r="F6" t="n">
-        <v>115.4542</v>
+        <v>113.6562</v>
       </c>
       <c r="G6" t="n">
-        <v>10136875</v>
+        <v>20855919.6</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>22750</v>
+        <v>1849000</v>
       </c>
       <c r="F7" t="n">
-        <v>891.1538</v>
+        <v>5.5521</v>
       </c>
       <c r="G7" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>33150</v>
+        <v>260000</v>
       </c>
       <c r="F8" t="n">
-        <v>569</v>
+        <v>39.4838</v>
       </c>
       <c r="G8" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H8" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10265800.4</v>
+      </c>
+      <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,98 +722,94 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>254500</v>
+        <v>24700</v>
       </c>
       <c r="F9" t="n">
-        <v>39.8306</v>
+        <v>415.6194</v>
       </c>
       <c r="G9" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>79400</v>
+        <v>48650</v>
       </c>
       <c r="F10" t="n">
-        <v>246</v>
+        <v>422.0267</v>
       </c>
       <c r="G10" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-8</v>
-      </c>
+        <v>20531600.8</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>14780</v>
+        <v>87800</v>
       </c>
       <c r="F11" t="n">
-        <v>1338</v>
+        <v>115.4542</v>
       </c>
       <c r="G11" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H11" t="n">
-        <v>33.89</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -818,322 +818,324 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>195800</v>
+        <v>22750</v>
       </c>
       <c r="F12" t="n">
-        <v>101.9921</v>
+        <v>891.1538</v>
       </c>
       <c r="G12" t="n">
-        <v>19970062</v>
+        <v>20273749.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>14600</v>
+        <v>33150</v>
       </c>
       <c r="F13" t="n">
-        <v>1367.8125</v>
+        <v>569</v>
       </c>
       <c r="G13" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>36300</v>
+        <v>254500</v>
       </c>
       <c r="F14" t="n">
-        <v>275.0697</v>
+        <v>39.8306</v>
       </c>
       <c r="G14" t="n">
-        <v>9985031</v>
+        <v>10136875</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>159300</v>
+        <v>79400</v>
       </c>
       <c r="F15" t="n">
-        <v>62.6807</v>
+        <v>246</v>
       </c>
       <c r="G15" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H15" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>147200</v>
+        <v>14780</v>
       </c>
       <c r="F16" t="n">
-        <v>67</v>
+        <v>1338</v>
       </c>
       <c r="G16" t="n">
-        <v>9862400</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H16" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>14540</v>
+        <v>195800</v>
       </c>
       <c r="F17" t="n">
-        <v>983</v>
+        <v>101.9921</v>
       </c>
       <c r="G17" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>113400</v>
+        <v>14600</v>
       </c>
       <c r="F18" t="n">
-        <v>167</v>
+        <v>1367.8125</v>
       </c>
       <c r="G18" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>19970062</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>24350</v>
+        <v>36300</v>
       </c>
       <c r="F19" t="n">
-        <v>407</v>
+        <v>275.0697</v>
       </c>
       <c r="G19" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>44100</v>
+        <v>159300</v>
       </c>
       <c r="F20" t="n">
-        <v>488</v>
+        <v>62.6807</v>
       </c>
       <c r="G20" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H20" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>165700</v>
+        <v>147200</v>
       </c>
       <c r="F21" t="n">
-        <v>120</v>
+        <v>67</v>
       </c>
       <c r="G21" t="n">
-        <v>19884000</v>
+        <v>9862400</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1142,126 +1144,130 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>28950</v>
+        <v>14540</v>
       </c>
       <c r="F22" t="n">
-        <v>353</v>
+        <v>983</v>
       </c>
       <c r="G22" t="n">
-        <v>10219350</v>
+        <v>14292820</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1853000</v>
+        <v>113400</v>
       </c>
       <c r="F23" t="n">
-        <v>11</v>
+        <v>167</v>
       </c>
       <c r="G23" t="n">
-        <v>20383000</v>
-      </c>
-      <c r="H23" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H23" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>269000</v>
+        <v>24350</v>
       </c>
       <c r="F24" t="n">
-        <v>76</v>
+        <v>407</v>
       </c>
       <c r="G24" t="n">
-        <v>20444000</v>
+        <v>9910450</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>106300</v>
+        <v>44100</v>
       </c>
       <c r="F25" t="n">
-        <v>194</v>
+        <v>488</v>
       </c>
       <c r="G25" t="n">
-        <v>20622200</v>
-      </c>
-      <c r="H25" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H25" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,30 +1276,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>123100</v>
+        <v>165700</v>
       </c>
       <c r="F26" t="n">
-        <v>167</v>
+        <v>120</v>
       </c>
       <c r="G26" t="n">
-        <v>20557700</v>
+        <v>19884000</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,30 +1308,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1856000</v>
+        <v>28950</v>
       </c>
       <c r="F27" t="n">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="G27" t="n">
-        <v>42688000</v>
+        <v>10219350</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1334,30 +1340,30 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>49000</v>
+        <v>1853000</v>
       </c>
       <c r="F28" t="n">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>8183000</v>
+        <v>20383000</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1366,77 +1372,77 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>13340</v>
+        <v>269000</v>
       </c>
       <c r="F29" t="n">
-        <v>236</v>
+        <v>76</v>
       </c>
       <c r="G29" t="n">
-        <v>3148240</v>
+        <v>20444000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>29800</v>
+        <v>106300</v>
       </c>
       <c r="F30" t="n">
-        <v>66</v>
+        <v>194</v>
       </c>
       <c r="G30" t="n">
-        <v>1966800</v>
+        <v>20622200</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>269500</v>
+        <v>123100</v>
       </c>
       <c r="F31" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G31" t="n">
-        <v>31801000</v>
+        <v>20557700</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1448,12 +1454,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1462,13 +1468,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>330000</v>
+        <v>1856000</v>
       </c>
       <c r="F32" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G32" t="n">
-        <v>7920000</v>
+        <v>42688000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1480,27 +1486,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>35550</v>
+        <v>49000</v>
       </c>
       <c r="F33" t="n">
-        <v>581</v>
+        <v>167</v>
       </c>
       <c r="G33" t="n">
-        <v>20654550</v>
+        <v>8183000</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1512,12 +1518,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1526,13 +1532,13 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>574000</v>
+        <v>13340</v>
       </c>
       <c r="F34" t="n">
-        <v>22</v>
+        <v>236</v>
       </c>
       <c r="G34" t="n">
-        <v>12628000</v>
+        <v>3148240</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1550,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1564,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>165900</v>
+        <v>29800</v>
       </c>
       <c r="F35" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G35" t="n">
-        <v>3981600</v>
+        <v>1966800</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1582,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>91300</v>
+        <v>269500</v>
       </c>
       <c r="F36" t="n">
-        <v>45</v>
+        <v>118</v>
       </c>
       <c r="G36" t="n">
-        <v>4108500</v>
+        <v>31801000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,27 +1614,27 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>224500</v>
+        <v>330000</v>
       </c>
       <c r="F37" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="G37" t="n">
-        <v>20654000</v>
+        <v>7920000</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1646,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,13 +1660,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6010</v>
+        <v>35550</v>
       </c>
       <c r="F38" t="n">
-        <v>3435</v>
+        <v>581</v>
       </c>
       <c r="G38" t="n">
-        <v>20644350</v>
+        <v>20654550</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1678,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1692,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>25800</v>
+        <v>574000</v>
       </c>
       <c r="F39" t="n">
-        <v>351</v>
+        <v>22</v>
       </c>
       <c r="G39" t="n">
-        <v>9055800</v>
+        <v>12628000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1710,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>49150</v>
+        <v>165900</v>
       </c>
       <c r="F40" t="n">
-        <v>420</v>
+        <v>24</v>
       </c>
       <c r="G40" t="n">
-        <v>20643000</v>
+        <v>3981600</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,27 +1742,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>19280</v>
+        <v>91300</v>
       </c>
       <c r="F41" t="n">
-        <v>1071</v>
+        <v>45</v>
       </c>
       <c r="G41" t="n">
-        <v>20648880</v>
+        <v>4108500</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,27 +1774,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>19740</v>
+        <v>224500</v>
       </c>
       <c r="F42" t="n">
-        <v>523</v>
+        <v>92</v>
       </c>
       <c r="G42" t="n">
-        <v>10324020</v>
+        <v>20654000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1800,12 +1806,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1814,13 +1820,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>25150</v>
+        <v>6010</v>
       </c>
       <c r="F43" t="n">
-        <v>821</v>
+        <v>3435</v>
       </c>
       <c r="G43" t="n">
-        <v>20648150</v>
+        <v>20644350</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1832,12 +1838,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,13 +1852,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>153500</v>
+        <v>25800</v>
       </c>
       <c r="F44" t="n">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="G44" t="n">
-        <v>3684000</v>
+        <v>9055800</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1864,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,13 +1884,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6240</v>
+        <v>49150</v>
       </c>
       <c r="F45" t="n">
-        <v>3308</v>
+        <v>420</v>
       </c>
       <c r="G45" t="n">
-        <v>20641920</v>
+        <v>20643000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1896,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1910,13 +1916,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>15520</v>
+        <v>19280</v>
       </c>
       <c r="F46" t="n">
-        <v>1330</v>
+        <v>1071</v>
       </c>
       <c r="G46" t="n">
-        <v>20641600</v>
+        <v>20648880</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,12 +1934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,13 +1948,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>24200</v>
+        <v>19740</v>
       </c>
       <c r="F47" t="n">
-        <v>210</v>
+        <v>523</v>
       </c>
       <c r="G47" t="n">
-        <v>5082000</v>
+        <v>10324020</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1960,12 +1966,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1974,13 +1980,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>36300</v>
+        <v>25150</v>
       </c>
       <c r="F48" t="n">
-        <v>569</v>
+        <v>821</v>
       </c>
       <c r="G48" t="n">
-        <v>20654700</v>
+        <v>20648150</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1992,12 +1998,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2006,13 +2012,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>279500</v>
+        <v>153500</v>
       </c>
       <c r="F49" t="n">
-        <v>43</v>
+        <v>24</v>
       </c>
       <c r="G49" t="n">
-        <v>12018500</v>
+        <v>3684000</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2024,27 +2030,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>132600</v>
+        <v>6240</v>
       </c>
       <c r="F50" t="n">
-        <v>90</v>
+        <v>3308</v>
       </c>
       <c r="G50" t="n">
-        <v>11934000</v>
+        <v>20641920</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2056,27 +2062,27 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>44600</v>
+        <v>15520</v>
       </c>
       <c r="F51" t="n">
-        <v>139</v>
+        <v>1330</v>
       </c>
       <c r="G51" t="n">
-        <v>6199400</v>
+        <v>20641600</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2088,12 +2094,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2102,13 +2108,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>147100</v>
+        <v>24200</v>
       </c>
       <c r="F52" t="n">
-        <v>6</v>
+        <v>210</v>
       </c>
       <c r="G52" t="n">
-        <v>882600</v>
+        <v>5082000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2120,27 +2126,27 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>33500</v>
+        <v>36300</v>
       </c>
       <c r="F53" t="n">
-        <v>8</v>
+        <v>569</v>
       </c>
       <c r="G53" t="n">
-        <v>268000</v>
+        <v>20654700</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2152,12 +2158,12 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -2166,13 +2172,13 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>143100</v>
+        <v>279500</v>
       </c>
       <c r="F54" t="n">
-        <v>95</v>
+        <v>43</v>
       </c>
       <c r="G54" t="n">
-        <v>13594500</v>
+        <v>12018500</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2184,12 +2190,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2198,13 +2204,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>83800</v>
+        <v>132600</v>
       </c>
       <c r="F55" t="n">
-        <v>106</v>
+        <v>90</v>
       </c>
       <c r="G55" t="n">
-        <v>8882800</v>
+        <v>11934000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2216,27 +2222,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>42300</v>
+        <v>44600</v>
       </c>
       <c r="F56" t="n">
-        <v>488</v>
+        <v>139</v>
       </c>
       <c r="G56" t="n">
-        <v>20642400</v>
+        <v>6199400</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2248,12 +2254,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2262,62 +2268,62 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>81200</v>
+        <v>147100</v>
       </c>
       <c r="F57" t="n">
-        <v>135</v>
+        <v>6</v>
       </c>
       <c r="G57" t="n">
-        <v>10962000</v>
+        <v>882600</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>78600</v>
+        <v>33500</v>
       </c>
       <c r="F58" t="n">
-        <v>389</v>
+        <v>8</v>
       </c>
       <c r="G58" t="n">
-        <v>30575400</v>
+        <v>268000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2326,196 +2332,190 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>92500</v>
+        <v>143100</v>
       </c>
       <c r="F59" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G59" t="n">
-        <v>9805000</v>
+        <v>13594500</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>25550</v>
+        <v>83800</v>
       </c>
       <c r="F60" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G60" t="n">
-        <v>29408050</v>
+        <v>8882800</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>21800</v>
+        <v>42300</v>
       </c>
       <c r="F61" t="n">
-        <v>832</v>
+        <v>488</v>
       </c>
       <c r="G61" t="n">
-        <v>18137600</v>
+        <v>20642400</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>32250</v>
+        <v>81200</v>
       </c>
       <c r="F62" t="n">
-        <v>878</v>
+        <v>135</v>
       </c>
       <c r="G62" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H62" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>10962000</v>
+      </c>
+      <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>105800</v>
+        <v>78600</v>
       </c>
       <c r="F63" t="n">
-        <v>332</v>
+        <v>389</v>
       </c>
       <c r="G63" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H63" t="n">
-        <v>17.17</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>33750</v>
+        <v>92500</v>
       </c>
       <c r="F64" t="n">
-        <v>791</v>
+        <v>106</v>
       </c>
       <c r="G64" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H64" t="n">
-        <v>0.29</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2524,194 +2524,196 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>86300</v>
+        <v>25550</v>
       </c>
       <c r="F65" t="n">
-        <v>352</v>
+        <v>1151</v>
       </c>
       <c r="G65" t="n">
-        <v>30377600</v>
+        <v>29408050</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21000</v>
+        <v>21800</v>
       </c>
       <c r="F66" t="n">
-        <v>1517</v>
+        <v>832</v>
       </c>
       <c r="G66" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H66" t="n">
-        <v>3.96</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>21900</v>
+        <v>32250</v>
       </c>
       <c r="F67" t="n">
-        <v>906</v>
+        <v>878</v>
       </c>
       <c r="G67" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H67" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>135300</v>
+        <v>105800</v>
       </c>
       <c r="F68" t="n">
-        <v>226</v>
+        <v>332</v>
       </c>
       <c r="G68" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H68" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>22250</v>
+        <v>33750</v>
       </c>
       <c r="F69" t="n">
-        <v>1399</v>
+        <v>791</v>
       </c>
       <c r="G69" t="n">
-        <v>31127750</v>
-      </c>
-      <c r="H69" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>33500</v>
+        <v>86300</v>
       </c>
       <c r="F70" t="n">
-        <v>848</v>
+        <v>352</v>
       </c>
       <c r="G70" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2720,307 +2722,311 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>300000</v>
+        <v>21000</v>
       </c>
       <c r="F71" t="n">
-        <v>104</v>
+        <v>1517</v>
       </c>
       <c r="G71" t="n">
-        <v>31200000</v>
+        <v>31857000</v>
       </c>
       <c r="H71" t="n">
-        <v>20.95</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>28200</v>
+        <v>21900</v>
       </c>
       <c r="F72" t="n">
-        <v>1105</v>
+        <v>906</v>
       </c>
       <c r="G72" t="n">
-        <v>31161000</v>
+        <v>19841400</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>398000</v>
+        <v>135300</v>
       </c>
       <c r="F73" t="n">
-        <v>72</v>
+        <v>226</v>
       </c>
       <c r="G73" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H73" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>30577800</v>
+      </c>
+      <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>5620</v>
+        <v>22250</v>
       </c>
       <c r="F74" t="n">
-        <v>4707</v>
+        <v>1399</v>
       </c>
       <c r="G74" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H74" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>126900</v>
+        <v>33500</v>
       </c>
       <c r="F75" t="n">
-        <v>246</v>
+        <v>848</v>
       </c>
       <c r="G75" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H75" t="inlineStr"/>
+        <v>28408000</v>
+      </c>
+      <c r="H75" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1671000</v>
+        <v>300000</v>
       </c>
       <c r="F76" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="G76" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H76" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>50600</v>
+        <v>28200</v>
       </c>
       <c r="F77" t="n">
-        <v>186</v>
+        <v>1105</v>
       </c>
       <c r="G77" t="n">
-        <v>9411600</v>
+        <v>31161000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>11720</v>
+        <v>398000</v>
       </c>
       <c r="F78" t="n">
-        <v>665</v>
+        <v>72</v>
       </c>
       <c r="G78" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H78" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H78" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>414000</v>
+        <v>5620</v>
       </c>
       <c r="F79" t="n">
-        <v>26</v>
+        <v>4707</v>
       </c>
       <c r="G79" t="n">
-        <v>10764000</v>
-      </c>
-      <c r="H79" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H79" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>257000</v>
+        <v>126900</v>
       </c>
       <c r="F80" t="n">
-        <v>239</v>
+        <v>246</v>
       </c>
       <c r="G80" t="n">
-        <v>61423000</v>
+        <v>31217400</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3032,27 +3038,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>33900</v>
+        <v>1671000</v>
       </c>
       <c r="F81" t="n">
-        <v>292</v>
+        <v>44</v>
       </c>
       <c r="G81" t="n">
-        <v>9898800</v>
+        <v>73524000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3064,12 +3070,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3078,13 +3084,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>515000</v>
+        <v>50600</v>
       </c>
       <c r="F82" t="n">
-        <v>17</v>
+        <v>186</v>
       </c>
       <c r="G82" t="n">
-        <v>8755000</v>
+        <v>9411600</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3096,12 +3102,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3110,13 +3116,13 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>141200</v>
+        <v>11720</v>
       </c>
       <c r="F83" t="n">
-        <v>81</v>
+        <v>665</v>
       </c>
       <c r="G83" t="n">
-        <v>11437200</v>
+        <v>7793800</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3128,12 +3134,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3142,13 +3148,13 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6320</v>
+        <v>414000</v>
       </c>
       <c r="F84" t="n">
-        <v>1396</v>
+        <v>26</v>
       </c>
       <c r="G84" t="n">
-        <v>8822720</v>
+        <v>10764000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3160,27 +3166,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>90300</v>
+        <v>257000</v>
       </c>
       <c r="F85" t="n">
-        <v>332</v>
+        <v>239</v>
       </c>
       <c r="G85" t="n">
-        <v>29979600</v>
+        <v>61423000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3192,31 +3198,29 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>163100</v>
+        <v>33900</v>
       </c>
       <c r="F86" t="n">
-        <v>119</v>
+        <v>292</v>
       </c>
       <c r="G86" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H86" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>9898800</v>
+      </c>
+      <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3226,12 +3230,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3240,13 +3244,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>37900</v>
+        <v>515000</v>
       </c>
       <c r="F87" t="n">
-        <v>163</v>
+        <v>17</v>
       </c>
       <c r="G87" t="n">
-        <v>6177700</v>
+        <v>8755000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3258,12 +3262,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3272,13 +3276,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>19990</v>
+        <v>141200</v>
       </c>
       <c r="F88" t="n">
-        <v>615</v>
+        <v>81</v>
       </c>
       <c r="G88" t="n">
-        <v>12293850</v>
+        <v>11437200</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3290,12 +3294,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3304,13 +3308,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>35100</v>
+        <v>6320</v>
       </c>
       <c r="F89" t="n">
-        <v>320</v>
+        <v>1396</v>
       </c>
       <c r="G89" t="n">
-        <v>11232000</v>
+        <v>8822720</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3322,27 +3326,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>286000</v>
+        <v>90300</v>
       </c>
       <c r="F90" t="n">
-        <v>20</v>
+        <v>332</v>
       </c>
       <c r="G90" t="n">
-        <v>5720000</v>
+        <v>29979600</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3354,12 +3358,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3368,16 +3372,16 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>416000</v>
+        <v>163100</v>
       </c>
       <c r="F91" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="G91" t="n">
-        <v>21216000</v>
+        <v>19408900</v>
       </c>
       <c r="H91" t="n">
-        <v>5.85</v>
+        <v>-3.2</v>
       </c>
     </row>
     <row r="92">
@@ -3388,12 +3392,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3402,13 +3406,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>49450</v>
+        <v>37900</v>
       </c>
       <c r="F92" t="n">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="G92" t="n">
-        <v>7565850</v>
+        <v>6177700</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3420,12 +3424,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3434,13 +3438,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>138000</v>
+        <v>19990</v>
       </c>
       <c r="F93" t="n">
-        <v>68</v>
+        <v>615</v>
       </c>
       <c r="G93" t="n">
-        <v>9384000</v>
+        <v>12293850</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3452,12 +3456,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3466,13 +3470,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>31950</v>
+        <v>35100</v>
       </c>
       <c r="F94" t="n">
-        <v>339</v>
+        <v>320</v>
       </c>
       <c r="G94" t="n">
-        <v>10831050</v>
+        <v>11232000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3484,12 +3488,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3498,128 +3502,128 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>124800</v>
+        <v>286000</v>
       </c>
       <c r="F95" t="n">
-        <v>78</v>
+        <v>20</v>
       </c>
       <c r="G95" t="n">
-        <v>9734400</v>
+        <v>5720000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>10800</v>
+        <v>416000</v>
       </c>
       <c r="F96" t="n">
-        <v>1892</v>
+        <v>51</v>
       </c>
       <c r="G96" t="n">
-        <v>20433600</v>
-      </c>
-      <c r="H96" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H96" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>11880</v>
+        <v>49450</v>
       </c>
       <c r="F97" t="n">
-        <v>1474</v>
+        <v>153</v>
       </c>
       <c r="G97" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H97" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>7565850</v>
+      </c>
+      <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>20200</v>
+        <v>138000</v>
       </c>
       <c r="F98" t="n">
-        <v>1517</v>
+        <v>68</v>
       </c>
       <c r="G98" t="n">
-        <v>30643400</v>
+        <v>9384000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3628,49 +3632,47 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>102200</v>
+        <v>31950</v>
       </c>
       <c r="F99" t="n">
-        <v>200</v>
+        <v>339</v>
       </c>
       <c r="G99" t="n">
-        <v>20440000</v>
+        <v>10831050</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>23450</v>
+        <v>124800</v>
       </c>
       <c r="F100" t="n">
-        <v>762</v>
+        <v>78</v>
       </c>
       <c r="G100" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H100" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>9734400</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3680,31 +3682,29 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>22050</v>
+        <v>10800</v>
       </c>
       <c r="F101" t="n">
-        <v>875</v>
+        <v>1892</v>
       </c>
       <c r="G101" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H101" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3714,29 +3714,31 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>32550</v>
+        <v>11880</v>
       </c>
       <c r="F102" t="n">
-        <v>628</v>
+        <v>1474</v>
       </c>
       <c r="G102" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3746,142 +3748,144 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>99700</v>
+        <v>20200</v>
       </c>
       <c r="F103" t="n">
-        <v>180</v>
+        <v>1517</v>
       </c>
       <c r="G103" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>30643400</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1662000</v>
+        <v>102200</v>
       </c>
       <c r="F104" t="n">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="G104" t="n">
-        <v>249300000</v>
+        <v>20440000</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>49700</v>
+        <v>23450</v>
       </c>
       <c r="F105" t="n">
-        <v>402</v>
+        <v>762</v>
       </c>
       <c r="G105" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H105" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>435000</v>
+        <v>22050</v>
       </c>
       <c r="F106" t="n">
-        <v>46</v>
+        <v>875</v>
       </c>
       <c r="G106" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3890,47 +3894,49 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>268500</v>
+        <v>32550</v>
       </c>
       <c r="F107" t="n">
-        <v>931</v>
+        <v>628</v>
       </c>
       <c r="G107" t="n">
-        <v>249973500</v>
+        <v>20441400</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>13570</v>
+        <v>99700</v>
       </c>
       <c r="F108" t="n">
-        <v>1474</v>
+        <v>180</v>
       </c>
       <c r="G108" t="n">
-        <v>20002180</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H108" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3940,12 +3946,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3954,13 +3960,13 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>343500</v>
+        <v>1662000</v>
       </c>
       <c r="F109" t="n">
-        <v>87</v>
+        <v>150</v>
       </c>
       <c r="G109" t="n">
-        <v>29884500</v>
+        <v>249300000</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
@@ -3972,12 +3978,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3986,13 +3992,13 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>34150</v>
+        <v>49700</v>
       </c>
       <c r="F110" t="n">
-        <v>586</v>
+        <v>402</v>
       </c>
       <c r="G110" t="n">
-        <v>20011900</v>
+        <v>19979400</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
@@ -4004,12 +4010,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4018,13 +4024,13 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>488000</v>
+        <v>435000</v>
       </c>
       <c r="F111" t="n">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="G111" t="n">
-        <v>20008000</v>
+        <v>20010000</v>
       </c>
       <c r="H111" t="inlineStr"/>
     </row>
@@ -4036,12 +4042,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4050,13 +4056,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>153600</v>
+        <v>268500</v>
       </c>
       <c r="F112" t="n">
-        <v>130</v>
+        <v>931</v>
       </c>
       <c r="G112" t="n">
-        <v>19968000</v>
+        <v>249973500</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4068,12 +4074,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4082,13 +4088,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>99800</v>
+        <v>13570</v>
       </c>
       <c r="F113" t="n">
-        <v>200</v>
+        <v>1474</v>
       </c>
       <c r="G113" t="n">
-        <v>19960000</v>
+        <v>20002180</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4100,12 +4106,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4114,13 +4120,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6040</v>
+        <v>343500</v>
       </c>
       <c r="F114" t="n">
-        <v>3311</v>
+        <v>87</v>
       </c>
       <c r="G114" t="n">
-        <v>19998440</v>
+        <v>29884500</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4132,12 +4138,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4146,13 +4152,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>26250</v>
+        <v>34150</v>
       </c>
       <c r="F115" t="n">
-        <v>762</v>
+        <v>586</v>
       </c>
       <c r="G115" t="n">
-        <v>20002500</v>
+        <v>20011900</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4164,12 +4170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4178,13 +4184,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22850</v>
+        <v>488000</v>
       </c>
       <c r="F116" t="n">
-        <v>875</v>
+        <v>41</v>
       </c>
       <c r="G116" t="n">
-        <v>19993750</v>
+        <v>20008000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4196,12 +4202,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4210,13 +4216,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>168500</v>
+        <v>153600</v>
       </c>
       <c r="F117" t="n">
-        <v>119</v>
+        <v>130</v>
       </c>
       <c r="G117" t="n">
-        <v>20051500</v>
+        <v>19968000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4228,12 +4234,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4242,13 +4248,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>22850</v>
+        <v>99800</v>
       </c>
       <c r="F118" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G118" t="n">
-        <v>19993750</v>
+        <v>19960000</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4260,12 +4266,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4274,13 +4280,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>37900</v>
+        <v>6040</v>
       </c>
       <c r="F119" t="n">
-        <v>528</v>
+        <v>3311</v>
       </c>
       <c r="G119" t="n">
-        <v>20011200</v>
+        <v>19998440</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4292,12 +4298,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4306,13 +4312,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>239000</v>
+        <v>26250</v>
       </c>
       <c r="F120" t="n">
-        <v>84</v>
+        <v>762</v>
       </c>
       <c r="G120" t="n">
-        <v>20076000</v>
+        <v>20002500</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4324,12 +4330,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4338,13 +4344,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>298000</v>
+        <v>22850</v>
       </c>
       <c r="F121" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G121" t="n">
-        <v>34866000</v>
+        <v>19993750</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4356,12 +4362,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4370,13 +4376,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>393000</v>
+        <v>168500</v>
       </c>
       <c r="F122" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="G122" t="n">
-        <v>20043000</v>
+        <v>20051500</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4388,12 +4394,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4402,13 +4408,13 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>110900</v>
+        <v>22850</v>
       </c>
       <c r="F123" t="n">
-        <v>180</v>
+        <v>875</v>
       </c>
       <c r="G123" t="n">
-        <v>19962000</v>
+        <v>19993750</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4420,12 +4426,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4434,13 +4440,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>44500</v>
+        <v>37900</v>
       </c>
       <c r="F124" t="n">
-        <v>449</v>
+        <v>528</v>
       </c>
       <c r="G124" t="n">
-        <v>19980500</v>
+        <v>20011200</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4452,12 +4458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4466,13 +4472,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>135000</v>
+        <v>239000</v>
       </c>
       <c r="F125" t="n">
-        <v>148</v>
+        <v>84</v>
       </c>
       <c r="G125" t="n">
-        <v>19980000</v>
+        <v>20076000</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4484,12 +4490,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4498,13 +4504,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>33750</v>
+        <v>298000</v>
       </c>
       <c r="F126" t="n">
-        <v>593</v>
+        <v>117</v>
       </c>
       <c r="G126" t="n">
-        <v>20013750</v>
+        <v>34866000</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4516,29 +4522,189 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F127" t="n">
+        <v>51</v>
+      </c>
+      <c r="G127" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E128" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F128" t="n">
+        <v>180</v>
+      </c>
+      <c r="G128" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E129" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F129" t="n">
+        <v>449</v>
+      </c>
+      <c r="G129" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E130" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F130" t="n">
+        <v>148</v>
+      </c>
+      <c r="G130" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E131" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F131" t="n">
+        <v>593</v>
+      </c>
+      <c r="G131" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C127" t="inlineStr">
+      <c r="C132" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E127" t="n">
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
         <v>124600</v>
       </c>
-      <c r="F127" t="n">
+      <c r="F132" t="n">
         <v>161</v>
       </c>
-      <c r="G127" t="n">
+      <c r="G132" t="n">
         <v>20060600</v>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H132"/>
+  <dimension ref="A1:H135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,31 +478,29 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>29050</v>
+        <v>126300</v>
       </c>
       <c r="F2" t="n">
-        <v>686</v>
+        <v>165.13</v>
       </c>
       <c r="G2" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3.01</v>
-      </c>
+        <v>20855919.6</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,12 +510,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,16 +524,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>19430</v>
+        <v>29050</v>
       </c>
       <c r="F3" t="n">
-        <v>1071</v>
+        <v>686</v>
       </c>
       <c r="G3" t="n">
-        <v>20809530</v>
+        <v>19928300</v>
       </c>
       <c r="H3" t="n">
-        <v>0.78</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="4">
@@ -546,27 +544,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>21200</v>
+        <v>1074000</v>
       </c>
       <c r="F4" t="n">
-        <v>1475.6547</v>
+        <v>19.4189</v>
       </c>
       <c r="G4" t="n">
-        <v>31283879.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
@@ -578,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,16 +590,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>256000</v>
+        <v>19430</v>
       </c>
       <c r="F5" t="n">
-        <v>113.8306</v>
+        <v>1071</v>
       </c>
       <c r="G5" t="n">
-        <v>29140620.8</v>
+        <v>20809530</v>
       </c>
       <c r="H5" t="n">
-        <v>-9.470000000000001</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="6">
@@ -612,108 +610,110 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>183500</v>
+        <v>21200</v>
       </c>
       <c r="F6" t="n">
-        <v>113.6562</v>
+        <v>1475.6547</v>
       </c>
       <c r="G6" t="n">
-        <v>20855919.6</v>
+        <v>31283879.4</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1849000</v>
+        <v>256000</v>
       </c>
       <c r="F7" t="n">
-        <v>5.5521</v>
+        <v>113.8306</v>
       </c>
       <c r="G7" t="n">
-        <v>10265800.4</v>
-      </c>
-      <c r="H7" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H7" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>260000</v>
+        <v>75700</v>
       </c>
       <c r="F8" t="n">
-        <v>39.4838</v>
+        <v>275.5075</v>
       </c>
       <c r="G8" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,13 +722,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>24700</v>
+        <v>183500</v>
       </c>
       <c r="F9" t="n">
-        <v>415.6194</v>
+        <v>113.6562</v>
       </c>
       <c r="G9" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -740,44 +740,44 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>48650</v>
+        <v>1849000</v>
       </c>
       <c r="F10" t="n">
-        <v>422.0267</v>
+        <v>5.5521</v>
       </c>
       <c r="G10" t="n">
-        <v>20531600.8</v>
+        <v>10265800.4</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,20 +786,20 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>87800</v>
+        <v>260000</v>
       </c>
       <c r="F11" t="n">
-        <v>115.4542</v>
+        <v>39.4838</v>
       </c>
       <c r="G11" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -814,53 +814,51 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>22750</v>
+        <v>24700</v>
       </c>
       <c r="F12" t="n">
-        <v>891.1538</v>
+        <v>415.6194</v>
       </c>
       <c r="G12" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>33150</v>
+        <v>48650</v>
       </c>
       <c r="F13" t="n">
-        <v>569</v>
+        <v>422.0267</v>
       </c>
       <c r="G13" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>20531600.8</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -870,24 +868,24 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>254500</v>
+        <v>87800</v>
       </c>
       <c r="F14" t="n">
-        <v>39.8306</v>
+        <v>115.4542</v>
       </c>
       <c r="G14" t="n">
         <v>10136875</v>
@@ -902,46 +900,44 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>79400</v>
+        <v>22750</v>
       </c>
       <c r="F15" t="n">
-        <v>246</v>
+        <v>891.1538</v>
       </c>
       <c r="G15" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H15" t="n">
-        <v>-8</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,81 +946,83 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>14780</v>
+        <v>33150</v>
       </c>
       <c r="F16" t="n">
-        <v>1338</v>
+        <v>569</v>
       </c>
       <c r="G16" t="n">
-        <v>19775640</v>
+        <v>18862350</v>
       </c>
       <c r="H16" t="n">
-        <v>33.89</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>195800</v>
+        <v>254500</v>
       </c>
       <c r="F17" t="n">
-        <v>101.9921</v>
+        <v>39.8306</v>
       </c>
       <c r="G17" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14600</v>
+        <v>79400</v>
       </c>
       <c r="F18" t="n">
-        <v>1367.8125</v>
+        <v>246</v>
       </c>
       <c r="G18" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H18" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H18" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1034,29 +1032,31 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36300</v>
+        <v>14780</v>
       </c>
       <c r="F19" t="n">
-        <v>275.0697</v>
+        <v>1338</v>
       </c>
       <c r="G19" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H19" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H19" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1066,76 +1066,76 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>159300</v>
+        <v>195800</v>
       </c>
       <c r="F20" t="n">
-        <v>62.6807</v>
+        <v>101.9921</v>
       </c>
       <c r="G20" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>147200</v>
+        <v>14600</v>
       </c>
       <c r="F21" t="n">
-        <v>67</v>
+        <v>1367.8125</v>
       </c>
       <c r="G21" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1144,64 +1144,62 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>14540</v>
+        <v>36300</v>
       </c>
       <c r="F22" t="n">
-        <v>983</v>
+        <v>275.0697</v>
       </c>
       <c r="G22" t="n">
-        <v>14292820</v>
+        <v>9985031</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>113400</v>
+        <v>159300</v>
       </c>
       <c r="F23" t="n">
-        <v>167</v>
+        <v>62.6807</v>
       </c>
       <c r="G23" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H23" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1210,13 +1208,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>24350</v>
+        <v>147200</v>
       </c>
       <c r="F24" t="n">
-        <v>407</v>
+        <v>67</v>
       </c>
       <c r="G24" t="n">
-        <v>9910450</v>
+        <v>9862400</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1228,31 +1226,29 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>44100</v>
+        <v>14540</v>
       </c>
       <c r="F25" t="n">
-        <v>488</v>
+        <v>983</v>
       </c>
       <c r="G25" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H25" t="n">
-        <v>4.26</v>
-      </c>
+        <v>14292820</v>
+      </c>
+      <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1262,155 +1258,159 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>165700</v>
+        <v>113400</v>
       </c>
       <c r="F26" t="n">
-        <v>120</v>
+        <v>167</v>
       </c>
       <c r="G26" t="n">
-        <v>19884000</v>
-      </c>
-      <c r="H26" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H26" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>28950</v>
+        <v>24350</v>
       </c>
       <c r="F27" t="n">
-        <v>353</v>
+        <v>407</v>
       </c>
       <c r="G27" t="n">
-        <v>10219350</v>
+        <v>9910450</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1853000</v>
+        <v>44100</v>
       </c>
       <c r="F28" t="n">
-        <v>11</v>
+        <v>488</v>
       </c>
       <c r="G28" t="n">
-        <v>20383000</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H28" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>269000</v>
+        <v>165700</v>
       </c>
       <c r="F29" t="n">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="G29" t="n">
-        <v>20444000</v>
+        <v>19884000</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>106300</v>
+        <v>28950</v>
       </c>
       <c r="F30" t="n">
-        <v>194</v>
+        <v>353</v>
       </c>
       <c r="G30" t="n">
-        <v>20622200</v>
+        <v>10219350</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1422,44 +1422,44 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>123100</v>
+        <v>1853000</v>
       </c>
       <c r="F31" t="n">
-        <v>167</v>
+        <v>11</v>
       </c>
       <c r="G31" t="n">
-        <v>20557700</v>
+        <v>20383000</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1468,77 +1468,77 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1856000</v>
+        <v>269000</v>
       </c>
       <c r="F32" t="n">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="G32" t="n">
-        <v>42688000</v>
+        <v>20444000</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>49000</v>
+        <v>106300</v>
       </c>
       <c r="F33" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G33" t="n">
-        <v>8183000</v>
+        <v>20622200</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>13340</v>
+        <v>123100</v>
       </c>
       <c r="F34" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G34" t="n">
-        <v>3148240</v>
+        <v>20557700</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1550,12 +1550,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,13 +1564,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>29800</v>
+        <v>1856000</v>
       </c>
       <c r="F35" t="n">
-        <v>66</v>
+        <v>23</v>
       </c>
       <c r="G35" t="n">
-        <v>1966800</v>
+        <v>42688000</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1582,12 +1582,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1596,13 +1596,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>269500</v>
+        <v>49000</v>
       </c>
       <c r="F36" t="n">
-        <v>118</v>
+        <v>167</v>
       </c>
       <c r="G36" t="n">
-        <v>31801000</v>
+        <v>8183000</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1614,12 +1614,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1628,13 +1628,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>330000</v>
+        <v>13340</v>
       </c>
       <c r="F37" t="n">
-        <v>24</v>
+        <v>236</v>
       </c>
       <c r="G37" t="n">
-        <v>7920000</v>
+        <v>3148240</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1646,27 +1646,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>35550</v>
+        <v>29800</v>
       </c>
       <c r="F38" t="n">
-        <v>581</v>
+        <v>66</v>
       </c>
       <c r="G38" t="n">
-        <v>20654550</v>
+        <v>1966800</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1678,12 +1678,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1692,13 +1692,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>574000</v>
+        <v>269500</v>
       </c>
       <c r="F39" t="n">
-        <v>22</v>
+        <v>118</v>
       </c>
       <c r="G39" t="n">
-        <v>12628000</v>
+        <v>31801000</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1710,12 +1710,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1724,13 +1724,13 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>165900</v>
+        <v>330000</v>
       </c>
       <c r="F40" t="n">
         <v>24</v>
       </c>
       <c r="G40" t="n">
-        <v>3981600</v>
+        <v>7920000</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1742,27 +1742,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>91300</v>
+        <v>35550</v>
       </c>
       <c r="F41" t="n">
-        <v>45</v>
+        <v>581</v>
       </c>
       <c r="G41" t="n">
-        <v>4108500</v>
+        <v>20654550</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1774,27 +1774,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>224500</v>
+        <v>574000</v>
       </c>
       <c r="F42" t="n">
-        <v>92</v>
+        <v>22</v>
       </c>
       <c r="G42" t="n">
-        <v>20654000</v>
+        <v>12628000</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1806,27 +1806,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6010</v>
+        <v>165900</v>
       </c>
       <c r="F43" t="n">
-        <v>3435</v>
+        <v>24</v>
       </c>
       <c r="G43" t="n">
-        <v>20644350</v>
+        <v>3981600</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>25800</v>
+        <v>91300</v>
       </c>
       <c r="F44" t="n">
-        <v>351</v>
+        <v>45</v>
       </c>
       <c r="G44" t="n">
-        <v>9055800</v>
+        <v>4108500</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1870,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1884,13 +1884,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>49150</v>
+        <v>224500</v>
       </c>
       <c r="F45" t="n">
-        <v>420</v>
+        <v>92</v>
       </c>
       <c r="G45" t="n">
-        <v>20643000</v>
+        <v>20654000</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1902,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>19280</v>
+        <v>6010</v>
       </c>
       <c r="F46" t="n">
-        <v>1071</v>
+        <v>3435</v>
       </c>
       <c r="G46" t="n">
-        <v>20648880</v>
+        <v>20644350</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1934,12 +1934,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1948,13 +1948,13 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>19740</v>
+        <v>25800</v>
       </c>
       <c r="F47" t="n">
-        <v>523</v>
+        <v>351</v>
       </c>
       <c r="G47" t="n">
-        <v>10324020</v>
+        <v>9055800</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1966,12 +1966,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1980,13 +1980,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>25150</v>
+        <v>49150</v>
       </c>
       <c r="F48" t="n">
-        <v>821</v>
+        <v>420</v>
       </c>
       <c r="G48" t="n">
-        <v>20648150</v>
+        <v>20643000</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1998,27 +1998,27 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>153500</v>
+        <v>19280</v>
       </c>
       <c r="F49" t="n">
-        <v>24</v>
+        <v>1071</v>
       </c>
       <c r="G49" t="n">
-        <v>3684000</v>
+        <v>20648880</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2030,27 +2030,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6240</v>
+        <v>19740</v>
       </c>
       <c r="F50" t="n">
-        <v>3308</v>
+        <v>523</v>
       </c>
       <c r="G50" t="n">
-        <v>20641920</v>
+        <v>10324020</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2062,12 +2062,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2076,13 +2076,13 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>15520</v>
+        <v>25150</v>
       </c>
       <c r="F51" t="n">
-        <v>1330</v>
+        <v>821</v>
       </c>
       <c r="G51" t="n">
-        <v>20641600</v>
+        <v>20648150</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2108,13 +2108,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>24200</v>
+        <v>153500</v>
       </c>
       <c r="F52" t="n">
-        <v>210</v>
+        <v>24</v>
       </c>
       <c r="G52" t="n">
-        <v>5082000</v>
+        <v>3684000</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2126,12 +2126,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -2140,13 +2140,13 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>36300</v>
+        <v>6240</v>
       </c>
       <c r="F53" t="n">
-        <v>569</v>
+        <v>3308</v>
       </c>
       <c r="G53" t="n">
-        <v>20654700</v>
+        <v>20641920</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2158,27 +2158,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>279500</v>
+        <v>15520</v>
       </c>
       <c r="F54" t="n">
-        <v>43</v>
+        <v>1330</v>
       </c>
       <c r="G54" t="n">
-        <v>12018500</v>
+        <v>20641600</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2204,13 +2204,13 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>132600</v>
+        <v>24200</v>
       </c>
       <c r="F55" t="n">
-        <v>90</v>
+        <v>210</v>
       </c>
       <c r="G55" t="n">
-        <v>11934000</v>
+        <v>5082000</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
@@ -2222,27 +2222,27 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>44600</v>
+        <v>36300</v>
       </c>
       <c r="F56" t="n">
-        <v>139</v>
+        <v>569</v>
       </c>
       <c r="G56" t="n">
-        <v>6199400</v>
+        <v>20654700</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
@@ -2254,12 +2254,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2268,13 +2268,13 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>147100</v>
+        <v>279500</v>
       </c>
       <c r="F57" t="n">
-        <v>6</v>
+        <v>43</v>
       </c>
       <c r="G57" t="n">
-        <v>882600</v>
+        <v>12018500</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
@@ -2286,12 +2286,12 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,13 +2300,13 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>33500</v>
+        <v>132600</v>
       </c>
       <c r="F58" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="G58" t="n">
-        <v>268000</v>
+        <v>11934000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
@@ -2318,12 +2318,12 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>143100</v>
+        <v>44600</v>
       </c>
       <c r="F59" t="n">
-        <v>95</v>
+        <v>139</v>
       </c>
       <c r="G59" t="n">
-        <v>13594500</v>
+        <v>6199400</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>83800</v>
+        <v>147100</v>
       </c>
       <c r="F60" t="n">
-        <v>106</v>
+        <v>6</v>
       </c>
       <c r="G60" t="n">
-        <v>8882800</v>
+        <v>882600</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2382,27 +2382,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>42300</v>
+        <v>33500</v>
       </c>
       <c r="F61" t="n">
-        <v>488</v>
+        <v>8</v>
       </c>
       <c r="G61" t="n">
-        <v>20642400</v>
+        <v>268000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,245 +2428,239 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>81200</v>
+        <v>143100</v>
       </c>
       <c r="F62" t="n">
-        <v>135</v>
+        <v>95</v>
       </c>
       <c r="G62" t="n">
-        <v>10962000</v>
+        <v>13594500</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>78600</v>
+        <v>83800</v>
       </c>
       <c r="F63" t="n">
-        <v>389</v>
+        <v>106</v>
       </c>
       <c r="G63" t="n">
-        <v>30575400</v>
+        <v>8882800</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>92500</v>
+        <v>42300</v>
       </c>
       <c r="F64" t="n">
-        <v>106</v>
+        <v>488</v>
       </c>
       <c r="G64" t="n">
-        <v>9805000</v>
+        <v>20642400</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>25550</v>
+        <v>81200</v>
       </c>
       <c r="F65" t="n">
-        <v>1151</v>
+        <v>135</v>
       </c>
       <c r="G65" t="n">
-        <v>29408050</v>
+        <v>10962000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>21800</v>
+        <v>78600</v>
       </c>
       <c r="F66" t="n">
-        <v>832</v>
+        <v>389</v>
       </c>
       <c r="G66" t="n">
-        <v>18137600</v>
+        <v>30575400</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>32250</v>
+        <v>92500</v>
       </c>
       <c r="F67" t="n">
-        <v>878</v>
+        <v>106</v>
       </c>
       <c r="G67" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H67" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>105800</v>
+        <v>25550</v>
       </c>
       <c r="F68" t="n">
-        <v>332</v>
+        <v>1151</v>
       </c>
       <c r="G68" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H68" t="n">
-        <v>17.17</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>33750</v>
+        <v>21800</v>
       </c>
       <c r="F69" t="n">
-        <v>791</v>
+        <v>832</v>
       </c>
       <c r="G69" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H69" t="n">
-        <v>0.29</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2676,44 +2670,46 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>86300</v>
+        <v>32250</v>
       </c>
       <c r="F70" t="n">
-        <v>352</v>
+        <v>878</v>
       </c>
       <c r="G70" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H70" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H70" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2722,64 +2718,66 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>21000</v>
+        <v>105800</v>
       </c>
       <c r="F71" t="n">
-        <v>1517</v>
+        <v>332</v>
       </c>
       <c r="G71" t="n">
-        <v>31857000</v>
+        <v>35125600</v>
       </c>
       <c r="H71" t="n">
-        <v>3.96</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>21900</v>
+        <v>33750</v>
       </c>
       <c r="F72" t="n">
-        <v>906</v>
+        <v>791</v>
       </c>
       <c r="G72" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H72" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2788,130 +2786,128 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>135300</v>
+        <v>86300</v>
       </c>
       <c r="F73" t="n">
-        <v>226</v>
+        <v>352</v>
       </c>
       <c r="G73" t="n">
-        <v>30577800</v>
+        <v>30377600</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>22250</v>
+        <v>21000</v>
       </c>
       <c r="F74" t="n">
-        <v>1399</v>
+        <v>1517</v>
       </c>
       <c r="G74" t="n">
-        <v>31127750</v>
-      </c>
-      <c r="H74" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H74" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>33500</v>
+        <v>21900</v>
       </c>
       <c r="F75" t="n">
-        <v>848</v>
+        <v>906</v>
       </c>
       <c r="G75" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H75" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>300000</v>
+        <v>135300</v>
       </c>
       <c r="F76" t="n">
-        <v>104</v>
+        <v>226</v>
       </c>
       <c r="G76" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H76" t="n">
-        <v>20.95</v>
-      </c>
+        <v>30577800</v>
+      </c>
+      <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2920,30 +2916,30 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>28200</v>
+        <v>22250</v>
       </c>
       <c r="F77" t="n">
-        <v>1105</v>
+        <v>1399</v>
       </c>
       <c r="G77" t="n">
-        <v>31161000</v>
+        <v>31127750</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2952,32 +2948,32 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>398000</v>
+        <v>33500</v>
       </c>
       <c r="F78" t="n">
-        <v>72</v>
+        <v>848</v>
       </c>
       <c r="G78" t="n">
-        <v>28656000</v>
+        <v>28408000</v>
       </c>
       <c r="H78" t="n">
-        <v>-6.88</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2986,16 +2982,16 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5620</v>
+        <v>300000</v>
       </c>
       <c r="F79" t="n">
-        <v>4707</v>
+        <v>104</v>
       </c>
       <c r="G79" t="n">
-        <v>26453340</v>
+        <v>31200000</v>
       </c>
       <c r="H79" t="n">
-        <v>-8.220000000000001</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="80">
@@ -3006,12 +3002,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3020,109 +3016,113 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>126900</v>
+        <v>28200</v>
       </c>
       <c r="F80" t="n">
-        <v>246</v>
+        <v>1105</v>
       </c>
       <c r="G80" t="n">
-        <v>31217400</v>
+        <v>31161000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1671000</v>
+        <v>398000</v>
       </c>
       <c r="F81" t="n">
-        <v>44</v>
+        <v>72</v>
       </c>
       <c r="G81" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H81" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H81" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>50600</v>
+        <v>5620</v>
       </c>
       <c r="F82" t="n">
-        <v>186</v>
+        <v>4707</v>
       </c>
       <c r="G82" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H82" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H82" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>11720</v>
+        <v>126900</v>
       </c>
       <c r="F83" t="n">
-        <v>665</v>
+        <v>246</v>
       </c>
       <c r="G83" t="n">
-        <v>7793800</v>
+        <v>31217400</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3134,27 +3134,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>414000</v>
+        <v>1671000</v>
       </c>
       <c r="F84" t="n">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="G84" t="n">
-        <v>10764000</v>
+        <v>73524000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3166,27 +3166,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>257000</v>
+        <v>50600</v>
       </c>
       <c r="F85" t="n">
-        <v>239</v>
+        <v>186</v>
       </c>
       <c r="G85" t="n">
-        <v>61423000</v>
+        <v>9411600</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3198,12 +3198,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3212,13 +3212,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>33900</v>
+        <v>11720</v>
       </c>
       <c r="F86" t="n">
-        <v>292</v>
+        <v>665</v>
       </c>
       <c r="G86" t="n">
-        <v>9898800</v>
+        <v>7793800</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3230,12 +3230,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3244,13 +3244,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>515000</v>
+        <v>414000</v>
       </c>
       <c r="F87" t="n">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="G87" t="n">
-        <v>8755000</v>
+        <v>10764000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3262,27 +3262,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>141200</v>
+        <v>257000</v>
       </c>
       <c r="F88" t="n">
-        <v>81</v>
+        <v>239</v>
       </c>
       <c r="G88" t="n">
-        <v>11437200</v>
+        <v>61423000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3294,12 +3294,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3308,13 +3308,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6320</v>
+        <v>33900</v>
       </c>
       <c r="F89" t="n">
-        <v>1396</v>
+        <v>292</v>
       </c>
       <c r="G89" t="n">
-        <v>8822720</v>
+        <v>9898800</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3326,27 +3326,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>90300</v>
+        <v>515000</v>
       </c>
       <c r="F90" t="n">
-        <v>332</v>
+        <v>17</v>
       </c>
       <c r="G90" t="n">
-        <v>29979600</v>
+        <v>8755000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3358,31 +3358,29 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>163100</v>
+        <v>141200</v>
       </c>
       <c r="F91" t="n">
-        <v>119</v>
+        <v>81</v>
       </c>
       <c r="G91" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H91" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>11437200</v>
+      </c>
+      <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3392,12 +3390,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3406,13 +3404,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>37900</v>
+        <v>6320</v>
       </c>
       <c r="F92" t="n">
-        <v>163</v>
+        <v>1396</v>
       </c>
       <c r="G92" t="n">
-        <v>6177700</v>
+        <v>8822720</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3424,27 +3422,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>19990</v>
+        <v>90300</v>
       </c>
       <c r="F93" t="n">
-        <v>615</v>
+        <v>332</v>
       </c>
       <c r="G93" t="n">
-        <v>12293850</v>
+        <v>29979600</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3456,29 +3454,31 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>35100</v>
+        <v>163100</v>
       </c>
       <c r="F94" t="n">
-        <v>320</v>
+        <v>119</v>
       </c>
       <c r="G94" t="n">
-        <v>11232000</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3488,12 +3488,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3502,13 +3502,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>286000</v>
+        <v>37900</v>
       </c>
       <c r="F95" t="n">
-        <v>20</v>
+        <v>163</v>
       </c>
       <c r="G95" t="n">
-        <v>5720000</v>
+        <v>6177700</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3520,31 +3520,29 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>416000</v>
+        <v>19990</v>
       </c>
       <c r="F96" t="n">
-        <v>51</v>
+        <v>615</v>
       </c>
       <c r="G96" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H96" t="n">
-        <v>5.85</v>
-      </c>
+        <v>12293850</v>
+      </c>
+      <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3554,12 +3552,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3568,13 +3566,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>49450</v>
+        <v>35100</v>
       </c>
       <c r="F97" t="n">
-        <v>153</v>
+        <v>320</v>
       </c>
       <c r="G97" t="n">
-        <v>7565850</v>
+        <v>11232000</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3586,12 +3584,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3600,13 +3598,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>138000</v>
+        <v>286000</v>
       </c>
       <c r="F98" t="n">
-        <v>68</v>
+        <v>20</v>
       </c>
       <c r="G98" t="n">
-        <v>9384000</v>
+        <v>5720000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3618,29 +3616,31 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>31950</v>
+        <v>416000</v>
       </c>
       <c r="F99" t="n">
-        <v>339</v>
+        <v>51</v>
       </c>
       <c r="G99" t="n">
-        <v>10831050</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H99" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3650,12 +3650,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3664,111 +3664,109 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>124800</v>
+        <v>49450</v>
       </c>
       <c r="F100" t="n">
-        <v>78</v>
+        <v>153</v>
       </c>
       <c r="G100" t="n">
-        <v>9734400</v>
+        <v>7565850</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>10800</v>
+        <v>138000</v>
       </c>
       <c r="F101" t="n">
-        <v>1892</v>
+        <v>68</v>
       </c>
       <c r="G101" t="n">
-        <v>20433600</v>
+        <v>9384000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>11880</v>
+        <v>31950</v>
       </c>
       <c r="F102" t="n">
-        <v>1474</v>
+        <v>339</v>
       </c>
       <c r="G102" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H102" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>10831050</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>20200</v>
+        <v>124800</v>
       </c>
       <c r="F103" t="n">
-        <v>1517</v>
+        <v>78</v>
       </c>
       <c r="G103" t="n">
-        <v>30643400</v>
+        <v>9734400</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3780,27 +3778,27 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>102200</v>
+        <v>10800</v>
       </c>
       <c r="F104" t="n">
-        <v>200</v>
+        <v>1892</v>
       </c>
       <c r="G104" t="n">
-        <v>20440000</v>
+        <v>20433600</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
@@ -3812,12 +3810,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3826,16 +3824,16 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>23450</v>
+        <v>11880</v>
       </c>
       <c r="F105" t="n">
-        <v>762</v>
+        <v>1474</v>
       </c>
       <c r="G105" t="n">
-        <v>17868900</v>
+        <v>17511120</v>
       </c>
       <c r="H105" t="n">
-        <v>-10.67</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="106">
@@ -3846,31 +3844,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22050</v>
+        <v>20200</v>
       </c>
       <c r="F106" t="n">
-        <v>875</v>
+        <v>1517</v>
       </c>
       <c r="G106" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>30643400</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3880,27 +3876,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>32550</v>
+        <v>102200</v>
       </c>
       <c r="F107" t="n">
-        <v>628</v>
+        <v>200</v>
       </c>
       <c r="G107" t="n">
-        <v>20441400</v>
+        <v>20440000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
@@ -3912,12 +3908,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -3926,64 +3922,66 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>99700</v>
+        <v>23450</v>
       </c>
       <c r="F108" t="n">
-        <v>180</v>
+        <v>762</v>
       </c>
       <c r="G108" t="n">
-        <v>17946000</v>
+        <v>17868900</v>
       </c>
       <c r="H108" t="n">
-        <v>-10.1</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>1662000</v>
+        <v>22050</v>
       </c>
       <c r="F109" t="n">
-        <v>150</v>
+        <v>875</v>
       </c>
       <c r="G109" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H109" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3992,47 +3990,49 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>49700</v>
+        <v>32550</v>
       </c>
       <c r="F110" t="n">
-        <v>402</v>
+        <v>628</v>
       </c>
       <c r="G110" t="n">
-        <v>19979400</v>
+        <v>20441400</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>435000</v>
+        <v>99700</v>
       </c>
       <c r="F111" t="n">
-        <v>46</v>
+        <v>180</v>
       </c>
       <c r="G111" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4042,12 +4042,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -4056,13 +4056,13 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>268500</v>
+        <v>1662000</v>
       </c>
       <c r="F112" t="n">
-        <v>931</v>
+        <v>150</v>
       </c>
       <c r="G112" t="n">
-        <v>249973500</v>
+        <v>249300000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4074,12 +4074,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4088,13 +4088,13 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>13570</v>
+        <v>49700</v>
       </c>
       <c r="F113" t="n">
-        <v>1474</v>
+        <v>402</v>
       </c>
       <c r="G113" t="n">
-        <v>20002180</v>
+        <v>19979400</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4106,12 +4106,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4120,13 +4120,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>343500</v>
+        <v>435000</v>
       </c>
       <c r="F114" t="n">
-        <v>87</v>
+        <v>46</v>
       </c>
       <c r="G114" t="n">
-        <v>29884500</v>
+        <v>20010000</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4138,12 +4138,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4152,13 +4152,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>34150</v>
+        <v>268500</v>
       </c>
       <c r="F115" t="n">
-        <v>586</v>
+        <v>931</v>
       </c>
       <c r="G115" t="n">
-        <v>20011900</v>
+        <v>249973500</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4170,12 +4170,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4184,13 +4184,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>488000</v>
+        <v>13570</v>
       </c>
       <c r="F116" t="n">
-        <v>41</v>
+        <v>1474</v>
       </c>
       <c r="G116" t="n">
-        <v>20008000</v>
+        <v>20002180</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4202,12 +4202,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4216,13 +4216,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>153600</v>
+        <v>343500</v>
       </c>
       <c r="F117" t="n">
-        <v>130</v>
+        <v>87</v>
       </c>
       <c r="G117" t="n">
-        <v>19968000</v>
+        <v>29884500</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4234,12 +4234,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4248,13 +4248,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>99800</v>
+        <v>34150</v>
       </c>
       <c r="F118" t="n">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="G118" t="n">
-        <v>19960000</v>
+        <v>20011900</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4266,12 +4266,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4280,13 +4280,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6040</v>
+        <v>488000</v>
       </c>
       <c r="F119" t="n">
-        <v>3311</v>
+        <v>41</v>
       </c>
       <c r="G119" t="n">
-        <v>19998440</v>
+        <v>20008000</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4298,12 +4298,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4312,13 +4312,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>26250</v>
+        <v>153600</v>
       </c>
       <c r="F120" t="n">
-        <v>762</v>
+        <v>130</v>
       </c>
       <c r="G120" t="n">
-        <v>20002500</v>
+        <v>19968000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4330,12 +4330,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4344,13 +4344,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>22850</v>
+        <v>99800</v>
       </c>
       <c r="F121" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G121" t="n">
-        <v>19993750</v>
+        <v>19960000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4376,13 +4376,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>168500</v>
+        <v>6040</v>
       </c>
       <c r="F122" t="n">
-        <v>119</v>
+        <v>3311</v>
       </c>
       <c r="G122" t="n">
-        <v>20051500</v>
+        <v>19998440</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4408,13 +4408,13 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F123" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G123" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4426,12 +4426,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4440,13 +4440,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F124" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G124" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4458,12 +4458,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4472,13 +4472,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>239000</v>
+        <v>168500</v>
       </c>
       <c r="F125" t="n">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="G125" t="n">
-        <v>20076000</v>
+        <v>20051500</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4490,12 +4490,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4504,13 +4504,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>298000</v>
+        <v>22850</v>
       </c>
       <c r="F126" t="n">
-        <v>117</v>
+        <v>875</v>
       </c>
       <c r="G126" t="n">
-        <v>34866000</v>
+        <v>19993750</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4522,12 +4522,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -4536,13 +4536,13 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>393000</v>
+        <v>37900</v>
       </c>
       <c r="F127" t="n">
-        <v>51</v>
+        <v>528</v>
       </c>
       <c r="G127" t="n">
-        <v>20043000</v>
+        <v>20011200</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4554,12 +4554,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4568,13 +4568,13 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>110900</v>
+        <v>239000</v>
       </c>
       <c r="F128" t="n">
-        <v>180</v>
+        <v>84</v>
       </c>
       <c r="G128" t="n">
-        <v>19962000</v>
+        <v>20076000</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4586,12 +4586,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4600,13 +4600,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>44500</v>
+        <v>298000</v>
       </c>
       <c r="F129" t="n">
-        <v>449</v>
+        <v>117</v>
       </c>
       <c r="G129" t="n">
-        <v>19980500</v>
+        <v>34866000</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4618,12 +4618,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4632,13 +4632,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>135000</v>
+        <v>393000</v>
       </c>
       <c r="F130" t="n">
-        <v>148</v>
+        <v>51</v>
       </c>
       <c r="G130" t="n">
-        <v>19980000</v>
+        <v>20043000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4650,12 +4650,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4664,13 +4664,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>33750</v>
+        <v>110900</v>
       </c>
       <c r="F131" t="n">
-        <v>593</v>
+        <v>180</v>
       </c>
       <c r="G131" t="n">
-        <v>20013750</v>
+        <v>19962000</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4682,29 +4682,125 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E132" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F132" t="n">
+        <v>449</v>
+      </c>
+      <c r="G132" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E133" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F133" t="n">
+        <v>148</v>
+      </c>
+      <c r="G133" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E134" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F134" t="n">
+        <v>593</v>
+      </c>
+      <c r="G134" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C132" t="inlineStr">
+      <c r="C135" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E132" t="n">
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
         <v>124600</v>
       </c>
-      <c r="F132" t="n">
+      <c r="F135" t="n">
         <v>161</v>
       </c>
-      <c r="G132" t="n">
+      <c r="G135" t="n">
         <v>20060600</v>
       </c>
-      <c r="H132" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H135"/>
+  <dimension ref="A1:H163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -510,31 +510,29 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>29050</v>
+        <v>48800</v>
       </c>
       <c r="F3" t="n">
-        <v>686</v>
+        <v>6.3754</v>
       </c>
       <c r="G3" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H3" t="n">
-        <v>3.01</v>
-      </c>
+        <v>311119.6</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -544,29 +542,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1074000</v>
+        <v>29050</v>
       </c>
       <c r="F4" t="n">
-        <v>19.4189</v>
+        <v>686</v>
       </c>
       <c r="G4" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H4" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,31 +576,29 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>19430</v>
+        <v>275000</v>
       </c>
       <c r="F5" t="n">
-        <v>1071</v>
+        <v>3.4779</v>
       </c>
       <c r="G5" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0.78</v>
-      </c>
+        <v>956424.2</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -610,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>21200</v>
+        <v>326500</v>
       </c>
       <c r="F6" t="n">
-        <v>1475.6547</v>
+        <v>0.8772</v>
       </c>
       <c r="G6" t="n">
-        <v>31283879.4</v>
+        <v>286419.6</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -642,31 +640,29 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>256000</v>
+        <v>36800</v>
       </c>
       <c r="F7" t="n">
-        <v>113.8306</v>
+        <v>14.2631</v>
       </c>
       <c r="G7" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>524880.4</v>
+      </c>
+      <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -676,27 +672,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>75700</v>
+        <v>536000</v>
       </c>
       <c r="F8" t="n">
-        <v>275.5075</v>
+        <v>2.9103</v>
       </c>
       <c r="G8" t="n">
-        <v>20855919.6</v>
+        <v>1559919.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -708,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,94 +718,94 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>183500</v>
+        <v>97600</v>
       </c>
       <c r="F9" t="n">
-        <v>113.6562</v>
+        <v>19.6877</v>
       </c>
       <c r="G9" t="n">
-        <v>20855919.6</v>
+        <v>1921519.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1849000</v>
+        <v>153900</v>
       </c>
       <c r="F10" t="n">
-        <v>5.5521</v>
+        <v>17.0321</v>
       </c>
       <c r="G10" t="n">
-        <v>10265800.4</v>
+        <v>2621239.2</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>260000</v>
+        <v>1074000</v>
       </c>
       <c r="F11" t="n">
-        <v>39.4838</v>
+        <v>19.4189</v>
       </c>
       <c r="G11" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -818,226 +814,222 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>24700</v>
+        <v>87400</v>
       </c>
       <c r="F12" t="n">
-        <v>415.6194</v>
+        <v>15.0802</v>
       </c>
       <c r="G12" t="n">
-        <v>10265800.4</v>
+        <v>1318012.9</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>48650</v>
+        <v>225000</v>
       </c>
       <c r="F13" t="n">
-        <v>422.0267</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G13" t="n">
-        <v>20531600.8</v>
+        <v>155919.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>87800</v>
+        <v>5810</v>
       </c>
       <c r="F14" t="n">
-        <v>115.4542</v>
+        <v>154.6591</v>
       </c>
       <c r="G14" t="n">
-        <v>10136875</v>
+        <v>898569.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>22750</v>
+        <v>30200</v>
       </c>
       <c r="F15" t="n">
-        <v>891.1538</v>
+        <v>109.4066</v>
       </c>
       <c r="G15" t="n">
-        <v>20273749.9</v>
+        <v>3304080.4</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>33150</v>
+        <v>207000</v>
       </c>
       <c r="F16" t="n">
-        <v>569</v>
+        <v>1.2389</v>
       </c>
       <c r="G16" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H16" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>256454.4</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>254500</v>
+        <v>28150</v>
       </c>
       <c r="F17" t="n">
-        <v>39.8306</v>
+        <v>195.4454</v>
       </c>
       <c r="G17" t="n">
-        <v>10136875</v>
+        <v>5501788.7</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>79400</v>
+        <v>50500</v>
       </c>
       <c r="F18" t="n">
-        <v>246</v>
+        <v>7.0115</v>
       </c>
       <c r="G18" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H18" t="n">
-        <v>-8</v>
-      </c>
+        <v>354080.4</v>
+      </c>
+      <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,96 +1038,96 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>14780</v>
+        <v>19430</v>
       </c>
       <c r="F19" t="n">
-        <v>1338</v>
+        <v>1071</v>
       </c>
       <c r="G19" t="n">
-        <v>19775640</v>
+        <v>20809530</v>
       </c>
       <c r="H19" t="n">
-        <v>33.89</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>195800</v>
+        <v>21200</v>
       </c>
       <c r="F20" t="n">
-        <v>101.9921</v>
+        <v>1475.6547</v>
       </c>
       <c r="G20" t="n">
-        <v>19970062</v>
+        <v>31283879.4</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>14600</v>
+        <v>21200</v>
       </c>
       <c r="F21" t="n">
-        <v>1367.8125</v>
+        <v>154.5755</v>
       </c>
       <c r="G21" t="n">
-        <v>19970062</v>
+        <v>3277001</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1144,30 +1136,30 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>36300</v>
+        <v>27700</v>
       </c>
       <c r="F22" t="n">
-        <v>275.0697</v>
+        <v>98.6181</v>
       </c>
       <c r="G22" t="n">
-        <v>9985031</v>
+        <v>2731720.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1176,30 +1168,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>159300</v>
+        <v>13960</v>
       </c>
       <c r="F23" t="n">
-        <v>62.6807</v>
+        <v>126.1646</v>
       </c>
       <c r="G23" t="n">
-        <v>9985031</v>
+        <v>1761257.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,30 +1200,30 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>147200</v>
+        <v>140200</v>
       </c>
       <c r="F24" t="n">
-        <v>67</v>
+        <v>21.1375</v>
       </c>
       <c r="G24" t="n">
-        <v>9862400</v>
+        <v>2963479.4</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,64 +1232,62 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>14540</v>
+        <v>6330</v>
       </c>
       <c r="F25" t="n">
-        <v>983</v>
+        <v>13.226</v>
       </c>
       <c r="G25" t="n">
-        <v>14292820</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>113400</v>
+        <v>15750</v>
       </c>
       <c r="F26" t="n">
-        <v>167</v>
+        <v>5.8146</v>
       </c>
       <c r="G26" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H26" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>91580.39999999999</v>
+      </c>
+      <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1306,30 +1296,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>24350</v>
+        <v>22500</v>
       </c>
       <c r="F27" t="n">
-        <v>407</v>
+        <v>110.3946</v>
       </c>
       <c r="G27" t="n">
-        <v>9910450</v>
+        <v>2483879.4</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1338,32 +1328,32 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>44100</v>
+        <v>256000</v>
       </c>
       <c r="F28" t="n">
-        <v>488</v>
+        <v>113.8306</v>
       </c>
       <c r="G28" t="n">
-        <v>21520800</v>
+        <v>29140620.8</v>
       </c>
       <c r="H28" t="n">
-        <v>4.26</v>
+        <v>-9.470000000000001</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1372,190 +1362,190 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>165700</v>
+        <v>75700</v>
       </c>
       <c r="F29" t="n">
-        <v>120</v>
+        <v>275.5075</v>
       </c>
       <c r="G29" t="n">
-        <v>19884000</v>
+        <v>20855919.6</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>28950</v>
+        <v>131600</v>
       </c>
       <c r="F30" t="n">
-        <v>353</v>
+        <v>2.4796</v>
       </c>
       <c r="G30" t="n">
-        <v>10219350</v>
+        <v>326319.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1853000</v>
+        <v>41150</v>
       </c>
       <c r="F31" t="n">
-        <v>11</v>
+        <v>43.8267</v>
       </c>
       <c r="G31" t="n">
-        <v>20383000</v>
+        <v>1803469.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>269000</v>
+        <v>147300</v>
       </c>
       <c r="F32" t="n">
-        <v>76</v>
+        <v>2.3821</v>
       </c>
       <c r="G32" t="n">
-        <v>20444000</v>
+        <v>350879.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106300</v>
+        <v>36450</v>
       </c>
       <c r="F33" t="n">
-        <v>194</v>
+        <v>76.7514</v>
       </c>
       <c r="G33" t="n">
-        <v>20622200</v>
+        <v>2797588.9</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>123100</v>
+        <v>119700</v>
       </c>
       <c r="F34" t="n">
-        <v>167</v>
+        <v>30.2349</v>
       </c>
       <c r="G34" t="n">
-        <v>20557700</v>
+        <v>3619119.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1564,62 +1554,62 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1856000</v>
+        <v>85400</v>
       </c>
       <c r="F35" t="n">
-        <v>23</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G35" t="n">
-        <v>42688000</v>
+        <v>835680.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>49000</v>
+        <v>183500</v>
       </c>
       <c r="F36" t="n">
-        <v>167</v>
+        <v>113.6562</v>
       </c>
       <c r="G36" t="n">
-        <v>8183000</v>
+        <v>20855919.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1628,30 +1618,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>13340</v>
+        <v>183500</v>
       </c>
       <c r="F37" t="n">
-        <v>236</v>
+        <v>12.1963</v>
       </c>
       <c r="G37" t="n">
-        <v>3148240</v>
+        <v>2238023.8</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1660,20 +1650,20 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>29800</v>
+        <v>1849000</v>
       </c>
       <c r="F38" t="n">
-        <v>66</v>
+        <v>5.5521</v>
       </c>
       <c r="G38" t="n">
-        <v>1966800</v>
+        <v>10265800.4</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1692,62 +1682,62 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>269500</v>
+        <v>260000</v>
       </c>
       <c r="F39" t="n">
-        <v>118</v>
+        <v>39.4838</v>
       </c>
       <c r="G39" t="n">
-        <v>31801000</v>
+        <v>10265800.4</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>330000</v>
+        <v>24700</v>
       </c>
       <c r="F40" t="n">
-        <v>24</v>
+        <v>415.6194</v>
       </c>
       <c r="G40" t="n">
-        <v>7920000</v>
+        <v>10265800.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1756,30 +1746,30 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>35550</v>
+        <v>48650</v>
       </c>
       <c r="F41" t="n">
-        <v>581</v>
+        <v>422.0267</v>
       </c>
       <c r="G41" t="n">
-        <v>20654550</v>
+        <v>20531600.8</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1788,190 +1778,196 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>574000</v>
+        <v>87800</v>
       </c>
       <c r="F42" t="n">
-        <v>22</v>
+        <v>115.4542</v>
       </c>
       <c r="G42" t="n">
-        <v>12628000</v>
+        <v>10136875</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>165900</v>
+        <v>22750</v>
       </c>
       <c r="F43" t="n">
-        <v>24</v>
+        <v>891.1538</v>
       </c>
       <c r="G43" t="n">
-        <v>3981600</v>
+        <v>20273749.9</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>91300</v>
+        <v>33150</v>
       </c>
       <c r="F44" t="n">
-        <v>45</v>
+        <v>569</v>
       </c>
       <c r="G44" t="n">
-        <v>4108500</v>
-      </c>
-      <c r="H44" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H44" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>224500</v>
+        <v>254500</v>
       </c>
       <c r="F45" t="n">
-        <v>92</v>
+        <v>39.8306</v>
       </c>
       <c r="G45" t="n">
-        <v>20654000</v>
+        <v>10136875</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6010</v>
+        <v>79400</v>
       </c>
       <c r="F46" t="n">
-        <v>3435</v>
+        <v>246</v>
       </c>
       <c r="G46" t="n">
-        <v>20644350</v>
-      </c>
-      <c r="H46" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H46" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>25800</v>
+        <v>14780</v>
       </c>
       <c r="F47" t="n">
-        <v>351</v>
+        <v>1338</v>
       </c>
       <c r="G47" t="n">
-        <v>9055800</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H47" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1980,30 +1976,30 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>49150</v>
+        <v>195800</v>
       </c>
       <c r="F48" t="n">
-        <v>420</v>
+        <v>101.9921</v>
       </c>
       <c r="G48" t="n">
-        <v>20643000</v>
+        <v>19970062</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2012,30 +2008,30 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>19280</v>
+        <v>14600</v>
       </c>
       <c r="F49" t="n">
-        <v>1071</v>
+        <v>1367.8125</v>
       </c>
       <c r="G49" t="n">
-        <v>20648880</v>
+        <v>19970062</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2044,254 +2040,258 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>19740</v>
+        <v>36300</v>
       </c>
       <c r="F50" t="n">
-        <v>523</v>
+        <v>275.0697</v>
       </c>
       <c r="G50" t="n">
-        <v>10324020</v>
+        <v>9985031</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>25150</v>
+        <v>159300</v>
       </c>
       <c r="F51" t="n">
-        <v>821</v>
+        <v>62.6807</v>
       </c>
       <c r="G51" t="n">
-        <v>20648150</v>
+        <v>9985031</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>153500</v>
+        <v>147200</v>
       </c>
       <c r="F52" t="n">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="G52" t="n">
-        <v>3684000</v>
+        <v>9862400</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6240</v>
+        <v>14540</v>
       </c>
       <c r="F53" t="n">
-        <v>3308</v>
+        <v>983</v>
       </c>
       <c r="G53" t="n">
-        <v>20641920</v>
+        <v>14292820</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>15520</v>
+        <v>113400</v>
       </c>
       <c r="F54" t="n">
-        <v>1330</v>
+        <v>167</v>
       </c>
       <c r="G54" t="n">
-        <v>20641600</v>
-      </c>
-      <c r="H54" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H54" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24200</v>
+        <v>24350</v>
       </c>
       <c r="F55" t="n">
-        <v>210</v>
+        <v>407</v>
       </c>
       <c r="G55" t="n">
-        <v>5082000</v>
+        <v>9910450</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>36300</v>
+        <v>44100</v>
       </c>
       <c r="F56" t="n">
-        <v>569</v>
+        <v>488</v>
       </c>
       <c r="G56" t="n">
-        <v>20654700</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H56" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>279500</v>
+        <v>165700</v>
       </c>
       <c r="F57" t="n">
-        <v>43</v>
+        <v>120</v>
       </c>
       <c r="G57" t="n">
-        <v>12018500</v>
+        <v>19884000</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2300,30 +2300,30 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>132600</v>
+        <v>28950</v>
       </c>
       <c r="F58" t="n">
-        <v>90</v>
+        <v>353</v>
       </c>
       <c r="G58" t="n">
-        <v>11934000</v>
+        <v>10219350</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2332,30 +2332,30 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>44600</v>
+        <v>1853000</v>
       </c>
       <c r="F59" t="n">
-        <v>139</v>
+        <v>11</v>
       </c>
       <c r="G59" t="n">
-        <v>6199400</v>
+        <v>20383000</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2364,77 +2364,77 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>147100</v>
+        <v>269000</v>
       </c>
       <c r="F60" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="G60" t="n">
-        <v>882600</v>
+        <v>20444000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>33500</v>
+        <v>106300</v>
       </c>
       <c r="F61" t="n">
-        <v>8</v>
+        <v>194</v>
       </c>
       <c r="G61" t="n">
-        <v>268000</v>
+        <v>20622200</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>143100</v>
+        <v>123100</v>
       </c>
       <c r="F62" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="G62" t="n">
-        <v>13594500</v>
+        <v>20557700</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
@@ -2446,12 +2446,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2460,13 +2460,13 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>83800</v>
+        <v>1856000</v>
       </c>
       <c r="F63" t="n">
-        <v>106</v>
+        <v>23</v>
       </c>
       <c r="G63" t="n">
-        <v>8882800</v>
+        <v>42688000</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2478,27 +2478,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>42300</v>
+        <v>49000</v>
       </c>
       <c r="F64" t="n">
-        <v>488</v>
+        <v>167</v>
       </c>
       <c r="G64" t="n">
-        <v>20642400</v>
+        <v>8183000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2524,62 +2524,62 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>81200</v>
+        <v>13340</v>
       </c>
       <c r="F65" t="n">
-        <v>135</v>
+        <v>236</v>
       </c>
       <c r="G65" t="n">
-        <v>10962000</v>
+        <v>3148240</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>78600</v>
+        <v>29800</v>
       </c>
       <c r="F66" t="n">
-        <v>389</v>
+        <v>66</v>
       </c>
       <c r="G66" t="n">
-        <v>30575400</v>
+        <v>1966800</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2588,196 +2588,190 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>92500</v>
+        <v>269500</v>
       </c>
       <c r="F67" t="n">
-        <v>106</v>
+        <v>118</v>
       </c>
       <c r="G67" t="n">
-        <v>9805000</v>
+        <v>31801000</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>25550</v>
+        <v>330000</v>
       </c>
       <c r="F68" t="n">
-        <v>1151</v>
+        <v>24</v>
       </c>
       <c r="G68" t="n">
-        <v>29408050</v>
+        <v>7920000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>21800</v>
+        <v>35550</v>
       </c>
       <c r="F69" t="n">
-        <v>832</v>
+        <v>581</v>
       </c>
       <c r="G69" t="n">
-        <v>18137600</v>
+        <v>20654550</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>32250</v>
+        <v>574000</v>
       </c>
       <c r="F70" t="n">
-        <v>878</v>
+        <v>22</v>
       </c>
       <c r="G70" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H70" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>12628000</v>
+      </c>
+      <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>105800</v>
+        <v>165900</v>
       </c>
       <c r="F71" t="n">
-        <v>332</v>
+        <v>24</v>
       </c>
       <c r="G71" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H71" t="n">
-        <v>17.17</v>
-      </c>
+        <v>3981600</v>
+      </c>
+      <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>33750</v>
+        <v>91300</v>
       </c>
       <c r="F72" t="n">
-        <v>791</v>
+        <v>45</v>
       </c>
       <c r="G72" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H72" t="n">
-        <v>0.29</v>
-      </c>
+        <v>4108500</v>
+      </c>
+      <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2786,96 +2780,94 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>86300</v>
+        <v>224500</v>
       </c>
       <c r="F73" t="n">
-        <v>352</v>
+        <v>92</v>
       </c>
       <c r="G73" t="n">
-        <v>30377600</v>
+        <v>20654000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>21000</v>
+        <v>6010</v>
       </c>
       <c r="F74" t="n">
-        <v>1517</v>
+        <v>3435</v>
       </c>
       <c r="G74" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H74" t="n">
-        <v>3.96</v>
-      </c>
+        <v>20644350</v>
+      </c>
+      <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>21900</v>
+        <v>25800</v>
       </c>
       <c r="F75" t="n">
-        <v>906</v>
+        <v>351</v>
       </c>
       <c r="G75" t="n">
-        <v>19841400</v>
+        <v>9055800</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2884,30 +2876,30 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>135300</v>
+        <v>49150</v>
       </c>
       <c r="F76" t="n">
-        <v>226</v>
+        <v>420</v>
       </c>
       <c r="G76" t="n">
-        <v>30577800</v>
+        <v>20643000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2916,358 +2908,350 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>22250</v>
+        <v>19280</v>
       </c>
       <c r="F77" t="n">
-        <v>1399</v>
+        <v>1071</v>
       </c>
       <c r="G77" t="n">
-        <v>31127750</v>
+        <v>20648880</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>33500</v>
+        <v>19740</v>
       </c>
       <c r="F78" t="n">
-        <v>848</v>
+        <v>523</v>
       </c>
       <c r="G78" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H78" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>10324020</v>
+      </c>
+      <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>300000</v>
+        <v>25150</v>
       </c>
       <c r="F79" t="n">
-        <v>104</v>
+        <v>821</v>
       </c>
       <c r="G79" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H79" t="n">
-        <v>20.95</v>
-      </c>
+        <v>20648150</v>
+      </c>
+      <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>28200</v>
+        <v>153500</v>
       </c>
       <c r="F80" t="n">
-        <v>1105</v>
+        <v>24</v>
       </c>
       <c r="G80" t="n">
-        <v>31161000</v>
+        <v>3684000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>398000</v>
+        <v>6240</v>
       </c>
       <c r="F81" t="n">
-        <v>72</v>
+        <v>3308</v>
       </c>
       <c r="G81" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H81" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>20641920</v>
+      </c>
+      <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>5620</v>
+        <v>15520</v>
       </c>
       <c r="F82" t="n">
-        <v>4707</v>
+        <v>1330</v>
       </c>
       <c r="G82" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H82" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>20641600</v>
+      </c>
+      <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>126900</v>
+        <v>24200</v>
       </c>
       <c r="F83" t="n">
-        <v>246</v>
+        <v>210</v>
       </c>
       <c r="G83" t="n">
-        <v>31217400</v>
+        <v>5082000</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1671000</v>
+        <v>36300</v>
       </c>
       <c r="F84" t="n">
-        <v>44</v>
+        <v>569</v>
       </c>
       <c r="G84" t="n">
-        <v>73524000</v>
+        <v>20654700</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>50600</v>
+        <v>279500</v>
       </c>
       <c r="F85" t="n">
-        <v>186</v>
+        <v>43</v>
       </c>
       <c r="G85" t="n">
-        <v>9411600</v>
+        <v>12018500</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>11720</v>
+        <v>132600</v>
       </c>
       <c r="F86" t="n">
-        <v>665</v>
+        <v>90</v>
       </c>
       <c r="G86" t="n">
-        <v>7793800</v>
+        <v>11934000</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>414000</v>
+        <v>44600</v>
       </c>
       <c r="F87" t="n">
-        <v>26</v>
+        <v>139</v>
       </c>
       <c r="G87" t="n">
-        <v>10764000</v>
+        <v>6199400</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3276,288 +3260,286 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>257000</v>
+        <v>147100</v>
       </c>
       <c r="F88" t="n">
-        <v>239</v>
+        <v>6</v>
       </c>
       <c r="G88" t="n">
-        <v>61423000</v>
+        <v>882600</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33900</v>
+        <v>33500</v>
       </c>
       <c r="F89" t="n">
-        <v>292</v>
+        <v>8</v>
       </c>
       <c r="G89" t="n">
-        <v>9898800</v>
+        <v>268000</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>515000</v>
+        <v>143100</v>
       </c>
       <c r="F90" t="n">
-        <v>17</v>
+        <v>95</v>
       </c>
       <c r="G90" t="n">
-        <v>8755000</v>
+        <v>13594500</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>141200</v>
+        <v>83800</v>
       </c>
       <c r="F91" t="n">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="G91" t="n">
-        <v>11437200</v>
+        <v>8882800</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6320</v>
+        <v>42300</v>
       </c>
       <c r="F92" t="n">
-        <v>1396</v>
+        <v>488</v>
       </c>
       <c r="G92" t="n">
-        <v>8822720</v>
+        <v>20642400</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>90300</v>
+        <v>81200</v>
       </c>
       <c r="F93" t="n">
-        <v>332</v>
+        <v>135</v>
       </c>
       <c r="G93" t="n">
-        <v>29979600</v>
+        <v>10962000</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>163100</v>
+        <v>78600</v>
       </c>
       <c r="F94" t="n">
-        <v>119</v>
+        <v>389</v>
       </c>
       <c r="G94" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H94" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>37900</v>
+        <v>92500</v>
       </c>
       <c r="F95" t="n">
-        <v>163</v>
+        <v>106</v>
       </c>
       <c r="G95" t="n">
-        <v>6177700</v>
+        <v>9805000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>19990</v>
+        <v>25550</v>
       </c>
       <c r="F96" t="n">
-        <v>615</v>
+        <v>1151</v>
       </c>
       <c r="G96" t="n">
-        <v>12293850</v>
+        <v>29408050</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3566,62 +3548,64 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>35100</v>
+        <v>21800</v>
       </c>
       <c r="F97" t="n">
-        <v>320</v>
+        <v>832</v>
       </c>
       <c r="G97" t="n">
-        <v>11232000</v>
+        <v>18137600</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>286000</v>
+        <v>32250</v>
       </c>
       <c r="F98" t="n">
-        <v>20</v>
+        <v>878</v>
       </c>
       <c r="G98" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H98" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H98" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3630,128 +3614,132 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>416000</v>
+        <v>105800</v>
       </c>
       <c r="F99" t="n">
-        <v>51</v>
+        <v>332</v>
       </c>
       <c r="G99" t="n">
-        <v>21216000</v>
+        <v>35125600</v>
       </c>
       <c r="H99" t="n">
-        <v>5.85</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>49450</v>
+        <v>33750</v>
       </c>
       <c r="F100" t="n">
-        <v>153</v>
+        <v>791</v>
       </c>
       <c r="G100" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>138000</v>
+        <v>86300</v>
       </c>
       <c r="F101" t="n">
-        <v>68</v>
+        <v>352</v>
       </c>
       <c r="G101" t="n">
-        <v>9384000</v>
+        <v>30377600</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>31950</v>
+        <v>21000</v>
       </c>
       <c r="F102" t="n">
-        <v>339</v>
+        <v>1517</v>
       </c>
       <c r="G102" t="n">
-        <v>10831050</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H102" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3760,30 +3748,30 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>124800</v>
+        <v>21900</v>
       </c>
       <c r="F103" t="n">
-        <v>78</v>
+        <v>906</v>
       </c>
       <c r="G103" t="n">
-        <v>9734400</v>
+        <v>19841400</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3792,162 +3780,162 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>10800</v>
+        <v>135300</v>
       </c>
       <c r="F104" t="n">
-        <v>1892</v>
+        <v>226</v>
       </c>
       <c r="G104" t="n">
-        <v>20433600</v>
+        <v>30577800</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>11880</v>
+        <v>22250</v>
       </c>
       <c r="F105" t="n">
-        <v>1474</v>
+        <v>1399</v>
       </c>
       <c r="G105" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H105" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>20200</v>
+        <v>33500</v>
       </c>
       <c r="F106" t="n">
-        <v>1517</v>
+        <v>848</v>
       </c>
       <c r="G106" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H106" t="inlineStr"/>
+        <v>28408000</v>
+      </c>
+      <c r="H106" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>102200</v>
+        <v>300000</v>
       </c>
       <c r="F107" t="n">
-        <v>200</v>
+        <v>104</v>
       </c>
       <c r="G107" t="n">
-        <v>20440000</v>
-      </c>
-      <c r="H107" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H107" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>23450</v>
+        <v>28200</v>
       </c>
       <c r="F108" t="n">
-        <v>762</v>
+        <v>1105</v>
       </c>
       <c r="G108" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H108" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3956,54 +3944,56 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>22050</v>
+        <v>398000</v>
       </c>
       <c r="F109" t="n">
-        <v>875</v>
+        <v>72</v>
       </c>
       <c r="G109" t="n">
-        <v>19293750</v>
+        <v>28656000</v>
       </c>
       <c r="H109" t="n">
-        <v>-3.5</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>32550</v>
+        <v>5620</v>
       </c>
       <c r="F110" t="n">
-        <v>628</v>
+        <v>4707</v>
       </c>
       <c r="G110" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4018,26 +4008,24 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>99700</v>
+        <v>126900</v>
       </c>
       <c r="F111" t="n">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="G111" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>31217400</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4052,24 +4040,24 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1662000</v>
+        <v>1671000</v>
       </c>
       <c r="F112" t="n">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="G112" t="n">
-        <v>249300000</v>
+        <v>73524000</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4084,258 +4072,258 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>49700</v>
+        <v>50600</v>
       </c>
       <c r="F113" t="n">
-        <v>402</v>
+        <v>186</v>
       </c>
       <c r="G113" t="n">
-        <v>19979400</v>
+        <v>9411600</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>435000</v>
+        <v>11720</v>
       </c>
       <c r="F114" t="n">
-        <v>46</v>
+        <v>665</v>
       </c>
       <c r="G114" t="n">
-        <v>20010000</v>
+        <v>7793800</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>268500</v>
+        <v>414000</v>
       </c>
       <c r="F115" t="n">
-        <v>931</v>
+        <v>26</v>
       </c>
       <c r="G115" t="n">
-        <v>249973500</v>
+        <v>10764000</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>13570</v>
+        <v>257000</v>
       </c>
       <c r="F116" t="n">
-        <v>1474</v>
+        <v>239</v>
       </c>
       <c r="G116" t="n">
-        <v>20002180</v>
+        <v>61423000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>343500</v>
+        <v>33900</v>
       </c>
       <c r="F117" t="n">
-        <v>87</v>
+        <v>292</v>
       </c>
       <c r="G117" t="n">
-        <v>29884500</v>
+        <v>9898800</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>34150</v>
+        <v>515000</v>
       </c>
       <c r="F118" t="n">
-        <v>586</v>
+        <v>17</v>
       </c>
       <c r="G118" t="n">
-        <v>20011900</v>
+        <v>8755000</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>488000</v>
+        <v>141200</v>
       </c>
       <c r="F119" t="n">
-        <v>41</v>
+        <v>81</v>
       </c>
       <c r="G119" t="n">
-        <v>20008000</v>
+        <v>11437200</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>153600</v>
+        <v>6320</v>
       </c>
       <c r="F120" t="n">
-        <v>130</v>
+        <v>1396</v>
       </c>
       <c r="G120" t="n">
-        <v>19968000</v>
+        <v>8822720</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4344,350 +4332,354 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>99800</v>
+        <v>90300</v>
       </c>
       <c r="F121" t="n">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="G121" t="n">
-        <v>19960000</v>
+        <v>29979600</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6040</v>
+        <v>163100</v>
       </c>
       <c r="F122" t="n">
-        <v>3311</v>
+        <v>119</v>
       </c>
       <c r="G122" t="n">
-        <v>19998440</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>26250</v>
+        <v>37900</v>
       </c>
       <c r="F123" t="n">
-        <v>762</v>
+        <v>163</v>
       </c>
       <c r="G123" t="n">
-        <v>20002500</v>
+        <v>6177700</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>22850</v>
+        <v>19990</v>
       </c>
       <c r="F124" t="n">
-        <v>875</v>
+        <v>615</v>
       </c>
       <c r="G124" t="n">
-        <v>19993750</v>
+        <v>12293850</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>168500</v>
+        <v>35100</v>
       </c>
       <c r="F125" t="n">
-        <v>119</v>
+        <v>320</v>
       </c>
       <c r="G125" t="n">
-        <v>20051500</v>
+        <v>11232000</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>22850</v>
+        <v>286000</v>
       </c>
       <c r="F126" t="n">
-        <v>875</v>
+        <v>20</v>
       </c>
       <c r="G126" t="n">
-        <v>19993750</v>
+        <v>5720000</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>37900</v>
+        <v>416000</v>
       </c>
       <c r="F127" t="n">
-        <v>528</v>
+        <v>51</v>
       </c>
       <c r="G127" t="n">
-        <v>20011200</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H127" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>239000</v>
+        <v>49450</v>
       </c>
       <c r="F128" t="n">
-        <v>84</v>
+        <v>153</v>
       </c>
       <c r="G128" t="n">
-        <v>20076000</v>
+        <v>7565850</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>298000</v>
+        <v>138000</v>
       </c>
       <c r="F129" t="n">
-        <v>117</v>
+        <v>68</v>
       </c>
       <c r="G129" t="n">
-        <v>34866000</v>
+        <v>9384000</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>393000</v>
+        <v>31950</v>
       </c>
       <c r="F130" t="n">
-        <v>51</v>
+        <v>339</v>
       </c>
       <c r="G130" t="n">
-        <v>20043000</v>
+        <v>10831050</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>110900</v>
+        <v>124800</v>
       </c>
       <c r="F131" t="n">
-        <v>180</v>
+        <v>78</v>
       </c>
       <c r="G131" t="n">
-        <v>19962000</v>
+        <v>9734400</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -4696,62 +4688,64 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>44500</v>
+        <v>10800</v>
       </c>
       <c r="F132" t="n">
-        <v>449</v>
+        <v>1892</v>
       </c>
       <c r="G132" t="n">
-        <v>19980500</v>
+        <v>20433600</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>135000</v>
+        <v>11880</v>
       </c>
       <c r="F133" t="n">
-        <v>148</v>
+        <v>1474</v>
       </c>
       <c r="G133" t="n">
-        <v>19980000</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4760,47 +4754,949 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>33750</v>
+        <v>20200</v>
       </c>
       <c r="F134" t="n">
-        <v>593</v>
+        <v>1517</v>
       </c>
       <c r="G134" t="n">
-        <v>20013750</v>
+        <v>30643400</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E135" t="n">
+        <v>102200</v>
+      </c>
+      <c r="F135" t="n">
+        <v>200</v>
+      </c>
+      <c r="G135" t="n">
+        <v>20440000</v>
+      </c>
+      <c r="H135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E136" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F136" t="n">
+        <v>762</v>
+      </c>
+      <c r="G136" t="n">
+        <v>17868900</v>
+      </c>
+      <c r="H136" t="n">
+        <v>-10.67</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E137" t="n">
+        <v>22050</v>
+      </c>
+      <c r="F137" t="n">
+        <v>875</v>
+      </c>
+      <c r="G137" t="n">
+        <v>19293750</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E138" t="n">
+        <v>32550</v>
+      </c>
+      <c r="F138" t="n">
+        <v>628</v>
+      </c>
+      <c r="G138" t="n">
+        <v>20441400</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E139" t="n">
+        <v>99700</v>
+      </c>
+      <c r="F139" t="n">
+        <v>180</v>
+      </c>
+      <c r="G139" t="n">
+        <v>17946000</v>
+      </c>
+      <c r="H139" t="n">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B135" t="inlineStr">
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E140" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="F140" t="n">
+        <v>150</v>
+      </c>
+      <c r="G140" t="n">
+        <v>249300000</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E141" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F141" t="n">
+        <v>402</v>
+      </c>
+      <c r="G141" t="n">
+        <v>19979400</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>005380</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>435000</v>
+      </c>
+      <c r="F142" t="n">
+        <v>46</v>
+      </c>
+      <c r="G142" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>268500</v>
+      </c>
+      <c r="F143" t="n">
+        <v>931</v>
+      </c>
+      <c r="G143" t="n">
+        <v>249973500</v>
+      </c>
+      <c r="H143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>13570</v>
+      </c>
+      <c r="F144" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G144" t="n">
+        <v>20002180</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>343500</v>
+      </c>
+      <c r="F145" t="n">
+        <v>87</v>
+      </c>
+      <c r="G145" t="n">
+        <v>29884500</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>34150</v>
+      </c>
+      <c r="F146" t="n">
+        <v>586</v>
+      </c>
+      <c r="G146" t="n">
+        <v>20011900</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>488000</v>
+      </c>
+      <c r="F147" t="n">
+        <v>41</v>
+      </c>
+      <c r="G147" t="n">
+        <v>20008000</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>153600</v>
+      </c>
+      <c r="F148" t="n">
+        <v>130</v>
+      </c>
+      <c r="G148" t="n">
+        <v>19968000</v>
+      </c>
+      <c r="H148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E149" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F149" t="n">
+        <v>200</v>
+      </c>
+      <c r="G149" t="n">
+        <v>19960000</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>028670</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E150" t="n">
+        <v>6040</v>
+      </c>
+      <c r="F150" t="n">
+        <v>3311</v>
+      </c>
+      <c r="G150" t="n">
+        <v>19998440</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E151" t="n">
+        <v>26250</v>
+      </c>
+      <c r="F151" t="n">
+        <v>762</v>
+      </c>
+      <c r="G151" t="n">
+        <v>20002500</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E152" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F152" t="n">
+        <v>875</v>
+      </c>
+      <c r="G152" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E153" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F153" t="n">
+        <v>119</v>
+      </c>
+      <c r="G153" t="n">
+        <v>20051500</v>
+      </c>
+      <c r="H153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E154" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F154" t="n">
+        <v>875</v>
+      </c>
+      <c r="G154" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F155" t="n">
+        <v>528</v>
+      </c>
+      <c r="G155" t="n">
+        <v>20011200</v>
+      </c>
+      <c r="H155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>239000</v>
+      </c>
+      <c r="F156" t="n">
+        <v>84</v>
+      </c>
+      <c r="G156" t="n">
+        <v>20076000</v>
+      </c>
+      <c r="H156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>298000</v>
+      </c>
+      <c r="F157" t="n">
+        <v>117</v>
+      </c>
+      <c r="G157" t="n">
+        <v>34866000</v>
+      </c>
+      <c r="H157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F158" t="n">
+        <v>51</v>
+      </c>
+      <c r="G158" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F159" t="n">
+        <v>180</v>
+      </c>
+      <c r="G159" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F160" t="n">
+        <v>449</v>
+      </c>
+      <c r="G160" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E161" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F161" t="n">
+        <v>148</v>
+      </c>
+      <c r="G161" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F162" t="n">
+        <v>593</v>
+      </c>
+      <c r="G162" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
         <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C135" t="inlineStr">
+      <c r="C163" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr">
+      <c r="D163" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E135" t="n">
+      <c r="E163" t="n">
         <v>124600</v>
       </c>
-      <c r="F135" t="n">
+      <c r="F163" t="n">
         <v>161</v>
       </c>
-      <c r="G135" t="n">
+      <c r="G163" t="n">
         <v>20060600</v>
       </c>
-      <c r="H135" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H163"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,32 +473,32 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>126300</v>
+        <v>13580</v>
       </c>
       <c r="F2" t="n">
-        <v>165.13</v>
+        <v>1493.977</v>
       </c>
       <c r="G2" t="n">
-        <v>20855919.6</v>
+        <v>20288208.3</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
@@ -510,27 +510,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>48800</v>
+        <v>126300</v>
       </c>
       <c r="F3" t="n">
-        <v>6.3754</v>
+        <v>165.13</v>
       </c>
       <c r="G3" t="n">
-        <v>311119.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
@@ -542,31 +542,29 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>29050</v>
+        <v>48800</v>
       </c>
       <c r="F4" t="n">
-        <v>686</v>
+        <v>6.3754</v>
       </c>
       <c r="G4" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H4" t="n">
-        <v>3.01</v>
-      </c>
+        <v>311119.6</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -576,29 +574,31 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>275000</v>
+        <v>29050</v>
       </c>
       <c r="F5" t="n">
-        <v>3.4779</v>
+        <v>686</v>
       </c>
       <c r="G5" t="n">
-        <v>956424.2</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H5" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -608,27 +608,27 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>326500</v>
+        <v>275000</v>
       </c>
       <c r="F6" t="n">
-        <v>0.8772</v>
+        <v>3.4779</v>
       </c>
       <c r="G6" t="n">
-        <v>286419.6</v>
+        <v>956424.2</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
@@ -640,27 +640,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>36800</v>
+        <v>326500</v>
       </c>
       <c r="F7" t="n">
-        <v>14.2631</v>
+        <v>0.8772</v>
       </c>
       <c r="G7" t="n">
-        <v>524880.4</v>
+        <v>286419.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -672,27 +672,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>536000</v>
+        <v>36800</v>
       </c>
       <c r="F8" t="n">
-        <v>2.9103</v>
+        <v>14.2631</v>
       </c>
       <c r="G8" t="n">
-        <v>1559919.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -704,12 +704,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -718,13 +718,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>97600</v>
+        <v>536000</v>
       </c>
       <c r="F9" t="n">
-        <v>19.6877</v>
+        <v>2.9103</v>
       </c>
       <c r="G9" t="n">
-        <v>1921519.6</v>
+        <v>1559919.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -736,12 +736,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -750,13 +750,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>153900</v>
+        <v>97600</v>
       </c>
       <c r="F10" t="n">
-        <v>17.0321</v>
+        <v>19.6877</v>
       </c>
       <c r="G10" t="n">
-        <v>2621239.2</v>
+        <v>1921519.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -768,27 +768,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1074000</v>
+        <v>153900</v>
       </c>
       <c r="F11" t="n">
-        <v>19.4189</v>
+        <v>17.0321</v>
       </c>
       <c r="G11" t="n">
-        <v>20855919.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -800,27 +800,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>87400</v>
+        <v>1074000</v>
       </c>
       <c r="F12" t="n">
-        <v>15.0802</v>
+        <v>19.4189</v>
       </c>
       <c r="G12" t="n">
-        <v>1318012.9</v>
+        <v>20855919.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -832,12 +832,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>225000</v>
+        <v>87400</v>
       </c>
       <c r="F13" t="n">
-        <v>0.6929999999999999</v>
+        <v>15.0802</v>
       </c>
       <c r="G13" t="n">
-        <v>155919.6</v>
+        <v>1318012.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -864,12 +864,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -878,13 +878,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5810</v>
+        <v>225000</v>
       </c>
       <c r="F14" t="n">
-        <v>154.6591</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>898569.6</v>
+        <v>155919.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -896,27 +896,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>30200</v>
+        <v>5810</v>
       </c>
       <c r="F15" t="n">
-        <v>109.4066</v>
+        <v>154.6591</v>
       </c>
       <c r="G15" t="n">
-        <v>3304080.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -928,12 +928,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -942,13 +942,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>207000</v>
+        <v>30200</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2389</v>
+        <v>109.4066</v>
       </c>
       <c r="G16" t="n">
-        <v>256454.4</v>
+        <v>3304080.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -974,13 +974,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>28150</v>
+        <v>207000</v>
       </c>
       <c r="F17" t="n">
-        <v>195.4454</v>
+        <v>1.2389</v>
       </c>
       <c r="G17" t="n">
-        <v>5501788.7</v>
+        <v>256454.4</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -992,12 +992,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>50500</v>
+        <v>28150</v>
       </c>
       <c r="F18" t="n">
-        <v>7.0115</v>
+        <v>195.4454</v>
       </c>
       <c r="G18" t="n">
-        <v>354080.4</v>
+        <v>5501788.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1024,31 +1024,29 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>19430</v>
+        <v>50500</v>
       </c>
       <c r="F19" t="n">
-        <v>1071</v>
+        <v>7.0115</v>
       </c>
       <c r="G19" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.78</v>
-      </c>
+        <v>354080.4</v>
+      </c>
+      <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1058,29 +1056,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>21200</v>
+        <v>19430</v>
       </c>
       <c r="F20" t="n">
-        <v>1475.6547</v>
+        <v>1071</v>
       </c>
       <c r="G20" t="n">
-        <v>31283879.4</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1107,10 +1107,10 @@
         <v>21200</v>
       </c>
       <c r="F21" t="n">
-        <v>154.5755</v>
+        <v>1475.6547</v>
       </c>
       <c r="G21" t="n">
-        <v>3277001</v>
+        <v>31283879.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1122,12 +1122,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1136,13 +1136,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F22" t="n">
-        <v>98.6181</v>
+        <v>154.5755</v>
       </c>
       <c r="G22" t="n">
-        <v>2731720.6</v>
+        <v>3277001</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1154,27 +1154,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>13960</v>
+        <v>27700</v>
       </c>
       <c r="F23" t="n">
-        <v>126.1646</v>
+        <v>98.6181</v>
       </c>
       <c r="G23" t="n">
-        <v>1761257.6</v>
+        <v>2731720.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>140200</v>
+        <v>13960</v>
       </c>
       <c r="F24" t="n">
-        <v>21.1375</v>
+        <v>126.1646</v>
       </c>
       <c r="G24" t="n">
-        <v>2963479.4</v>
+        <v>1761257.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1218,27 +1218,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6330</v>
+        <v>140200</v>
       </c>
       <c r="F25" t="n">
-        <v>13.226</v>
+        <v>21.1375</v>
       </c>
       <c r="G25" t="n">
-        <v>83720.39999999999</v>
+        <v>2963479.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>15750</v>
+        <v>6330</v>
       </c>
       <c r="F26" t="n">
-        <v>5.8146</v>
+        <v>13.226</v>
       </c>
       <c r="G26" t="n">
-        <v>91580.39999999999</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1282,27 +1282,27 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>22500</v>
+        <v>15750</v>
       </c>
       <c r="F27" t="n">
-        <v>110.3946</v>
+        <v>5.8146</v>
       </c>
       <c r="G27" t="n">
-        <v>2483879.4</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1314,31 +1314,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>256000</v>
+        <v>22500</v>
       </c>
       <c r="F28" t="n">
-        <v>113.8306</v>
+        <v>110.3946</v>
       </c>
       <c r="G28" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H28" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>2483879.4</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1348,29 +1346,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>75700</v>
+        <v>256000</v>
       </c>
       <c r="F29" t="n">
-        <v>275.5075</v>
+        <v>113.8306</v>
       </c>
       <c r="G29" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1380,27 +1380,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>131600</v>
+        <v>75700</v>
       </c>
       <c r="F30" t="n">
-        <v>2.4796</v>
+        <v>275.5075</v>
       </c>
       <c r="G30" t="n">
-        <v>326319.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1426,13 +1426,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>41150</v>
+        <v>131600</v>
       </c>
       <c r="F31" t="n">
-        <v>43.8267</v>
+        <v>2.4796</v>
       </c>
       <c r="G31" t="n">
-        <v>1803469.6</v>
+        <v>326319.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1444,12 +1444,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1458,13 +1458,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>147300</v>
+        <v>41150</v>
       </c>
       <c r="F32" t="n">
-        <v>2.3821</v>
+        <v>43.8267</v>
       </c>
       <c r="G32" t="n">
-        <v>350879.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1476,27 +1476,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>36450</v>
+        <v>147300</v>
       </c>
       <c r="F33" t="n">
-        <v>76.7514</v>
+        <v>2.3821</v>
       </c>
       <c r="G33" t="n">
-        <v>2797588.9</v>
+        <v>350879.4</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1508,27 +1508,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>119700</v>
+        <v>36450</v>
       </c>
       <c r="F34" t="n">
-        <v>30.2349</v>
+        <v>76.7514</v>
       </c>
       <c r="G34" t="n">
-        <v>3619119.6</v>
+        <v>2797588.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1540,27 +1540,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>85400</v>
+        <v>119700</v>
       </c>
       <c r="F35" t="n">
-        <v>9.785500000000001</v>
+        <v>30.2349</v>
       </c>
       <c r="G35" t="n">
-        <v>835680.4</v>
+        <v>3619119.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1572,27 +1572,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>183500</v>
+        <v>85400</v>
       </c>
       <c r="F36" t="n">
-        <v>113.6562</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>20855919.6</v>
+        <v>835680.4</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1614,34 +1614,34 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E37" t="n">
         <v>183500</v>
       </c>
       <c r="F37" t="n">
-        <v>12.1963</v>
+        <v>113.6562</v>
       </c>
       <c r="G37" t="n">
-        <v>2238023.8</v>
+        <v>20855919.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1650,13 +1650,13 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1849000</v>
+        <v>183500</v>
       </c>
       <c r="F38" t="n">
-        <v>5.5521</v>
+        <v>12.1963</v>
       </c>
       <c r="G38" t="n">
-        <v>10265800.4</v>
+        <v>2238023.8</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1668,12 +1668,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1682,10 +1682,10 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>260000</v>
+        <v>1849000</v>
       </c>
       <c r="F39" t="n">
-        <v>39.4838</v>
+        <v>5.5521</v>
       </c>
       <c r="G39" t="n">
         <v>10265800.4</v>
@@ -1700,24 +1700,24 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>24700</v>
+        <v>260000</v>
       </c>
       <c r="F40" t="n">
-        <v>415.6194</v>
+        <v>39.4838</v>
       </c>
       <c r="G40" t="n">
         <v>10265800.4</v>
@@ -1732,59 +1732,59 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>48650</v>
+        <v>24700</v>
       </c>
       <c r="F41" t="n">
-        <v>422.0267</v>
+        <v>415.6194</v>
       </c>
       <c r="G41" t="n">
-        <v>20531600.8</v>
+        <v>10265800.4</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>87800</v>
+        <v>48650</v>
       </c>
       <c r="F42" t="n">
-        <v>115.4542</v>
+        <v>422.0267</v>
       </c>
       <c r="G42" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1796,27 +1796,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>22750</v>
+        <v>87800</v>
       </c>
       <c r="F43" t="n">
-        <v>891.1538</v>
+        <v>115.4542</v>
       </c>
       <c r="G43" t="n">
-        <v>20273749.9</v>
+        <v>10136875</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1828,31 +1828,29 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F44" t="n">
-        <v>569</v>
+        <v>891.1538</v>
       </c>
       <c r="G44" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H44" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1862,29 +1860,31 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>254500</v>
+        <v>33150</v>
       </c>
       <c r="F45" t="n">
-        <v>39.8306</v>
+        <v>569</v>
       </c>
       <c r="G45" t="n">
-        <v>10136875</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1894,46 +1894,44 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>79400</v>
+        <v>254500</v>
       </c>
       <c r="F46" t="n">
-        <v>246</v>
+        <v>39.8306</v>
       </c>
       <c r="G46" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H46" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,16 +1940,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>14780</v>
+        <v>79400</v>
       </c>
       <c r="F47" t="n">
-        <v>1338</v>
+        <v>246</v>
       </c>
       <c r="G47" t="n">
-        <v>19775640</v>
+        <v>19532400</v>
       </c>
       <c r="H47" t="n">
-        <v>33.89</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="48">
@@ -1962,29 +1960,31 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>195800</v>
+        <v>14780</v>
       </c>
       <c r="F48" t="n">
-        <v>101.9921</v>
+        <v>1338</v>
       </c>
       <c r="G48" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H48" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1994,12 +1994,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>14600</v>
+        <v>195800</v>
       </c>
       <c r="F49" t="n">
-        <v>1367.8125</v>
+        <v>101.9921</v>
       </c>
       <c r="G49" t="n">
         <v>19970062</v>
@@ -2026,27 +2026,27 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>36300</v>
+        <v>14600</v>
       </c>
       <c r="F50" t="n">
-        <v>275.0697</v>
+        <v>1367.8125</v>
       </c>
       <c r="G50" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2058,24 +2058,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>159300</v>
+        <v>36300</v>
       </c>
       <c r="F51" t="n">
-        <v>62.6807</v>
+        <v>275.0697</v>
       </c>
       <c r="G51" t="n">
         <v>9985031</v>
@@ -2085,17 +2085,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2104,45 +2104,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>147200</v>
+        <v>159300</v>
       </c>
       <c r="F52" t="n">
-        <v>67</v>
+        <v>62.6807</v>
       </c>
       <c r="G52" t="n">
-        <v>9862400</v>
+        <v>9985031</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>14540</v>
+        <v>147200</v>
       </c>
       <c r="F53" t="n">
-        <v>983</v>
+        <v>67</v>
       </c>
       <c r="G53" t="n">
-        <v>14292820</v>
+        <v>9862400</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2154,31 +2154,29 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>113400</v>
+        <v>14540</v>
       </c>
       <c r="F54" t="n">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="G54" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H54" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>14292820</v>
+      </c>
+      <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2188,29 +2186,31 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>24350</v>
+        <v>113400</v>
       </c>
       <c r="F55" t="n">
-        <v>407</v>
+        <v>167</v>
       </c>
       <c r="G55" t="n">
-        <v>9910450</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2220,31 +2220,29 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>44100</v>
+        <v>24350</v>
       </c>
       <c r="F56" t="n">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G56" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H56" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9910450</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2254,76 +2252,78 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>165700</v>
+        <v>44100</v>
       </c>
       <c r="F57" t="n">
-        <v>120</v>
+        <v>488</v>
       </c>
       <c r="G57" t="n">
-        <v>19884000</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>28950</v>
+        <v>165700</v>
       </c>
       <c r="F58" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>10219350</v>
+        <v>19884000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -2332,13 +2332,13 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1853000</v>
+        <v>28950</v>
       </c>
       <c r="F59" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G59" t="n">
-        <v>20383000</v>
+        <v>10219350</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2350,12 +2350,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2364,13 +2364,13 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F60" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
@@ -2382,27 +2382,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F61" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G61" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2414,12 +2414,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2428,45 +2428,45 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F62" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G62" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F63" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G63" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
@@ -2478,12 +2478,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -2492,13 +2492,13 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F64" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G64" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2510,12 +2510,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2524,13 +2524,13 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F65" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G65" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
@@ -2542,12 +2542,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2556,13 +2556,13 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F66" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G66" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F67" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G67" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2606,12 +2606,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2620,13 +2620,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F68" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G68" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2638,27 +2638,27 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F69" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G69" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2670,27 +2670,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F70" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G70" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2702,12 +2702,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F71" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G71" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2734,27 +2734,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F72" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G72" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2766,27 +2766,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F73" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G73" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2798,12 +2798,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2812,13 +2812,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F74" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G74" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2830,27 +2830,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F75" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G75" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2862,27 +2862,27 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F76" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G76" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2894,12 +2894,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2908,13 +2908,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F77" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G77" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2926,27 +2926,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F78" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G78" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2958,27 +2958,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F79" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G79" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2990,27 +2990,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F80" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G80" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3022,27 +3022,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F81" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G81" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3054,12 +3054,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3068,13 +3068,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F82" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G82" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3086,27 +3086,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F83" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G83" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3118,27 +3118,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F84" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G84" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3150,27 +3150,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F85" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G85" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3182,12 +3182,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3196,13 +3196,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F86" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G86" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3214,12 +3214,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3228,13 +3228,13 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F87" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G87" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3260,13 +3260,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F88" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G88" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3278,12 +3278,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3292,13 +3292,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F89" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3310,12 +3310,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3324,13 +3324,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F90" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3342,12 +3342,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3356,13 +3356,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F91" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G91" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3374,27 +3374,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F92" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G92" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3406,34 +3406,34 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F93" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G93" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3448,49 +3448,49 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F94" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G94" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F95" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G95" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3502,95 +3502,93 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F96" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G96" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F97" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G97" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F98" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G98" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H98" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3600,12 +3598,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3614,16 +3612,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F99" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G99" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H99" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="100">
@@ -3634,12 +3632,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3648,16 +3646,16 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F100" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G100" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H100" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="101">
@@ -3668,63 +3666,63 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F101" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G101" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F102" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G102" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H102" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3734,29 +3732,31 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F103" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G103" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H103" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H103" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3766,44 +3766,44 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F104" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G104" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3812,13 +3812,13 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F105" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G105" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
@@ -3830,31 +3830,29 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F106" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G106" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H106" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -3864,12 +3862,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,49 +3876,51 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F107" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G107" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H107" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F108" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G108" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H108" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3930,31 +3930,29 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F109" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G109" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3964,12 +3962,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3978,16 +3976,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F110" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G110" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H110" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="111">
@@ -3998,59 +3996,61 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F111" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G111" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H111" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H111" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F112" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G112" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4062,27 +4062,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F113" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G113" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
@@ -4094,12 +4094,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -4108,13 +4108,13 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F114" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G114" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
@@ -4126,12 +4126,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4140,13 +4140,13 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F115" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G115" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
@@ -4158,27 +4158,27 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F116" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G116" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4190,27 +4190,27 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F117" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G117" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4222,12 +4222,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4236,13 +4236,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F118" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G118" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4254,12 +4254,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4268,13 +4268,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F119" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G119" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4286,12 +4286,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4300,13 +4300,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F120" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G120" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4318,27 +4318,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F121" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G121" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4350,31 +4350,29 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F122" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G122" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4384,29 +4382,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F123" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G123" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4416,12 +4416,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4430,13 +4430,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F124" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G124" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4448,12 +4448,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4462,13 +4462,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F125" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G125" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4480,12 +4480,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4494,13 +4494,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F126" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G126" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4512,31 +4512,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F127" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G127" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H127" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4546,29 +4544,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F128" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G128" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4578,12 +4578,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4592,13 +4592,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F129" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G129" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4610,12 +4610,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4624,13 +4624,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F130" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G130" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4642,12 +4642,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4656,45 +4656,45 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F131" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G131" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F132" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G132" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4706,31 +4706,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F133" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G133" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4740,29 +4738,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F134" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G134" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4772,27 +4772,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F135" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G135" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4804,31 +4804,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F136" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G136" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H136" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4838,12 +4836,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4852,16 +4850,16 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F137" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G137" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H137" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="138">
@@ -4872,29 +4870,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F138" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G138" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H138" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4904,63 +4904,63 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F139" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G139" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F140" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G140" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -4970,12 +4970,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4984,13 +4984,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F141" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G141" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5002,12 +5002,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5016,13 +5016,13 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F142" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G142" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
@@ -5034,12 +5034,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5048,13 +5048,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F143" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G143" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5066,12 +5066,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5080,13 +5080,13 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F144" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G144" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
@@ -5098,12 +5098,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5112,13 +5112,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F145" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G145" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5130,12 +5130,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5144,13 +5144,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F146" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G146" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5162,12 +5162,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5176,13 +5176,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F147" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G147" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5194,12 +5194,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5208,13 +5208,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F148" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G148" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5226,12 +5226,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5240,13 +5240,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F149" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G149" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5258,12 +5258,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5272,13 +5272,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F150" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G150" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5290,12 +5290,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5304,13 +5304,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F151" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G151" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5322,12 +5322,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5336,13 +5336,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F152" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G152" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5354,12 +5354,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5368,13 +5368,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F153" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G153" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5386,12 +5386,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F154" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G154" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5418,12 +5418,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5432,13 +5432,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F155" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G155" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5450,12 +5450,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5464,13 +5464,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F156" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G156" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5482,12 +5482,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5496,13 +5496,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F157" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G157" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5514,12 +5514,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5528,13 +5528,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F158" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G158" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5546,12 +5546,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5560,13 +5560,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F159" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G159" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5578,12 +5578,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5592,13 +5592,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F160" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G160" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5610,12 +5610,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5624,13 +5624,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F161" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G161" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5656,13 +5656,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F162" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G162" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5674,29 +5674,61 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E163" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F163" t="n">
+        <v>593</v>
+      </c>
+      <c r="G163" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C163" t="inlineStr">
+      <c r="C164" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E163" t="n">
+      <c r="E164" t="n">
         <v>124600</v>
       </c>
-      <c r="F163" t="n">
+      <c r="F164" t="n">
         <v>161</v>
       </c>
-      <c r="G163" t="n">
+      <c r="G164" t="n">
         <v>20060600</v>
       </c>
-      <c r="H163" t="inlineStr"/>
+      <c r="H164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -500,7 +500,9 @@
       <c r="G2" t="n">
         <v>20288208.3</v>
       </c>
-      <c r="H2" t="inlineStr"/>
+      <c r="H2" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,51 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13580</v>
+        <v>296500</v>
       </c>
       <c r="F2" t="n">
-        <v>1493.977</v>
+        <v>71.0389</v>
       </c>
       <c r="G2" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>21063043.1</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,62 +524,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>126300</v>
+        <v>12230</v>
       </c>
       <c r="F3" t="n">
-        <v>165.13</v>
+        <v>1722.2439</v>
       </c>
       <c r="G3" t="n">
-        <v>20855919.6</v>
+        <v>21063043.1</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48800</v>
+        <v>156400</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3754</v>
+        <v>134.6742</v>
       </c>
       <c r="G4" t="n">
-        <v>311119.6</v>
+        <v>21063043.1</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,49 +588,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29050</v>
+        <v>39650</v>
       </c>
       <c r="F5" t="n">
-        <v>686</v>
+        <v>506.8267</v>
       </c>
       <c r="G5" t="n">
-        <v>19928300</v>
+        <v>20095679.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.01</v>
+        <v>-12.59</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>275000</v>
+        <v>13580</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4779</v>
+        <v>1493.977</v>
       </c>
       <c r="G6" t="n">
-        <v>956424.2</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>326500</v>
+        <v>126300</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8772</v>
+        <v>165.13</v>
       </c>
       <c r="G7" t="n">
-        <v>286419.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36800</v>
+        <v>48800</v>
       </c>
       <c r="F8" t="n">
-        <v>14.2631</v>
+        <v>6.3754</v>
       </c>
       <c r="G8" t="n">
-        <v>524880.4</v>
+        <v>311119.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,29 +706,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>536000</v>
+        <v>29050</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9103</v>
+        <v>686</v>
       </c>
       <c r="G9" t="n">
-        <v>1559919.6</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,27 +740,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>97600</v>
+        <v>275000</v>
       </c>
       <c r="F10" t="n">
-        <v>19.6877</v>
+        <v>3.4779</v>
       </c>
       <c r="G10" t="n">
-        <v>1921519.6</v>
+        <v>956424.2</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>153900</v>
+        <v>326500</v>
       </c>
       <c r="F11" t="n">
-        <v>17.0321</v>
+        <v>0.8772</v>
       </c>
       <c r="G11" t="n">
-        <v>2621239.2</v>
+        <v>286419.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,27 +804,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1074000</v>
+        <v>36800</v>
       </c>
       <c r="F12" t="n">
-        <v>19.4189</v>
+        <v>14.2631</v>
       </c>
       <c r="G12" t="n">
-        <v>20855919.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +836,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +850,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>87400</v>
+        <v>536000</v>
       </c>
       <c r="F13" t="n">
-        <v>15.0802</v>
+        <v>2.9103</v>
       </c>
       <c r="G13" t="n">
-        <v>1318012.9</v>
+        <v>1559919.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +868,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +882,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225000</v>
+        <v>97600</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6929999999999999</v>
+        <v>19.6877</v>
       </c>
       <c r="G14" t="n">
-        <v>155919.6</v>
+        <v>1921519.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +914,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5810</v>
+        <v>153900</v>
       </c>
       <c r="F15" t="n">
-        <v>154.6591</v>
+        <v>17.0321</v>
       </c>
       <c r="G15" t="n">
-        <v>898569.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,27 +932,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30200</v>
+        <v>1074000</v>
       </c>
       <c r="F16" t="n">
-        <v>109.4066</v>
+        <v>19.4189</v>
       </c>
       <c r="G16" t="n">
-        <v>3304080.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,27 +964,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>207000</v>
+        <v>87400</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2389</v>
+        <v>15.0802</v>
       </c>
       <c r="G17" t="n">
-        <v>256454.4</v>
+        <v>1318012.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +996,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28150</v>
+        <v>225000</v>
       </c>
       <c r="F18" t="n">
-        <v>195.4454</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>5501788.7</v>
+        <v>155919.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,27 +1028,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50500</v>
+        <v>5810</v>
       </c>
       <c r="F19" t="n">
-        <v>7.0115</v>
+        <v>154.6591</v>
       </c>
       <c r="G19" t="n">
-        <v>354080.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,31 +1060,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19430</v>
+        <v>30200</v>
       </c>
       <c r="F20" t="n">
-        <v>1071</v>
+        <v>109.4066</v>
       </c>
       <c r="G20" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.78</v>
-      </c>
+        <v>3304080.4</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21200</v>
+        <v>207000</v>
       </c>
       <c r="F21" t="n">
-        <v>1475.6547</v>
+        <v>1.2389</v>
       </c>
       <c r="G21" t="n">
-        <v>31283879.4</v>
+        <v>256454.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21200</v>
+        <v>28150</v>
       </c>
       <c r="F22" t="n">
-        <v>154.5755</v>
+        <v>195.4454</v>
       </c>
       <c r="G22" t="n">
-        <v>3277001</v>
+        <v>5501788.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>27700</v>
+        <v>50500</v>
       </c>
       <c r="F23" t="n">
-        <v>98.6181</v>
+        <v>7.0115</v>
       </c>
       <c r="G23" t="n">
-        <v>2731720.6</v>
+        <v>354080.4</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,29 +1188,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13960</v>
+        <v>19430</v>
       </c>
       <c r="F24" t="n">
-        <v>126.1646</v>
+        <v>1071</v>
       </c>
       <c r="G24" t="n">
-        <v>1761257.6</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1220,27 +1222,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>140200</v>
+        <v>21200</v>
       </c>
       <c r="F25" t="n">
-        <v>21.1375</v>
+        <v>1475.6547</v>
       </c>
       <c r="G25" t="n">
-        <v>2963479.4</v>
+        <v>31283879.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6330</v>
+        <v>21200</v>
       </c>
       <c r="F26" t="n">
-        <v>13.226</v>
+        <v>154.5755</v>
       </c>
       <c r="G26" t="n">
-        <v>83720.39999999999</v>
+        <v>3277001</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15750</v>
+        <v>27700</v>
       </c>
       <c r="F27" t="n">
-        <v>5.8146</v>
+        <v>98.6181</v>
       </c>
       <c r="G27" t="n">
-        <v>91580.39999999999</v>
+        <v>2731720.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22500</v>
+        <v>13960</v>
       </c>
       <c r="F28" t="n">
-        <v>110.3946</v>
+        <v>126.1646</v>
       </c>
       <c r="G28" t="n">
-        <v>2483879.4</v>
+        <v>1761257.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,31 +1350,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>256000</v>
+        <v>140200</v>
       </c>
       <c r="F29" t="n">
-        <v>113.8306</v>
+        <v>21.1375</v>
       </c>
       <c r="G29" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>2963479.4</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>75700</v>
+        <v>6330</v>
       </c>
       <c r="F30" t="n">
-        <v>275.5075</v>
+        <v>13.226</v>
       </c>
       <c r="G30" t="n">
-        <v>20855919.6</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>131600</v>
+        <v>15750</v>
       </c>
       <c r="F31" t="n">
-        <v>2.4796</v>
+        <v>5.8146</v>
       </c>
       <c r="G31" t="n">
-        <v>326319.6</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>41150</v>
+        <v>22500</v>
       </c>
       <c r="F32" t="n">
-        <v>43.8267</v>
+        <v>110.3946</v>
       </c>
       <c r="G32" t="n">
-        <v>1803469.6</v>
+        <v>2483879.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,29 +1478,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>147300</v>
+        <v>256000</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3821</v>
+        <v>113.8306</v>
       </c>
       <c r="G33" t="n">
-        <v>350879.4</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1510,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>36450</v>
+        <v>75700</v>
       </c>
       <c r="F34" t="n">
-        <v>76.7514</v>
+        <v>275.5075</v>
       </c>
       <c r="G34" t="n">
-        <v>2797588.9</v>
+        <v>20855919.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>119700</v>
+        <v>131600</v>
       </c>
       <c r="F35" t="n">
-        <v>30.2349</v>
+        <v>2.4796</v>
       </c>
       <c r="G35" t="n">
-        <v>3619119.6</v>
+        <v>326319.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>85400</v>
+        <v>41150</v>
       </c>
       <c r="F36" t="n">
-        <v>9.785500000000001</v>
+        <v>43.8267</v>
       </c>
       <c r="G36" t="n">
-        <v>835680.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>183500</v>
+        <v>147300</v>
       </c>
       <c r="F37" t="n">
-        <v>113.6562</v>
+        <v>2.3821</v>
       </c>
       <c r="G37" t="n">
-        <v>20855919.6</v>
+        <v>350879.4</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1638,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,62 +1654,62 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>183500</v>
+        <v>36450</v>
       </c>
       <c r="F38" t="n">
-        <v>12.1963</v>
+        <v>76.7514</v>
       </c>
       <c r="G38" t="n">
-        <v>2238023.8</v>
+        <v>2797588.9</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1849000</v>
+        <v>119700</v>
       </c>
       <c r="F39" t="n">
-        <v>5.5521</v>
+        <v>30.2349</v>
       </c>
       <c r="G39" t="n">
-        <v>10265800.4</v>
+        <v>3619119.6</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,30 +1718,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>260000</v>
+        <v>85400</v>
       </c>
       <c r="F40" t="n">
-        <v>39.4838</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>10265800.4</v>
+        <v>835680.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,62 +1750,62 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>24700</v>
+        <v>183500</v>
       </c>
       <c r="F41" t="n">
-        <v>415.6194</v>
+        <v>113.6562</v>
       </c>
       <c r="G41" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48650</v>
+        <v>183500</v>
       </c>
       <c r="F42" t="n">
-        <v>422.0267</v>
+        <v>12.1963</v>
       </c>
       <c r="G42" t="n">
-        <v>20531600.8</v>
+        <v>2238023.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1812,111 +1814,109 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>87800</v>
+        <v>1849000</v>
       </c>
       <c r="F43" t="n">
-        <v>115.4542</v>
+        <v>5.5521</v>
       </c>
       <c r="G43" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22750</v>
+        <v>260000</v>
       </c>
       <c r="F44" t="n">
-        <v>891.1538</v>
+        <v>39.4838</v>
       </c>
       <c r="G44" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>33150</v>
+        <v>24700</v>
       </c>
       <c r="F45" t="n">
-        <v>569</v>
+        <v>415.6194</v>
       </c>
       <c r="G45" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10265800.4</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>254500</v>
+        <v>48650</v>
       </c>
       <c r="F46" t="n">
-        <v>39.8306</v>
+        <v>422.0267</v>
       </c>
       <c r="G46" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,161 +1928,161 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>79400</v>
+        <v>87800</v>
       </c>
       <c r="F47" t="n">
-        <v>246</v>
+        <v>115.4542</v>
       </c>
       <c r="G47" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14780</v>
+        <v>22750</v>
       </c>
       <c r="F48" t="n">
-        <v>1338</v>
+        <v>891.1538</v>
       </c>
       <c r="G48" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H48" t="n">
-        <v>33.89</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>195800</v>
+        <v>33150</v>
       </c>
       <c r="F49" t="n">
-        <v>101.9921</v>
+        <v>569</v>
       </c>
       <c r="G49" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14600</v>
+        <v>254500</v>
       </c>
       <c r="F50" t="n">
-        <v>1367.8125</v>
+        <v>39.8306</v>
       </c>
       <c r="G50" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>36300</v>
+        <v>79400</v>
       </c>
       <c r="F51" t="n">
-        <v>275.0697</v>
+        <v>246</v>
       </c>
       <c r="G51" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2092,142 +2092,142 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>159300</v>
+        <v>14780</v>
       </c>
       <c r="F52" t="n">
-        <v>62.6807</v>
+        <v>1338</v>
       </c>
       <c r="G52" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H52" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F53" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G53" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F54" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G54" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F55" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G55" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,49 +2236,47 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F56" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G56" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F57" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G57" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H57" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2288,140 +2286,144 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G58" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F59" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G59" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G60" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F61" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G61" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2430,52 +2432,52 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F62" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G62" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F63" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G63" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2494,30 +2496,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F64" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2526,77 +2528,77 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F65" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G65" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F66" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G66" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F67" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G67" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2608,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2622,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F68" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2640,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2654,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F69" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G69" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2672,27 +2674,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F70" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G70" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2704,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2718,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G71" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2736,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2750,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G72" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2768,27 +2770,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F73" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G73" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2800,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2814,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F74" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G74" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2832,27 +2834,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F75" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2864,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2878,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F76" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G76" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2896,27 +2898,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F77" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G77" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2928,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2942,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F78" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G78" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2960,27 +2962,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F79" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G79" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2992,27 +2994,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F80" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G80" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3024,27 +3026,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F81" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G81" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3056,12 +3058,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3070,13 +3072,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F82" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G82" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3088,27 +3090,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F83" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G83" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3120,27 +3122,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F84" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G84" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3152,27 +3154,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F85" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G85" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3184,27 +3186,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F86" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G86" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3216,27 +3218,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F87" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G87" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3248,12 +3250,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3262,13 +3264,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F88" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G88" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3280,27 +3282,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G89" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3312,12 +3314,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3326,13 +3328,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G90" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3344,12 +3346,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3358,13 +3360,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F91" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G91" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3376,12 +3378,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3390,13 +3392,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F92" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G92" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3408,27 +3410,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F93" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3440,12 +3442,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3454,62 +3456,62 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F94" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F95" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G95" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3518,30 +3520,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F96" t="n">
         <v>106</v>
       </c>
       <c r="G96" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3550,196 +3552,190 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F97" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G97" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F98" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G98" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F99" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G99" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F100" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G100" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H100" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F101" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G101" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F102" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G102" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3748,96 +3744,100 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F103" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G103" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H103" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F104" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G104" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H104" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F105" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G105" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3846,30 +3846,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F106" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G106" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,66 +3878,64 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F107" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G107" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H107" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F108" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G108" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H108" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3946,64 +3944,62 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F109" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G109" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F110" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G110" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,175 +4008,181 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F111" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G111" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H111" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F112" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G112" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H112" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F113" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G113" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F114" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G114" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F115" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G115" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F116" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G116" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4192,12 +4194,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4206,13 +4208,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F117" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G117" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4224,12 +4226,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4238,13 +4240,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F118" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G118" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4256,12 +4258,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4270,13 +4272,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F119" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G119" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4288,12 +4290,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4302,13 +4304,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F120" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G120" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4320,27 +4322,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F121" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G121" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4352,27 +4354,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F122" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G122" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4384,31 +4386,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F123" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G123" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F124" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G124" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F125" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G125" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4482,27 +4482,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F126" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G126" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4514,29 +4514,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F127" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G127" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4546,31 +4548,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F128" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G128" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H128" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F129" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G129" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F130" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G130" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4658,13 +4658,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F131" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G131" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4676,142 +4676,142 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F132" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G132" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H132" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F133" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G133" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F134" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G134" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F135" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G135" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F136" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G136" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4838,31 +4838,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F137" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G137" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4872,12 +4870,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4886,16 +4884,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F138" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G138" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H138" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="139">
@@ -4906,12 +4904,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4920,13 +4918,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F139" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G139" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4938,110 +4936,112 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F140" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G140" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F141" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G141" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F142" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G142" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,47 +5050,49 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F143" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G143" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F144" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G144" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5100,12 +5102,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5114,13 +5116,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F145" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G145" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5132,12 +5134,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5146,13 +5148,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F146" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G146" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5164,12 +5166,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5178,13 +5180,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F147" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G147" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5196,12 +5198,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5210,13 +5212,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F148" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G148" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5228,12 +5230,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5242,13 +5244,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F149" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G149" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5260,12 +5262,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5274,13 +5276,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F150" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G150" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5292,12 +5294,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5306,13 +5308,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F151" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G151" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5324,12 +5326,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5338,13 +5340,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F152" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G152" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5356,12 +5358,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5370,13 +5372,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F153" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G153" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5388,12 +5390,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5402,13 +5404,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F154" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G154" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5420,12 +5422,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5434,13 +5436,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F155" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G155" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5452,12 +5454,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5466,13 +5468,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F156" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G156" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5484,12 +5486,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5498,13 +5500,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F157" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G157" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5516,12 +5518,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5530,13 +5532,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F158" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G158" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5548,12 +5550,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5562,13 +5564,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F159" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G159" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5580,12 +5582,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5594,13 +5596,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F160" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G160" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5612,12 +5614,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5626,13 +5628,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F161" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G161" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5644,12 +5646,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5658,13 +5660,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F162" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G162" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5676,12 +5678,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5690,13 +5692,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F163" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G163" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5708,29 +5710,157 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F164" t="n">
+        <v>180</v>
+      </c>
+      <c r="G164" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F165" t="n">
+        <v>449</v>
+      </c>
+      <c r="G165" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F166" t="n">
+        <v>148</v>
+      </c>
+      <c r="G166" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F167" t="n">
+        <v>593</v>
+      </c>
+      <c r="G167" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E164" t="n">
+      <c r="E168" t="n">
         <v>124600</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F168" t="n">
         <v>161</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G168" t="n">
         <v>20060600</v>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,49 +473,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>296500</v>
+        <v>13580</v>
       </c>
       <c r="F2" t="n">
-        <v>71.0389</v>
+        <v>1493.977</v>
       </c>
       <c r="G2" t="n">
-        <v>21063043.1</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -524,62 +526,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12230</v>
+        <v>126300</v>
       </c>
       <c r="F3" t="n">
-        <v>1722.2439</v>
+        <v>165.13</v>
       </c>
       <c r="G3" t="n">
-        <v>21063043.1</v>
+        <v>20855919.6</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>156400</v>
+        <v>48800</v>
       </c>
       <c r="F4" t="n">
-        <v>134.6742</v>
+        <v>6.3754</v>
       </c>
       <c r="G4" t="n">
-        <v>21063043.1</v>
+        <v>311119.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -588,51 +590,49 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>39650</v>
+        <v>29050</v>
       </c>
       <c r="F5" t="n">
-        <v>506.8267</v>
+        <v>686</v>
       </c>
       <c r="G5" t="n">
-        <v>20095679.5</v>
+        <v>19928300</v>
       </c>
       <c r="H5" t="n">
-        <v>-12.59</v>
+        <v>3.01</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13580</v>
+        <v>275000</v>
       </c>
       <c r="F6" t="n">
-        <v>1493.977</v>
+        <v>3.4779</v>
       </c>
       <c r="G6" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>956424.2</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126300</v>
+        <v>326500</v>
       </c>
       <c r="F7" t="n">
-        <v>165.13</v>
+        <v>0.8772</v>
       </c>
       <c r="G7" t="n">
-        <v>20855919.6</v>
+        <v>286419.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48800</v>
+        <v>36800</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3754</v>
+        <v>14.2631</v>
       </c>
       <c r="G8" t="n">
-        <v>311119.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,31 +706,29 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29050</v>
+        <v>536000</v>
       </c>
       <c r="F9" t="n">
-        <v>686</v>
+        <v>2.9103</v>
       </c>
       <c r="G9" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.01</v>
-      </c>
+        <v>1559919.6</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -740,27 +738,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>275000</v>
+        <v>97600</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4779</v>
+        <v>19.6877</v>
       </c>
       <c r="G10" t="n">
-        <v>956424.2</v>
+        <v>1921519.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -772,12 +770,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -786,13 +784,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>326500</v>
+        <v>153900</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8772</v>
+        <v>17.0321</v>
       </c>
       <c r="G11" t="n">
-        <v>286419.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -804,27 +802,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36800</v>
+        <v>1074000</v>
       </c>
       <c r="F12" t="n">
-        <v>14.2631</v>
+        <v>19.4189</v>
       </c>
       <c r="G12" t="n">
-        <v>524880.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,12 +834,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -850,13 +848,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>536000</v>
+        <v>87400</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9103</v>
+        <v>15.0802</v>
       </c>
       <c r="G13" t="n">
-        <v>1559919.6</v>
+        <v>1318012.9</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -868,12 +866,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -882,13 +880,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>97600</v>
+        <v>225000</v>
       </c>
       <c r="F14" t="n">
-        <v>19.6877</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>1921519.6</v>
+        <v>155919.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,12 +898,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,13 +912,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>153900</v>
+        <v>5810</v>
       </c>
       <c r="F15" t="n">
-        <v>17.0321</v>
+        <v>154.6591</v>
       </c>
       <c r="G15" t="n">
-        <v>2621239.2</v>
+        <v>898569.6</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,27 +930,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1074000</v>
+        <v>30200</v>
       </c>
       <c r="F16" t="n">
-        <v>19.4189</v>
+        <v>109.4066</v>
       </c>
       <c r="G16" t="n">
-        <v>20855919.6</v>
+        <v>3304080.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,27 +962,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>87400</v>
+        <v>207000</v>
       </c>
       <c r="F17" t="n">
-        <v>15.0802</v>
+        <v>1.2389</v>
       </c>
       <c r="G17" t="n">
-        <v>1318012.9</v>
+        <v>256454.4</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,27 +994,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>225000</v>
+        <v>28150</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6929999999999999</v>
+        <v>195.4454</v>
       </c>
       <c r="G18" t="n">
-        <v>155919.6</v>
+        <v>5501788.7</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,27 +1026,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5810</v>
+        <v>50500</v>
       </c>
       <c r="F19" t="n">
-        <v>154.6591</v>
+        <v>7.0115</v>
       </c>
       <c r="G19" t="n">
-        <v>898569.6</v>
+        <v>354080.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1060,29 +1058,31 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30200</v>
+        <v>19430</v>
       </c>
       <c r="F20" t="n">
-        <v>109.4066</v>
+        <v>1071</v>
       </c>
       <c r="G20" t="n">
-        <v>3304080.4</v>
-      </c>
-      <c r="H20" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H20" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>207000</v>
+        <v>21200</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2389</v>
+        <v>1475.6547</v>
       </c>
       <c r="G21" t="n">
-        <v>256454.4</v>
+        <v>31283879.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>28150</v>
+        <v>21200</v>
       </c>
       <c r="F22" t="n">
-        <v>195.4454</v>
+        <v>154.5755</v>
       </c>
       <c r="G22" t="n">
-        <v>5501788.7</v>
+        <v>3277001</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50500</v>
+        <v>27700</v>
       </c>
       <c r="F23" t="n">
-        <v>7.0115</v>
+        <v>98.6181</v>
       </c>
       <c r="G23" t="n">
-        <v>354080.4</v>
+        <v>2731720.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,31 +1188,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19430</v>
+        <v>13960</v>
       </c>
       <c r="F24" t="n">
-        <v>1071</v>
+        <v>126.1646</v>
       </c>
       <c r="G24" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.78</v>
-      </c>
+        <v>1761257.6</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1222,27 +1220,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21200</v>
+        <v>140200</v>
       </c>
       <c r="F25" t="n">
-        <v>1475.6547</v>
+        <v>21.1375</v>
       </c>
       <c r="G25" t="n">
-        <v>31283879.4</v>
+        <v>2963479.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,12 +1252,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1266,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>21200</v>
+        <v>6330</v>
       </c>
       <c r="F26" t="n">
-        <v>154.5755</v>
+        <v>13.226</v>
       </c>
       <c r="G26" t="n">
-        <v>3277001</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,13 +1298,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>27700</v>
+        <v>15750</v>
       </c>
       <c r="F27" t="n">
-        <v>98.6181</v>
+        <v>5.8146</v>
       </c>
       <c r="G27" t="n">
-        <v>2731720.6</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1318,12 +1316,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1332,13 +1330,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13960</v>
+        <v>22500</v>
       </c>
       <c r="F28" t="n">
-        <v>126.1646</v>
+        <v>110.3946</v>
       </c>
       <c r="G28" t="n">
-        <v>1761257.6</v>
+        <v>2483879.4</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1350,29 +1348,31 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>140200</v>
+        <v>256000</v>
       </c>
       <c r="F29" t="n">
-        <v>21.1375</v>
+        <v>113.8306</v>
       </c>
       <c r="G29" t="n">
-        <v>2963479.4</v>
-      </c>
-      <c r="H29" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H29" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6330</v>
+        <v>75700</v>
       </c>
       <c r="F30" t="n">
-        <v>13.226</v>
+        <v>275.5075</v>
       </c>
       <c r="G30" t="n">
-        <v>83720.39999999999</v>
+        <v>20855919.6</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15750</v>
+        <v>131600</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8146</v>
+        <v>2.4796</v>
       </c>
       <c r="G31" t="n">
-        <v>91580.39999999999</v>
+        <v>326319.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22500</v>
+        <v>41150</v>
       </c>
       <c r="F32" t="n">
-        <v>110.3946</v>
+        <v>43.8267</v>
       </c>
       <c r="G32" t="n">
-        <v>2483879.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,31 +1478,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>256000</v>
+        <v>147300</v>
       </c>
       <c r="F33" t="n">
-        <v>113.8306</v>
+        <v>2.3821</v>
       </c>
       <c r="G33" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>350879.4</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1512,27 +1510,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>75700</v>
+        <v>36450</v>
       </c>
       <c r="F34" t="n">
-        <v>275.5075</v>
+        <v>76.7514</v>
       </c>
       <c r="G34" t="n">
-        <v>20855919.6</v>
+        <v>2797588.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,12 +1542,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1558,13 +1556,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>131600</v>
+        <v>119700</v>
       </c>
       <c r="F35" t="n">
-        <v>2.4796</v>
+        <v>30.2349</v>
       </c>
       <c r="G35" t="n">
-        <v>326319.6</v>
+        <v>3619119.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,27 +1574,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>41150</v>
+        <v>85400</v>
       </c>
       <c r="F36" t="n">
-        <v>43.8267</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G36" t="n">
-        <v>1803469.6</v>
+        <v>835680.4</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,12 +1606,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1622,13 +1620,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>147300</v>
+        <v>183500</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3821</v>
+        <v>113.6562</v>
       </c>
       <c r="G37" t="n">
-        <v>350879.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1640,12 +1638,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1654,62 +1652,62 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>36450</v>
+        <v>183500</v>
       </c>
       <c r="F38" t="n">
-        <v>76.7514</v>
+        <v>12.1963</v>
       </c>
       <c r="G38" t="n">
-        <v>2797588.9</v>
+        <v>2238023.8</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>119700</v>
+        <v>1849000</v>
       </c>
       <c r="F39" t="n">
-        <v>30.2349</v>
+        <v>5.5521</v>
       </c>
       <c r="G39" t="n">
-        <v>3619119.6</v>
+        <v>10265800.4</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1718,30 +1716,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>85400</v>
+        <v>260000</v>
       </c>
       <c r="F40" t="n">
-        <v>9.785500000000001</v>
+        <v>39.4838</v>
       </c>
       <c r="G40" t="n">
-        <v>835680.4</v>
+        <v>10265800.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,62 +1748,62 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>183500</v>
+        <v>24700</v>
       </c>
       <c r="F41" t="n">
-        <v>113.6562</v>
+        <v>415.6194</v>
       </c>
       <c r="G41" t="n">
-        <v>20855919.6</v>
+        <v>10265800.4</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>183500</v>
+        <v>48650</v>
       </c>
       <c r="F42" t="n">
-        <v>12.1963</v>
+        <v>422.0267</v>
       </c>
       <c r="G42" t="n">
-        <v>2238023.8</v>
+        <v>20531600.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1814,109 +1812,111 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1849000</v>
+        <v>87800</v>
       </c>
       <c r="F43" t="n">
-        <v>5.5521</v>
+        <v>115.4542</v>
       </c>
       <c r="G43" t="n">
-        <v>10265800.4</v>
+        <v>10136875</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>260000</v>
+        <v>22750</v>
       </c>
       <c r="F44" t="n">
-        <v>39.4838</v>
+        <v>891.1538</v>
       </c>
       <c r="G44" t="n">
-        <v>10265800.4</v>
+        <v>20273749.9</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>24700</v>
+        <v>33150</v>
       </c>
       <c r="F45" t="n">
-        <v>415.6194</v>
+        <v>569</v>
       </c>
       <c r="G45" t="n">
-        <v>10265800.4</v>
-      </c>
-      <c r="H45" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H45" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>48650</v>
+        <v>254500</v>
       </c>
       <c r="F46" t="n">
-        <v>422.0267</v>
+        <v>39.8306</v>
       </c>
       <c r="G46" t="n">
-        <v>20531600.8</v>
+        <v>10136875</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,161 +1928,161 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>87800</v>
+        <v>79400</v>
       </c>
       <c r="F47" t="n">
-        <v>115.4542</v>
+        <v>246</v>
       </c>
       <c r="G47" t="n">
-        <v>10136875</v>
-      </c>
-      <c r="H47" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H47" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22750</v>
+        <v>14780</v>
       </c>
       <c r="F48" t="n">
-        <v>891.1538</v>
+        <v>1338</v>
       </c>
       <c r="G48" t="n">
-        <v>20273749.9</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H48" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33150</v>
+        <v>195800</v>
       </c>
       <c r="F49" t="n">
-        <v>569</v>
+        <v>101.9921</v>
       </c>
       <c r="G49" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>19970062</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>254500</v>
+        <v>14600</v>
       </c>
       <c r="F50" t="n">
-        <v>39.8306</v>
+        <v>1367.8125</v>
       </c>
       <c r="G50" t="n">
-        <v>10136875</v>
+        <v>19970062</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>79400</v>
+        <v>36300</v>
       </c>
       <c r="F51" t="n">
-        <v>246</v>
+        <v>275.0697</v>
       </c>
       <c r="G51" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-8</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2092,142 +2092,142 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>14780</v>
+        <v>159300</v>
       </c>
       <c r="F52" t="n">
-        <v>1338</v>
+        <v>62.6807</v>
       </c>
       <c r="G52" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H52" t="n">
-        <v>33.89</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>195800</v>
+        <v>147200</v>
       </c>
       <c r="F53" t="n">
-        <v>101.9921</v>
+        <v>67</v>
       </c>
       <c r="G53" t="n">
-        <v>19970062</v>
+        <v>9862400</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14600</v>
+        <v>14540</v>
       </c>
       <c r="F54" t="n">
-        <v>1367.8125</v>
+        <v>983</v>
       </c>
       <c r="G54" t="n">
-        <v>19970062</v>
+        <v>14292820</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>36300</v>
+        <v>113400</v>
       </c>
       <c r="F55" t="n">
-        <v>275.0697</v>
+        <v>167</v>
       </c>
       <c r="G55" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,47 +2236,49 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>159300</v>
+        <v>24350</v>
       </c>
       <c r="F56" t="n">
-        <v>62.6807</v>
+        <v>407</v>
       </c>
       <c r="G56" t="n">
-        <v>9985031</v>
+        <v>9910450</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>147200</v>
+        <v>44100</v>
       </c>
       <c r="F57" t="n">
-        <v>67</v>
+        <v>488</v>
       </c>
       <c r="G57" t="n">
-        <v>9862400</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H57" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2286,144 +2288,140 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>14540</v>
+        <v>165700</v>
       </c>
       <c r="F58" t="n">
-        <v>983</v>
+        <v>120</v>
       </c>
       <c r="G58" t="n">
-        <v>14292820</v>
+        <v>19884000</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>113400</v>
+        <v>28950</v>
       </c>
       <c r="F59" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G59" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>10219350</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>24350</v>
+        <v>1853000</v>
       </c>
       <c r="F60" t="n">
-        <v>407</v>
+        <v>11</v>
       </c>
       <c r="G60" t="n">
-        <v>9910450</v>
+        <v>20383000</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44100</v>
+        <v>269000</v>
       </c>
       <c r="F61" t="n">
-        <v>488</v>
+        <v>76</v>
       </c>
       <c r="G61" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.26</v>
-      </c>
+        <v>20444000</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2432,52 +2430,52 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>165700</v>
+        <v>106300</v>
       </c>
       <c r="F62" t="n">
-        <v>120</v>
+        <v>194</v>
       </c>
       <c r="G62" t="n">
-        <v>19884000</v>
+        <v>20622200</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>28950</v>
+        <v>123100</v>
       </c>
       <c r="F63" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G63" t="n">
-        <v>10219350</v>
+        <v>20557700</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2496,30 +2494,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1853000</v>
+        <v>1856000</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="G64" t="n">
-        <v>20383000</v>
+        <v>42688000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2528,77 +2526,77 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>269000</v>
+        <v>49000</v>
       </c>
       <c r="F65" t="n">
-        <v>76</v>
+        <v>167</v>
       </c>
       <c r="G65" t="n">
-        <v>20444000</v>
+        <v>8183000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106300</v>
+        <v>13340</v>
       </c>
       <c r="F66" t="n">
-        <v>194</v>
+        <v>236</v>
       </c>
       <c r="G66" t="n">
-        <v>20622200</v>
+        <v>3148240</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123100</v>
+        <v>29800</v>
       </c>
       <c r="F67" t="n">
-        <v>167</v>
+        <v>66</v>
       </c>
       <c r="G67" t="n">
-        <v>20557700</v>
+        <v>1966800</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2610,12 +2608,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2624,13 +2622,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1856000</v>
+        <v>269500</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>118</v>
       </c>
       <c r="G68" t="n">
-        <v>42688000</v>
+        <v>31801000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2642,12 +2640,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,13 +2654,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>49000</v>
+        <v>330000</v>
       </c>
       <c r="F69" t="n">
-        <v>167</v>
+        <v>24</v>
       </c>
       <c r="G69" t="n">
-        <v>8183000</v>
+        <v>7920000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2674,27 +2672,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>13340</v>
+        <v>35550</v>
       </c>
       <c r="F70" t="n">
-        <v>236</v>
+        <v>581</v>
       </c>
       <c r="G70" t="n">
-        <v>3148240</v>
+        <v>20654550</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2706,12 +2704,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2720,13 +2718,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>29800</v>
+        <v>574000</v>
       </c>
       <c r="F71" t="n">
-        <v>66</v>
+        <v>22</v>
       </c>
       <c r="G71" t="n">
-        <v>1966800</v>
+        <v>12628000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2736,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2750,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>269500</v>
+        <v>165900</v>
       </c>
       <c r="F72" t="n">
-        <v>118</v>
+        <v>24</v>
       </c>
       <c r="G72" t="n">
-        <v>31801000</v>
+        <v>3981600</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,27 +2768,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>330000</v>
+        <v>91300</v>
       </c>
       <c r="F73" t="n">
-        <v>24</v>
+        <v>45</v>
       </c>
       <c r="G73" t="n">
-        <v>7920000</v>
+        <v>4108500</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,12 +2800,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2816,13 +2814,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35550</v>
+        <v>224500</v>
       </c>
       <c r="F74" t="n">
-        <v>581</v>
+        <v>92</v>
       </c>
       <c r="G74" t="n">
-        <v>20654550</v>
+        <v>20654000</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,27 +2832,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>574000</v>
+        <v>6010</v>
       </c>
       <c r="F75" t="n">
-        <v>22</v>
+        <v>3435</v>
       </c>
       <c r="G75" t="n">
-        <v>12628000</v>
+        <v>20644350</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,12 +2864,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2880,13 +2878,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>165900</v>
+        <v>25800</v>
       </c>
       <c r="F76" t="n">
-        <v>24</v>
+        <v>351</v>
       </c>
       <c r="G76" t="n">
-        <v>3981600</v>
+        <v>9055800</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2898,27 +2896,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>91300</v>
+        <v>49150</v>
       </c>
       <c r="F77" t="n">
-        <v>45</v>
+        <v>420</v>
       </c>
       <c r="G77" t="n">
-        <v>4108500</v>
+        <v>20643000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2930,12 +2928,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2944,13 +2942,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224500</v>
+        <v>19280</v>
       </c>
       <c r="F78" t="n">
-        <v>92</v>
+        <v>1071</v>
       </c>
       <c r="G78" t="n">
-        <v>20654000</v>
+        <v>20648880</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2962,27 +2960,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6010</v>
+        <v>19740</v>
       </c>
       <c r="F79" t="n">
-        <v>3435</v>
+        <v>523</v>
       </c>
       <c r="G79" t="n">
-        <v>20644350</v>
+        <v>10324020</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2994,27 +2992,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25800</v>
+        <v>25150</v>
       </c>
       <c r="F80" t="n">
-        <v>351</v>
+        <v>821</v>
       </c>
       <c r="G80" t="n">
-        <v>9055800</v>
+        <v>20648150</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3026,27 +3024,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>49150</v>
+        <v>153500</v>
       </c>
       <c r="F81" t="n">
-        <v>420</v>
+        <v>24</v>
       </c>
       <c r="G81" t="n">
-        <v>20643000</v>
+        <v>3684000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3058,12 +3056,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3072,13 +3070,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>19280</v>
+        <v>6240</v>
       </c>
       <c r="F82" t="n">
-        <v>1071</v>
+        <v>3308</v>
       </c>
       <c r="G82" t="n">
-        <v>20648880</v>
+        <v>20641920</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3090,27 +3088,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>19740</v>
+        <v>15520</v>
       </c>
       <c r="F83" t="n">
-        <v>523</v>
+        <v>1330</v>
       </c>
       <c r="G83" t="n">
-        <v>10324020</v>
+        <v>20641600</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,27 +3120,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>25150</v>
+        <v>24200</v>
       </c>
       <c r="F84" t="n">
-        <v>821</v>
+        <v>210</v>
       </c>
       <c r="G84" t="n">
-        <v>20648150</v>
+        <v>5082000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,27 +3152,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>153500</v>
+        <v>36300</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>569</v>
       </c>
       <c r="G85" t="n">
-        <v>3684000</v>
+        <v>20654700</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,27 +3184,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6240</v>
+        <v>279500</v>
       </c>
       <c r="F86" t="n">
-        <v>3308</v>
+        <v>43</v>
       </c>
       <c r="G86" t="n">
-        <v>20641920</v>
+        <v>12018500</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,27 +3216,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15520</v>
+        <v>132600</v>
       </c>
       <c r="F87" t="n">
-        <v>1330</v>
+        <v>90</v>
       </c>
       <c r="G87" t="n">
-        <v>20641600</v>
+        <v>11934000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3250,12 +3248,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3264,13 +3262,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24200</v>
+        <v>44600</v>
       </c>
       <c r="F88" t="n">
-        <v>210</v>
+        <v>139</v>
       </c>
       <c r="G88" t="n">
-        <v>5082000</v>
+        <v>6199400</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3282,27 +3280,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>36300</v>
+        <v>147100</v>
       </c>
       <c r="F89" t="n">
-        <v>569</v>
+        <v>6</v>
       </c>
       <c r="G89" t="n">
-        <v>20654700</v>
+        <v>882600</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3314,12 +3312,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3328,13 +3326,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>279500</v>
+        <v>33500</v>
       </c>
       <c r="F90" t="n">
-        <v>43</v>
+        <v>8</v>
       </c>
       <c r="G90" t="n">
-        <v>12018500</v>
+        <v>268000</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3346,12 +3344,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3360,13 +3358,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>132600</v>
+        <v>143100</v>
       </c>
       <c r="F91" t="n">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G91" t="n">
-        <v>11934000</v>
+        <v>13594500</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3378,12 +3376,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3392,13 +3390,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>44600</v>
+        <v>83800</v>
       </c>
       <c r="F92" t="n">
-        <v>139</v>
+        <v>106</v>
       </c>
       <c r="G92" t="n">
-        <v>6199400</v>
+        <v>8882800</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3410,27 +3408,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>147100</v>
+        <v>42300</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>488</v>
       </c>
       <c r="G93" t="n">
-        <v>882600</v>
+        <v>20642400</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3442,12 +3440,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3456,62 +3454,62 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>33500</v>
+        <v>81200</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>135</v>
       </c>
       <c r="G94" t="n">
-        <v>268000</v>
+        <v>10962000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>143100</v>
+        <v>78600</v>
       </c>
       <c r="F95" t="n">
-        <v>95</v>
+        <v>389</v>
       </c>
       <c r="G95" t="n">
-        <v>13594500</v>
+        <v>30575400</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3520,30 +3518,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>83800</v>
+        <v>92500</v>
       </c>
       <c r="F96" t="n">
         <v>106</v>
       </c>
       <c r="G96" t="n">
-        <v>8882800</v>
+        <v>9805000</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3552,190 +3550,196 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>42300</v>
+        <v>25550</v>
       </c>
       <c r="F97" t="n">
-        <v>488</v>
+        <v>1151</v>
       </c>
       <c r="G97" t="n">
-        <v>20642400</v>
+        <v>29408050</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>81200</v>
+        <v>21800</v>
       </c>
       <c r="F98" t="n">
-        <v>135</v>
+        <v>832</v>
       </c>
       <c r="G98" t="n">
-        <v>10962000</v>
+        <v>18137600</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>78600</v>
+        <v>32250</v>
       </c>
       <c r="F99" t="n">
-        <v>389</v>
+        <v>878</v>
       </c>
       <c r="G99" t="n">
-        <v>30575400</v>
-      </c>
-      <c r="H99" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H99" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>92500</v>
+        <v>105800</v>
       </c>
       <c r="F100" t="n">
-        <v>106</v>
+        <v>332</v>
       </c>
       <c r="G100" t="n">
-        <v>9805000</v>
-      </c>
-      <c r="H100" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H100" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>25550</v>
+        <v>33750</v>
       </c>
       <c r="F101" t="n">
-        <v>1151</v>
+        <v>791</v>
       </c>
       <c r="G101" t="n">
-        <v>29408050</v>
-      </c>
-      <c r="H101" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>21800</v>
+        <v>86300</v>
       </c>
       <c r="F102" t="n">
-        <v>832</v>
+        <v>352</v>
       </c>
       <c r="G102" t="n">
-        <v>18137600</v>
+        <v>30377600</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3744,100 +3748,96 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>32250</v>
+        <v>21000</v>
       </c>
       <c r="F103" t="n">
-        <v>878</v>
+        <v>1517</v>
       </c>
       <c r="G103" t="n">
-        <v>28315500</v>
+        <v>31857000</v>
       </c>
       <c r="H103" t="n">
-        <v>-5.33</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>105800</v>
+        <v>21900</v>
       </c>
       <c r="F104" t="n">
-        <v>332</v>
+        <v>906</v>
       </c>
       <c r="G104" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H104" t="n">
-        <v>17.17</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>33750</v>
+        <v>135300</v>
       </c>
       <c r="F105" t="n">
-        <v>791</v>
+        <v>226</v>
       </c>
       <c r="G105" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.29</v>
-      </c>
+        <v>30577800</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3846,30 +3846,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>86300</v>
+        <v>22250</v>
       </c>
       <c r="F106" t="n">
-        <v>352</v>
+        <v>1399</v>
       </c>
       <c r="G106" t="n">
-        <v>30377600</v>
+        <v>31127750</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,64 +3878,66 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>21000</v>
+        <v>33500</v>
       </c>
       <c r="F107" t="n">
-        <v>1517</v>
+        <v>848</v>
       </c>
       <c r="G107" t="n">
-        <v>31857000</v>
+        <v>28408000</v>
       </c>
       <c r="H107" t="n">
-        <v>3.96</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>21900</v>
+        <v>300000</v>
       </c>
       <c r="F108" t="n">
-        <v>906</v>
+        <v>104</v>
       </c>
       <c r="G108" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H108" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3944,62 +3946,64 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>135300</v>
+        <v>28200</v>
       </c>
       <c r="F109" t="n">
-        <v>226</v>
+        <v>1105</v>
       </c>
       <c r="G109" t="n">
-        <v>30577800</v>
+        <v>31161000</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>22250</v>
+        <v>398000</v>
       </c>
       <c r="F110" t="n">
-        <v>1399</v>
+        <v>72</v>
       </c>
       <c r="G110" t="n">
-        <v>31127750</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H110" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4008,181 +4012,175 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>33500</v>
+        <v>5620</v>
       </c>
       <c r="F111" t="n">
-        <v>848</v>
+        <v>4707</v>
       </c>
       <c r="G111" t="n">
-        <v>28408000</v>
+        <v>26453340</v>
       </c>
       <c r="H111" t="n">
-        <v>-9.07</v>
+        <v>-8.220000000000001</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>300000</v>
+        <v>126900</v>
       </c>
       <c r="F112" t="n">
-        <v>104</v>
+        <v>246</v>
       </c>
       <c r="G112" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H112" t="n">
-        <v>20.95</v>
-      </c>
+        <v>31217400</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>28200</v>
+        <v>1671000</v>
       </c>
       <c r="F113" t="n">
-        <v>1105</v>
+        <v>44</v>
       </c>
       <c r="G113" t="n">
-        <v>31161000</v>
+        <v>73524000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>398000</v>
+        <v>50600</v>
       </c>
       <c r="F114" t="n">
-        <v>72</v>
+        <v>186</v>
       </c>
       <c r="G114" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>9411600</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5620</v>
+        <v>11720</v>
       </c>
       <c r="F115" t="n">
-        <v>4707</v>
+        <v>665</v>
       </c>
       <c r="G115" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>7793800</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>126900</v>
+        <v>414000</v>
       </c>
       <c r="F116" t="n">
-        <v>246</v>
+        <v>26</v>
       </c>
       <c r="G116" t="n">
-        <v>31217400</v>
+        <v>10764000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4194,12 +4192,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4208,13 +4206,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1671000</v>
+        <v>257000</v>
       </c>
       <c r="F117" t="n">
-        <v>44</v>
+        <v>239</v>
       </c>
       <c r="G117" t="n">
-        <v>73524000</v>
+        <v>61423000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4226,12 +4224,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4240,13 +4238,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>50600</v>
+        <v>33900</v>
       </c>
       <c r="F118" t="n">
-        <v>186</v>
+        <v>292</v>
       </c>
       <c r="G118" t="n">
-        <v>9411600</v>
+        <v>9898800</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4258,12 +4256,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4272,13 +4270,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>11720</v>
+        <v>515000</v>
       </c>
       <c r="F119" t="n">
-        <v>665</v>
+        <v>17</v>
       </c>
       <c r="G119" t="n">
-        <v>7793800</v>
+        <v>8755000</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4290,12 +4288,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4304,13 +4302,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>414000</v>
+        <v>141200</v>
       </c>
       <c r="F120" t="n">
-        <v>26</v>
+        <v>81</v>
       </c>
       <c r="G120" t="n">
-        <v>10764000</v>
+        <v>11437200</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4322,27 +4320,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>257000</v>
+        <v>6320</v>
       </c>
       <c r="F121" t="n">
-        <v>239</v>
+        <v>1396</v>
       </c>
       <c r="G121" t="n">
-        <v>61423000</v>
+        <v>8822720</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4354,27 +4352,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>33900</v>
+        <v>90300</v>
       </c>
       <c r="F122" t="n">
-        <v>292</v>
+        <v>332</v>
       </c>
       <c r="G122" t="n">
-        <v>9898800</v>
+        <v>29979600</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4386,29 +4384,31 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>515000</v>
+        <v>163100</v>
       </c>
       <c r="F123" t="n">
-        <v>17</v>
+        <v>119</v>
       </c>
       <c r="G123" t="n">
-        <v>8755000</v>
-      </c>
-      <c r="H123" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H123" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>141200</v>
+        <v>37900</v>
       </c>
       <c r="F124" t="n">
-        <v>81</v>
+        <v>163</v>
       </c>
       <c r="G124" t="n">
-        <v>11437200</v>
+        <v>6177700</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6320</v>
+        <v>19990</v>
       </c>
       <c r="F125" t="n">
-        <v>1396</v>
+        <v>615</v>
       </c>
       <c r="G125" t="n">
-        <v>8822720</v>
+        <v>12293850</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4482,27 +4482,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>90300</v>
+        <v>35100</v>
       </c>
       <c r="F126" t="n">
-        <v>332</v>
+        <v>320</v>
       </c>
       <c r="G126" t="n">
-        <v>29979600</v>
+        <v>11232000</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4514,31 +4514,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>163100</v>
+        <v>286000</v>
       </c>
       <c r="F127" t="n">
-        <v>119</v>
+        <v>20</v>
       </c>
       <c r="G127" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4548,29 +4546,31 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>37900</v>
+        <v>416000</v>
       </c>
       <c r="F128" t="n">
-        <v>163</v>
+        <v>51</v>
       </c>
       <c r="G128" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H128" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H128" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>19990</v>
+        <v>49450</v>
       </c>
       <c r="F129" t="n">
-        <v>615</v>
+        <v>153</v>
       </c>
       <c r="G129" t="n">
-        <v>12293850</v>
+        <v>7565850</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>35100</v>
+        <v>138000</v>
       </c>
       <c r="F130" t="n">
-        <v>320</v>
+        <v>68</v>
       </c>
       <c r="G130" t="n">
-        <v>11232000</v>
+        <v>9384000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4658,13 +4658,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>286000</v>
+        <v>31950</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>339</v>
       </c>
       <c r="G131" t="n">
-        <v>5720000</v>
+        <v>10831050</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4676,142 +4676,142 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>416000</v>
+        <v>124800</v>
       </c>
       <c r="F132" t="n">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="G132" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H132" t="n">
-        <v>5.85</v>
-      </c>
+        <v>9734400</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>49450</v>
+        <v>10800</v>
       </c>
       <c r="F133" t="n">
-        <v>153</v>
+        <v>1892</v>
       </c>
       <c r="G133" t="n">
-        <v>7565850</v>
+        <v>20433600</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>138000</v>
+        <v>11880</v>
       </c>
       <c r="F134" t="n">
-        <v>68</v>
+        <v>1474</v>
       </c>
       <c r="G134" t="n">
-        <v>9384000</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>31950</v>
+        <v>20200</v>
       </c>
       <c r="F135" t="n">
-        <v>339</v>
+        <v>1517</v>
       </c>
       <c r="G135" t="n">
-        <v>10831050</v>
+        <v>30643400</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>124800</v>
+        <v>102200</v>
       </c>
       <c r="F136" t="n">
-        <v>78</v>
+        <v>200</v>
       </c>
       <c r="G136" t="n">
-        <v>9734400</v>
+        <v>20440000</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4838,29 +4838,31 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10800</v>
+        <v>23450</v>
       </c>
       <c r="F137" t="n">
-        <v>1892</v>
+        <v>762</v>
       </c>
       <c r="G137" t="n">
-        <v>20433600</v>
-      </c>
-      <c r="H137" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H137" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4870,12 +4872,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4884,16 +4886,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>11880</v>
+        <v>22050</v>
       </c>
       <c r="F138" t="n">
-        <v>1474</v>
+        <v>875</v>
       </c>
       <c r="G138" t="n">
-        <v>17511120</v>
+        <v>19293750</v>
       </c>
       <c r="H138" t="n">
-        <v>-12.45</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="139">
@@ -4904,12 +4906,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4918,13 +4920,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>20200</v>
+        <v>32550</v>
       </c>
       <c r="F139" t="n">
-        <v>1517</v>
+        <v>628</v>
       </c>
       <c r="G139" t="n">
-        <v>30643400</v>
+        <v>20441400</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4936,112 +4938,110 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>102200</v>
+        <v>99700</v>
       </c>
       <c r="F140" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="G140" t="n">
-        <v>20440000</v>
-      </c>
-      <c r="H140" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H140" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>23450</v>
+        <v>1662000</v>
       </c>
       <c r="F141" t="n">
-        <v>762</v>
+        <v>150</v>
       </c>
       <c r="G141" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>249300000</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>22050</v>
+        <v>49700</v>
       </c>
       <c r="F142" t="n">
-        <v>875</v>
+        <v>402</v>
       </c>
       <c r="G142" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>19979400</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,49 +5050,47 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>32550</v>
+        <v>435000</v>
       </c>
       <c r="F143" t="n">
-        <v>628</v>
+        <v>46</v>
       </c>
       <c r="G143" t="n">
-        <v>20441400</v>
+        <v>20010000</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>99700</v>
+        <v>268500</v>
       </c>
       <c r="F144" t="n">
-        <v>180</v>
+        <v>931</v>
       </c>
       <c r="G144" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>249973500</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5102,12 +5100,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5116,13 +5114,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1662000</v>
+        <v>13570</v>
       </c>
       <c r="F145" t="n">
-        <v>150</v>
+        <v>1474</v>
       </c>
       <c r="G145" t="n">
-        <v>249300000</v>
+        <v>20002180</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5134,12 +5132,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5148,13 +5146,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>49700</v>
+        <v>343500</v>
       </c>
       <c r="F146" t="n">
-        <v>402</v>
+        <v>87</v>
       </c>
       <c r="G146" t="n">
-        <v>19979400</v>
+        <v>29884500</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5166,12 +5164,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5180,13 +5178,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>435000</v>
+        <v>34150</v>
       </c>
       <c r="F147" t="n">
-        <v>46</v>
+        <v>586</v>
       </c>
       <c r="G147" t="n">
-        <v>20010000</v>
+        <v>20011900</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5198,12 +5196,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5212,13 +5210,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>268500</v>
+        <v>488000</v>
       </c>
       <c r="F148" t="n">
-        <v>931</v>
+        <v>41</v>
       </c>
       <c r="G148" t="n">
-        <v>249973500</v>
+        <v>20008000</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5230,12 +5228,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5244,13 +5242,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>13570</v>
+        <v>153600</v>
       </c>
       <c r="F149" t="n">
-        <v>1474</v>
+        <v>130</v>
       </c>
       <c r="G149" t="n">
-        <v>20002180</v>
+        <v>19968000</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5262,12 +5260,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5276,13 +5274,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>343500</v>
+        <v>99800</v>
       </c>
       <c r="F150" t="n">
-        <v>87</v>
+        <v>200</v>
       </c>
       <c r="G150" t="n">
-        <v>29884500</v>
+        <v>19960000</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5294,12 +5292,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5308,13 +5306,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>34150</v>
+        <v>6040</v>
       </c>
       <c r="F151" t="n">
-        <v>586</v>
+        <v>3311</v>
       </c>
       <c r="G151" t="n">
-        <v>20011900</v>
+        <v>19998440</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5326,12 +5324,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5340,13 +5338,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>488000</v>
+        <v>26250</v>
       </c>
       <c r="F152" t="n">
-        <v>41</v>
+        <v>762</v>
       </c>
       <c r="G152" t="n">
-        <v>20008000</v>
+        <v>20002500</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5358,12 +5356,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5372,13 +5370,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>153600</v>
+        <v>22850</v>
       </c>
       <c r="F153" t="n">
-        <v>130</v>
+        <v>875</v>
       </c>
       <c r="G153" t="n">
-        <v>19968000</v>
+        <v>19993750</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5390,12 +5388,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5404,13 +5402,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>99800</v>
+        <v>168500</v>
       </c>
       <c r="F154" t="n">
-        <v>200</v>
+        <v>119</v>
       </c>
       <c r="G154" t="n">
-        <v>19960000</v>
+        <v>20051500</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5422,12 +5420,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5436,13 +5434,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6040</v>
+        <v>22850</v>
       </c>
       <c r="F155" t="n">
-        <v>3311</v>
+        <v>875</v>
       </c>
       <c r="G155" t="n">
-        <v>19998440</v>
+        <v>19993750</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5454,12 +5452,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5468,13 +5466,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>26250</v>
+        <v>37900</v>
       </c>
       <c r="F156" t="n">
-        <v>762</v>
+        <v>528</v>
       </c>
       <c r="G156" t="n">
-        <v>20002500</v>
+        <v>20011200</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5486,12 +5484,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5500,13 +5498,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>22850</v>
+        <v>239000</v>
       </c>
       <c r="F157" t="n">
-        <v>875</v>
+        <v>84</v>
       </c>
       <c r="G157" t="n">
-        <v>19993750</v>
+        <v>20076000</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5518,12 +5516,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5532,13 +5530,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>168500</v>
+        <v>298000</v>
       </c>
       <c r="F158" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G158" t="n">
-        <v>20051500</v>
+        <v>34866000</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5550,12 +5548,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5564,13 +5562,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>22850</v>
+        <v>393000</v>
       </c>
       <c r="F159" t="n">
-        <v>875</v>
+        <v>51</v>
       </c>
       <c r="G159" t="n">
-        <v>19993750</v>
+        <v>20043000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5582,12 +5580,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5596,13 +5594,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>37900</v>
+        <v>110900</v>
       </c>
       <c r="F160" t="n">
-        <v>528</v>
+        <v>180</v>
       </c>
       <c r="G160" t="n">
-        <v>20011200</v>
+        <v>19962000</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5614,12 +5612,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5628,13 +5626,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>239000</v>
+        <v>44500</v>
       </c>
       <c r="F161" t="n">
-        <v>84</v>
+        <v>449</v>
       </c>
       <c r="G161" t="n">
-        <v>20076000</v>
+        <v>19980500</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5646,12 +5644,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5660,13 +5658,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>298000</v>
+        <v>135000</v>
       </c>
       <c r="F162" t="n">
-        <v>117</v>
+        <v>148</v>
       </c>
       <c r="G162" t="n">
-        <v>34866000</v>
+        <v>19980000</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5678,12 +5676,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5692,13 +5690,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>393000</v>
+        <v>33750</v>
       </c>
       <c r="F163" t="n">
-        <v>51</v>
+        <v>593</v>
       </c>
       <c r="G163" t="n">
-        <v>20043000</v>
+        <v>20013750</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5710,12 +5708,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5724,143 +5722,15 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>110900</v>
+        <v>124600</v>
       </c>
       <c r="F164" t="n">
-        <v>180</v>
+        <v>161</v>
       </c>
       <c r="G164" t="n">
-        <v>19962000</v>
+        <v>20060600</v>
       </c>
       <c r="H164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>실리콘투</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>257720</t>
-        </is>
-      </c>
-      <c r="D165" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E165" t="n">
-        <v>44500</v>
-      </c>
-      <c r="F165" t="n">
-        <v>449</v>
-      </c>
-      <c r="G165" t="n">
-        <v>19980500</v>
-      </c>
-      <c r="H165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>세아제강</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>306200</t>
-        </is>
-      </c>
-      <c r="D166" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E166" t="n">
-        <v>135000</v>
-      </c>
-      <c r="F166" t="n">
-        <v>148</v>
-      </c>
-      <c r="G166" t="n">
-        <v>19980000</v>
-      </c>
-      <c r="H166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>우리금융지주</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>316140</t>
-        </is>
-      </c>
-      <c r="D167" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E167" t="n">
-        <v>33750</v>
-      </c>
-      <c r="F167" t="n">
-        <v>593</v>
-      </c>
-      <c r="G167" t="n">
-        <v>20013750</v>
-      </c>
-      <c r="H167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>2026-08-18</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>HD현대에너지솔루션</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>322000</t>
-        </is>
-      </c>
-      <c r="D168" t="inlineStr">
-        <is>
-          <t>편입</t>
-        </is>
-      </c>
-      <c r="E168" t="n">
-        <v>124600</v>
-      </c>
-      <c r="F168" t="n">
-        <v>161</v>
-      </c>
-      <c r="G168" t="n">
-        <v>20060600</v>
-      </c>
-      <c r="H168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H164"/>
+  <dimension ref="A1:H168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,51 +473,49 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13580</v>
+        <v>295000</v>
       </c>
       <c r="F2" t="n">
-        <v>1493.977</v>
+        <v>71.24209999999999</v>
       </c>
       <c r="G2" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H2" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>21016430.2</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -526,62 +524,62 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>126300</v>
+        <v>12870</v>
       </c>
       <c r="F3" t="n">
-        <v>165.13</v>
+        <v>1632.9783</v>
       </c>
       <c r="G3" t="n">
-        <v>20855919.6</v>
+        <v>21016430.2</v>
       </c>
       <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>48800</v>
+        <v>161900</v>
       </c>
       <c r="F4" t="n">
-        <v>6.3754</v>
+        <v>129.8112</v>
       </c>
       <c r="G4" t="n">
-        <v>311119.6</v>
+        <v>21016430.2</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -590,49 +588,51 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>29050</v>
+        <v>38900</v>
       </c>
       <c r="F5" t="n">
-        <v>686</v>
+        <v>506.8267</v>
       </c>
       <c r="G5" t="n">
-        <v>19928300</v>
+        <v>19715559.5</v>
       </c>
       <c r="H5" t="n">
-        <v>3.01</v>
+        <v>-14.24</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>275000</v>
+        <v>13580</v>
       </c>
       <c r="F6" t="n">
-        <v>3.4779</v>
+        <v>1493.977</v>
       </c>
       <c r="G6" t="n">
-        <v>956424.2</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -642,27 +642,27 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>326500</v>
+        <v>126300</v>
       </c>
       <c r="F7" t="n">
-        <v>0.8772</v>
+        <v>165.13</v>
       </c>
       <c r="G7" t="n">
-        <v>286419.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,27 +674,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>36800</v>
+        <v>48800</v>
       </c>
       <c r="F8" t="n">
-        <v>14.2631</v>
+        <v>6.3754</v>
       </c>
       <c r="G8" t="n">
-        <v>524880.4</v>
+        <v>311119.6</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -706,29 +706,31 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>536000</v>
+        <v>29050</v>
       </c>
       <c r="F9" t="n">
-        <v>2.9103</v>
+        <v>686</v>
       </c>
       <c r="G9" t="n">
-        <v>1559919.6</v>
-      </c>
-      <c r="H9" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H9" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -738,27 +740,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>97600</v>
+        <v>275000</v>
       </c>
       <c r="F10" t="n">
-        <v>19.6877</v>
+        <v>3.4779</v>
       </c>
       <c r="G10" t="n">
-        <v>1921519.6</v>
+        <v>956424.2</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -770,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -784,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>153900</v>
+        <v>326500</v>
       </c>
       <c r="F11" t="n">
-        <v>17.0321</v>
+        <v>0.8772</v>
       </c>
       <c r="G11" t="n">
-        <v>2621239.2</v>
+        <v>286419.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -802,27 +804,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1074000</v>
+        <v>36800</v>
       </c>
       <c r="F12" t="n">
-        <v>19.4189</v>
+        <v>14.2631</v>
       </c>
       <c r="G12" t="n">
-        <v>20855919.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -834,12 +836,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -848,13 +850,13 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>87400</v>
+        <v>536000</v>
       </c>
       <c r="F13" t="n">
-        <v>15.0802</v>
+        <v>2.9103</v>
       </c>
       <c r="G13" t="n">
-        <v>1318012.9</v>
+        <v>1559919.6</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -866,12 +868,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -880,13 +882,13 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>225000</v>
+        <v>97600</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6929999999999999</v>
+        <v>19.6877</v>
       </c>
       <c r="G14" t="n">
-        <v>155919.6</v>
+        <v>1921519.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -898,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -912,13 +914,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5810</v>
+        <v>153900</v>
       </c>
       <c r="F15" t="n">
-        <v>154.6591</v>
+        <v>17.0321</v>
       </c>
       <c r="G15" t="n">
-        <v>898569.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -930,27 +932,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>30200</v>
+        <v>1074000</v>
       </c>
       <c r="F16" t="n">
-        <v>109.4066</v>
+        <v>19.4189</v>
       </c>
       <c r="G16" t="n">
-        <v>3304080.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -962,27 +964,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>207000</v>
+        <v>87400</v>
       </c>
       <c r="F17" t="n">
-        <v>1.2389</v>
+        <v>15.0802</v>
       </c>
       <c r="G17" t="n">
-        <v>256454.4</v>
+        <v>1318012.9</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -994,27 +996,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>28150</v>
+        <v>225000</v>
       </c>
       <c r="F18" t="n">
-        <v>195.4454</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G18" t="n">
-        <v>5501788.7</v>
+        <v>155919.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1026,27 +1028,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>50500</v>
+        <v>5810</v>
       </c>
       <c r="F19" t="n">
-        <v>7.0115</v>
+        <v>154.6591</v>
       </c>
       <c r="G19" t="n">
-        <v>354080.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1058,31 +1060,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>19430</v>
+        <v>30200</v>
       </c>
       <c r="F20" t="n">
-        <v>1071</v>
+        <v>109.4066</v>
       </c>
       <c r="G20" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.78</v>
-      </c>
+        <v>3304080.4</v>
+      </c>
+      <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1092,12 +1092,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1106,13 +1106,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>21200</v>
+        <v>207000</v>
       </c>
       <c r="F21" t="n">
-        <v>1475.6547</v>
+        <v>1.2389</v>
       </c>
       <c r="G21" t="n">
-        <v>31283879.4</v>
+        <v>256454.4</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1138,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>21200</v>
+        <v>28150</v>
       </c>
       <c r="F22" t="n">
-        <v>154.5755</v>
+        <v>195.4454</v>
       </c>
       <c r="G22" t="n">
-        <v>3277001</v>
+        <v>5501788.7</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1170,13 +1170,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>27700</v>
+        <v>50500</v>
       </c>
       <c r="F23" t="n">
-        <v>98.6181</v>
+        <v>7.0115</v>
       </c>
       <c r="G23" t="n">
-        <v>2731720.6</v>
+        <v>354080.4</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,29 +1188,31 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>13960</v>
+        <v>19430</v>
       </c>
       <c r="F24" t="n">
-        <v>126.1646</v>
+        <v>1071</v>
       </c>
       <c r="G24" t="n">
-        <v>1761257.6</v>
-      </c>
-      <c r="H24" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1220,27 +1222,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>140200</v>
+        <v>21200</v>
       </c>
       <c r="F25" t="n">
-        <v>21.1375</v>
+        <v>1475.6547</v>
       </c>
       <c r="G25" t="n">
-        <v>2963479.4</v>
+        <v>31283879.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1252,12 +1254,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1266,13 +1268,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6330</v>
+        <v>21200</v>
       </c>
       <c r="F26" t="n">
-        <v>13.226</v>
+        <v>154.5755</v>
       </c>
       <c r="G26" t="n">
-        <v>83720.39999999999</v>
+        <v>3277001</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1284,12 +1286,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1298,13 +1300,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>15750</v>
+        <v>27700</v>
       </c>
       <c r="F27" t="n">
-        <v>5.8146</v>
+        <v>98.6181</v>
       </c>
       <c r="G27" t="n">
-        <v>91580.39999999999</v>
+        <v>2731720.6</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1316,12 +1318,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1330,13 +1332,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>22500</v>
+        <v>13960</v>
       </c>
       <c r="F28" t="n">
-        <v>110.3946</v>
+        <v>126.1646</v>
       </c>
       <c r="G28" t="n">
-        <v>2483879.4</v>
+        <v>1761257.6</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1348,31 +1350,29 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>256000</v>
+        <v>140200</v>
       </c>
       <c r="F29" t="n">
-        <v>113.8306</v>
+        <v>21.1375</v>
       </c>
       <c r="G29" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H29" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>2963479.4</v>
+      </c>
+      <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1382,27 +1382,27 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>75700</v>
+        <v>6330</v>
       </c>
       <c r="F30" t="n">
-        <v>275.5075</v>
+        <v>13.226</v>
       </c>
       <c r="G30" t="n">
-        <v>20855919.6</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,27 +1414,27 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>131600</v>
+        <v>15750</v>
       </c>
       <c r="F31" t="n">
-        <v>2.4796</v>
+        <v>5.8146</v>
       </c>
       <c r="G31" t="n">
-        <v>326319.6</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1446,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1460,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>41150</v>
+        <v>22500</v>
       </c>
       <c r="F32" t="n">
-        <v>43.8267</v>
+        <v>110.3946</v>
       </c>
       <c r="G32" t="n">
-        <v>1803469.6</v>
+        <v>2483879.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,29 +1478,31 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>147300</v>
+        <v>256000</v>
       </c>
       <c r="F33" t="n">
-        <v>2.3821</v>
+        <v>113.8306</v>
       </c>
       <c r="G33" t="n">
-        <v>350879.4</v>
-      </c>
-      <c r="H33" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H33" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1510,27 +1512,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>36450</v>
+        <v>75700</v>
       </c>
       <c r="F34" t="n">
-        <v>76.7514</v>
+        <v>275.5075</v>
       </c>
       <c r="G34" t="n">
-        <v>2797588.9</v>
+        <v>20855919.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1542,12 +1544,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1556,13 +1558,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>119700</v>
+        <v>131600</v>
       </c>
       <c r="F35" t="n">
-        <v>30.2349</v>
+        <v>2.4796</v>
       </c>
       <c r="G35" t="n">
-        <v>3619119.6</v>
+        <v>326319.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1574,27 +1576,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>85400</v>
+        <v>41150</v>
       </c>
       <c r="F36" t="n">
-        <v>9.785500000000001</v>
+        <v>43.8267</v>
       </c>
       <c r="G36" t="n">
-        <v>835680.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1606,12 +1608,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1620,13 +1622,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>183500</v>
+        <v>147300</v>
       </c>
       <c r="F37" t="n">
-        <v>113.6562</v>
+        <v>2.3821</v>
       </c>
       <c r="G37" t="n">
-        <v>20855919.6</v>
+        <v>350879.4</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1638,12 +1640,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1652,62 +1654,62 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>183500</v>
+        <v>36450</v>
       </c>
       <c r="F38" t="n">
-        <v>12.1963</v>
+        <v>76.7514</v>
       </c>
       <c r="G38" t="n">
-        <v>2238023.8</v>
+        <v>2797588.9</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1849000</v>
+        <v>119700</v>
       </c>
       <c r="F39" t="n">
-        <v>5.5521</v>
+        <v>30.2349</v>
       </c>
       <c r="G39" t="n">
-        <v>10265800.4</v>
+        <v>3619119.6</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1716,30 +1718,30 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>260000</v>
+        <v>85400</v>
       </c>
       <c r="F40" t="n">
-        <v>39.4838</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G40" t="n">
-        <v>10265800.4</v>
+        <v>835680.4</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1748,62 +1750,62 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>24700</v>
+        <v>183500</v>
       </c>
       <c r="F41" t="n">
-        <v>415.6194</v>
+        <v>113.6562</v>
       </c>
       <c r="G41" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>48650</v>
+        <v>183500</v>
       </c>
       <c r="F42" t="n">
-        <v>422.0267</v>
+        <v>12.1963</v>
       </c>
       <c r="G42" t="n">
-        <v>20531600.8</v>
+        <v>2238023.8</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1812,111 +1814,109 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>87800</v>
+        <v>1849000</v>
       </c>
       <c r="F43" t="n">
-        <v>115.4542</v>
+        <v>5.5521</v>
       </c>
       <c r="G43" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>22750</v>
+        <v>260000</v>
       </c>
       <c r="F44" t="n">
-        <v>891.1538</v>
+        <v>39.4838</v>
       </c>
       <c r="G44" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>33150</v>
+        <v>24700</v>
       </c>
       <c r="F45" t="n">
-        <v>569</v>
+        <v>415.6194</v>
       </c>
       <c r="G45" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H45" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10265800.4</v>
+      </c>
+      <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>254500</v>
+        <v>48650</v>
       </c>
       <c r="F46" t="n">
-        <v>39.8306</v>
+        <v>422.0267</v>
       </c>
       <c r="G46" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1928,161 +1928,161 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>79400</v>
+        <v>87800</v>
       </c>
       <c r="F47" t="n">
-        <v>246</v>
+        <v>115.4542</v>
       </c>
       <c r="G47" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H47" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>14780</v>
+        <v>22750</v>
       </c>
       <c r="F48" t="n">
-        <v>1338</v>
+        <v>891.1538</v>
       </c>
       <c r="G48" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H48" t="n">
-        <v>33.89</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>195800</v>
+        <v>33150</v>
       </c>
       <c r="F49" t="n">
-        <v>101.9921</v>
+        <v>569</v>
       </c>
       <c r="G49" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>14600</v>
+        <v>254500</v>
       </c>
       <c r="F50" t="n">
-        <v>1367.8125</v>
+        <v>39.8306</v>
       </c>
       <c r="G50" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>36300</v>
+        <v>79400</v>
       </c>
       <c r="F51" t="n">
-        <v>275.0697</v>
+        <v>246</v>
       </c>
       <c r="G51" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H51" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H51" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2092,142 +2092,142 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>159300</v>
+        <v>14780</v>
       </c>
       <c r="F52" t="n">
-        <v>62.6807</v>
+        <v>1338</v>
       </c>
       <c r="G52" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H52" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F53" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G53" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F54" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G54" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F55" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G55" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -2236,49 +2236,47 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F56" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G56" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F57" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G57" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H57" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2288,140 +2286,144 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F58" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G58" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F59" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G59" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H59" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F60" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G60" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F61" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G61" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H61" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H61" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -2430,52 +2432,52 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F62" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G62" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F63" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G63" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -2494,30 +2496,30 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F64" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G64" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2526,77 +2528,77 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F65" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G65" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F66" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G66" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F67" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G67" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
@@ -2608,12 +2610,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -2622,13 +2624,13 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F68" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G68" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
@@ -2640,12 +2642,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2654,13 +2656,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F69" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G69" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2672,27 +2674,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F70" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G70" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2704,12 +2706,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2718,13 +2720,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G71" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2736,12 +2738,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2750,13 +2752,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F72" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G72" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2768,27 +2770,27 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F73" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G73" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2800,12 +2802,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2814,13 +2816,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F74" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G74" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2832,27 +2834,27 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F75" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G75" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2864,12 +2866,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2878,13 +2880,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F76" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G76" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2896,27 +2898,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F77" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G77" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2928,12 +2930,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2942,13 +2944,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F78" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G78" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2960,27 +2962,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F79" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G79" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2992,27 +2994,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F80" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G80" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3024,27 +3026,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F81" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G81" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3056,12 +3058,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3070,13 +3072,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F82" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G82" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3088,27 +3090,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F83" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G83" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3120,27 +3122,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F84" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G84" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3152,27 +3154,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F85" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G85" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3184,27 +3186,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F86" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G86" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3216,27 +3218,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F87" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G87" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3248,12 +3250,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3262,13 +3264,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F88" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G88" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3280,27 +3282,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F89" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G89" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3312,12 +3314,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3326,13 +3328,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F90" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G90" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3344,12 +3346,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3358,13 +3360,13 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F91" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G91" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3376,12 +3378,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3390,13 +3392,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F92" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G92" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3408,27 +3410,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F93" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G93" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3440,12 +3442,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3454,62 +3456,62 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F94" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G94" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F95" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G95" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3518,30 +3520,30 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F96" t="n">
         <v>106</v>
       </c>
       <c r="G96" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3550,196 +3552,190 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F97" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G97" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F98" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G98" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F99" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G99" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H99" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F100" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G100" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H100" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F101" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G101" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F102" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G102" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3748,96 +3744,100 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F103" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G103" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H103" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F104" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G104" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H104" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F105" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G105" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H105" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -3846,30 +3846,30 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F106" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G106" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,66 +3878,64 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F107" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G107" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H107" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F108" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G108" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H108" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3946,64 +3944,62 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F109" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G109" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F110" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G110" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4012,175 +4008,181 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F111" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G111" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H111" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F112" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G112" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H112" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F113" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G113" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F114" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G114" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H114" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F115" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G115" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H115" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H115" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F116" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G116" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4192,12 +4194,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4206,13 +4208,13 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F117" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G117" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
@@ -4224,12 +4226,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4238,13 +4240,13 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F118" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G118" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H118" t="inlineStr"/>
     </row>
@@ -4256,12 +4258,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -4270,13 +4272,13 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F119" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G119" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H119" t="inlineStr"/>
     </row>
@@ -4288,12 +4290,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -4302,13 +4304,13 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F120" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G120" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4320,27 +4322,27 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F121" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G121" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4352,27 +4354,27 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F122" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G122" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4384,31 +4386,29 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F123" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G123" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H123" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4432,13 +4432,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F124" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G124" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4450,12 +4450,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4464,13 +4464,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F125" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G125" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4482,27 +4482,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F126" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G126" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4514,29 +4514,31 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F127" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G127" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H127" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H127" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4546,31 +4548,29 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F128" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G128" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H128" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4594,13 +4594,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F129" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G129" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4612,12 +4612,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4626,13 +4626,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F130" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G130" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4644,12 +4644,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4658,13 +4658,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F131" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G131" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4676,142 +4676,142 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F132" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G132" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H132" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H132" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F133" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G133" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F134" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G134" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F135" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G135" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4820,13 +4820,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F136" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G136" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4838,31 +4838,29 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F137" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G137" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H137" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -4872,12 +4870,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -4886,16 +4884,16 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F138" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G138" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H138" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="139">
@@ -4906,12 +4904,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4920,13 +4918,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F139" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G139" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4938,110 +4936,112 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F140" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G140" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H140" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F141" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G141" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H141" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H141" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F142" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G142" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H142" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H142" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,47 +5050,49 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F143" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G143" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F144" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G144" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5100,12 +5102,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -5114,13 +5116,13 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F145" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G145" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H145" t="inlineStr"/>
     </row>
@@ -5132,12 +5134,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -5146,13 +5148,13 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F146" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G146" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5164,12 +5166,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5178,13 +5180,13 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F147" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G147" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
@@ -5196,12 +5198,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5210,13 +5212,13 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F148" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G148" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H148" t="inlineStr"/>
     </row>
@@ -5228,12 +5230,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5242,13 +5244,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F149" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G149" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5260,12 +5262,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5274,13 +5276,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F150" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G150" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5292,12 +5294,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5306,13 +5308,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F151" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G151" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5324,12 +5326,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5338,13 +5340,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F152" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G152" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5356,12 +5358,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5370,13 +5372,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F153" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G153" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5388,12 +5390,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5402,13 +5404,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F154" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G154" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5420,12 +5422,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5434,13 +5436,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F155" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G155" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5452,12 +5454,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5466,13 +5468,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F156" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G156" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5484,12 +5486,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5498,13 +5500,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F157" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G157" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5516,12 +5518,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5530,13 +5532,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F158" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G158" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5548,12 +5550,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5562,13 +5564,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F159" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G159" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5580,12 +5582,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5594,13 +5596,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F160" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G160" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5612,12 +5614,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5626,13 +5628,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F161" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G161" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5644,12 +5646,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5658,13 +5660,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F162" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G162" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5676,12 +5678,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5690,13 +5692,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F163" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G163" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5708,29 +5710,157 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E164" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F164" t="n">
+        <v>180</v>
+      </c>
+      <c r="G164" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E165" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F165" t="n">
+        <v>449</v>
+      </c>
+      <c r="G165" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E166" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F166" t="n">
+        <v>148</v>
+      </c>
+      <c r="G166" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F167" t="n">
+        <v>593</v>
+      </c>
+      <c r="G167" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C164" t="inlineStr">
+      <c r="C168" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr">
+      <c r="D168" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E164" t="n">
+      <c r="E168" t="n">
         <v>124600</v>
       </c>
-      <c r="F164" t="n">
+      <c r="F168" t="n">
         <v>161</v>
       </c>
-      <c r="G164" t="n">
+      <c r="G168" t="n">
         <v>20060600</v>
       </c>
-      <c r="H164" t="inlineStr"/>
+      <c r="H168" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H168"/>
+  <dimension ref="A1:H172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,181 +473,181 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>295000</v>
+        <v>35350</v>
       </c>
       <c r="F2" t="n">
-        <v>71.24209999999999</v>
+        <v>566.7369</v>
       </c>
       <c r="G2" t="n">
-        <v>21016430.2</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>20034151</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>12870</v>
+        <v>91800</v>
       </c>
       <c r="F3" t="n">
-        <v>1632.9783</v>
+        <v>213.6877</v>
       </c>
       <c r="G3" t="n">
-        <v>21016430.2</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>19616530.9</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-12.98</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>161900</v>
+        <v>87700</v>
       </c>
       <c r="F4" t="n">
-        <v>129.8112</v>
+        <v>118.7012</v>
       </c>
       <c r="G4" t="n">
-        <v>21016430.2</v>
+        <v>10410097.5</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>38900</v>
+        <v>12310</v>
       </c>
       <c r="F5" t="n">
-        <v>506.8267</v>
+        <v>845.6618999999999</v>
       </c>
       <c r="G5" t="n">
-        <v>19715559.5</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-14.24</v>
-      </c>
+        <v>10410097.5</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>13580</v>
+        <v>295000</v>
       </c>
       <c r="F6" t="n">
-        <v>1493.977</v>
+        <v>71.24209999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>21016430.2</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -656,62 +656,62 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>126300</v>
+        <v>12870</v>
       </c>
       <c r="F7" t="n">
-        <v>165.13</v>
+        <v>1632.9783</v>
       </c>
       <c r="G7" t="n">
-        <v>20855919.6</v>
+        <v>21016430.2</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>48800</v>
+        <v>161900</v>
       </c>
       <c r="F8" t="n">
-        <v>6.3754</v>
+        <v>129.8112</v>
       </c>
       <c r="G8" t="n">
-        <v>311119.6</v>
+        <v>21016430.2</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -720,49 +720,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>29050</v>
+        <v>38900</v>
       </c>
       <c r="F9" t="n">
-        <v>686</v>
+        <v>506.8267</v>
       </c>
       <c r="G9" t="n">
-        <v>19928300</v>
+        <v>19715559.5</v>
       </c>
       <c r="H9" t="n">
-        <v>3.01</v>
+        <v>-14.24</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>275000</v>
+        <v>13580</v>
       </c>
       <c r="F10" t="n">
-        <v>3.4779</v>
+        <v>1493.977</v>
       </c>
       <c r="G10" t="n">
-        <v>956424.2</v>
-      </c>
-      <c r="H10" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H10" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -772,27 +774,27 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>326500</v>
+        <v>126300</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8772</v>
+        <v>165.13</v>
       </c>
       <c r="G11" t="n">
-        <v>286419.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -804,27 +806,27 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>36800</v>
+        <v>48800</v>
       </c>
       <c r="F12" t="n">
-        <v>14.2631</v>
+        <v>6.3754</v>
       </c>
       <c r="G12" t="n">
-        <v>524880.4</v>
+        <v>311119.6</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -836,29 +838,31 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>536000</v>
+        <v>29050</v>
       </c>
       <c r="F13" t="n">
-        <v>2.9103</v>
+        <v>686</v>
       </c>
       <c r="G13" t="n">
-        <v>1559919.6</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H13" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -868,27 +872,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>97600</v>
+        <v>275000</v>
       </c>
       <c r="F14" t="n">
-        <v>19.6877</v>
+        <v>3.4779</v>
       </c>
       <c r="G14" t="n">
-        <v>1921519.6</v>
+        <v>956424.2</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -900,12 +904,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -914,13 +918,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>153900</v>
+        <v>326500</v>
       </c>
       <c r="F15" t="n">
-        <v>17.0321</v>
+        <v>0.8772</v>
       </c>
       <c r="G15" t="n">
-        <v>2621239.2</v>
+        <v>286419.6</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -932,27 +936,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1074000</v>
+        <v>36800</v>
       </c>
       <c r="F16" t="n">
-        <v>19.4189</v>
+        <v>14.2631</v>
       </c>
       <c r="G16" t="n">
-        <v>20855919.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -964,12 +968,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -978,13 +982,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>87400</v>
+        <v>536000</v>
       </c>
       <c r="F17" t="n">
-        <v>15.0802</v>
+        <v>2.9103</v>
       </c>
       <c r="G17" t="n">
-        <v>1318012.9</v>
+        <v>1559919.6</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -996,12 +1000,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1010,13 +1014,13 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>225000</v>
+        <v>97600</v>
       </c>
       <c r="F18" t="n">
-        <v>0.6929999999999999</v>
+        <v>19.6877</v>
       </c>
       <c r="G18" t="n">
-        <v>155919.6</v>
+        <v>1921519.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1028,12 +1032,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1042,13 +1046,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5810</v>
+        <v>153900</v>
       </c>
       <c r="F19" t="n">
-        <v>154.6591</v>
+        <v>17.0321</v>
       </c>
       <c r="G19" t="n">
-        <v>898569.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1060,27 +1064,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>30200</v>
+        <v>1074000</v>
       </c>
       <c r="F20" t="n">
-        <v>109.4066</v>
+        <v>19.4189</v>
       </c>
       <c r="G20" t="n">
-        <v>3304080.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1092,27 +1096,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>207000</v>
+        <v>87400</v>
       </c>
       <c r="F21" t="n">
-        <v>1.2389</v>
+        <v>15.0802</v>
       </c>
       <c r="G21" t="n">
-        <v>256454.4</v>
+        <v>1318012.9</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1124,27 +1128,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>28150</v>
+        <v>225000</v>
       </c>
       <c r="F22" t="n">
-        <v>195.4454</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>5501788.7</v>
+        <v>155919.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1156,27 +1160,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>50500</v>
+        <v>5810</v>
       </c>
       <c r="F23" t="n">
-        <v>7.0115</v>
+        <v>154.6591</v>
       </c>
       <c r="G23" t="n">
-        <v>354080.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1188,31 +1192,29 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>19430</v>
+        <v>30200</v>
       </c>
       <c r="F24" t="n">
-        <v>1071</v>
+        <v>109.4066</v>
       </c>
       <c r="G24" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0.78</v>
-      </c>
+        <v>3304080.4</v>
+      </c>
+      <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1222,12 +1224,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1236,13 +1238,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>21200</v>
+        <v>207000</v>
       </c>
       <c r="F25" t="n">
-        <v>1475.6547</v>
+        <v>1.2389</v>
       </c>
       <c r="G25" t="n">
-        <v>31283879.4</v>
+        <v>256454.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1254,12 +1256,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1268,13 +1270,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>21200</v>
+        <v>28150</v>
       </c>
       <c r="F26" t="n">
-        <v>154.5755</v>
+        <v>195.4454</v>
       </c>
       <c r="G26" t="n">
-        <v>3277001</v>
+        <v>5501788.7</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1286,12 +1288,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1300,13 +1302,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>27700</v>
+        <v>50500</v>
       </c>
       <c r="F27" t="n">
-        <v>98.6181</v>
+        <v>7.0115</v>
       </c>
       <c r="G27" t="n">
-        <v>2731720.6</v>
+        <v>354080.4</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1318,29 +1320,31 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>13960</v>
+        <v>19430</v>
       </c>
       <c r="F28" t="n">
-        <v>126.1646</v>
+        <v>1071</v>
       </c>
       <c r="G28" t="n">
-        <v>1761257.6</v>
-      </c>
-      <c r="H28" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1350,27 +1354,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>140200</v>
+        <v>21200</v>
       </c>
       <c r="F29" t="n">
-        <v>21.1375</v>
+        <v>1475.6547</v>
       </c>
       <c r="G29" t="n">
-        <v>2963479.4</v>
+        <v>31283879.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1382,12 +1386,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1396,13 +1400,13 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6330</v>
+        <v>21200</v>
       </c>
       <c r="F30" t="n">
-        <v>13.226</v>
+        <v>154.5755</v>
       </c>
       <c r="G30" t="n">
-        <v>83720.39999999999</v>
+        <v>3277001</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
@@ -1414,12 +1418,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1428,13 +1432,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>15750</v>
+        <v>27700</v>
       </c>
       <c r="F31" t="n">
-        <v>5.8146</v>
+        <v>98.6181</v>
       </c>
       <c r="G31" t="n">
-        <v>91580.39999999999</v>
+        <v>2731720.6</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1446,12 +1450,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1460,13 +1464,13 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>22500</v>
+        <v>13960</v>
       </c>
       <c r="F32" t="n">
-        <v>110.3946</v>
+        <v>126.1646</v>
       </c>
       <c r="G32" t="n">
-        <v>2483879.4</v>
+        <v>1761257.6</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1478,31 +1482,29 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>256000</v>
+        <v>140200</v>
       </c>
       <c r="F33" t="n">
-        <v>113.8306</v>
+        <v>21.1375</v>
       </c>
       <c r="G33" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H33" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>2963479.4</v>
+      </c>
+      <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1512,27 +1514,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>75700</v>
+        <v>6330</v>
       </c>
       <c r="F34" t="n">
-        <v>275.5075</v>
+        <v>13.226</v>
       </c>
       <c r="G34" t="n">
-        <v>20855919.6</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1544,27 +1546,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>131600</v>
+        <v>15750</v>
       </c>
       <c r="F35" t="n">
-        <v>2.4796</v>
+        <v>5.8146</v>
       </c>
       <c r="G35" t="n">
-        <v>326319.6</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1576,12 +1578,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -1590,13 +1592,13 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>41150</v>
+        <v>22500</v>
       </c>
       <c r="F36" t="n">
-        <v>43.8267</v>
+        <v>110.3946</v>
       </c>
       <c r="G36" t="n">
-        <v>1803469.6</v>
+        <v>2483879.4</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1608,29 +1610,31 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>147300</v>
+        <v>256000</v>
       </c>
       <c r="F37" t="n">
-        <v>2.3821</v>
+        <v>113.8306</v>
       </c>
       <c r="G37" t="n">
-        <v>350879.4</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H37" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1640,27 +1644,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>36450</v>
+        <v>75700</v>
       </c>
       <c r="F38" t="n">
-        <v>76.7514</v>
+        <v>275.5075</v>
       </c>
       <c r="G38" t="n">
-        <v>2797588.9</v>
+        <v>20855919.6</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1672,12 +1676,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1686,13 +1690,13 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>119700</v>
+        <v>131600</v>
       </c>
       <c r="F39" t="n">
-        <v>30.2349</v>
+        <v>2.4796</v>
       </c>
       <c r="G39" t="n">
-        <v>3619119.6</v>
+        <v>326319.6</v>
       </c>
       <c r="H39" t="inlineStr"/>
     </row>
@@ -1704,27 +1708,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>85400</v>
+        <v>41150</v>
       </c>
       <c r="F40" t="n">
-        <v>9.785500000000001</v>
+        <v>43.8267</v>
       </c>
       <c r="G40" t="n">
-        <v>835680.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1736,12 +1740,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1750,13 +1754,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>183500</v>
+        <v>147300</v>
       </c>
       <c r="F41" t="n">
-        <v>113.6562</v>
+        <v>2.3821</v>
       </c>
       <c r="G41" t="n">
-        <v>20855919.6</v>
+        <v>350879.4</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1768,12 +1772,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1782,62 +1786,62 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>183500</v>
+        <v>36450</v>
       </c>
       <c r="F42" t="n">
-        <v>12.1963</v>
+        <v>76.7514</v>
       </c>
       <c r="G42" t="n">
-        <v>2238023.8</v>
+        <v>2797588.9</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1849000</v>
+        <v>119700</v>
       </c>
       <c r="F43" t="n">
-        <v>5.5521</v>
+        <v>30.2349</v>
       </c>
       <c r="G43" t="n">
-        <v>10265800.4</v>
+        <v>3619119.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1846,30 +1850,30 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>260000</v>
+        <v>85400</v>
       </c>
       <c r="F44" t="n">
-        <v>39.4838</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G44" t="n">
-        <v>10265800.4</v>
+        <v>835680.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1878,62 +1882,62 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>24700</v>
+        <v>183500</v>
       </c>
       <c r="F45" t="n">
-        <v>415.6194</v>
+        <v>113.6562</v>
       </c>
       <c r="G45" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>48650</v>
+        <v>183500</v>
       </c>
       <c r="F46" t="n">
-        <v>422.0267</v>
+        <v>12.1963</v>
       </c>
       <c r="G46" t="n">
-        <v>20531600.8</v>
+        <v>2238023.8</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1942,111 +1946,109 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>87800</v>
+        <v>1849000</v>
       </c>
       <c r="F47" t="n">
-        <v>115.4542</v>
+        <v>5.5521</v>
       </c>
       <c r="G47" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>22750</v>
+        <v>260000</v>
       </c>
       <c r="F48" t="n">
-        <v>891.1538</v>
+        <v>39.4838</v>
       </c>
       <c r="G48" t="n">
-        <v>20273749.9</v>
+        <v>10265800.4</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>33150</v>
+        <v>24700</v>
       </c>
       <c r="F49" t="n">
-        <v>569</v>
+        <v>415.6194</v>
       </c>
       <c r="G49" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H49" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10265800.4</v>
+      </c>
+      <c r="H49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>254500</v>
+        <v>48650</v>
       </c>
       <c r="F50" t="n">
-        <v>39.8306</v>
+        <v>422.0267</v>
       </c>
       <c r="G50" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
@@ -2058,161 +2060,161 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>79400</v>
+        <v>87800</v>
       </c>
       <c r="F51" t="n">
-        <v>246</v>
+        <v>115.4542</v>
       </c>
       <c r="G51" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H51" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>14780</v>
+        <v>22750</v>
       </c>
       <c r="F52" t="n">
-        <v>1338</v>
+        <v>891.1538</v>
       </c>
       <c r="G52" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H52" t="n">
-        <v>33.89</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>195800</v>
+        <v>33150</v>
       </c>
       <c r="F53" t="n">
-        <v>101.9921</v>
+        <v>569</v>
       </c>
       <c r="G53" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H53" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H53" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>14600</v>
+        <v>254500</v>
       </c>
       <c r="F54" t="n">
-        <v>1367.8125</v>
+        <v>39.8306</v>
       </c>
       <c r="G54" t="n">
-        <v>19970062</v>
+        <v>10136875</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>36300</v>
+        <v>79400</v>
       </c>
       <c r="F55" t="n">
-        <v>275.0697</v>
+        <v>246</v>
       </c>
       <c r="G55" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H55" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H55" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2222,142 +2224,142 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>159300</v>
+        <v>14780</v>
       </c>
       <c r="F56" t="n">
-        <v>62.6807</v>
+        <v>1338</v>
       </c>
       <c r="G56" t="n">
-        <v>9985031</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H56" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>147200</v>
+        <v>195800</v>
       </c>
       <c r="F57" t="n">
-        <v>67</v>
+        <v>101.9921</v>
       </c>
       <c r="G57" t="n">
-        <v>9862400</v>
+        <v>19970062</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>14540</v>
+        <v>14600</v>
       </c>
       <c r="F58" t="n">
-        <v>983</v>
+        <v>1367.8125</v>
       </c>
       <c r="G58" t="n">
-        <v>14292820</v>
+        <v>19970062</v>
       </c>
       <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>113400</v>
+        <v>36300</v>
       </c>
       <c r="F59" t="n">
-        <v>167</v>
+        <v>275.0697</v>
       </c>
       <c r="G59" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H59" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9985031</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2366,49 +2368,47 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>24350</v>
+        <v>159300</v>
       </c>
       <c r="F60" t="n">
-        <v>407</v>
+        <v>62.6807</v>
       </c>
       <c r="G60" t="n">
-        <v>9910450</v>
+        <v>9985031</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>44100</v>
+        <v>147200</v>
       </c>
       <c r="F61" t="n">
-        <v>488</v>
+        <v>67</v>
       </c>
       <c r="G61" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H61" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2418,140 +2418,144 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>165700</v>
+        <v>14540</v>
       </c>
       <c r="F62" t="n">
-        <v>120</v>
+        <v>983</v>
       </c>
       <c r="G62" t="n">
-        <v>19884000</v>
+        <v>14292820</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>28950</v>
+        <v>113400</v>
       </c>
       <c r="F63" t="n">
-        <v>353</v>
+        <v>167</v>
       </c>
       <c r="G63" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H63" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H63" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1853000</v>
+        <v>24350</v>
       </c>
       <c r="F64" t="n">
-        <v>11</v>
+        <v>407</v>
       </c>
       <c r="G64" t="n">
-        <v>20383000</v>
+        <v>9910450</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>269000</v>
+        <v>44100</v>
       </c>
       <c r="F65" t="n">
-        <v>76</v>
+        <v>488</v>
       </c>
       <c r="G65" t="n">
-        <v>20444000</v>
-      </c>
-      <c r="H65" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H65" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -2560,52 +2564,52 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>106300</v>
+        <v>165700</v>
       </c>
       <c r="F66" t="n">
-        <v>194</v>
+        <v>120</v>
       </c>
       <c r="G66" t="n">
-        <v>20622200</v>
+        <v>19884000</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>123100</v>
+        <v>28950</v>
       </c>
       <c r="F67" t="n">
-        <v>167</v>
+        <v>353</v>
       </c>
       <c r="G67" t="n">
-        <v>20557700</v>
+        <v>10219350</v>
       </c>
       <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -2624,30 +2628,30 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1856000</v>
+        <v>1853000</v>
       </c>
       <c r="F68" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="G68" t="n">
-        <v>42688000</v>
+        <v>20383000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2656,77 +2660,77 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>49000</v>
+        <v>269000</v>
       </c>
       <c r="F69" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G69" t="n">
-        <v>8183000</v>
+        <v>20444000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>13340</v>
+        <v>106300</v>
       </c>
       <c r="F70" t="n">
-        <v>236</v>
+        <v>194</v>
       </c>
       <c r="G70" t="n">
-        <v>3148240</v>
+        <v>20622200</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>29800</v>
+        <v>123100</v>
       </c>
       <c r="F71" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G71" t="n">
-        <v>1966800</v>
+        <v>20557700</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2738,12 +2742,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -2752,13 +2756,13 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>269500</v>
+        <v>1856000</v>
       </c>
       <c r="F72" t="n">
-        <v>118</v>
+        <v>23</v>
       </c>
       <c r="G72" t="n">
-        <v>31801000</v>
+        <v>42688000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2770,12 +2774,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2784,13 +2788,13 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>330000</v>
+        <v>49000</v>
       </c>
       <c r="F73" t="n">
-        <v>24</v>
+        <v>167</v>
       </c>
       <c r="G73" t="n">
-        <v>7920000</v>
+        <v>8183000</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2802,27 +2806,27 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>35550</v>
+        <v>13340</v>
       </c>
       <c r="F74" t="n">
-        <v>581</v>
+        <v>236</v>
       </c>
       <c r="G74" t="n">
-        <v>20654550</v>
+        <v>3148240</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2834,12 +2838,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2848,13 +2852,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>574000</v>
+        <v>29800</v>
       </c>
       <c r="F75" t="n">
-        <v>22</v>
+        <v>66</v>
       </c>
       <c r="G75" t="n">
-        <v>12628000</v>
+        <v>1966800</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2866,12 +2870,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2880,13 +2884,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>165900</v>
+        <v>269500</v>
       </c>
       <c r="F76" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G76" t="n">
-        <v>3981600</v>
+        <v>31801000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2898,27 +2902,27 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>91300</v>
+        <v>330000</v>
       </c>
       <c r="F77" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G77" t="n">
-        <v>4108500</v>
+        <v>7920000</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2930,12 +2934,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2944,13 +2948,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>224500</v>
+        <v>35550</v>
       </c>
       <c r="F78" t="n">
-        <v>92</v>
+        <v>581</v>
       </c>
       <c r="G78" t="n">
-        <v>20654000</v>
+        <v>20654550</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2962,27 +2966,27 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6010</v>
+        <v>574000</v>
       </c>
       <c r="F79" t="n">
-        <v>3435</v>
+        <v>22</v>
       </c>
       <c r="G79" t="n">
-        <v>20644350</v>
+        <v>12628000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2994,12 +2998,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -3008,13 +3012,13 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>25800</v>
+        <v>165900</v>
       </c>
       <c r="F80" t="n">
-        <v>351</v>
+        <v>24</v>
       </c>
       <c r="G80" t="n">
-        <v>9055800</v>
+        <v>3981600</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3026,27 +3030,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>49150</v>
+        <v>91300</v>
       </c>
       <c r="F81" t="n">
-        <v>420</v>
+        <v>45</v>
       </c>
       <c r="G81" t="n">
-        <v>20643000</v>
+        <v>4108500</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3058,12 +3062,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3072,13 +3076,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>19280</v>
+        <v>224500</v>
       </c>
       <c r="F82" t="n">
-        <v>1071</v>
+        <v>92</v>
       </c>
       <c r="G82" t="n">
-        <v>20648880</v>
+        <v>20654000</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3090,27 +3094,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>19740</v>
+        <v>6010</v>
       </c>
       <c r="F83" t="n">
-        <v>523</v>
+        <v>3435</v>
       </c>
       <c r="G83" t="n">
-        <v>10324020</v>
+        <v>20644350</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3122,27 +3126,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>25150</v>
+        <v>25800</v>
       </c>
       <c r="F84" t="n">
-        <v>821</v>
+        <v>351</v>
       </c>
       <c r="G84" t="n">
-        <v>20648150</v>
+        <v>9055800</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3154,27 +3158,27 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>153500</v>
+        <v>49150</v>
       </c>
       <c r="F85" t="n">
-        <v>24</v>
+        <v>420</v>
       </c>
       <c r="G85" t="n">
-        <v>3684000</v>
+        <v>20643000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3186,12 +3190,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -3200,13 +3204,13 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6240</v>
+        <v>19280</v>
       </c>
       <c r="F86" t="n">
-        <v>3308</v>
+        <v>1071</v>
       </c>
       <c r="G86" t="n">
-        <v>20641920</v>
+        <v>20648880</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3218,27 +3222,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>15520</v>
+        <v>19740</v>
       </c>
       <c r="F87" t="n">
-        <v>1330</v>
+        <v>523</v>
       </c>
       <c r="G87" t="n">
-        <v>20641600</v>
+        <v>10324020</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3250,27 +3254,27 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>24200</v>
+        <v>25150</v>
       </c>
       <c r="F88" t="n">
-        <v>210</v>
+        <v>821</v>
       </c>
       <c r="G88" t="n">
-        <v>5082000</v>
+        <v>20648150</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3282,27 +3286,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>36300</v>
+        <v>153500</v>
       </c>
       <c r="F89" t="n">
-        <v>569</v>
+        <v>24</v>
       </c>
       <c r="G89" t="n">
-        <v>20654700</v>
+        <v>3684000</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3314,27 +3318,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>279500</v>
+        <v>6240</v>
       </c>
       <c r="F90" t="n">
-        <v>43</v>
+        <v>3308</v>
       </c>
       <c r="G90" t="n">
-        <v>12018500</v>
+        <v>20641920</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3346,27 +3350,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>132600</v>
+        <v>15520</v>
       </c>
       <c r="F91" t="n">
-        <v>90</v>
+        <v>1330</v>
       </c>
       <c r="G91" t="n">
-        <v>11934000</v>
+        <v>20641600</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3378,12 +3382,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -3392,13 +3396,13 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>44600</v>
+        <v>24200</v>
       </c>
       <c r="F92" t="n">
-        <v>139</v>
+        <v>210</v>
       </c>
       <c r="G92" t="n">
-        <v>6199400</v>
+        <v>5082000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3410,27 +3414,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>147100</v>
+        <v>36300</v>
       </c>
       <c r="F93" t="n">
-        <v>6</v>
+        <v>569</v>
       </c>
       <c r="G93" t="n">
-        <v>882600</v>
+        <v>20654700</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3442,12 +3446,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3456,13 +3460,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>33500</v>
+        <v>279500</v>
       </c>
       <c r="F94" t="n">
-        <v>8</v>
+        <v>43</v>
       </c>
       <c r="G94" t="n">
-        <v>268000</v>
+        <v>12018500</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3474,12 +3478,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -3488,13 +3492,13 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>143100</v>
+        <v>132600</v>
       </c>
       <c r="F95" t="n">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G95" t="n">
-        <v>13594500</v>
+        <v>11934000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3506,12 +3510,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3520,13 +3524,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>83800</v>
+        <v>44600</v>
       </c>
       <c r="F96" t="n">
-        <v>106</v>
+        <v>139</v>
       </c>
       <c r="G96" t="n">
-        <v>8882800</v>
+        <v>6199400</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3538,27 +3542,27 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>42300</v>
+        <v>147100</v>
       </c>
       <c r="F97" t="n">
-        <v>488</v>
+        <v>6</v>
       </c>
       <c r="G97" t="n">
-        <v>20642400</v>
+        <v>882600</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3570,12 +3574,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3584,62 +3588,62 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>81200</v>
+        <v>33500</v>
       </c>
       <c r="F98" t="n">
-        <v>135</v>
+        <v>8</v>
       </c>
       <c r="G98" t="n">
-        <v>10962000</v>
+        <v>268000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>78600</v>
+        <v>143100</v>
       </c>
       <c r="F99" t="n">
-        <v>389</v>
+        <v>95</v>
       </c>
       <c r="G99" t="n">
-        <v>30575400</v>
+        <v>13594500</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3648,30 +3652,30 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>92500</v>
+        <v>83800</v>
       </c>
       <c r="F100" t="n">
         <v>106</v>
       </c>
       <c r="G100" t="n">
-        <v>9805000</v>
+        <v>8882800</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3680,196 +3684,190 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>25550</v>
+        <v>42300</v>
       </c>
       <c r="F101" t="n">
-        <v>1151</v>
+        <v>488</v>
       </c>
       <c r="G101" t="n">
-        <v>29408050</v>
+        <v>20642400</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>21800</v>
+        <v>81200</v>
       </c>
       <c r="F102" t="n">
-        <v>832</v>
+        <v>135</v>
       </c>
       <c r="G102" t="n">
-        <v>18137600</v>
+        <v>10962000</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>32250</v>
+        <v>78600</v>
       </c>
       <c r="F103" t="n">
-        <v>878</v>
+        <v>389</v>
       </c>
       <c r="G103" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H103" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>30575400</v>
+      </c>
+      <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>105800</v>
+        <v>92500</v>
       </c>
       <c r="F104" t="n">
-        <v>332</v>
+        <v>106</v>
       </c>
       <c r="G104" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H104" t="n">
-        <v>17.17</v>
-      </c>
+        <v>9805000</v>
+      </c>
+      <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>33750</v>
+        <v>25550</v>
       </c>
       <c r="F105" t="n">
-        <v>791</v>
+        <v>1151</v>
       </c>
       <c r="G105" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.29</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>86300</v>
+        <v>21800</v>
       </c>
       <c r="F106" t="n">
-        <v>352</v>
+        <v>832</v>
       </c>
       <c r="G106" t="n">
-        <v>30377600</v>
+        <v>18137600</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,96 +3876,100 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>21000</v>
+        <v>32250</v>
       </c>
       <c r="F107" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G107" t="n">
-        <v>31857000</v>
+        <v>28315500</v>
       </c>
       <c r="H107" t="n">
-        <v>3.96</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>21900</v>
+        <v>105800</v>
       </c>
       <c r="F108" t="n">
-        <v>906</v>
+        <v>332</v>
       </c>
       <c r="G108" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H108" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H108" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>135300</v>
+        <v>33750</v>
       </c>
       <c r="F109" t="n">
-        <v>226</v>
+        <v>791</v>
       </c>
       <c r="G109" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H109" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3976,30 +3978,30 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>22250</v>
+        <v>86300</v>
       </c>
       <c r="F110" t="n">
-        <v>1399</v>
+        <v>352</v>
       </c>
       <c r="G110" t="n">
-        <v>31127750</v>
+        <v>30377600</v>
       </c>
       <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4008,66 +4010,64 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>33500</v>
+        <v>21000</v>
       </c>
       <c r="F111" t="n">
-        <v>848</v>
+        <v>1517</v>
       </c>
       <c r="G111" t="n">
-        <v>28408000</v>
+        <v>31857000</v>
       </c>
       <c r="H111" t="n">
-        <v>-9.07</v>
+        <v>3.96</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>300000</v>
+        <v>21900</v>
       </c>
       <c r="F112" t="n">
-        <v>104</v>
+        <v>906</v>
       </c>
       <c r="G112" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H112" t="n">
-        <v>20.95</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -4076,64 +4076,62 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>28200</v>
+        <v>135300</v>
       </c>
       <c r="F113" t="n">
-        <v>1105</v>
+        <v>226</v>
       </c>
       <c r="G113" t="n">
-        <v>31161000</v>
+        <v>30577800</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>398000</v>
+        <v>22250</v>
       </c>
       <c r="F114" t="n">
-        <v>72</v>
+        <v>1399</v>
       </c>
       <c r="G114" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H114" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -4142,175 +4140,181 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>5620</v>
+        <v>33500</v>
       </c>
       <c r="F115" t="n">
-        <v>4707</v>
+        <v>848</v>
       </c>
       <c r="G115" t="n">
-        <v>26453340</v>
+        <v>28408000</v>
       </c>
       <c r="H115" t="n">
-        <v>-8.220000000000001</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>126900</v>
+        <v>300000</v>
       </c>
       <c r="F116" t="n">
-        <v>246</v>
+        <v>104</v>
       </c>
       <c r="G116" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H116" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H116" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1671000</v>
+        <v>28200</v>
       </c>
       <c r="F117" t="n">
-        <v>44</v>
+        <v>1105</v>
       </c>
       <c r="G117" t="n">
-        <v>73524000</v>
+        <v>31161000</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>50600</v>
+        <v>398000</v>
       </c>
       <c r="F118" t="n">
-        <v>186</v>
+        <v>72</v>
       </c>
       <c r="G118" t="n">
-        <v>9411600</v>
-      </c>
-      <c r="H118" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H118" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>11720</v>
+        <v>5620</v>
       </c>
       <c r="F119" t="n">
-        <v>665</v>
+        <v>4707</v>
       </c>
       <c r="G119" t="n">
-        <v>7793800</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H119" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>414000</v>
+        <v>126900</v>
       </c>
       <c r="F120" t="n">
-        <v>26</v>
+        <v>246</v>
       </c>
       <c r="G120" t="n">
-        <v>10764000</v>
+        <v>31217400</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
@@ -4322,12 +4326,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4336,13 +4340,13 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>257000</v>
+        <v>1671000</v>
       </c>
       <c r="F121" t="n">
-        <v>239</v>
+        <v>44</v>
       </c>
       <c r="G121" t="n">
-        <v>61423000</v>
+        <v>73524000</v>
       </c>
       <c r="H121" t="inlineStr"/>
     </row>
@@ -4354,12 +4358,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -4368,13 +4372,13 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>33900</v>
+        <v>50600</v>
       </c>
       <c r="F122" t="n">
-        <v>292</v>
+        <v>186</v>
       </c>
       <c r="G122" t="n">
-        <v>9898800</v>
+        <v>9411600</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4386,12 +4390,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -4400,13 +4404,13 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>515000</v>
+        <v>11720</v>
       </c>
       <c r="F123" t="n">
-        <v>17</v>
+        <v>665</v>
       </c>
       <c r="G123" t="n">
-        <v>8755000</v>
+        <v>7793800</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4418,12 +4422,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4432,13 +4436,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>141200</v>
+        <v>414000</v>
       </c>
       <c r="F124" t="n">
-        <v>81</v>
+        <v>26</v>
       </c>
       <c r="G124" t="n">
-        <v>11437200</v>
+        <v>10764000</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4450,27 +4454,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>6320</v>
+        <v>257000</v>
       </c>
       <c r="F125" t="n">
-        <v>1396</v>
+        <v>239</v>
       </c>
       <c r="G125" t="n">
-        <v>8822720</v>
+        <v>61423000</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4482,27 +4486,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>90300</v>
+        <v>33900</v>
       </c>
       <c r="F126" t="n">
-        <v>332</v>
+        <v>292</v>
       </c>
       <c r="G126" t="n">
-        <v>29979600</v>
+        <v>9898800</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4514,31 +4518,29 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>163100</v>
+        <v>515000</v>
       </c>
       <c r="F127" t="n">
-        <v>119</v>
+        <v>17</v>
       </c>
       <c r="G127" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H127" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8755000</v>
+      </c>
+      <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -4548,12 +4550,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4562,13 +4564,13 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F128" t="n">
-        <v>163</v>
+        <v>81</v>
       </c>
       <c r="G128" t="n">
-        <v>6177700</v>
+        <v>11437200</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4580,12 +4582,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4594,13 +4596,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>19990</v>
+        <v>6320</v>
       </c>
       <c r="F129" t="n">
-        <v>615</v>
+        <v>1396</v>
       </c>
       <c r="G129" t="n">
-        <v>12293850</v>
+        <v>8822720</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4612,27 +4614,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>35100</v>
+        <v>90300</v>
       </c>
       <c r="F130" t="n">
-        <v>320</v>
+        <v>332</v>
       </c>
       <c r="G130" t="n">
-        <v>11232000</v>
+        <v>29979600</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4644,29 +4646,31 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>286000</v>
+        <v>163100</v>
       </c>
       <c r="F131" t="n">
-        <v>20</v>
+        <v>119</v>
       </c>
       <c r="G131" t="n">
-        <v>5720000</v>
-      </c>
-      <c r="H131" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H131" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4676,31 +4680,29 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>416000</v>
+        <v>37900</v>
       </c>
       <c r="F132" t="n">
-        <v>51</v>
+        <v>163</v>
       </c>
       <c r="G132" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H132" t="n">
-        <v>5.85</v>
-      </c>
+        <v>6177700</v>
+      </c>
+      <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -4710,12 +4712,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -4724,13 +4726,13 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>49450</v>
+        <v>19990</v>
       </c>
       <c r="F133" t="n">
-        <v>153</v>
+        <v>615</v>
       </c>
       <c r="G133" t="n">
-        <v>7565850</v>
+        <v>12293850</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
@@ -4742,12 +4744,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4756,13 +4758,13 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>138000</v>
+        <v>35100</v>
       </c>
       <c r="F134" t="n">
-        <v>68</v>
+        <v>320</v>
       </c>
       <c r="G134" t="n">
-        <v>9384000</v>
+        <v>11232000</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -4774,12 +4776,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4788,13 +4790,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>31950</v>
+        <v>286000</v>
       </c>
       <c r="F135" t="n">
-        <v>339</v>
+        <v>20</v>
       </c>
       <c r="G135" t="n">
-        <v>10831050</v>
+        <v>5720000</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4806,142 +4808,142 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>124800</v>
+        <v>416000</v>
       </c>
       <c r="F136" t="n">
-        <v>78</v>
+        <v>51</v>
       </c>
       <c r="G136" t="n">
-        <v>9734400</v>
-      </c>
-      <c r="H136" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H136" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>10800</v>
+        <v>49450</v>
       </c>
       <c r="F137" t="n">
-        <v>1892</v>
+        <v>153</v>
       </c>
       <c r="G137" t="n">
-        <v>20433600</v>
+        <v>7565850</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>11880</v>
+        <v>138000</v>
       </c>
       <c r="F138" t="n">
-        <v>1474</v>
+        <v>68</v>
       </c>
       <c r="G138" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H138" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9384000</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>20200</v>
+        <v>31950</v>
       </c>
       <c r="F139" t="n">
-        <v>1517</v>
+        <v>339</v>
       </c>
       <c r="G139" t="n">
-        <v>30643400</v>
+        <v>10831050</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4950,13 +4952,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>102200</v>
+        <v>124800</v>
       </c>
       <c r="F140" t="n">
-        <v>200</v>
+        <v>78</v>
       </c>
       <c r="G140" t="n">
-        <v>20440000</v>
+        <v>9734400</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4968,31 +4970,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>23450</v>
+        <v>10800</v>
       </c>
       <c r="F141" t="n">
-        <v>762</v>
+        <v>1892</v>
       </c>
       <c r="G141" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H141" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5016,16 +5016,16 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>22050</v>
+        <v>11880</v>
       </c>
       <c r="F142" t="n">
-        <v>875</v>
+        <v>1474</v>
       </c>
       <c r="G142" t="n">
-        <v>19293750</v>
+        <v>17511120</v>
       </c>
       <c r="H142" t="n">
-        <v>-3.5</v>
+        <v>-12.45</v>
       </c>
     </row>
     <row r="143">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>32550</v>
+        <v>20200</v>
       </c>
       <c r="F143" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G143" t="n">
-        <v>20441400</v>
+        <v>30643400</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5068,110 +5068,112 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>99700</v>
+        <v>102200</v>
       </c>
       <c r="F144" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="G144" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1662000</v>
+        <v>23450</v>
       </c>
       <c r="F145" t="n">
-        <v>150</v>
+        <v>762</v>
       </c>
       <c r="G145" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>49700</v>
+        <v>22050</v>
       </c>
       <c r="F146" t="n">
-        <v>402</v>
+        <v>875</v>
       </c>
       <c r="G146" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -5180,47 +5182,49 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>435000</v>
+        <v>32550</v>
       </c>
       <c r="F147" t="n">
-        <v>46</v>
+        <v>628</v>
       </c>
       <c r="G147" t="n">
-        <v>20010000</v>
+        <v>20441400</v>
       </c>
       <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E148" t="n">
-        <v>268500</v>
+        <v>99700</v>
       </c>
       <c r="F148" t="n">
-        <v>931</v>
+        <v>180</v>
       </c>
       <c r="G148" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H148" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H148" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5230,12 +5234,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5244,13 +5248,13 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>13570</v>
+        <v>1662000</v>
       </c>
       <c r="F149" t="n">
-        <v>1474</v>
+        <v>150</v>
       </c>
       <c r="G149" t="n">
-        <v>20002180</v>
+        <v>249300000</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
@@ -5262,12 +5266,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -5276,13 +5280,13 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>343500</v>
+        <v>49700</v>
       </c>
       <c r="F150" t="n">
-        <v>87</v>
+        <v>402</v>
       </c>
       <c r="G150" t="n">
-        <v>29884500</v>
+        <v>19979400</v>
       </c>
       <c r="H150" t="inlineStr"/>
     </row>
@@ -5294,12 +5298,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5308,13 +5312,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>34150</v>
+        <v>435000</v>
       </c>
       <c r="F151" t="n">
-        <v>586</v>
+        <v>46</v>
       </c>
       <c r="G151" t="n">
-        <v>20011900</v>
+        <v>20010000</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5326,12 +5330,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5340,13 +5344,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>488000</v>
+        <v>268500</v>
       </c>
       <c r="F152" t="n">
-        <v>41</v>
+        <v>931</v>
       </c>
       <c r="G152" t="n">
-        <v>20008000</v>
+        <v>249973500</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5358,12 +5362,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5372,13 +5376,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>153600</v>
+        <v>13570</v>
       </c>
       <c r="F153" t="n">
-        <v>130</v>
+        <v>1474</v>
       </c>
       <c r="G153" t="n">
-        <v>19968000</v>
+        <v>20002180</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5390,12 +5394,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5404,13 +5408,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>99800</v>
+        <v>343500</v>
       </c>
       <c r="F154" t="n">
-        <v>200</v>
+        <v>87</v>
       </c>
       <c r="G154" t="n">
-        <v>19960000</v>
+        <v>29884500</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5422,12 +5426,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5436,13 +5440,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>6040</v>
+        <v>34150</v>
       </c>
       <c r="F155" t="n">
-        <v>3311</v>
+        <v>586</v>
       </c>
       <c r="G155" t="n">
-        <v>19998440</v>
+        <v>20011900</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5454,12 +5458,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5468,13 +5472,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>26250</v>
+        <v>488000</v>
       </c>
       <c r="F156" t="n">
-        <v>762</v>
+        <v>41</v>
       </c>
       <c r="G156" t="n">
-        <v>20002500</v>
+        <v>20008000</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5486,12 +5490,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5500,13 +5504,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>22850</v>
+        <v>153600</v>
       </c>
       <c r="F157" t="n">
-        <v>875</v>
+        <v>130</v>
       </c>
       <c r="G157" t="n">
-        <v>19993750</v>
+        <v>19968000</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5518,12 +5522,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5532,13 +5536,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>168500</v>
+        <v>99800</v>
       </c>
       <c r="F158" t="n">
-        <v>119</v>
+        <v>200</v>
       </c>
       <c r="G158" t="n">
-        <v>20051500</v>
+        <v>19960000</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5550,12 +5554,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5564,13 +5568,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F159" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G159" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5582,12 +5586,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5596,13 +5600,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>37900</v>
+        <v>26250</v>
       </c>
       <c r="F160" t="n">
-        <v>528</v>
+        <v>762</v>
       </c>
       <c r="G160" t="n">
-        <v>20011200</v>
+        <v>20002500</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5614,12 +5618,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5628,13 +5632,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F161" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G161" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5646,12 +5650,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5660,13 +5664,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>298000</v>
+        <v>168500</v>
       </c>
       <c r="F162" t="n">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="G162" t="n">
-        <v>34866000</v>
+        <v>20051500</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5678,12 +5682,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5692,13 +5696,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>393000</v>
+        <v>22850</v>
       </c>
       <c r="F163" t="n">
-        <v>51</v>
+        <v>875</v>
       </c>
       <c r="G163" t="n">
-        <v>20043000</v>
+        <v>19993750</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5710,12 +5714,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5724,13 +5728,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F164" t="n">
-        <v>180</v>
+        <v>528</v>
       </c>
       <c r="G164" t="n">
-        <v>19962000</v>
+        <v>20011200</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -5742,12 +5746,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5756,13 +5760,13 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>44500</v>
+        <v>239000</v>
       </c>
       <c r="F165" t="n">
-        <v>449</v>
+        <v>84</v>
       </c>
       <c r="G165" t="n">
-        <v>19980500</v>
+        <v>20076000</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
@@ -5774,12 +5778,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5788,13 +5792,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>135000</v>
+        <v>298000</v>
       </c>
       <c r="F166" t="n">
-        <v>148</v>
+        <v>117</v>
       </c>
       <c r="G166" t="n">
-        <v>19980000</v>
+        <v>34866000</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
@@ -5806,12 +5810,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5820,13 +5824,13 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>33750</v>
+        <v>393000</v>
       </c>
       <c r="F167" t="n">
-        <v>593</v>
+        <v>51</v>
       </c>
       <c r="G167" t="n">
-        <v>20013750</v>
+        <v>20043000</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
@@ -5838,29 +5842,157 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F168" t="n">
+        <v>180</v>
+      </c>
+      <c r="G168" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F169" t="n">
+        <v>449</v>
+      </c>
+      <c r="G169" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F170" t="n">
+        <v>148</v>
+      </c>
+      <c r="G170" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F171" t="n">
+        <v>593</v>
+      </c>
+      <c r="G171" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C168" t="inlineStr">
+      <c r="C172" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr">
+      <c r="D172" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E168" t="n">
+      <c r="E172" t="n">
         <v>124600</v>
       </c>
-      <c r="F168" t="n">
+      <c r="F172" t="n">
         <v>161</v>
       </c>
-      <c r="G168" t="n">
+      <c r="G172" t="n">
         <v>20060600</v>
       </c>
-      <c r="H168" t="inlineStr"/>
+      <c r="H172" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H172"/>
+  <dimension ref="A1:H174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,17 +473,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -492,51 +492,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>35350</v>
+        <v>91800</v>
       </c>
       <c r="F2" t="n">
-        <v>566.7369</v>
+        <v>275.5075</v>
       </c>
       <c r="G2" t="n">
-        <v>20034151</v>
+        <v>25291590.7</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.5600000000000001</v>
+        <v>21.27</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>토모큐브</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>475960</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>91800</v>
+        <v>34700</v>
       </c>
       <c r="F3" t="n">
-        <v>213.6877</v>
+        <v>913.8656999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>19616530.9</v>
-      </c>
-      <c r="H3" t="n">
-        <v>-12.98</v>
-      </c>
+        <v>31711139.3</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -546,29 +544,31 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>87700</v>
+        <v>35350</v>
       </c>
       <c r="F4" t="n">
-        <v>118.7012</v>
+        <v>566.7369</v>
       </c>
       <c r="G4" t="n">
-        <v>10410097.5</v>
-      </c>
-      <c r="H4" t="inlineStr"/>
+        <v>20034151</v>
+      </c>
+      <c r="H4" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,66 +578,68 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>12310</v>
+        <v>91800</v>
       </c>
       <c r="F5" t="n">
-        <v>845.6618999999999</v>
+        <v>213.6877</v>
       </c>
       <c r="G5" t="n">
-        <v>10410097.5</v>
-      </c>
-      <c r="H5" t="inlineStr"/>
+        <v>19616530.9</v>
+      </c>
+      <c r="H5" t="n">
+        <v>-12.98</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>295000</v>
+        <v>87700</v>
       </c>
       <c r="F6" t="n">
-        <v>71.24209999999999</v>
+        <v>118.7012</v>
       </c>
       <c r="G6" t="n">
-        <v>21016430.2</v>
+        <v>10410097.5</v>
       </c>
       <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -652,17 +654,17 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12870</v>
+        <v>12310</v>
       </c>
       <c r="F7" t="n">
-        <v>1632.9783</v>
+        <v>845.6618999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>21016430.2</v>
+        <v>10410097.5</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -674,12 +676,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -688,10 +690,10 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>161900</v>
+        <v>295000</v>
       </c>
       <c r="F8" t="n">
-        <v>129.8112</v>
+        <v>71.24209999999999</v>
       </c>
       <c r="G8" t="n">
         <v>21016430.2</v>
@@ -706,129 +708,129 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>38900</v>
+        <v>12870</v>
       </c>
       <c r="F9" t="n">
-        <v>506.8267</v>
+        <v>1632.9783</v>
       </c>
       <c r="G9" t="n">
-        <v>19715559.5</v>
-      </c>
-      <c r="H9" t="n">
-        <v>-14.24</v>
-      </c>
+        <v>21016430.2</v>
+      </c>
+      <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>13580</v>
+        <v>161900</v>
       </c>
       <c r="F10" t="n">
-        <v>1493.977</v>
+        <v>129.8112</v>
       </c>
       <c r="G10" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H10" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>21016430.2</v>
+      </c>
+      <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>126300</v>
+        <v>38900</v>
       </c>
       <c r="F11" t="n">
-        <v>165.13</v>
+        <v>506.8267</v>
       </c>
       <c r="G11" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H11" t="inlineStr"/>
+        <v>19715559.5</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-14.24</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>48800</v>
+        <v>13580</v>
       </c>
       <c r="F12" t="n">
-        <v>6.3754</v>
+        <v>1493.977</v>
       </c>
       <c r="G12" t="n">
-        <v>311119.6</v>
-      </c>
-      <c r="H12" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -838,31 +840,29 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>29050</v>
+        <v>126300</v>
       </c>
       <c r="F13" t="n">
-        <v>686</v>
+        <v>165.13</v>
       </c>
       <c r="G13" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H13" t="n">
-        <v>3.01</v>
-      </c>
+        <v>20855919.6</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -872,27 +872,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>275000</v>
+        <v>48800</v>
       </c>
       <c r="F14" t="n">
-        <v>3.4779</v>
+        <v>6.3754</v>
       </c>
       <c r="G14" t="n">
-        <v>956424.2</v>
+        <v>311119.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -904,29 +904,31 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>326500</v>
+        <v>29050</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8772</v>
+        <v>686</v>
       </c>
       <c r="G15" t="n">
-        <v>286419.6</v>
-      </c>
-      <c r="H15" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -936,12 +938,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -950,13 +952,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>36800</v>
+        <v>275000</v>
       </c>
       <c r="F16" t="n">
-        <v>14.2631</v>
+        <v>3.4779</v>
       </c>
       <c r="G16" t="n">
-        <v>524880.4</v>
+        <v>956424.2</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -968,12 +970,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -982,13 +984,13 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>536000</v>
+        <v>326500</v>
       </c>
       <c r="F17" t="n">
-        <v>2.9103</v>
+        <v>0.8772</v>
       </c>
       <c r="G17" t="n">
-        <v>1559919.6</v>
+        <v>286419.6</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1000,27 +1002,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>97600</v>
+        <v>36800</v>
       </c>
       <c r="F18" t="n">
-        <v>19.6877</v>
+        <v>14.2631</v>
       </c>
       <c r="G18" t="n">
-        <v>1921519.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1032,12 +1034,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1046,13 +1048,13 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>153900</v>
+        <v>536000</v>
       </c>
       <c r="F19" t="n">
-        <v>17.0321</v>
+        <v>2.9103</v>
       </c>
       <c r="G19" t="n">
-        <v>2621239.2</v>
+        <v>1559919.6</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1064,27 +1066,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1074000</v>
+        <v>97600</v>
       </c>
       <c r="F20" t="n">
-        <v>19.4189</v>
+        <v>19.6877</v>
       </c>
       <c r="G20" t="n">
-        <v>20855919.6</v>
+        <v>1921519.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1096,12 +1098,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1110,13 +1112,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>87400</v>
+        <v>153900</v>
       </c>
       <c r="F21" t="n">
-        <v>15.0802</v>
+        <v>17.0321</v>
       </c>
       <c r="G21" t="n">
-        <v>1318012.9</v>
+        <v>2621239.2</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1128,27 +1130,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>225000</v>
+        <v>1074000</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6929999999999999</v>
+        <v>19.4189</v>
       </c>
       <c r="G22" t="n">
-        <v>155919.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1160,12 +1162,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1174,13 +1176,13 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5810</v>
+        <v>87400</v>
       </c>
       <c r="F23" t="n">
-        <v>154.6591</v>
+        <v>15.0802</v>
       </c>
       <c r="G23" t="n">
-        <v>898569.6</v>
+        <v>1318012.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1192,27 +1194,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>30200</v>
+        <v>225000</v>
       </c>
       <c r="F24" t="n">
-        <v>109.4066</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>3304080.4</v>
+        <v>155919.6</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1224,27 +1226,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>207000</v>
+        <v>5810</v>
       </c>
       <c r="F25" t="n">
-        <v>1.2389</v>
+        <v>154.6591</v>
       </c>
       <c r="G25" t="n">
-        <v>256454.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1256,12 +1258,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1270,13 +1272,13 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>28150</v>
+        <v>30200</v>
       </c>
       <c r="F26" t="n">
-        <v>195.4454</v>
+        <v>109.4066</v>
       </c>
       <c r="G26" t="n">
-        <v>5501788.7</v>
+        <v>3304080.4</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1288,12 +1290,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1302,13 +1304,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>50500</v>
+        <v>207000</v>
       </c>
       <c r="F27" t="n">
-        <v>7.0115</v>
+        <v>1.2389</v>
       </c>
       <c r="G27" t="n">
-        <v>354080.4</v>
+        <v>256454.4</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1320,31 +1322,29 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>19430</v>
+        <v>28150</v>
       </c>
       <c r="F28" t="n">
-        <v>1071</v>
+        <v>195.4454</v>
       </c>
       <c r="G28" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0.78</v>
-      </c>
+        <v>5501788.7</v>
+      </c>
+      <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>21200</v>
+        <v>50500</v>
       </c>
       <c r="F29" t="n">
-        <v>1475.6547</v>
+        <v>7.0115</v>
       </c>
       <c r="G29" t="n">
-        <v>31283879.4</v>
+        <v>354080.4</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1386,29 +1386,31 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>21200</v>
+        <v>19430</v>
       </c>
       <c r="F30" t="n">
-        <v>154.5755</v>
+        <v>1071</v>
       </c>
       <c r="G30" t="n">
-        <v>3277001</v>
-      </c>
-      <c r="H30" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1418,12 +1420,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1432,13 +1434,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F31" t="n">
-        <v>98.6181</v>
+        <v>1475.6547</v>
       </c>
       <c r="G31" t="n">
-        <v>2731720.6</v>
+        <v>31283879.4</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1450,27 +1452,27 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>13960</v>
+        <v>21200</v>
       </c>
       <c r="F32" t="n">
-        <v>126.1646</v>
+        <v>154.5755</v>
       </c>
       <c r="G32" t="n">
-        <v>1761257.6</v>
+        <v>3277001</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1482,27 +1484,27 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>140200</v>
+        <v>27700</v>
       </c>
       <c r="F33" t="n">
-        <v>21.1375</v>
+        <v>98.6181</v>
       </c>
       <c r="G33" t="n">
-        <v>2963479.4</v>
+        <v>2731720.6</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1514,27 +1516,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6330</v>
+        <v>13960</v>
       </c>
       <c r="F34" t="n">
-        <v>13.226</v>
+        <v>126.1646</v>
       </c>
       <c r="G34" t="n">
-        <v>83720.39999999999</v>
+        <v>1761257.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1546,27 +1548,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>15750</v>
+        <v>140200</v>
       </c>
       <c r="F35" t="n">
-        <v>5.8146</v>
+        <v>21.1375</v>
       </c>
       <c r="G35" t="n">
-        <v>91580.39999999999</v>
+        <v>2963479.4</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1578,27 +1580,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>22500</v>
+        <v>6330</v>
       </c>
       <c r="F36" t="n">
-        <v>110.3946</v>
+        <v>13.226</v>
       </c>
       <c r="G36" t="n">
-        <v>2483879.4</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1610,31 +1612,29 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>256000</v>
+        <v>15750</v>
       </c>
       <c r="F37" t="n">
-        <v>113.8306</v>
+        <v>5.8146</v>
       </c>
       <c r="G37" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H37" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>91580.39999999999</v>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1644,27 +1644,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>75700</v>
+        <v>22500</v>
       </c>
       <c r="F38" t="n">
-        <v>275.5075</v>
+        <v>110.3946</v>
       </c>
       <c r="G38" t="n">
-        <v>20855919.6</v>
+        <v>2483879.4</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1676,29 +1676,31 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>131600</v>
+        <v>256000</v>
       </c>
       <c r="F39" t="n">
-        <v>2.4796</v>
+        <v>113.8306</v>
       </c>
       <c r="G39" t="n">
-        <v>326319.6</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1708,27 +1710,27 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>41150</v>
+        <v>75700</v>
       </c>
       <c r="F40" t="n">
-        <v>43.8267</v>
+        <v>275.5075</v>
       </c>
       <c r="G40" t="n">
-        <v>1803469.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H40" t="inlineStr"/>
     </row>
@@ -1740,12 +1742,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1754,13 +1756,13 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>147300</v>
+        <v>131600</v>
       </c>
       <c r="F41" t="n">
-        <v>2.3821</v>
+        <v>2.4796</v>
       </c>
       <c r="G41" t="n">
-        <v>350879.4</v>
+        <v>326319.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1772,27 +1774,27 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>36450</v>
+        <v>41150</v>
       </c>
       <c r="F42" t="n">
-        <v>76.7514</v>
+        <v>43.8267</v>
       </c>
       <c r="G42" t="n">
-        <v>2797588.9</v>
+        <v>1803469.6</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1804,12 +1806,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1818,13 +1820,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>119700</v>
+        <v>147300</v>
       </c>
       <c r="F43" t="n">
-        <v>30.2349</v>
+        <v>2.3821</v>
       </c>
       <c r="G43" t="n">
-        <v>3619119.6</v>
+        <v>350879.4</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1836,12 +1838,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1850,13 +1852,13 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>85400</v>
+        <v>36450</v>
       </c>
       <c r="F44" t="n">
-        <v>9.785500000000001</v>
+        <v>76.7514</v>
       </c>
       <c r="G44" t="n">
-        <v>835680.4</v>
+        <v>2797588.9</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1868,12 +1870,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1882,13 +1884,13 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>183500</v>
+        <v>119700</v>
       </c>
       <c r="F45" t="n">
-        <v>113.6562</v>
+        <v>30.2349</v>
       </c>
       <c r="G45" t="n">
-        <v>20855919.6</v>
+        <v>3619119.6</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1900,12 +1902,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1914,62 +1916,62 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>183500</v>
+        <v>85400</v>
       </c>
       <c r="F46" t="n">
-        <v>12.1963</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G46" t="n">
-        <v>2238023.8</v>
+        <v>835680.4</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1849000</v>
+        <v>183500</v>
       </c>
       <c r="F47" t="n">
-        <v>5.5521</v>
+        <v>113.6562</v>
       </c>
       <c r="G47" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1978,13 +1980,13 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>260000</v>
+        <v>183500</v>
       </c>
       <c r="F48" t="n">
-        <v>39.4838</v>
+        <v>12.1963</v>
       </c>
       <c r="G48" t="n">
-        <v>10265800.4</v>
+        <v>2238023.8</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
@@ -1996,24 +1998,24 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>24700</v>
+        <v>1849000</v>
       </c>
       <c r="F49" t="n">
-        <v>415.6194</v>
+        <v>5.5521</v>
       </c>
       <c r="G49" t="n">
         <v>10265800.4</v>
@@ -2028,76 +2030,76 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>48650</v>
+        <v>260000</v>
       </c>
       <c r="F50" t="n">
-        <v>422.0267</v>
+        <v>39.4838</v>
       </c>
       <c r="G50" t="n">
-        <v>20531600.8</v>
+        <v>10265800.4</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>87800</v>
+        <v>24700</v>
       </c>
       <c r="F51" t="n">
-        <v>115.4542</v>
+        <v>415.6194</v>
       </c>
       <c r="G51" t="n">
-        <v>10136875</v>
+        <v>10265800.4</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -2106,13 +2108,13 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>22750</v>
+        <v>48650</v>
       </c>
       <c r="F52" t="n">
-        <v>891.1538</v>
+        <v>422.0267</v>
       </c>
       <c r="G52" t="n">
-        <v>20273749.9</v>
+        <v>20531600.8</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
@@ -2124,31 +2126,29 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>33150</v>
+        <v>87800</v>
       </c>
       <c r="F53" t="n">
-        <v>569</v>
+        <v>115.4542</v>
       </c>
       <c r="G53" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H53" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2158,27 +2158,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>254500</v>
+        <v>22750</v>
       </c>
       <c r="F54" t="n">
-        <v>39.8306</v>
+        <v>891.1538</v>
       </c>
       <c r="G54" t="n">
-        <v>10136875</v>
+        <v>20273749.9</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2190,12 +2190,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -2204,83 +2204,83 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>79400</v>
+        <v>33150</v>
       </c>
       <c r="F55" t="n">
-        <v>246</v>
+        <v>569</v>
       </c>
       <c r="G55" t="n">
-        <v>19532400</v>
+        <v>18862350</v>
       </c>
       <c r="H55" t="n">
-        <v>-8</v>
+        <v>-8.68</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>14780</v>
+        <v>254500</v>
       </c>
       <c r="F56" t="n">
-        <v>1338</v>
+        <v>39.8306</v>
       </c>
       <c r="G56" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H56" t="n">
-        <v>33.89</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>195800</v>
+        <v>79400</v>
       </c>
       <c r="F57" t="n">
-        <v>101.9921</v>
+        <v>246</v>
       </c>
       <c r="G57" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H57" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H57" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2290,29 +2290,31 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>14600</v>
+        <v>14780</v>
       </c>
       <c r="F58" t="n">
-        <v>1367.8125</v>
+        <v>1338</v>
       </c>
       <c r="G58" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H58" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H58" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2322,27 +2324,27 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>36300</v>
+        <v>195800</v>
       </c>
       <c r="F59" t="n">
-        <v>275.0697</v>
+        <v>101.9921</v>
       </c>
       <c r="G59" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H59" t="inlineStr"/>
     </row>
@@ -2354,127 +2356,125 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>159300</v>
+        <v>14600</v>
       </c>
       <c r="F60" t="n">
-        <v>62.6807</v>
+        <v>1367.8125</v>
       </c>
       <c r="G60" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>147200</v>
+        <v>36300</v>
       </c>
       <c r="F61" t="n">
-        <v>67</v>
+        <v>275.0697</v>
       </c>
       <c r="G61" t="n">
-        <v>9862400</v>
+        <v>9985031</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>14540</v>
+        <v>159300</v>
       </c>
       <c r="F62" t="n">
-        <v>983</v>
+        <v>62.6807</v>
       </c>
       <c r="G62" t="n">
-        <v>14292820</v>
+        <v>9985031</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>113400</v>
+        <v>147200</v>
       </c>
       <c r="F63" t="n">
-        <v>167</v>
+        <v>67</v>
       </c>
       <c r="G63" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H63" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>9862400</v>
+      </c>
+      <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2484,27 +2484,27 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>24350</v>
+        <v>14540</v>
       </c>
       <c r="F64" t="n">
-        <v>407</v>
+        <v>983</v>
       </c>
       <c r="G64" t="n">
-        <v>9910450</v>
+        <v>14292820</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2516,12 +2516,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2530,16 +2530,16 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>44100</v>
+        <v>113400</v>
       </c>
       <c r="F65" t="n">
-        <v>488</v>
+        <v>167</v>
       </c>
       <c r="G65" t="n">
-        <v>21520800</v>
+        <v>18937800</v>
       </c>
       <c r="H65" t="n">
-        <v>4.26</v>
+        <v>-7.88</v>
       </c>
     </row>
     <row r="66">
@@ -2550,108 +2550,110 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>165700</v>
+        <v>24350</v>
       </c>
       <c r="F66" t="n">
-        <v>120</v>
+        <v>407</v>
       </c>
       <c r="G66" t="n">
-        <v>19884000</v>
+        <v>9910450</v>
       </c>
       <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>28950</v>
+        <v>44100</v>
       </c>
       <c r="F67" t="n">
-        <v>353</v>
+        <v>488</v>
       </c>
       <c r="G67" t="n">
-        <v>10219350</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H67" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1853000</v>
+        <v>165700</v>
       </c>
       <c r="F68" t="n">
-        <v>11</v>
+        <v>120</v>
       </c>
       <c r="G68" t="n">
-        <v>20383000</v>
+        <v>19884000</v>
       </c>
       <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -2660,13 +2662,13 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>269000</v>
+        <v>28950</v>
       </c>
       <c r="F69" t="n">
-        <v>76</v>
+        <v>353</v>
       </c>
       <c r="G69" t="n">
-        <v>20444000</v>
+        <v>10219350</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
@@ -2678,27 +2680,27 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>106300</v>
+        <v>1853000</v>
       </c>
       <c r="F70" t="n">
-        <v>194</v>
+        <v>11</v>
       </c>
       <c r="G70" t="n">
-        <v>20622200</v>
+        <v>20383000</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2710,91 +2712,91 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>123100</v>
+        <v>269000</v>
       </c>
       <c r="F71" t="n">
-        <v>167</v>
+        <v>76</v>
       </c>
       <c r="G71" t="n">
-        <v>20557700</v>
+        <v>20444000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>1856000</v>
+        <v>106300</v>
       </c>
       <c r="F72" t="n">
-        <v>23</v>
+        <v>194</v>
       </c>
       <c r="G72" t="n">
-        <v>42688000</v>
+        <v>20622200</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>49000</v>
+        <v>123100</v>
       </c>
       <c r="F73" t="n">
         <v>167</v>
       </c>
       <c r="G73" t="n">
-        <v>8183000</v>
+        <v>20557700</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
@@ -2806,12 +2808,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -2820,13 +2822,13 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>13340</v>
+        <v>1856000</v>
       </c>
       <c r="F74" t="n">
-        <v>236</v>
+        <v>23</v>
       </c>
       <c r="G74" t="n">
-        <v>3148240</v>
+        <v>42688000</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2838,12 +2840,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2852,13 +2854,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>29800</v>
+        <v>49000</v>
       </c>
       <c r="F75" t="n">
-        <v>66</v>
+        <v>167</v>
       </c>
       <c r="G75" t="n">
-        <v>1966800</v>
+        <v>8183000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2870,12 +2872,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2884,13 +2886,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>269500</v>
+        <v>13340</v>
       </c>
       <c r="F76" t="n">
-        <v>118</v>
+        <v>236</v>
       </c>
       <c r="G76" t="n">
-        <v>31801000</v>
+        <v>3148240</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2902,12 +2904,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2916,13 +2918,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>330000</v>
+        <v>29800</v>
       </c>
       <c r="F77" t="n">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="G77" t="n">
-        <v>7920000</v>
+        <v>1966800</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2934,27 +2936,27 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>35550</v>
+        <v>269500</v>
       </c>
       <c r="F78" t="n">
-        <v>581</v>
+        <v>118</v>
       </c>
       <c r="G78" t="n">
-        <v>20654550</v>
+        <v>31801000</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2966,12 +2968,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2980,13 +2982,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>574000</v>
+        <v>330000</v>
       </c>
       <c r="F79" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G79" t="n">
-        <v>12628000</v>
+        <v>7920000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -2998,27 +3000,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>165900</v>
+        <v>35550</v>
       </c>
       <c r="F80" t="n">
-        <v>24</v>
+        <v>581</v>
       </c>
       <c r="G80" t="n">
-        <v>3981600</v>
+        <v>20654550</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3030,27 +3032,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>91300</v>
+        <v>574000</v>
       </c>
       <c r="F81" t="n">
-        <v>45</v>
+        <v>22</v>
       </c>
       <c r="G81" t="n">
-        <v>4108500</v>
+        <v>12628000</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3062,27 +3064,27 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>224500</v>
+        <v>165900</v>
       </c>
       <c r="F82" t="n">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="G82" t="n">
-        <v>20654000</v>
+        <v>3981600</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3094,27 +3096,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6010</v>
+        <v>91300</v>
       </c>
       <c r="F83" t="n">
-        <v>3435</v>
+        <v>45</v>
       </c>
       <c r="G83" t="n">
-        <v>20644350</v>
+        <v>4108500</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3126,27 +3128,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>25800</v>
+        <v>224500</v>
       </c>
       <c r="F84" t="n">
-        <v>351</v>
+        <v>92</v>
       </c>
       <c r="G84" t="n">
-        <v>9055800</v>
+        <v>20654000</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3158,12 +3160,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3172,13 +3174,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>49150</v>
+        <v>6010</v>
       </c>
       <c r="F85" t="n">
-        <v>420</v>
+        <v>3435</v>
       </c>
       <c r="G85" t="n">
-        <v>20643000</v>
+        <v>20644350</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3190,27 +3192,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>19280</v>
+        <v>25800</v>
       </c>
       <c r="F86" t="n">
-        <v>1071</v>
+        <v>351</v>
       </c>
       <c r="G86" t="n">
-        <v>20648880</v>
+        <v>9055800</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3222,27 +3224,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>19740</v>
+        <v>49150</v>
       </c>
       <c r="F87" t="n">
-        <v>523</v>
+        <v>420</v>
       </c>
       <c r="G87" t="n">
-        <v>10324020</v>
+        <v>20643000</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3254,12 +3256,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3268,13 +3270,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>25150</v>
+        <v>19280</v>
       </c>
       <c r="F88" t="n">
-        <v>821</v>
+        <v>1071</v>
       </c>
       <c r="G88" t="n">
-        <v>20648150</v>
+        <v>20648880</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3286,12 +3288,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3300,13 +3302,13 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>153500</v>
+        <v>19740</v>
       </c>
       <c r="F89" t="n">
-        <v>24</v>
+        <v>523</v>
       </c>
       <c r="G89" t="n">
-        <v>3684000</v>
+        <v>10324020</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3318,12 +3320,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3332,13 +3334,13 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6240</v>
+        <v>25150</v>
       </c>
       <c r="F90" t="n">
-        <v>3308</v>
+        <v>821</v>
       </c>
       <c r="G90" t="n">
-        <v>20641920</v>
+        <v>20648150</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3350,27 +3352,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>15520</v>
+        <v>153500</v>
       </c>
       <c r="F91" t="n">
-        <v>1330</v>
+        <v>24</v>
       </c>
       <c r="G91" t="n">
-        <v>20641600</v>
+        <v>3684000</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3382,27 +3384,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>24200</v>
+        <v>6240</v>
       </c>
       <c r="F92" t="n">
-        <v>210</v>
+        <v>3308</v>
       </c>
       <c r="G92" t="n">
-        <v>5082000</v>
+        <v>20641920</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3414,12 +3416,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3428,13 +3430,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>36300</v>
+        <v>15520</v>
       </c>
       <c r="F93" t="n">
-        <v>569</v>
+        <v>1330</v>
       </c>
       <c r="G93" t="n">
-        <v>20654700</v>
+        <v>20641600</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3446,12 +3448,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -3460,13 +3462,13 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>279500</v>
+        <v>24200</v>
       </c>
       <c r="F94" t="n">
-        <v>43</v>
+        <v>210</v>
       </c>
       <c r="G94" t="n">
-        <v>12018500</v>
+        <v>5082000</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3478,27 +3480,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>132600</v>
+        <v>36300</v>
       </c>
       <c r="F95" t="n">
-        <v>90</v>
+        <v>569</v>
       </c>
       <c r="G95" t="n">
-        <v>11934000</v>
+        <v>20654700</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3510,12 +3512,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3524,13 +3526,13 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>44600</v>
+        <v>279500</v>
       </c>
       <c r="F96" t="n">
-        <v>139</v>
+        <v>43</v>
       </c>
       <c r="G96" t="n">
-        <v>6199400</v>
+        <v>12018500</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3542,12 +3544,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3556,13 +3558,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>147100</v>
+        <v>132600</v>
       </c>
       <c r="F97" t="n">
-        <v>6</v>
+        <v>90</v>
       </c>
       <c r="G97" t="n">
-        <v>882600</v>
+        <v>11934000</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3574,12 +3576,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3588,13 +3590,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>33500</v>
+        <v>44600</v>
       </c>
       <c r="F98" t="n">
-        <v>8</v>
+        <v>139</v>
       </c>
       <c r="G98" t="n">
-        <v>268000</v>
+        <v>6199400</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3606,12 +3608,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3620,13 +3622,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>143100</v>
+        <v>147100</v>
       </c>
       <c r="F99" t="n">
-        <v>95</v>
+        <v>6</v>
       </c>
       <c r="G99" t="n">
-        <v>13594500</v>
+        <v>882600</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3638,12 +3640,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3652,13 +3654,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>83800</v>
+        <v>33500</v>
       </c>
       <c r="F100" t="n">
-        <v>106</v>
+        <v>8</v>
       </c>
       <c r="G100" t="n">
-        <v>8882800</v>
+        <v>268000</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3670,27 +3672,27 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>42300</v>
+        <v>143100</v>
       </c>
       <c r="F101" t="n">
-        <v>488</v>
+        <v>95</v>
       </c>
       <c r="G101" t="n">
-        <v>20642400</v>
+        <v>13594500</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3702,12 +3704,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3716,30 +3718,30 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>81200</v>
+        <v>83800</v>
       </c>
       <c r="F102" t="n">
-        <v>135</v>
+        <v>106</v>
       </c>
       <c r="G102" t="n">
-        <v>10962000</v>
+        <v>8882800</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -3748,30 +3750,30 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>78600</v>
+        <v>42300</v>
       </c>
       <c r="F103" t="n">
-        <v>389</v>
+        <v>488</v>
       </c>
       <c r="G103" t="n">
-        <v>30575400</v>
+        <v>20642400</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -3780,30 +3782,30 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>92500</v>
+        <v>81200</v>
       </c>
       <c r="F104" t="n">
-        <v>106</v>
+        <v>135</v>
       </c>
       <c r="G104" t="n">
-        <v>9805000</v>
+        <v>10962000</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -3812,115 +3814,111 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>25550</v>
+        <v>78600</v>
       </c>
       <c r="F105" t="n">
-        <v>1151</v>
+        <v>389</v>
       </c>
       <c r="G105" t="n">
-        <v>29408050</v>
+        <v>30575400</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>21800</v>
+        <v>92500</v>
       </c>
       <c r="F106" t="n">
-        <v>832</v>
+        <v>106</v>
       </c>
       <c r="G106" t="n">
-        <v>18137600</v>
+        <v>9805000</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>32250</v>
+        <v>25550</v>
       </c>
       <c r="F107" t="n">
-        <v>878</v>
+        <v>1151</v>
       </c>
       <c r="G107" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H107" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>29408050</v>
+      </c>
+      <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>105800</v>
+        <v>21800</v>
       </c>
       <c r="F108" t="n">
-        <v>332</v>
+        <v>832</v>
       </c>
       <c r="G108" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H108" t="n">
-        <v>17.17</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -3930,12 +3928,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -3944,16 +3942,16 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>33750</v>
+        <v>32250</v>
       </c>
       <c r="F109" t="n">
-        <v>791</v>
+        <v>878</v>
       </c>
       <c r="G109" t="n">
-        <v>26696250</v>
+        <v>28315500</v>
       </c>
       <c r="H109" t="n">
-        <v>0.29</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="110">
@@ -3964,44 +3962,46 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>86300</v>
+        <v>105800</v>
       </c>
       <c r="F110" t="n">
-        <v>352</v>
+        <v>332</v>
       </c>
       <c r="G110" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H110" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H110" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4010,47 +4010,47 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>21000</v>
+        <v>33750</v>
       </c>
       <c r="F111" t="n">
-        <v>1517</v>
+        <v>791</v>
       </c>
       <c r="G111" t="n">
-        <v>31857000</v>
+        <v>26696250</v>
       </c>
       <c r="H111" t="n">
-        <v>3.96</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>21900</v>
+        <v>86300</v>
       </c>
       <c r="F112" t="n">
-        <v>906</v>
+        <v>352</v>
       </c>
       <c r="G112" t="n">
-        <v>19841400</v>
+        <v>30377600</v>
       </c>
       <c r="H112" t="inlineStr"/>
     </row>
@@ -4062,34 +4062,36 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>135300</v>
+        <v>21000</v>
       </c>
       <c r="F113" t="n">
-        <v>226</v>
+        <v>1517</v>
       </c>
       <c r="G113" t="n">
-        <v>30577800</v>
-      </c>
-      <c r="H113" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4104,53 +4106,51 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>22250</v>
+        <v>21900</v>
       </c>
       <c r="F114" t="n">
-        <v>1399</v>
+        <v>906</v>
       </c>
       <c r="G114" t="n">
-        <v>31127750</v>
+        <v>19841400</v>
       </c>
       <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>33500</v>
+        <v>135300</v>
       </c>
       <c r="F115" t="n">
-        <v>848</v>
+        <v>226</v>
       </c>
       <c r="G115" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H115" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>30577800</v>
+      </c>
+      <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4160,78 +4160,78 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>300000</v>
+        <v>22250</v>
       </c>
       <c r="F116" t="n">
-        <v>104</v>
+        <v>1399</v>
       </c>
       <c r="G116" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H116" t="n">
-        <v>20.95</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>28200</v>
+        <v>33500</v>
       </c>
       <c r="F117" t="n">
-        <v>1105</v>
+        <v>848</v>
       </c>
       <c r="G117" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H117" t="inlineStr"/>
+        <v>28408000</v>
+      </c>
+      <c r="H117" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4240,16 +4240,16 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>398000</v>
+        <v>300000</v>
       </c>
       <c r="F118" t="n">
-        <v>72</v>
+        <v>104</v>
       </c>
       <c r="G118" t="n">
-        <v>28656000</v>
+        <v>31200000</v>
       </c>
       <c r="H118" t="n">
-        <v>-6.88</v>
+        <v>20.95</v>
       </c>
     </row>
     <row r="119">
@@ -4260,31 +4260,29 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5620</v>
+        <v>28200</v>
       </c>
       <c r="F119" t="n">
-        <v>4707</v>
+        <v>1105</v>
       </c>
       <c r="G119" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H119" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4294,91 +4292,95 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>126900</v>
+        <v>398000</v>
       </c>
       <c r="F120" t="n">
-        <v>246</v>
+        <v>72</v>
       </c>
       <c r="G120" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H120" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H120" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1671000</v>
+        <v>5620</v>
       </c>
       <c r="F121" t="n">
-        <v>44</v>
+        <v>4707</v>
       </c>
       <c r="G121" t="n">
-        <v>73524000</v>
-      </c>
-      <c r="H121" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H121" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>50600</v>
+        <v>126900</v>
       </c>
       <c r="F122" t="n">
-        <v>186</v>
+        <v>246</v>
       </c>
       <c r="G122" t="n">
-        <v>9411600</v>
+        <v>31217400</v>
       </c>
       <c r="H122" t="inlineStr"/>
     </row>
@@ -4390,27 +4392,27 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>11720</v>
+        <v>1671000</v>
       </c>
       <c r="F123" t="n">
-        <v>665</v>
+        <v>44</v>
       </c>
       <c r="G123" t="n">
-        <v>7793800</v>
+        <v>73524000</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4422,12 +4424,12 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -4436,13 +4438,13 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>414000</v>
+        <v>50600</v>
       </c>
       <c r="F124" t="n">
-        <v>26</v>
+        <v>186</v>
       </c>
       <c r="G124" t="n">
-        <v>10764000</v>
+        <v>9411600</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4454,27 +4456,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>257000</v>
+        <v>11720</v>
       </c>
       <c r="F125" t="n">
-        <v>239</v>
+        <v>665</v>
       </c>
       <c r="G125" t="n">
-        <v>61423000</v>
+        <v>7793800</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4486,12 +4488,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4500,13 +4502,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>33900</v>
+        <v>414000</v>
       </c>
       <c r="F126" t="n">
-        <v>292</v>
+        <v>26</v>
       </c>
       <c r="G126" t="n">
-        <v>9898800</v>
+        <v>10764000</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4518,27 +4520,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>515000</v>
+        <v>257000</v>
       </c>
       <c r="F127" t="n">
-        <v>17</v>
+        <v>239</v>
       </c>
       <c r="G127" t="n">
-        <v>8755000</v>
+        <v>61423000</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4550,12 +4552,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4564,13 +4566,13 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>141200</v>
+        <v>33900</v>
       </c>
       <c r="F128" t="n">
-        <v>81</v>
+        <v>292</v>
       </c>
       <c r="G128" t="n">
-        <v>11437200</v>
+        <v>9898800</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4582,12 +4584,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4596,13 +4598,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6320</v>
+        <v>515000</v>
       </c>
       <c r="F129" t="n">
-        <v>1396</v>
+        <v>17</v>
       </c>
       <c r="G129" t="n">
-        <v>8822720</v>
+        <v>8755000</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4614,27 +4616,27 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>90300</v>
+        <v>141200</v>
       </c>
       <c r="F130" t="n">
-        <v>332</v>
+        <v>81</v>
       </c>
       <c r="G130" t="n">
-        <v>29979600</v>
+        <v>11437200</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4646,31 +4648,29 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>163100</v>
+        <v>6320</v>
       </c>
       <c r="F131" t="n">
-        <v>119</v>
+        <v>1396</v>
       </c>
       <c r="G131" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H131" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>8822720</v>
+      </c>
+      <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -4680,27 +4680,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>37900</v>
+        <v>90300</v>
       </c>
       <c r="F132" t="n">
-        <v>163</v>
+        <v>332</v>
       </c>
       <c r="G132" t="n">
-        <v>6177700</v>
+        <v>29979600</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4712,29 +4712,31 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>19990</v>
+        <v>163100</v>
       </c>
       <c r="F133" t="n">
-        <v>615</v>
+        <v>119</v>
       </c>
       <c r="G133" t="n">
-        <v>12293850</v>
-      </c>
-      <c r="H133" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H133" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4744,12 +4746,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -4758,13 +4760,13 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>35100</v>
+        <v>37900</v>
       </c>
       <c r="F134" t="n">
-        <v>320</v>
+        <v>163</v>
       </c>
       <c r="G134" t="n">
-        <v>11232000</v>
+        <v>6177700</v>
       </c>
       <c r="H134" t="inlineStr"/>
     </row>
@@ -4776,12 +4778,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4790,13 +4792,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>286000</v>
+        <v>19990</v>
       </c>
       <c r="F135" t="n">
-        <v>20</v>
+        <v>615</v>
       </c>
       <c r="G135" t="n">
-        <v>5720000</v>
+        <v>12293850</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4808,31 +4810,29 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>416000</v>
+        <v>35100</v>
       </c>
       <c r="F136" t="n">
-        <v>51</v>
+        <v>320</v>
       </c>
       <c r="G136" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H136" t="n">
-        <v>5.85</v>
-      </c>
+        <v>11232000</v>
+      </c>
+      <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -4842,12 +4842,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>49450</v>
+        <v>286000</v>
       </c>
       <c r="F137" t="n">
-        <v>153</v>
+        <v>20</v>
       </c>
       <c r="G137" t="n">
-        <v>7565850</v>
+        <v>5720000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -4874,29 +4874,31 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>138000</v>
+        <v>416000</v>
       </c>
       <c r="F138" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="G138" t="n">
-        <v>9384000</v>
-      </c>
-      <c r="H138" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H138" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4906,12 +4908,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -4920,13 +4922,13 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>31950</v>
+        <v>49450</v>
       </c>
       <c r="F139" t="n">
-        <v>339</v>
+        <v>153</v>
       </c>
       <c r="G139" t="n">
-        <v>10831050</v>
+        <v>7565850</v>
       </c>
       <c r="H139" t="inlineStr"/>
     </row>
@@ -4938,12 +4940,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4952,81 +4954,79 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>124800</v>
+        <v>138000</v>
       </c>
       <c r="F140" t="n">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="G140" t="n">
-        <v>9734400</v>
+        <v>9384000</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>10800</v>
+        <v>31950</v>
       </c>
       <c r="F141" t="n">
-        <v>1892</v>
+        <v>339</v>
       </c>
       <c r="G141" t="n">
-        <v>20433600</v>
+        <v>10831050</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>11880</v>
+        <v>124800</v>
       </c>
       <c r="F142" t="n">
-        <v>1474</v>
+        <v>78</v>
       </c>
       <c r="G142" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H142" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>9734400</v>
+      </c>
+      <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5036,12 +5036,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -5050,13 +5050,13 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>20200</v>
+        <v>10800</v>
       </c>
       <c r="F143" t="n">
-        <v>1517</v>
+        <v>1892</v>
       </c>
       <c r="G143" t="n">
-        <v>30643400</v>
+        <v>20433600</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5068,29 +5068,31 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>102200</v>
+        <v>11880</v>
       </c>
       <c r="F144" t="n">
-        <v>200</v>
+        <v>1474</v>
       </c>
       <c r="G144" t="n">
-        <v>20440000</v>
-      </c>
-      <c r="H144" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H144" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5100,31 +5102,29 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>23450</v>
+        <v>20200</v>
       </c>
       <c r="F145" t="n">
-        <v>762</v>
+        <v>1517</v>
       </c>
       <c r="G145" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>30643400</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5134,31 +5134,29 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>22050</v>
+        <v>102200</v>
       </c>
       <c r="F146" t="n">
-        <v>875</v>
+        <v>200</v>
       </c>
       <c r="G146" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H146" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5168,29 +5166,31 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>32550</v>
+        <v>23450</v>
       </c>
       <c r="F147" t="n">
-        <v>628</v>
+        <v>762</v>
       </c>
       <c r="G147" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+        <v>17868900</v>
+      </c>
+      <c r="H147" t="n">
+        <v>-10.67</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5214,32 +5214,32 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>99700</v>
+        <v>22050</v>
       </c>
       <c r="F148" t="n">
-        <v>180</v>
+        <v>875</v>
       </c>
       <c r="G148" t="n">
-        <v>17946000</v>
+        <v>19293750</v>
       </c>
       <c r="H148" t="n">
-        <v>-10.1</v>
+        <v>-3.5</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -5248,47 +5248,49 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>1662000</v>
+        <v>32550</v>
       </c>
       <c r="F149" t="n">
-        <v>150</v>
+        <v>628</v>
       </c>
       <c r="G149" t="n">
-        <v>249300000</v>
+        <v>20441400</v>
       </c>
       <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>49700</v>
+        <v>99700</v>
       </c>
       <c r="F150" t="n">
-        <v>402</v>
+        <v>180</v>
       </c>
       <c r="G150" t="n">
-        <v>19979400</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H150" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5298,12 +5300,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -5312,13 +5314,13 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>435000</v>
+        <v>1662000</v>
       </c>
       <c r="F151" t="n">
-        <v>46</v>
+        <v>150</v>
       </c>
       <c r="G151" t="n">
-        <v>20010000</v>
+        <v>249300000</v>
       </c>
       <c r="H151" t="inlineStr"/>
     </row>
@@ -5330,12 +5332,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5344,13 +5346,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>268500</v>
+        <v>49700</v>
       </c>
       <c r="F152" t="n">
-        <v>931</v>
+        <v>402</v>
       </c>
       <c r="G152" t="n">
-        <v>249973500</v>
+        <v>19979400</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5362,12 +5364,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5376,13 +5378,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>13570</v>
+        <v>435000</v>
       </c>
       <c r="F153" t="n">
-        <v>1474</v>
+        <v>46</v>
       </c>
       <c r="G153" t="n">
-        <v>20002180</v>
+        <v>20010000</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5394,12 +5396,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5408,13 +5410,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>343500</v>
+        <v>268500</v>
       </c>
       <c r="F154" t="n">
-        <v>87</v>
+        <v>931</v>
       </c>
       <c r="G154" t="n">
-        <v>29884500</v>
+        <v>249973500</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5426,12 +5428,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5440,13 +5442,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>34150</v>
+        <v>13570</v>
       </c>
       <c r="F155" t="n">
-        <v>586</v>
+        <v>1474</v>
       </c>
       <c r="G155" t="n">
-        <v>20011900</v>
+        <v>20002180</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5458,12 +5460,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5472,13 +5474,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>488000</v>
+        <v>343500</v>
       </c>
       <c r="F156" t="n">
-        <v>41</v>
+        <v>87</v>
       </c>
       <c r="G156" t="n">
-        <v>20008000</v>
+        <v>29884500</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5490,12 +5492,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5504,13 +5506,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>153600</v>
+        <v>34150</v>
       </c>
       <c r="F157" t="n">
-        <v>130</v>
+        <v>586</v>
       </c>
       <c r="G157" t="n">
-        <v>19968000</v>
+        <v>20011900</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5522,12 +5524,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5536,13 +5538,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>99800</v>
+        <v>488000</v>
       </c>
       <c r="F158" t="n">
-        <v>200</v>
+        <v>41</v>
       </c>
       <c r="G158" t="n">
-        <v>19960000</v>
+        <v>20008000</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5554,12 +5556,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5568,13 +5570,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>6040</v>
+        <v>153600</v>
       </c>
       <c r="F159" t="n">
-        <v>3311</v>
+        <v>130</v>
       </c>
       <c r="G159" t="n">
-        <v>19998440</v>
+        <v>19968000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5586,12 +5588,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5600,13 +5602,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>26250</v>
+        <v>99800</v>
       </c>
       <c r="F160" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G160" t="n">
-        <v>20002500</v>
+        <v>19960000</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5618,12 +5620,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5632,13 +5634,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>22850</v>
+        <v>6040</v>
       </c>
       <c r="F161" t="n">
-        <v>875</v>
+        <v>3311</v>
       </c>
       <c r="G161" t="n">
-        <v>19993750</v>
+        <v>19998440</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5650,12 +5652,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5664,13 +5666,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>168500</v>
+        <v>26250</v>
       </c>
       <c r="F162" t="n">
-        <v>119</v>
+        <v>762</v>
       </c>
       <c r="G162" t="n">
-        <v>20051500</v>
+        <v>20002500</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5682,12 +5684,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5714,12 +5716,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5728,13 +5730,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>37900</v>
+        <v>168500</v>
       </c>
       <c r="F164" t="n">
-        <v>528</v>
+        <v>119</v>
       </c>
       <c r="G164" t="n">
-        <v>20011200</v>
+        <v>20051500</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -5746,12 +5748,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5760,13 +5762,13 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>239000</v>
+        <v>22850</v>
       </c>
       <c r="F165" t="n">
-        <v>84</v>
+        <v>875</v>
       </c>
       <c r="G165" t="n">
-        <v>20076000</v>
+        <v>19993750</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
@@ -5778,12 +5780,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5792,13 +5794,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>298000</v>
+        <v>37900</v>
       </c>
       <c r="F166" t="n">
-        <v>117</v>
+        <v>528</v>
       </c>
       <c r="G166" t="n">
-        <v>34866000</v>
+        <v>20011200</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
@@ -5810,12 +5812,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5824,13 +5826,13 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>393000</v>
+        <v>239000</v>
       </c>
       <c r="F167" t="n">
-        <v>51</v>
+        <v>84</v>
       </c>
       <c r="G167" t="n">
-        <v>20043000</v>
+        <v>20076000</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
@@ -5842,12 +5844,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5856,13 +5858,13 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>110900</v>
+        <v>298000</v>
       </c>
       <c r="F168" t="n">
-        <v>180</v>
+        <v>117</v>
       </c>
       <c r="G168" t="n">
-        <v>19962000</v>
+        <v>34866000</v>
       </c>
       <c r="H168" t="inlineStr"/>
     </row>
@@ -5874,12 +5876,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5888,13 +5890,13 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>44500</v>
+        <v>393000</v>
       </c>
       <c r="F169" t="n">
-        <v>449</v>
+        <v>51</v>
       </c>
       <c r="G169" t="n">
-        <v>19980500</v>
+        <v>20043000</v>
       </c>
       <c r="H169" t="inlineStr"/>
     </row>
@@ -5906,12 +5908,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5920,13 +5922,13 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>135000</v>
+        <v>110900</v>
       </c>
       <c r="F170" t="n">
-        <v>148</v>
+        <v>180</v>
       </c>
       <c r="G170" t="n">
-        <v>19980000</v>
+        <v>19962000</v>
       </c>
       <c r="H170" t="inlineStr"/>
     </row>
@@ -5938,12 +5940,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5952,13 +5954,13 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>33750</v>
+        <v>44500</v>
       </c>
       <c r="F171" t="n">
-        <v>593</v>
+        <v>449</v>
       </c>
       <c r="G171" t="n">
-        <v>20013750</v>
+        <v>19980500</v>
       </c>
       <c r="H171" t="inlineStr"/>
     </row>
@@ -5970,29 +5972,93 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F172" t="n">
+        <v>148</v>
+      </c>
+      <c r="G172" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F173" t="n">
+        <v>593</v>
+      </c>
+      <c r="G173" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C172" t="inlineStr">
+      <c r="C174" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D172" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E172" t="n">
+      <c r="E174" t="n">
         <v>124600</v>
       </c>
-      <c r="F172" t="n">
+      <c r="F174" t="n">
         <v>161</v>
       </c>
-      <c r="G172" t="n">
+      <c r="G174" t="n">
         <v>20060600</v>
       </c>
-      <c r="H172" t="inlineStr"/>
+      <c r="H174" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H174"/>
+  <dimension ref="A1:H175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,36 +473,34 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>91800</v>
+        <v>125800</v>
       </c>
       <c r="F2" t="n">
-        <v>275.5075</v>
+        <v>171.563</v>
       </c>
       <c r="G2" t="n">
-        <v>25291590.7</v>
-      </c>
-      <c r="H2" t="n">
-        <v>21.27</v>
-      </c>
+        <v>21582624.3</v>
+      </c>
+      <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -512,63 +510,63 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>토모큐브</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>475960</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>34700</v>
+        <v>91800</v>
       </c>
       <c r="F3" t="n">
-        <v>913.8656999999999</v>
+        <v>275.5075</v>
       </c>
       <c r="G3" t="n">
-        <v>31711139.3</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>25291590.7</v>
+      </c>
+      <c r="H3" t="n">
+        <v>21.27</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>토모큐브</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>475960</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>35350</v>
+        <v>34750</v>
       </c>
       <c r="F4" t="n">
-        <v>566.7369</v>
+        <v>912.5508</v>
       </c>
       <c r="G4" t="n">
-        <v>20034151</v>
-      </c>
-      <c r="H4" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
+        <v>31711139.3</v>
+      </c>
+      <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -578,12 +576,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -592,16 +590,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>91800</v>
+        <v>35350</v>
       </c>
       <c r="F5" t="n">
-        <v>213.6877</v>
+        <v>566.7369</v>
       </c>
       <c r="G5" t="n">
-        <v>19616530.9</v>
+        <v>20034151</v>
       </c>
       <c r="H5" t="n">
-        <v>-12.98</v>
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="6">
@@ -612,29 +610,31 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>87700</v>
+        <v>91800</v>
       </c>
       <c r="F6" t="n">
-        <v>118.7012</v>
+        <v>213.6877</v>
       </c>
       <c r="G6" t="n">
-        <v>10410097.5</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>19616530.9</v>
+      </c>
+      <c r="H6" t="n">
+        <v>-12.98</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,10 +658,10 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>12310</v>
+        <v>87700</v>
       </c>
       <c r="F7" t="n">
-        <v>845.6618999999999</v>
+        <v>118.7012</v>
       </c>
       <c r="G7" t="n">
         <v>10410097.5</v>
@@ -671,32 +671,32 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>295000</v>
+        <v>12310</v>
       </c>
       <c r="F8" t="n">
-        <v>71.24209999999999</v>
+        <v>845.6618999999999</v>
       </c>
       <c r="G8" t="n">
-        <v>21016430.2</v>
+        <v>10410097.5</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -708,12 +708,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -722,10 +722,10 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>12870</v>
+        <v>295000</v>
       </c>
       <c r="F9" t="n">
-        <v>1632.9783</v>
+        <v>71.24209999999999</v>
       </c>
       <c r="G9" t="n">
         <v>21016430.2</v>
@@ -740,12 +740,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -754,10 +754,10 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>161900</v>
+        <v>12870</v>
       </c>
       <c r="F10" t="n">
-        <v>129.8112</v>
+        <v>1632.9783</v>
       </c>
       <c r="G10" t="n">
         <v>21016430.2</v>
@@ -772,46 +772,44 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>38900</v>
+        <v>161900</v>
       </c>
       <c r="F11" t="n">
-        <v>506.8267</v>
+        <v>129.8112</v>
       </c>
       <c r="G11" t="n">
-        <v>19715559.5</v>
-      </c>
-      <c r="H11" t="n">
-        <v>-14.24</v>
-      </c>
+        <v>21016430.2</v>
+      </c>
+      <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -820,49 +818,51 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>13580</v>
+        <v>38900</v>
       </c>
       <c r="F12" t="n">
-        <v>1493.977</v>
+        <v>506.8267</v>
       </c>
       <c r="G12" t="n">
-        <v>20288208.3</v>
+        <v>19715559.5</v>
       </c>
       <c r="H12" t="n">
-        <v>-6.64</v>
+        <v>-14.24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>126300</v>
+        <v>13580</v>
       </c>
       <c r="F13" t="n">
-        <v>165.13</v>
+        <v>1493.977</v>
       </c>
       <c r="G13" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H13" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -872,27 +872,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>48800</v>
+        <v>126300</v>
       </c>
       <c r="F14" t="n">
-        <v>6.3754</v>
+        <v>165.13</v>
       </c>
       <c r="G14" t="n">
-        <v>311119.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -904,31 +904,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>29050</v>
+        <v>48800</v>
       </c>
       <c r="F15" t="n">
-        <v>686</v>
+        <v>6.3754</v>
       </c>
       <c r="G15" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H15" t="n">
-        <v>3.01</v>
-      </c>
+        <v>311119.6</v>
+      </c>
+      <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -938,29 +936,31 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>275000</v>
+        <v>29050</v>
       </c>
       <c r="F16" t="n">
-        <v>3.4779</v>
+        <v>686</v>
       </c>
       <c r="G16" t="n">
-        <v>956424.2</v>
-      </c>
-      <c r="H16" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -970,27 +970,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>326500</v>
+        <v>275000</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8772</v>
+        <v>3.4779</v>
       </c>
       <c r="G17" t="n">
-        <v>286419.6</v>
+        <v>956424.2</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -1002,27 +1002,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>36800</v>
+        <v>326500</v>
       </c>
       <c r="F18" t="n">
-        <v>14.2631</v>
+        <v>0.8772</v>
       </c>
       <c r="G18" t="n">
-        <v>524880.4</v>
+        <v>286419.6</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1034,27 +1034,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>536000</v>
+        <v>36800</v>
       </c>
       <c r="F19" t="n">
-        <v>2.9103</v>
+        <v>14.2631</v>
       </c>
       <c r="G19" t="n">
-        <v>1559919.6</v>
+        <v>524880.4</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1080,13 +1080,13 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>97600</v>
+        <v>536000</v>
       </c>
       <c r="F20" t="n">
-        <v>19.6877</v>
+        <v>2.9103</v>
       </c>
       <c r="G20" t="n">
-        <v>1921519.6</v>
+        <v>1559919.6</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1098,12 +1098,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1112,13 +1112,13 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>153900</v>
+        <v>97600</v>
       </c>
       <c r="F21" t="n">
-        <v>17.0321</v>
+        <v>19.6877</v>
       </c>
       <c r="G21" t="n">
-        <v>2621239.2</v>
+        <v>1921519.6</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1130,27 +1130,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1074000</v>
+        <v>153900</v>
       </c>
       <c r="F22" t="n">
-        <v>19.4189</v>
+        <v>17.0321</v>
       </c>
       <c r="G22" t="n">
-        <v>20855919.6</v>
+        <v>2621239.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1162,27 +1162,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>87400</v>
+        <v>1074000</v>
       </c>
       <c r="F23" t="n">
-        <v>15.0802</v>
+        <v>19.4189</v>
       </c>
       <c r="G23" t="n">
-        <v>1318012.9</v>
+        <v>20855919.6</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,13 +1208,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>225000</v>
+        <v>87400</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6929999999999999</v>
+        <v>15.0802</v>
       </c>
       <c r="G24" t="n">
-        <v>155919.6</v>
+        <v>1318012.9</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1226,12 +1226,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5810</v>
+        <v>225000</v>
       </c>
       <c r="F25" t="n">
-        <v>154.6591</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>898569.6</v>
+        <v>155919.6</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1258,27 +1258,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>30200</v>
+        <v>5810</v>
       </c>
       <c r="F26" t="n">
-        <v>109.4066</v>
+        <v>154.6591</v>
       </c>
       <c r="G26" t="n">
-        <v>3304080.4</v>
+        <v>898569.6</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1290,12 +1290,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1304,13 +1304,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>207000</v>
+        <v>30200</v>
       </c>
       <c r="F27" t="n">
-        <v>1.2389</v>
+        <v>109.4066</v>
       </c>
       <c r="G27" t="n">
-        <v>256454.4</v>
+        <v>3304080.4</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1336,13 +1336,13 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>28150</v>
+        <v>207000</v>
       </c>
       <c r="F28" t="n">
-        <v>195.4454</v>
+        <v>1.2389</v>
       </c>
       <c r="G28" t="n">
-        <v>5501788.7</v>
+        <v>256454.4</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1368,13 +1368,13 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>50500</v>
+        <v>28150</v>
       </c>
       <c r="F29" t="n">
-        <v>7.0115</v>
+        <v>195.4454</v>
       </c>
       <c r="G29" t="n">
-        <v>354080.4</v>
+        <v>5501788.7</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1386,31 +1386,29 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>19430</v>
+        <v>50500</v>
       </c>
       <c r="F30" t="n">
-        <v>1071</v>
+        <v>7.0115</v>
       </c>
       <c r="G30" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0.78</v>
-      </c>
+        <v>354080.4</v>
+      </c>
+      <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1420,29 +1418,31 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>21200</v>
+        <v>19430</v>
       </c>
       <c r="F31" t="n">
-        <v>1475.6547</v>
+        <v>1071</v>
       </c>
       <c r="G31" t="n">
-        <v>31283879.4</v>
-      </c>
-      <c r="H31" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1469,10 +1469,10 @@
         <v>21200</v>
       </c>
       <c r="F32" t="n">
-        <v>154.5755</v>
+        <v>1475.6547</v>
       </c>
       <c r="G32" t="n">
-        <v>3277001</v>
+        <v>31283879.4</v>
       </c>
       <c r="H32" t="inlineStr"/>
     </row>
@@ -1484,12 +1484,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,13 +1498,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>27700</v>
+        <v>21200</v>
       </c>
       <c r="F33" t="n">
-        <v>98.6181</v>
+        <v>154.5755</v>
       </c>
       <c r="G33" t="n">
-        <v>2731720.6</v>
+        <v>3277001</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1516,27 +1516,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>13960</v>
+        <v>27700</v>
       </c>
       <c r="F34" t="n">
-        <v>126.1646</v>
+        <v>98.6181</v>
       </c>
       <c r="G34" t="n">
-        <v>1761257.6</v>
+        <v>2731720.6</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1548,12 +1548,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1562,13 +1562,13 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>140200</v>
+        <v>13960</v>
       </c>
       <c r="F35" t="n">
-        <v>21.1375</v>
+        <v>126.1646</v>
       </c>
       <c r="G35" t="n">
-        <v>2963479.4</v>
+        <v>1761257.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1580,27 +1580,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6330</v>
+        <v>140200</v>
       </c>
       <c r="F36" t="n">
-        <v>13.226</v>
+        <v>21.1375</v>
       </c>
       <c r="G36" t="n">
-        <v>83720.39999999999</v>
+        <v>2963479.4</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1612,12 +1612,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1626,13 +1626,13 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>15750</v>
+        <v>6330</v>
       </c>
       <c r="F37" t="n">
-        <v>5.8146</v>
+        <v>13.226</v>
       </c>
       <c r="G37" t="n">
-        <v>91580.39999999999</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
@@ -1644,27 +1644,27 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>22500</v>
+        <v>15750</v>
       </c>
       <c r="F38" t="n">
-        <v>110.3946</v>
+        <v>5.8146</v>
       </c>
       <c r="G38" t="n">
-        <v>2483879.4</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
@@ -1676,31 +1676,29 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>256000</v>
+        <v>22500</v>
       </c>
       <c r="F39" t="n">
-        <v>113.8306</v>
+        <v>110.3946</v>
       </c>
       <c r="G39" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H39" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>2483879.4</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1710,29 +1708,31 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>75700</v>
+        <v>256000</v>
       </c>
       <c r="F40" t="n">
-        <v>275.5075</v>
+        <v>113.8306</v>
       </c>
       <c r="G40" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H40" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1742,27 +1742,27 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>131600</v>
+        <v>75700</v>
       </c>
       <c r="F41" t="n">
-        <v>2.4796</v>
+        <v>275.5075</v>
       </c>
       <c r="G41" t="n">
-        <v>326319.6</v>
+        <v>20855919.6</v>
       </c>
       <c r="H41" t="inlineStr"/>
     </row>
@@ -1774,12 +1774,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1788,13 +1788,13 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>41150</v>
+        <v>131600</v>
       </c>
       <c r="F42" t="n">
-        <v>43.8267</v>
+        <v>2.4796</v>
       </c>
       <c r="G42" t="n">
-        <v>1803469.6</v>
+        <v>326319.6</v>
       </c>
       <c r="H42" t="inlineStr"/>
     </row>
@@ -1806,12 +1806,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1820,13 +1820,13 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>147300</v>
+        <v>41150</v>
       </c>
       <c r="F43" t="n">
-        <v>2.3821</v>
+        <v>43.8267</v>
       </c>
       <c r="G43" t="n">
-        <v>350879.4</v>
+        <v>1803469.6</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
@@ -1838,27 +1838,27 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>36450</v>
+        <v>147300</v>
       </c>
       <c r="F44" t="n">
-        <v>76.7514</v>
+        <v>2.3821</v>
       </c>
       <c r="G44" t="n">
-        <v>2797588.9</v>
+        <v>350879.4</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
@@ -1870,27 +1870,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>119700</v>
+        <v>36450</v>
       </c>
       <c r="F45" t="n">
-        <v>30.2349</v>
+        <v>76.7514</v>
       </c>
       <c r="G45" t="n">
-        <v>3619119.6</v>
+        <v>2797588.9</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
@@ -1902,27 +1902,27 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>85400</v>
+        <v>119700</v>
       </c>
       <c r="F46" t="n">
-        <v>9.785500000000001</v>
+        <v>30.2349</v>
       </c>
       <c r="G46" t="n">
-        <v>835680.4</v>
+        <v>3619119.6</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
@@ -1934,27 +1934,27 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>183500</v>
+        <v>85400</v>
       </c>
       <c r="F47" t="n">
-        <v>113.6562</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G47" t="n">
-        <v>20855919.6</v>
+        <v>835680.4</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
@@ -1976,34 +1976,34 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E48" t="n">
         <v>183500</v>
       </c>
       <c r="F48" t="n">
-        <v>12.1963</v>
+        <v>113.6562</v>
       </c>
       <c r="G48" t="n">
-        <v>2238023.8</v>
+        <v>20855919.6</v>
       </c>
       <c r="H48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1849000</v>
+        <v>183500</v>
       </c>
       <c r="F49" t="n">
-        <v>5.5521</v>
+        <v>12.1963</v>
       </c>
       <c r="G49" t="n">
-        <v>10265800.4</v>
+        <v>2238023.8</v>
       </c>
       <c r="H49" t="inlineStr"/>
     </row>
@@ -2030,12 +2030,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2044,10 +2044,10 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>260000</v>
+        <v>1849000</v>
       </c>
       <c r="F50" t="n">
-        <v>39.4838</v>
+        <v>5.5521</v>
       </c>
       <c r="G50" t="n">
         <v>10265800.4</v>
@@ -2062,24 +2062,24 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>24700</v>
+        <v>260000</v>
       </c>
       <c r="F51" t="n">
-        <v>415.6194</v>
+        <v>39.4838</v>
       </c>
       <c r="G51" t="n">
         <v>10265800.4</v>
@@ -2094,59 +2094,59 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>48650</v>
+        <v>24700</v>
       </c>
       <c r="F52" t="n">
-        <v>422.0267</v>
+        <v>415.6194</v>
       </c>
       <c r="G52" t="n">
-        <v>20531600.8</v>
+        <v>10265800.4</v>
       </c>
       <c r="H52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>87800</v>
+        <v>48650</v>
       </c>
       <c r="F53" t="n">
-        <v>115.4542</v>
+        <v>422.0267</v>
       </c>
       <c r="G53" t="n">
-        <v>10136875</v>
+        <v>20531600.8</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
@@ -2158,27 +2158,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>22750</v>
+        <v>87800</v>
       </c>
       <c r="F54" t="n">
-        <v>891.1538</v>
+        <v>115.4542</v>
       </c>
       <c r="G54" t="n">
-        <v>20273749.9</v>
+        <v>10136875</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
@@ -2190,31 +2190,29 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>33150</v>
+        <v>22750</v>
       </c>
       <c r="F55" t="n">
-        <v>569</v>
+        <v>891.1538</v>
       </c>
       <c r="G55" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H55" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>20273749.9</v>
+      </c>
+      <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2224,29 +2222,31 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>254500</v>
+        <v>33150</v>
       </c>
       <c r="F56" t="n">
-        <v>39.8306</v>
+        <v>569</v>
       </c>
       <c r="G56" t="n">
-        <v>10136875</v>
-      </c>
-      <c r="H56" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H56" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2256,46 +2256,44 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>79400</v>
+        <v>254500</v>
       </c>
       <c r="F57" t="n">
-        <v>246</v>
+        <v>39.8306</v>
       </c>
       <c r="G57" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H57" t="n">
-        <v>-8</v>
-      </c>
+        <v>10136875</v>
+      </c>
+      <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -2304,16 +2302,16 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>14780</v>
+        <v>79400</v>
       </c>
       <c r="F58" t="n">
-        <v>1338</v>
+        <v>246</v>
       </c>
       <c r="G58" t="n">
-        <v>19775640</v>
+        <v>19532400</v>
       </c>
       <c r="H58" t="n">
-        <v>33.89</v>
+        <v>-8</v>
       </c>
     </row>
     <row r="59">
@@ -2324,29 +2322,31 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>195800</v>
+        <v>14780</v>
       </c>
       <c r="F59" t="n">
-        <v>101.9921</v>
+        <v>1338</v>
       </c>
       <c r="G59" t="n">
-        <v>19970062</v>
-      </c>
-      <c r="H59" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H59" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2356,12 +2356,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -2370,10 +2370,10 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>14600</v>
+        <v>195800</v>
       </c>
       <c r="F60" t="n">
-        <v>1367.8125</v>
+        <v>101.9921</v>
       </c>
       <c r="G60" t="n">
         <v>19970062</v>
@@ -2388,27 +2388,27 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>36300</v>
+        <v>14600</v>
       </c>
       <c r="F61" t="n">
-        <v>275.0697</v>
+        <v>1367.8125</v>
       </c>
       <c r="G61" t="n">
-        <v>9985031</v>
+        <v>19970062</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
@@ -2420,24 +2420,24 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>159300</v>
+        <v>36300</v>
       </c>
       <c r="F62" t="n">
-        <v>62.6807</v>
+        <v>275.0697</v>
       </c>
       <c r="G62" t="n">
         <v>9985031</v>
@@ -2447,17 +2447,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -2466,45 +2466,45 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>147200</v>
+        <v>159300</v>
       </c>
       <c r="F63" t="n">
-        <v>67</v>
+        <v>62.6807</v>
       </c>
       <c r="G63" t="n">
-        <v>9862400</v>
+        <v>9985031</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>14540</v>
+        <v>147200</v>
       </c>
       <c r="F64" t="n">
-        <v>983</v>
+        <v>67</v>
       </c>
       <c r="G64" t="n">
-        <v>14292820</v>
+        <v>9862400</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
@@ -2516,31 +2516,29 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>113400</v>
+        <v>14540</v>
       </c>
       <c r="F65" t="n">
-        <v>167</v>
+        <v>983</v>
       </c>
       <c r="G65" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H65" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>14292820</v>
+      </c>
+      <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2550,29 +2548,31 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>24350</v>
+        <v>113400</v>
       </c>
       <c r="F66" t="n">
-        <v>407</v>
+        <v>167</v>
       </c>
       <c r="G66" t="n">
-        <v>9910450</v>
-      </c>
-      <c r="H66" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H66" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2582,31 +2582,29 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>44100</v>
+        <v>24350</v>
       </c>
       <c r="F67" t="n">
-        <v>488</v>
+        <v>407</v>
       </c>
       <c r="G67" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H67" t="n">
-        <v>4.26</v>
-      </c>
+        <v>9910450</v>
+      </c>
+      <c r="H67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2616,76 +2614,78 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>165700</v>
+        <v>44100</v>
       </c>
       <c r="F68" t="n">
-        <v>120</v>
+        <v>488</v>
       </c>
       <c r="G68" t="n">
-        <v>19884000</v>
-      </c>
-      <c r="H68" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H68" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>28950</v>
+        <v>165700</v>
       </c>
       <c r="F69" t="n">
-        <v>353</v>
+        <v>120</v>
       </c>
       <c r="G69" t="n">
-        <v>10219350</v>
+        <v>19884000</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2694,13 +2694,13 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1853000</v>
+        <v>28950</v>
       </c>
       <c r="F70" t="n">
-        <v>11</v>
+        <v>353</v>
       </c>
       <c r="G70" t="n">
-        <v>20383000</v>
+        <v>10219350</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
@@ -2712,12 +2712,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -2726,13 +2726,13 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>269000</v>
+        <v>1853000</v>
       </c>
       <c r="F71" t="n">
-        <v>76</v>
+        <v>11</v>
       </c>
       <c r="G71" t="n">
-        <v>20444000</v>
+        <v>20383000</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
@@ -2744,27 +2744,27 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>106300</v>
+        <v>269000</v>
       </c>
       <c r="F72" t="n">
-        <v>194</v>
+        <v>76</v>
       </c>
       <c r="G72" t="n">
-        <v>20622200</v>
+        <v>20444000</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -2790,45 +2790,45 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>123100</v>
+        <v>106300</v>
       </c>
       <c r="F73" t="n">
-        <v>167</v>
+        <v>194</v>
       </c>
       <c r="G73" t="n">
-        <v>20557700</v>
+        <v>20622200</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1856000</v>
+        <v>123100</v>
       </c>
       <c r="F74" t="n">
-        <v>23</v>
+        <v>167</v>
       </c>
       <c r="G74" t="n">
-        <v>42688000</v>
+        <v>20557700</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
@@ -2840,12 +2840,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -2854,13 +2854,13 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>49000</v>
+        <v>1856000</v>
       </c>
       <c r="F75" t="n">
-        <v>167</v>
+        <v>23</v>
       </c>
       <c r="G75" t="n">
-        <v>8183000</v>
+        <v>42688000</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
@@ -2872,12 +2872,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -2886,13 +2886,13 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>13340</v>
+        <v>49000</v>
       </c>
       <c r="F76" t="n">
-        <v>236</v>
+        <v>167</v>
       </c>
       <c r="G76" t="n">
-        <v>3148240</v>
+        <v>8183000</v>
       </c>
       <c r="H76" t="inlineStr"/>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -2918,13 +2918,13 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>29800</v>
+        <v>13340</v>
       </c>
       <c r="F77" t="n">
-        <v>66</v>
+        <v>236</v>
       </c>
       <c r="G77" t="n">
-        <v>1966800</v>
+        <v>3148240</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
@@ -2936,12 +2936,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -2950,13 +2950,13 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>269500</v>
+        <v>29800</v>
       </c>
       <c r="F78" t="n">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="G78" t="n">
-        <v>31801000</v>
+        <v>1966800</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
@@ -2968,12 +2968,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -2982,13 +2982,13 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>330000</v>
+        <v>269500</v>
       </c>
       <c r="F79" t="n">
-        <v>24</v>
+        <v>118</v>
       </c>
       <c r="G79" t="n">
-        <v>7920000</v>
+        <v>31801000</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
@@ -3000,27 +3000,27 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>35550</v>
+        <v>330000</v>
       </c>
       <c r="F80" t="n">
-        <v>581</v>
+        <v>24</v>
       </c>
       <c r="G80" t="n">
-        <v>20654550</v>
+        <v>7920000</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
@@ -3032,27 +3032,27 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>574000</v>
+        <v>35550</v>
       </c>
       <c r="F81" t="n">
-        <v>22</v>
+        <v>581</v>
       </c>
       <c r="G81" t="n">
-        <v>12628000</v>
+        <v>20654550</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
@@ -3064,12 +3064,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -3078,13 +3078,13 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>165900</v>
+        <v>574000</v>
       </c>
       <c r="F82" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G82" t="n">
-        <v>3981600</v>
+        <v>12628000</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
@@ -3096,27 +3096,27 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>91300</v>
+        <v>165900</v>
       </c>
       <c r="F83" t="n">
-        <v>45</v>
+        <v>24</v>
       </c>
       <c r="G83" t="n">
-        <v>4108500</v>
+        <v>3981600</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
@@ -3128,27 +3128,27 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>224500</v>
+        <v>91300</v>
       </c>
       <c r="F84" t="n">
-        <v>92</v>
+        <v>45</v>
       </c>
       <c r="G84" t="n">
-        <v>20654000</v>
+        <v>4108500</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
@@ -3160,12 +3160,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -3174,13 +3174,13 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6010</v>
+        <v>224500</v>
       </c>
       <c r="F85" t="n">
-        <v>3435</v>
+        <v>92</v>
       </c>
       <c r="G85" t="n">
-        <v>20644350</v>
+        <v>20654000</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
@@ -3192,27 +3192,27 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>25800</v>
+        <v>6010</v>
       </c>
       <c r="F86" t="n">
-        <v>351</v>
+        <v>3435</v>
       </c>
       <c r="G86" t="n">
-        <v>9055800</v>
+        <v>20644350</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
@@ -3224,27 +3224,27 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>49150</v>
+        <v>25800</v>
       </c>
       <c r="F87" t="n">
-        <v>420</v>
+        <v>351</v>
       </c>
       <c r="G87" t="n">
-        <v>20643000</v>
+        <v>9055800</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
@@ -3256,12 +3256,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -3270,13 +3270,13 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>19280</v>
+        <v>49150</v>
       </c>
       <c r="F88" t="n">
-        <v>1071</v>
+        <v>420</v>
       </c>
       <c r="G88" t="n">
-        <v>20648880</v>
+        <v>20643000</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
@@ -3288,27 +3288,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>19740</v>
+        <v>19280</v>
       </c>
       <c r="F89" t="n">
-        <v>523</v>
+        <v>1071</v>
       </c>
       <c r="G89" t="n">
-        <v>10324020</v>
+        <v>20648880</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
@@ -3320,27 +3320,27 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>25150</v>
+        <v>19740</v>
       </c>
       <c r="F90" t="n">
-        <v>821</v>
+        <v>523</v>
       </c>
       <c r="G90" t="n">
-        <v>20648150</v>
+        <v>10324020</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
@@ -3352,27 +3352,27 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>153500</v>
+        <v>25150</v>
       </c>
       <c r="F91" t="n">
-        <v>24</v>
+        <v>821</v>
       </c>
       <c r="G91" t="n">
-        <v>3684000</v>
+        <v>20648150</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
@@ -3384,27 +3384,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6240</v>
+        <v>153500</v>
       </c>
       <c r="F92" t="n">
-        <v>3308</v>
+        <v>24</v>
       </c>
       <c r="G92" t="n">
-        <v>20641920</v>
+        <v>3684000</v>
       </c>
       <c r="H92" t="inlineStr"/>
     </row>
@@ -3416,12 +3416,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -3430,13 +3430,13 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>15520</v>
+        <v>6240</v>
       </c>
       <c r="F93" t="n">
-        <v>1330</v>
+        <v>3308</v>
       </c>
       <c r="G93" t="n">
-        <v>20641600</v>
+        <v>20641920</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
@@ -3448,27 +3448,27 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>24200</v>
+        <v>15520</v>
       </c>
       <c r="F94" t="n">
-        <v>210</v>
+        <v>1330</v>
       </c>
       <c r="G94" t="n">
-        <v>5082000</v>
+        <v>20641600</v>
       </c>
       <c r="H94" t="inlineStr"/>
     </row>
@@ -3480,27 +3480,27 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>36300</v>
+        <v>24200</v>
       </c>
       <c r="F95" t="n">
-        <v>569</v>
+        <v>210</v>
       </c>
       <c r="G95" t="n">
-        <v>20654700</v>
+        <v>5082000</v>
       </c>
       <c r="H95" t="inlineStr"/>
     </row>
@@ -3512,27 +3512,27 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>279500</v>
+        <v>36300</v>
       </c>
       <c r="F96" t="n">
-        <v>43</v>
+        <v>569</v>
       </c>
       <c r="G96" t="n">
-        <v>12018500</v>
+        <v>20654700</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
@@ -3544,12 +3544,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -3558,13 +3558,13 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>132600</v>
+        <v>279500</v>
       </c>
       <c r="F97" t="n">
-        <v>90</v>
+        <v>43</v>
       </c>
       <c r="G97" t="n">
-        <v>11934000</v>
+        <v>12018500</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
@@ -3576,12 +3576,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3590,13 +3590,13 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>44600</v>
+        <v>132600</v>
       </c>
       <c r="F98" t="n">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="G98" t="n">
-        <v>6199400</v>
+        <v>11934000</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
@@ -3608,12 +3608,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -3622,13 +3622,13 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>147100</v>
+        <v>44600</v>
       </c>
       <c r="F99" t="n">
-        <v>6</v>
+        <v>139</v>
       </c>
       <c r="G99" t="n">
-        <v>882600</v>
+        <v>6199400</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
@@ -3640,12 +3640,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -3654,13 +3654,13 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>33500</v>
+        <v>147100</v>
       </c>
       <c r="F100" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G100" t="n">
-        <v>268000</v>
+        <v>882600</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
@@ -3672,12 +3672,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3686,13 +3686,13 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>143100</v>
+        <v>33500</v>
       </c>
       <c r="F101" t="n">
-        <v>95</v>
+        <v>8</v>
       </c>
       <c r="G101" t="n">
-        <v>13594500</v>
+        <v>268000</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
@@ -3704,12 +3704,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -3718,13 +3718,13 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>83800</v>
+        <v>143100</v>
       </c>
       <c r="F102" t="n">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="G102" t="n">
-        <v>8882800</v>
+        <v>13594500</v>
       </c>
       <c r="H102" t="inlineStr"/>
     </row>
@@ -3736,27 +3736,27 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>42300</v>
+        <v>83800</v>
       </c>
       <c r="F103" t="n">
-        <v>488</v>
+        <v>106</v>
       </c>
       <c r="G103" t="n">
-        <v>20642400</v>
+        <v>8882800</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
@@ -3768,34 +3768,34 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>81200</v>
+        <v>42300</v>
       </c>
       <c r="F104" t="n">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c r="G104" t="n">
-        <v>10962000</v>
+        <v>20642400</v>
       </c>
       <c r="H104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -3810,49 +3810,49 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>78600</v>
+        <v>81200</v>
       </c>
       <c r="F105" t="n">
-        <v>389</v>
+        <v>135</v>
       </c>
       <c r="G105" t="n">
-        <v>30575400</v>
+        <v>10962000</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>92500</v>
+        <v>78600</v>
       </c>
       <c r="F106" t="n">
-        <v>106</v>
+        <v>389</v>
       </c>
       <c r="G106" t="n">
-        <v>9805000</v>
+        <v>30575400</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
@@ -3864,95 +3864,93 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>25550</v>
+        <v>92500</v>
       </c>
       <c r="F107" t="n">
-        <v>1151</v>
+        <v>106</v>
       </c>
       <c r="G107" t="n">
-        <v>29408050</v>
+        <v>9805000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>21800</v>
+        <v>25550</v>
       </c>
       <c r="F108" t="n">
-        <v>832</v>
+        <v>1151</v>
       </c>
       <c r="G108" t="n">
-        <v>18137600</v>
+        <v>29408050</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>32250</v>
+        <v>21800</v>
       </c>
       <c r="F109" t="n">
-        <v>878</v>
+        <v>832</v>
       </c>
       <c r="G109" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H109" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -3962,12 +3960,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -3976,16 +3974,16 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>105800</v>
+        <v>32250</v>
       </c>
       <c r="F110" t="n">
-        <v>332</v>
+        <v>878</v>
       </c>
       <c r="G110" t="n">
-        <v>35125600</v>
+        <v>28315500</v>
       </c>
       <c r="H110" t="n">
-        <v>17.17</v>
+        <v>-5.33</v>
       </c>
     </row>
     <row r="111">
@@ -3996,12 +3994,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -4010,16 +4008,16 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>33750</v>
+        <v>105800</v>
       </c>
       <c r="F111" t="n">
-        <v>791</v>
+        <v>332</v>
       </c>
       <c r="G111" t="n">
-        <v>26696250</v>
+        <v>35125600</v>
       </c>
       <c r="H111" t="n">
-        <v>0.29</v>
+        <v>17.17</v>
       </c>
     </row>
     <row r="112">
@@ -4030,63 +4028,63 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>86300</v>
+        <v>33750</v>
       </c>
       <c r="F112" t="n">
-        <v>352</v>
+        <v>791</v>
       </c>
       <c r="G112" t="n">
-        <v>30377600</v>
-      </c>
-      <c r="H112" t="inlineStr"/>
+        <v>26696250</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0.29</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>21000</v>
+        <v>86300</v>
       </c>
       <c r="F113" t="n">
-        <v>1517</v>
+        <v>352</v>
       </c>
       <c r="G113" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H113" t="n">
-        <v>3.96</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4096,29 +4094,31 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21900</v>
+        <v>21000</v>
       </c>
       <c r="F114" t="n">
-        <v>906</v>
+        <v>1517</v>
       </c>
       <c r="G114" t="n">
-        <v>19841400</v>
-      </c>
-      <c r="H114" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H114" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4128,44 +4128,44 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>135300</v>
+        <v>21900</v>
       </c>
       <c r="F115" t="n">
-        <v>226</v>
+        <v>906</v>
       </c>
       <c r="G115" t="n">
-        <v>30577800</v>
+        <v>19841400</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -4174,13 +4174,13 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>22250</v>
+        <v>135300</v>
       </c>
       <c r="F116" t="n">
-        <v>1399</v>
+        <v>226</v>
       </c>
       <c r="G116" t="n">
-        <v>31127750</v>
+        <v>30577800</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
@@ -4192,31 +4192,29 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>33500</v>
+        <v>22250</v>
       </c>
       <c r="F117" t="n">
-        <v>848</v>
+        <v>1399</v>
       </c>
       <c r="G117" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H117" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>31127750</v>
+      </c>
+      <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4226,12 +4224,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -4240,49 +4238,51 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>300000</v>
+        <v>33500</v>
       </c>
       <c r="F118" t="n">
-        <v>104</v>
+        <v>848</v>
       </c>
       <c r="G118" t="n">
-        <v>31200000</v>
+        <v>28408000</v>
       </c>
       <c r="H118" t="n">
-        <v>20.95</v>
+        <v>-9.07</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>28200</v>
+        <v>300000</v>
       </c>
       <c r="F119" t="n">
-        <v>1105</v>
+        <v>104</v>
       </c>
       <c r="G119" t="n">
-        <v>31161000</v>
-      </c>
-      <c r="H119" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H119" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4292,31 +4292,29 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>398000</v>
+        <v>28200</v>
       </c>
       <c r="F120" t="n">
-        <v>72</v>
+        <v>1105</v>
       </c>
       <c r="G120" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>31161000</v>
+      </c>
+      <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4326,12 +4324,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -4340,16 +4338,16 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5620</v>
+        <v>398000</v>
       </c>
       <c r="F121" t="n">
-        <v>4707</v>
+        <v>72</v>
       </c>
       <c r="G121" t="n">
-        <v>26453340</v>
+        <v>28656000</v>
       </c>
       <c r="H121" t="n">
-        <v>-8.220000000000001</v>
+        <v>-6.88</v>
       </c>
     </row>
     <row r="122">
@@ -4360,59 +4358,61 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>126900</v>
+        <v>5620</v>
       </c>
       <c r="F122" t="n">
-        <v>246</v>
+        <v>4707</v>
       </c>
       <c r="G122" t="n">
-        <v>31217400</v>
-      </c>
-      <c r="H122" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H122" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1671000</v>
+        <v>126900</v>
       </c>
       <c r="F123" t="n">
-        <v>44</v>
+        <v>246</v>
       </c>
       <c r="G123" t="n">
-        <v>73524000</v>
+        <v>31217400</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
@@ -4424,27 +4424,27 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>50600</v>
+        <v>1671000</v>
       </c>
       <c r="F124" t="n">
-        <v>186</v>
+        <v>44</v>
       </c>
       <c r="G124" t="n">
-        <v>9411600</v>
+        <v>73524000</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
@@ -4456,12 +4456,12 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -4470,13 +4470,13 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>11720</v>
+        <v>50600</v>
       </c>
       <c r="F125" t="n">
-        <v>665</v>
+        <v>186</v>
       </c>
       <c r="G125" t="n">
-        <v>7793800</v>
+        <v>9411600</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
@@ -4488,12 +4488,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -4502,13 +4502,13 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>414000</v>
+        <v>11720</v>
       </c>
       <c r="F126" t="n">
-        <v>26</v>
+        <v>665</v>
       </c>
       <c r="G126" t="n">
-        <v>10764000</v>
+        <v>7793800</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
@@ -4520,27 +4520,27 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>257000</v>
+        <v>414000</v>
       </c>
       <c r="F127" t="n">
-        <v>239</v>
+        <v>26</v>
       </c>
       <c r="G127" t="n">
-        <v>61423000</v>
+        <v>10764000</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
@@ -4552,27 +4552,27 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>33900</v>
+        <v>257000</v>
       </c>
       <c r="F128" t="n">
-        <v>292</v>
+        <v>239</v>
       </c>
       <c r="G128" t="n">
-        <v>9898800</v>
+        <v>61423000</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
@@ -4584,12 +4584,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -4598,13 +4598,13 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>515000</v>
+        <v>33900</v>
       </c>
       <c r="F129" t="n">
-        <v>17</v>
+        <v>292</v>
       </c>
       <c r="G129" t="n">
-        <v>8755000</v>
+        <v>9898800</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
@@ -4616,12 +4616,12 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -4630,13 +4630,13 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>141200</v>
+        <v>515000</v>
       </c>
       <c r="F130" t="n">
-        <v>81</v>
+        <v>17</v>
       </c>
       <c r="G130" t="n">
-        <v>11437200</v>
+        <v>8755000</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
@@ -4648,12 +4648,12 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -4662,13 +4662,13 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>6320</v>
+        <v>141200</v>
       </c>
       <c r="F131" t="n">
-        <v>1396</v>
+        <v>81</v>
       </c>
       <c r="G131" t="n">
-        <v>8822720</v>
+        <v>11437200</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
@@ -4680,27 +4680,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>90300</v>
+        <v>6320</v>
       </c>
       <c r="F132" t="n">
-        <v>332</v>
+        <v>1396</v>
       </c>
       <c r="G132" t="n">
-        <v>29979600</v>
+        <v>8822720</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
@@ -4712,31 +4712,29 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>163100</v>
+        <v>90300</v>
       </c>
       <c r="F133" t="n">
-        <v>119</v>
+        <v>332</v>
       </c>
       <c r="G133" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H133" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>29979600</v>
+      </c>
+      <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -4746,29 +4744,31 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>37900</v>
+        <v>163100</v>
       </c>
       <c r="F134" t="n">
-        <v>163</v>
+        <v>119</v>
       </c>
       <c r="G134" t="n">
-        <v>6177700</v>
-      </c>
-      <c r="H134" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H134" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -4778,12 +4778,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -4792,13 +4792,13 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>19990</v>
+        <v>37900</v>
       </c>
       <c r="F135" t="n">
-        <v>615</v>
+        <v>163</v>
       </c>
       <c r="G135" t="n">
-        <v>12293850</v>
+        <v>6177700</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
@@ -4810,12 +4810,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -4824,13 +4824,13 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>35100</v>
+        <v>19990</v>
       </c>
       <c r="F136" t="n">
-        <v>320</v>
+        <v>615</v>
       </c>
       <c r="G136" t="n">
-        <v>11232000</v>
+        <v>12293850</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
@@ -4842,12 +4842,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -4856,13 +4856,13 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>286000</v>
+        <v>35100</v>
       </c>
       <c r="F137" t="n">
-        <v>20</v>
+        <v>320</v>
       </c>
       <c r="G137" t="n">
-        <v>5720000</v>
+        <v>11232000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
@@ -4874,31 +4874,29 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>416000</v>
+        <v>286000</v>
       </c>
       <c r="F138" t="n">
-        <v>51</v>
+        <v>20</v>
       </c>
       <c r="G138" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H138" t="n">
-        <v>5.85</v>
-      </c>
+        <v>5720000</v>
+      </c>
+      <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -4908,29 +4906,31 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>49450</v>
+        <v>416000</v>
       </c>
       <c r="F139" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="G139" t="n">
-        <v>7565850</v>
-      </c>
-      <c r="H139" t="inlineStr"/>
+        <v>21216000</v>
+      </c>
+      <c r="H139" t="n">
+        <v>5.85</v>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -4954,13 +4954,13 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>138000</v>
+        <v>49450</v>
       </c>
       <c r="F140" t="n">
-        <v>68</v>
+        <v>153</v>
       </c>
       <c r="G140" t="n">
-        <v>9384000</v>
+        <v>7565850</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
@@ -4972,12 +4972,12 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -4986,13 +4986,13 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>31950</v>
+        <v>138000</v>
       </c>
       <c r="F141" t="n">
-        <v>339</v>
+        <v>68</v>
       </c>
       <c r="G141" t="n">
-        <v>10831050</v>
+        <v>9384000</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
@@ -5004,12 +5004,12 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -5018,45 +5018,45 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>124800</v>
+        <v>31950</v>
       </c>
       <c r="F142" t="n">
-        <v>78</v>
+        <v>339</v>
       </c>
       <c r="G142" t="n">
-        <v>9734400</v>
+        <v>10831050</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>10800</v>
+        <v>124800</v>
       </c>
       <c r="F143" t="n">
-        <v>1892</v>
+        <v>78</v>
       </c>
       <c r="G143" t="n">
-        <v>20433600</v>
+        <v>9734400</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
@@ -5068,31 +5068,29 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>11880</v>
+        <v>10800</v>
       </c>
       <c r="F144" t="n">
-        <v>1474</v>
+        <v>1892</v>
       </c>
       <c r="G144" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H144" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>20433600</v>
+      </c>
+      <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5102,29 +5100,31 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>20200</v>
+        <v>11880</v>
       </c>
       <c r="F145" t="n">
-        <v>1517</v>
+        <v>1474</v>
       </c>
       <c r="G145" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H145" t="inlineStr"/>
+        <v>17511120</v>
+      </c>
+      <c r="H145" t="n">
+        <v>-12.45</v>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5134,27 +5134,27 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>102200</v>
+        <v>20200</v>
       </c>
       <c r="F146" t="n">
-        <v>200</v>
+        <v>1517</v>
       </c>
       <c r="G146" t="n">
-        <v>20440000</v>
+        <v>30643400</v>
       </c>
       <c r="H146" t="inlineStr"/>
     </row>
@@ -5166,31 +5166,29 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>23450</v>
+        <v>102200</v>
       </c>
       <c r="F147" t="n">
-        <v>762</v>
+        <v>200</v>
       </c>
       <c r="G147" t="n">
-        <v>17868900</v>
-      </c>
-      <c r="H147" t="n">
-        <v>-10.67</v>
-      </c>
+        <v>20440000</v>
+      </c>
+      <c r="H147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5200,12 +5198,12 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5214,16 +5212,16 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>22050</v>
+        <v>23450</v>
       </c>
       <c r="F148" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G148" t="n">
-        <v>19293750</v>
+        <v>17868900</v>
       </c>
       <c r="H148" t="n">
-        <v>-3.5</v>
+        <v>-10.67</v>
       </c>
     </row>
     <row r="149">
@@ -5234,29 +5232,31 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>32550</v>
+        <v>22050</v>
       </c>
       <c r="F149" t="n">
-        <v>628</v>
+        <v>875</v>
       </c>
       <c r="G149" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H149" t="inlineStr"/>
+        <v>19293750</v>
+      </c>
+      <c r="H149" t="n">
+        <v>-3.5</v>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5266,63 +5266,63 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>99700</v>
+        <v>32550</v>
       </c>
       <c r="F150" t="n">
-        <v>180</v>
+        <v>628</v>
       </c>
       <c r="G150" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H150" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>20441400</v>
+      </c>
+      <c r="H150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1662000</v>
+        <v>99700</v>
       </c>
       <c r="F151" t="n">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="G151" t="n">
-        <v>249300000</v>
-      </c>
-      <c r="H151" t="inlineStr"/>
+        <v>17946000</v>
+      </c>
+      <c r="H151" t="n">
+        <v>-10.1</v>
+      </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5346,13 +5346,13 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>49700</v>
+        <v>1662000</v>
       </c>
       <c r="F152" t="n">
-        <v>402</v>
+        <v>150</v>
       </c>
       <c r="G152" t="n">
-        <v>19979400</v>
+        <v>249300000</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
@@ -5364,12 +5364,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>435000</v>
+        <v>49700</v>
       </c>
       <c r="F153" t="n">
-        <v>46</v>
+        <v>402</v>
       </c>
       <c r="G153" t="n">
-        <v>20010000</v>
+        <v>19979400</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
@@ -5396,12 +5396,12 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -5410,13 +5410,13 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>268500</v>
+        <v>435000</v>
       </c>
       <c r="F154" t="n">
-        <v>931</v>
+        <v>46</v>
       </c>
       <c r="G154" t="n">
-        <v>249973500</v>
+        <v>20010000</v>
       </c>
       <c r="H154" t="inlineStr"/>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -5442,13 +5442,13 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>13570</v>
+        <v>268500</v>
       </c>
       <c r="F155" t="n">
-        <v>1474</v>
+        <v>931</v>
       </c>
       <c r="G155" t="n">
-        <v>20002180</v>
+        <v>249973500</v>
       </c>
       <c r="H155" t="inlineStr"/>
     </row>
@@ -5460,12 +5460,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>이수화학</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005950</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5474,13 +5474,13 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>343500</v>
+        <v>13570</v>
       </c>
       <c r="F156" t="n">
-        <v>87</v>
+        <v>1474</v>
       </c>
       <c r="G156" t="n">
-        <v>29884500</v>
+        <v>20002180</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
@@ -5492,12 +5492,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -5506,13 +5506,13 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>34150</v>
+        <v>343500</v>
       </c>
       <c r="F157" t="n">
-        <v>586</v>
+        <v>87</v>
       </c>
       <c r="G157" t="n">
-        <v>20011900</v>
+        <v>29884500</v>
       </c>
       <c r="H157" t="inlineStr"/>
     </row>
@@ -5524,12 +5524,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -5538,13 +5538,13 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>488000</v>
+        <v>34150</v>
       </c>
       <c r="F158" t="n">
-        <v>41</v>
+        <v>586</v>
       </c>
       <c r="G158" t="n">
-        <v>20008000</v>
+        <v>20011900</v>
       </c>
       <c r="H158" t="inlineStr"/>
     </row>
@@ -5556,12 +5556,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5570,13 +5570,13 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>153600</v>
+        <v>488000</v>
       </c>
       <c r="F159" t="n">
-        <v>130</v>
+        <v>41</v>
       </c>
       <c r="G159" t="n">
-        <v>19968000</v>
+        <v>20008000</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
@@ -5588,12 +5588,12 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -5602,13 +5602,13 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>99800</v>
+        <v>153600</v>
       </c>
       <c r="F160" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="G160" t="n">
-        <v>19960000</v>
+        <v>19968000</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
@@ -5620,12 +5620,12 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -5634,13 +5634,13 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>6040</v>
+        <v>99800</v>
       </c>
       <c r="F161" t="n">
-        <v>3311</v>
+        <v>200</v>
       </c>
       <c r="G161" t="n">
-        <v>19998440</v>
+        <v>19960000</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
@@ -5652,12 +5652,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -5666,13 +5666,13 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>26250</v>
+        <v>6040</v>
       </c>
       <c r="F162" t="n">
-        <v>762</v>
+        <v>3311</v>
       </c>
       <c r="G162" t="n">
-        <v>20002500</v>
+        <v>19998440</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
@@ -5684,12 +5684,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>STX엔진</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>077970</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -5698,13 +5698,13 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>22850</v>
+        <v>26250</v>
       </c>
       <c r="F163" t="n">
-        <v>875</v>
+        <v>762</v>
       </c>
       <c r="G163" t="n">
-        <v>19993750</v>
+        <v>20002500</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
@@ -5716,12 +5716,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
@@ -5730,13 +5730,13 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>168500</v>
+        <v>22850</v>
       </c>
       <c r="F164" t="n">
-        <v>119</v>
+        <v>875</v>
       </c>
       <c r="G164" t="n">
-        <v>20051500</v>
+        <v>19993750</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
@@ -5748,12 +5748,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -5762,13 +5762,13 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>22850</v>
+        <v>168500</v>
       </c>
       <c r="F165" t="n">
-        <v>875</v>
+        <v>119</v>
       </c>
       <c r="G165" t="n">
-        <v>19993750</v>
+        <v>20051500</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
@@ -5780,12 +5780,12 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -5794,13 +5794,13 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>37900</v>
+        <v>22850</v>
       </c>
       <c r="F166" t="n">
-        <v>528</v>
+        <v>875</v>
       </c>
       <c r="G166" t="n">
-        <v>20011200</v>
+        <v>19993750</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
@@ -5812,12 +5812,12 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -5826,13 +5826,13 @@
         </is>
       </c>
       <c r="E167" t="n">
-        <v>239000</v>
+        <v>37900</v>
       </c>
       <c r="F167" t="n">
-        <v>84</v>
+        <v>528</v>
       </c>
       <c r="G167" t="n">
-        <v>20076000</v>
+        <v>20011200</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
@@ -5844,12 +5844,12 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -5858,13 +5858,13 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>298000</v>
+        <v>239000</v>
       </c>
       <c r="F168" t="n">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="G168" t="n">
-        <v>34866000</v>
+        <v>20076000</v>
       </c>
       <c r="H168" t="inlineStr"/>
     </row>
@@ -5876,12 +5876,12 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5890,13 +5890,13 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>393000</v>
+        <v>298000</v>
       </c>
       <c r="F169" t="n">
-        <v>51</v>
+        <v>117</v>
       </c>
       <c r="G169" t="n">
-        <v>20043000</v>
+        <v>34866000</v>
       </c>
       <c r="H169" t="inlineStr"/>
     </row>
@@ -5908,12 +5908,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>파마리서치</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>214450</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -5922,13 +5922,13 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>110900</v>
+        <v>393000</v>
       </c>
       <c r="F170" t="n">
-        <v>180</v>
+        <v>51</v>
       </c>
       <c r="G170" t="n">
-        <v>19962000</v>
+        <v>20043000</v>
       </c>
       <c r="H170" t="inlineStr"/>
     </row>
@@ -5940,12 +5940,12 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -5954,13 +5954,13 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>44500</v>
+        <v>110900</v>
       </c>
       <c r="F171" t="n">
-        <v>449</v>
+        <v>180</v>
       </c>
       <c r="G171" t="n">
-        <v>19980500</v>
+        <v>19962000</v>
       </c>
       <c r="H171" t="inlineStr"/>
     </row>
@@ -5972,12 +5972,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -5986,13 +5986,13 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>135000</v>
+        <v>44500</v>
       </c>
       <c r="F172" t="n">
-        <v>148</v>
+        <v>449</v>
       </c>
       <c r="G172" t="n">
-        <v>19980000</v>
+        <v>19980500</v>
       </c>
       <c r="H172" t="inlineStr"/>
     </row>
@@ -6004,12 +6004,12 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -6018,13 +6018,13 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>33750</v>
+        <v>135000</v>
       </c>
       <c r="F173" t="n">
-        <v>593</v>
+        <v>148</v>
       </c>
       <c r="G173" t="n">
-        <v>20013750</v>
+        <v>19980000</v>
       </c>
       <c r="H173" t="inlineStr"/>
     </row>
@@ -6036,29 +6036,61 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F174" t="n">
+        <v>593</v>
+      </c>
+      <c r="G174" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C174" t="inlineStr">
+      <c r="C175" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D174" t="inlineStr">
+      <c r="D175" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E174" t="n">
+      <c r="E175" t="n">
         <v>124600</v>
       </c>
-      <c r="F174" t="n">
+      <c r="F175" t="n">
         <v>161</v>
       </c>
-      <c r="G174" t="n">
+      <c r="G175" t="n">
         <v>20060600</v>
       </c>
-      <c r="H174" t="inlineStr"/>
+      <c r="H175" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H175"/>
+  <dimension ref="A1:H211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,183 +473,177 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>125800</v>
+        <v>1842000</v>
       </c>
       <c r="F2" t="n">
-        <v>171.563</v>
+        <v>4.4662</v>
       </c>
       <c r="G2" t="n">
-        <v>21582624.3</v>
+        <v>8226684.7</v>
       </c>
       <c r="H2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>91800</v>
+        <v>114700</v>
       </c>
       <c r="F3" t="n">
-        <v>275.5075</v>
+        <v>20.0826</v>
       </c>
       <c r="G3" t="n">
-        <v>25291590.7</v>
-      </c>
-      <c r="H3" t="n">
-        <v>21.27</v>
-      </c>
+        <v>2303471.7</v>
+      </c>
+      <c r="H3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>토모큐브</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>475960</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>34750</v>
+        <v>47650</v>
       </c>
       <c r="F4" t="n">
-        <v>912.5508</v>
+        <v>27.6237</v>
       </c>
       <c r="G4" t="n">
-        <v>31711139.3</v>
+        <v>1316269.6</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>35350</v>
+        <v>276000</v>
       </c>
       <c r="F5" t="n">
-        <v>566.7369</v>
+        <v>17.0892</v>
       </c>
       <c r="G5" t="n">
-        <v>20034151</v>
-      </c>
-      <c r="H5" t="n">
-        <v>-0.5600000000000001</v>
-      </c>
+        <v>4716632.6</v>
+      </c>
+      <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>91800</v>
+        <v>299000</v>
       </c>
       <c r="F6" t="n">
-        <v>213.6877</v>
+        <v>45.123</v>
       </c>
       <c r="G6" t="n">
-        <v>19616530.9</v>
-      </c>
-      <c r="H6" t="n">
-        <v>-12.98</v>
-      </c>
+        <v>13491762.9</v>
+      </c>
+      <c r="H6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -658,258 +652,254 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>87700</v>
+        <v>529000</v>
       </c>
       <c r="F7" t="n">
-        <v>118.7012</v>
+        <v>2.9029</v>
       </c>
       <c r="G7" t="n">
-        <v>10410097.5</v>
+        <v>1535647.8</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2026-09-28</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>12310</v>
+        <v>164900</v>
       </c>
       <c r="F8" t="n">
-        <v>845.6618999999999</v>
+        <v>53.2149</v>
       </c>
       <c r="G8" t="n">
-        <v>10410097.5</v>
+        <v>8775130.300000001</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>295000</v>
+        <v>1069000</v>
       </c>
       <c r="F9" t="n">
-        <v>71.24209999999999</v>
+        <v>1.5391</v>
       </c>
       <c r="G9" t="n">
-        <v>21016430.2</v>
+        <v>1645336.9</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>12870</v>
+        <v>88600</v>
       </c>
       <c r="F10" t="n">
-        <v>1632.9783</v>
+        <v>18.5704</v>
       </c>
       <c r="G10" t="n">
-        <v>21016430.2</v>
+        <v>1645336.9</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>161900</v>
+        <v>219000</v>
       </c>
       <c r="F11" t="n">
-        <v>129.8112</v>
+        <v>4.5078</v>
       </c>
       <c r="G11" t="n">
-        <v>21016430.2</v>
+        <v>987202.2</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>38900</v>
+        <v>6250</v>
       </c>
       <c r="F12" t="n">
-        <v>506.8267</v>
+        <v>87.7513</v>
       </c>
       <c r="G12" t="n">
-        <v>19715559.5</v>
-      </c>
-      <c r="H12" t="n">
-        <v>-14.24</v>
-      </c>
+        <v>548445.6</v>
+      </c>
+      <c r="H12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>13580</v>
+        <v>288000</v>
       </c>
       <c r="F13" t="n">
-        <v>1493.977</v>
+        <v>5.3321</v>
       </c>
       <c r="G13" t="n">
-        <v>20288208.3</v>
-      </c>
-      <c r="H13" t="n">
-        <v>-6.64</v>
-      </c>
+        <v>1535647.8</v>
+      </c>
+      <c r="H13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>126300</v>
+        <v>35700</v>
       </c>
       <c r="F14" t="n">
-        <v>165.13</v>
+        <v>73.7406</v>
       </c>
       <c r="G14" t="n">
-        <v>20855919.6</v>
+        <v>2632539.1</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -918,64 +908,62 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>48800</v>
+        <v>126700</v>
       </c>
       <c r="F15" t="n">
-        <v>6.3754</v>
+        <v>0.8657</v>
       </c>
       <c r="G15" t="n">
-        <v>311119.6</v>
+        <v>109689.1</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>29050</v>
+        <v>227000</v>
       </c>
       <c r="F16" t="n">
-        <v>686</v>
+        <v>0.4832</v>
       </c>
       <c r="G16" t="n">
-        <v>19928300</v>
-      </c>
-      <c r="H16" t="n">
-        <v>3.01</v>
-      </c>
+        <v>109689.1</v>
+      </c>
+      <c r="H16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -984,222 +972,222 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>275000</v>
+        <v>36000</v>
       </c>
       <c r="F17" t="n">
-        <v>3.4779</v>
+        <v>216.3313</v>
       </c>
       <c r="G17" t="n">
-        <v>956424.2</v>
+        <v>7787928.2</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>326500</v>
+        <v>14360</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8772</v>
+        <v>229.1556</v>
       </c>
       <c r="G18" t="n">
-        <v>286419.6</v>
+        <v>3290673.9</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>36800</v>
+        <v>48600</v>
       </c>
       <c r="F19" t="n">
-        <v>14.2631</v>
+        <v>29.3407</v>
       </c>
       <c r="G19" t="n">
-        <v>524880.4</v>
+        <v>1425958.7</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>536000</v>
+        <v>22900</v>
       </c>
       <c r="F20" t="n">
-        <v>2.9103</v>
+        <v>14.3698</v>
       </c>
       <c r="G20" t="n">
-        <v>1559919.6</v>
+        <v>329067.4</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>97600</v>
+        <v>36450</v>
       </c>
       <c r="F21" t="n">
-        <v>19.6877</v>
+        <v>240.7443</v>
       </c>
       <c r="G21" t="n">
-        <v>1921519.6</v>
+        <v>8775130.300000001</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>153900</v>
+        <v>178400</v>
       </c>
       <c r="F22" t="n">
-        <v>17.0321</v>
+        <v>11.0673</v>
       </c>
       <c r="G22" t="n">
-        <v>2621239.2</v>
+        <v>1974404.3</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1074000</v>
+        <v>151300</v>
       </c>
       <c r="F23" t="n">
-        <v>19.4189</v>
+        <v>5.7998</v>
       </c>
       <c r="G23" t="n">
-        <v>20855919.6</v>
+        <v>877513</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1208,62 +1196,62 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>87400</v>
+        <v>6250</v>
       </c>
       <c r="F24" t="n">
-        <v>15.0802</v>
+        <v>245.7036</v>
       </c>
       <c r="G24" t="n">
-        <v>1318012.9</v>
+        <v>1535647.8</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>225000</v>
+        <v>94900</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6929999999999999</v>
+        <v>231.1678</v>
       </c>
       <c r="G25" t="n">
-        <v>155919.6</v>
+        <v>21937825.9</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1272,30 +1260,30 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5810</v>
+        <v>16020</v>
       </c>
       <c r="F26" t="n">
-        <v>154.6591</v>
+        <v>41.0821</v>
       </c>
       <c r="G26" t="n">
-        <v>898569.6</v>
+        <v>658134.8</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1304,30 +1292,30 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>30200</v>
+        <v>32100</v>
       </c>
       <c r="F27" t="n">
-        <v>109.4066</v>
+        <v>392.9673</v>
       </c>
       <c r="G27" t="n">
-        <v>3304080.4</v>
+        <v>12614249.9</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1336,160 +1324,160 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>207000</v>
+        <v>170200</v>
       </c>
       <c r="F28" t="n">
-        <v>1.2389</v>
+        <v>22.5565</v>
       </c>
       <c r="G28" t="n">
-        <v>256454.4</v>
+        <v>3839119.5</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>28150</v>
+        <v>15580</v>
       </c>
       <c r="F29" t="n">
-        <v>195.4454</v>
+        <v>1408.0761</v>
       </c>
       <c r="G29" t="n">
-        <v>5501788.7</v>
+        <v>21937825.9</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>50500</v>
+        <v>54000</v>
       </c>
       <c r="F30" t="n">
-        <v>7.0115</v>
+        <v>406.256</v>
       </c>
       <c r="G30" t="n">
-        <v>354080.4</v>
+        <v>21937825.9</v>
       </c>
       <c r="H30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>19430</v>
+        <v>153700</v>
       </c>
       <c r="F31" t="n">
-        <v>1071</v>
+        <v>7.1366</v>
       </c>
       <c r="G31" t="n">
-        <v>20809530</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0.78</v>
-      </c>
+        <v>1096891.3</v>
+      </c>
+      <c r="H31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>21200</v>
+        <v>33750</v>
       </c>
       <c r="F32" t="n">
-        <v>1475.6547</v>
+        <v>572.1789</v>
       </c>
       <c r="G32" t="n">
-        <v>31283879.4</v>
-      </c>
-      <c r="H32" t="inlineStr"/>
+        <v>19311036.7</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1.98</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1498,62 +1486,62 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>21200</v>
+        <v>139200</v>
       </c>
       <c r="F33" t="n">
-        <v>154.5755</v>
+        <v>9.456</v>
       </c>
       <c r="G33" t="n">
-        <v>3277001</v>
+        <v>1316269.6</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>27700</v>
+        <v>53200</v>
       </c>
       <c r="F34" t="n">
-        <v>98.6181</v>
+        <v>12.371</v>
       </c>
       <c r="G34" t="n">
-        <v>2731720.6</v>
+        <v>658134.8</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1562,62 +1550,62 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>13960</v>
+        <v>75700</v>
       </c>
       <c r="F35" t="n">
-        <v>126.1646</v>
+        <v>40.5719</v>
       </c>
       <c r="G35" t="n">
-        <v>1761257.6</v>
+        <v>3071295.6</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>토모큐브</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>475960</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>140200</v>
+        <v>34600</v>
       </c>
       <c r="F36" t="n">
-        <v>21.1375</v>
+        <v>345.5525</v>
       </c>
       <c r="G36" t="n">
-        <v>2963479.4</v>
+        <v>11956115.1</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1626,192 +1614,196 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6330</v>
+        <v>183400</v>
       </c>
       <c r="F37" t="n">
-        <v>13.226</v>
+        <v>110.6461</v>
       </c>
       <c r="G37" t="n">
-        <v>83720.39999999999</v>
+        <v>20292488.9</v>
       </c>
       <c r="H37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>15750</v>
+        <v>125800</v>
       </c>
       <c r="F38" t="n">
-        <v>5.8146</v>
+        <v>171.563</v>
       </c>
       <c r="G38" t="n">
-        <v>91580.39999999999</v>
+        <v>21582624.3</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>22500</v>
+        <v>91800</v>
       </c>
       <c r="F39" t="n">
-        <v>110.3946</v>
+        <v>275.5075</v>
       </c>
       <c r="G39" t="n">
-        <v>2483879.4</v>
-      </c>
-      <c r="H39" t="inlineStr"/>
+        <v>25291590.7</v>
+      </c>
+      <c r="H39" t="n">
+        <v>21.27</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>토모큐브</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>475960</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>256000</v>
+        <v>34750</v>
       </c>
       <c r="F40" t="n">
-        <v>113.8306</v>
+        <v>912.5508</v>
       </c>
       <c r="G40" t="n">
-        <v>29140620.8</v>
-      </c>
-      <c r="H40" t="n">
-        <v>-9.470000000000001</v>
-      </c>
+        <v>31711139.3</v>
+      </c>
+      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>75700</v>
+        <v>35350</v>
       </c>
       <c r="F41" t="n">
-        <v>275.5075</v>
+        <v>566.7369</v>
       </c>
       <c r="G41" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H41" t="inlineStr"/>
+        <v>20034151</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-0.5600000000000001</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>131600</v>
+        <v>91800</v>
       </c>
       <c r="F42" t="n">
-        <v>2.4796</v>
+        <v>213.6877</v>
       </c>
       <c r="G42" t="n">
-        <v>326319.6</v>
-      </c>
-      <c r="H42" t="inlineStr"/>
+        <v>19616530.9</v>
+      </c>
+      <c r="H42" t="n">
+        <v>-12.98</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1820,30 +1812,30 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>41150</v>
+        <v>87700</v>
       </c>
       <c r="F43" t="n">
-        <v>43.8267</v>
+        <v>118.7012</v>
       </c>
       <c r="G43" t="n">
-        <v>1803469.6</v>
+        <v>10410097.5</v>
       </c>
       <c r="H43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-28</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1852,416 +1844,420 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>147300</v>
+        <v>12310</v>
       </c>
       <c r="F44" t="n">
-        <v>2.3821</v>
+        <v>845.6618999999999</v>
       </c>
       <c r="G44" t="n">
-        <v>350879.4</v>
+        <v>10410097.5</v>
       </c>
       <c r="H44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>36450</v>
+        <v>295000</v>
       </c>
       <c r="F45" t="n">
-        <v>76.7514</v>
+        <v>71.24209999999999</v>
       </c>
       <c r="G45" t="n">
-        <v>2797588.9</v>
+        <v>21016430.2</v>
       </c>
       <c r="H45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>119700</v>
+        <v>12870</v>
       </c>
       <c r="F46" t="n">
-        <v>30.2349</v>
+        <v>1632.9783</v>
       </c>
       <c r="G46" t="n">
-        <v>3619119.6</v>
+        <v>21016430.2</v>
       </c>
       <c r="H46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>85400</v>
+        <v>161900</v>
       </c>
       <c r="F47" t="n">
-        <v>9.785500000000001</v>
+        <v>129.8112</v>
       </c>
       <c r="G47" t="n">
-        <v>835680.4</v>
+        <v>21016430.2</v>
       </c>
       <c r="H47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>183500</v>
+        <v>38900</v>
       </c>
       <c r="F48" t="n">
-        <v>113.6562</v>
+        <v>506.8267</v>
       </c>
       <c r="G48" t="n">
-        <v>20855919.6</v>
-      </c>
-      <c r="H48" t="inlineStr"/>
+        <v>19715559.5</v>
+      </c>
+      <c r="H48" t="n">
+        <v>-14.24</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>183500</v>
+        <v>13580</v>
       </c>
       <c r="F49" t="n">
-        <v>12.1963</v>
+        <v>1493.977</v>
       </c>
       <c r="G49" t="n">
-        <v>2238023.8</v>
-      </c>
-      <c r="H49" t="inlineStr"/>
+        <v>20288208.3</v>
+      </c>
+      <c r="H49" t="n">
+        <v>-6.64</v>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>1849000</v>
+        <v>126300</v>
       </c>
       <c r="F50" t="n">
-        <v>5.5521</v>
+        <v>165.13</v>
       </c>
       <c r="G50" t="n">
-        <v>10265800.4</v>
+        <v>20855919.6</v>
       </c>
       <c r="H50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>260000</v>
+        <v>48800</v>
       </c>
       <c r="F51" t="n">
-        <v>39.4838</v>
+        <v>6.3754</v>
       </c>
       <c r="G51" t="n">
-        <v>10265800.4</v>
+        <v>311119.6</v>
       </c>
       <c r="H51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>24700</v>
+        <v>29050</v>
       </c>
       <c r="F52" t="n">
-        <v>415.6194</v>
+        <v>686</v>
       </c>
       <c r="G52" t="n">
-        <v>10265800.4</v>
-      </c>
-      <c r="H52" t="inlineStr"/>
+        <v>19928300</v>
+      </c>
+      <c r="H52" t="n">
+        <v>3.01</v>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>48650</v>
+        <v>275000</v>
       </c>
       <c r="F53" t="n">
-        <v>422.0267</v>
+        <v>3.4779</v>
       </c>
       <c r="G53" t="n">
-        <v>20531600.8</v>
+        <v>956424.2</v>
       </c>
       <c r="H53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>87800</v>
+        <v>326500</v>
       </c>
       <c r="F54" t="n">
-        <v>115.4542</v>
+        <v>0.8772</v>
       </c>
       <c r="G54" t="n">
-        <v>10136875</v>
+        <v>286419.6</v>
       </c>
       <c r="H54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>22750</v>
+        <v>36800</v>
       </c>
       <c r="F55" t="n">
-        <v>891.1538</v>
+        <v>14.2631</v>
       </c>
       <c r="G55" t="n">
-        <v>20273749.9</v>
+        <v>524880.4</v>
       </c>
       <c r="H55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>33150</v>
+        <v>536000</v>
       </c>
       <c r="F56" t="n">
-        <v>569</v>
+        <v>2.9103</v>
       </c>
       <c r="G56" t="n">
-        <v>18862350</v>
-      </c>
-      <c r="H56" t="n">
-        <v>-8.68</v>
-      </c>
+        <v>1559919.6</v>
+      </c>
+      <c r="H56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -2270,258 +2266,254 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>254500</v>
+        <v>97600</v>
       </c>
       <c r="F57" t="n">
-        <v>39.8306</v>
+        <v>19.6877</v>
       </c>
       <c r="G57" t="n">
-        <v>10136875</v>
+        <v>1921519.6</v>
       </c>
       <c r="H57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>2026-09-17</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>79400</v>
+        <v>153900</v>
       </c>
       <c r="F58" t="n">
-        <v>246</v>
+        <v>17.0321</v>
       </c>
       <c r="G58" t="n">
-        <v>19532400</v>
-      </c>
-      <c r="H58" t="n">
-        <v>-8</v>
-      </c>
+        <v>2621239.2</v>
+      </c>
+      <c r="H58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>14780</v>
+        <v>1074000</v>
       </c>
       <c r="F59" t="n">
-        <v>1338</v>
+        <v>19.4189</v>
       </c>
       <c r="G59" t="n">
-        <v>19775640</v>
-      </c>
-      <c r="H59" t="n">
-        <v>33.89</v>
-      </c>
+        <v>20855919.6</v>
+      </c>
+      <c r="H59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>195800</v>
+        <v>87400</v>
       </c>
       <c r="F60" t="n">
-        <v>101.9921</v>
+        <v>15.0802</v>
       </c>
       <c r="G60" t="n">
-        <v>19970062</v>
+        <v>1318012.9</v>
       </c>
       <c r="H60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>후성</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>093370</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>14600</v>
+        <v>225000</v>
       </c>
       <c r="F61" t="n">
-        <v>1367.8125</v>
+        <v>0.6929999999999999</v>
       </c>
       <c r="G61" t="n">
-        <v>19970062</v>
+        <v>155919.6</v>
       </c>
       <c r="H61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>36300</v>
+        <v>5810</v>
       </c>
       <c r="F62" t="n">
-        <v>275.0697</v>
+        <v>154.6591</v>
       </c>
       <c r="G62" t="n">
-        <v>9985031</v>
+        <v>898569.6</v>
       </c>
       <c r="H62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>159300</v>
+        <v>30200</v>
       </c>
       <c r="F63" t="n">
-        <v>62.6807</v>
+        <v>109.4066</v>
       </c>
       <c r="G63" t="n">
-        <v>9985031</v>
+        <v>3304080.4</v>
       </c>
       <c r="H63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>147200</v>
+        <v>207000</v>
       </c>
       <c r="F64" t="n">
-        <v>67</v>
+        <v>1.2389</v>
       </c>
       <c r="G64" t="n">
-        <v>9862400</v>
+        <v>256454.4</v>
       </c>
       <c r="H64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -2530,162 +2522,160 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>14540</v>
+        <v>28150</v>
       </c>
       <c r="F65" t="n">
-        <v>983</v>
+        <v>195.4454</v>
       </c>
       <c r="G65" t="n">
-        <v>14292820</v>
+        <v>5501788.7</v>
       </c>
       <c r="H65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>113400</v>
+        <v>50500</v>
       </c>
       <c r="F66" t="n">
-        <v>167</v>
+        <v>7.0115</v>
       </c>
       <c r="G66" t="n">
-        <v>18937800</v>
-      </c>
-      <c r="H66" t="n">
-        <v>-7.88</v>
-      </c>
+        <v>354080.4</v>
+      </c>
+      <c r="H66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>24350</v>
+        <v>19430</v>
       </c>
       <c r="F67" t="n">
-        <v>407</v>
+        <v>1071</v>
       </c>
       <c r="G67" t="n">
-        <v>9910450</v>
-      </c>
-      <c r="H67" t="inlineStr"/>
+        <v>20809530</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0.78</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>44100</v>
+        <v>21200</v>
       </c>
       <c r="F68" t="n">
-        <v>488</v>
+        <v>1475.6547</v>
       </c>
       <c r="G68" t="n">
-        <v>21520800</v>
-      </c>
-      <c r="H68" t="n">
-        <v>4.26</v>
-      </c>
+        <v>31283879.4</v>
+      </c>
+      <c r="H68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>165700</v>
+        <v>21200</v>
       </c>
       <c r="F69" t="n">
-        <v>120</v>
+        <v>154.5755</v>
       </c>
       <c r="G69" t="n">
-        <v>19884000</v>
+        <v>3277001</v>
       </c>
       <c r="H69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -2694,414 +2684,416 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>28950</v>
+        <v>27700</v>
       </c>
       <c r="F70" t="n">
-        <v>353</v>
+        <v>98.6181</v>
       </c>
       <c r="G70" t="n">
-        <v>10219350</v>
+        <v>2731720.6</v>
       </c>
       <c r="H70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1853000</v>
+        <v>13960</v>
       </c>
       <c r="F71" t="n">
-        <v>11</v>
+        <v>126.1646</v>
       </c>
       <c r="G71" t="n">
-        <v>20383000</v>
+        <v>1761257.6</v>
       </c>
       <c r="H71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>269000</v>
+        <v>140200</v>
       </c>
       <c r="F72" t="n">
-        <v>76</v>
+        <v>21.1375</v>
       </c>
       <c r="G72" t="n">
-        <v>20444000</v>
+        <v>2963479.4</v>
       </c>
       <c r="H72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>대한유화</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>006650</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>106300</v>
+        <v>6330</v>
       </c>
       <c r="F73" t="n">
-        <v>194</v>
+        <v>13.226</v>
       </c>
       <c r="G73" t="n">
-        <v>20622200</v>
+        <v>83720.39999999999</v>
       </c>
       <c r="H73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>엘앤에프</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>066970</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>123100</v>
+        <v>15750</v>
       </c>
       <c r="F74" t="n">
-        <v>167</v>
+        <v>5.8146</v>
       </c>
       <c r="G74" t="n">
-        <v>20557700</v>
+        <v>91580.39999999999</v>
       </c>
       <c r="H74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>1856000</v>
+        <v>22500</v>
       </c>
       <c r="F75" t="n">
-        <v>23</v>
+        <v>110.3946</v>
       </c>
       <c r="G75" t="n">
-        <v>42688000</v>
+        <v>2483879.4</v>
       </c>
       <c r="H75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>49000</v>
+        <v>256000</v>
       </c>
       <c r="F76" t="n">
-        <v>167</v>
+        <v>113.8306</v>
       </c>
       <c r="G76" t="n">
-        <v>8183000</v>
-      </c>
-      <c r="H76" t="inlineStr"/>
+        <v>29140620.8</v>
+      </c>
+      <c r="H76" t="n">
+        <v>-9.470000000000001</v>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>타이거일렉</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>219130</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>13340</v>
+        <v>75700</v>
       </c>
       <c r="F77" t="n">
-        <v>236</v>
+        <v>275.5075</v>
       </c>
       <c r="G77" t="n">
-        <v>3148240</v>
+        <v>20855919.6</v>
       </c>
       <c r="H77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>29800</v>
+        <v>131600</v>
       </c>
       <c r="F78" t="n">
-        <v>66</v>
+        <v>2.4796</v>
       </c>
       <c r="G78" t="n">
-        <v>1966800</v>
+        <v>326319.6</v>
       </c>
       <c r="H78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>269500</v>
+        <v>41150</v>
       </c>
       <c r="F79" t="n">
-        <v>118</v>
+        <v>43.8267</v>
       </c>
       <c r="G79" t="n">
-        <v>31801000</v>
+        <v>1803469.6</v>
       </c>
       <c r="H79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>330000</v>
+        <v>147300</v>
       </c>
       <c r="F80" t="n">
-        <v>24</v>
+        <v>2.3821</v>
       </c>
       <c r="G80" t="n">
-        <v>7920000</v>
+        <v>350879.4</v>
       </c>
       <c r="H80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>35550</v>
+        <v>36450</v>
       </c>
       <c r="F81" t="n">
-        <v>581</v>
+        <v>76.7514</v>
       </c>
       <c r="G81" t="n">
-        <v>20654550</v>
+        <v>2797588.9</v>
       </c>
       <c r="H81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>574000</v>
+        <v>119700</v>
       </c>
       <c r="F82" t="n">
-        <v>22</v>
+        <v>30.2349</v>
       </c>
       <c r="G82" t="n">
-        <v>12628000</v>
+        <v>3619119.6</v>
       </c>
       <c r="H82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -3110,30 +3102,30 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>165900</v>
+        <v>85400</v>
       </c>
       <c r="F83" t="n">
-        <v>24</v>
+        <v>9.785500000000001</v>
       </c>
       <c r="G83" t="n">
-        <v>3981600</v>
+        <v>835680.4</v>
       </c>
       <c r="H83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -3142,94 +3134,94 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>91300</v>
+        <v>183500</v>
       </c>
       <c r="F84" t="n">
-        <v>45</v>
+        <v>113.6562</v>
       </c>
       <c r="G84" t="n">
-        <v>4108500</v>
+        <v>20855919.6</v>
       </c>
       <c r="H84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-21</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>224500</v>
+        <v>183500</v>
       </c>
       <c r="F85" t="n">
-        <v>92</v>
+        <v>12.1963</v>
       </c>
       <c r="G85" t="n">
-        <v>20654000</v>
+        <v>2238023.8</v>
       </c>
       <c r="H85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6010</v>
+        <v>1849000</v>
       </c>
       <c r="F86" t="n">
-        <v>3435</v>
+        <v>5.5521</v>
       </c>
       <c r="G86" t="n">
-        <v>20644350</v>
+        <v>10265800.4</v>
       </c>
       <c r="H86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -3238,62 +3230,62 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>25800</v>
+        <v>260000</v>
       </c>
       <c r="F87" t="n">
-        <v>351</v>
+        <v>39.4838</v>
       </c>
       <c r="G87" t="n">
-        <v>9055800</v>
+        <v>10265800.4</v>
       </c>
       <c r="H87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>49150</v>
+        <v>24700</v>
       </c>
       <c r="F88" t="n">
-        <v>420</v>
+        <v>415.6194</v>
       </c>
       <c r="G88" t="n">
-        <v>20643000</v>
+        <v>10265800.4</v>
       </c>
       <c r="H88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>미래에셋생명</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>085620</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -3302,30 +3294,30 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>19280</v>
+        <v>48650</v>
       </c>
       <c r="F89" t="n">
-        <v>1071</v>
+        <v>422.0267</v>
       </c>
       <c r="G89" t="n">
-        <v>20648880</v>
+        <v>20531600.8</v>
       </c>
       <c r="H89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -3334,30 +3326,30 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>19740</v>
+        <v>87800</v>
       </c>
       <c r="F90" t="n">
-        <v>523</v>
+        <v>115.4542</v>
       </c>
       <c r="G90" t="n">
-        <v>10324020</v>
+        <v>10136875</v>
       </c>
       <c r="H90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -3366,158 +3358,164 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>25150</v>
+        <v>22750</v>
       </c>
       <c r="F91" t="n">
-        <v>821</v>
+        <v>891.1538</v>
       </c>
       <c r="G91" t="n">
-        <v>20648150</v>
+        <v>20273749.9</v>
       </c>
       <c r="H91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>153500</v>
+        <v>33150</v>
       </c>
       <c r="F92" t="n">
-        <v>24</v>
+        <v>569</v>
       </c>
       <c r="G92" t="n">
-        <v>3684000</v>
-      </c>
-      <c r="H92" t="inlineStr"/>
+        <v>18862350</v>
+      </c>
+      <c r="H92" t="n">
+        <v>-8.68</v>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6240</v>
+        <v>254500</v>
       </c>
       <c r="F93" t="n">
-        <v>3308</v>
+        <v>39.8306</v>
       </c>
       <c r="G93" t="n">
-        <v>20641920</v>
+        <v>10136875</v>
       </c>
       <c r="H93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>15520</v>
+        <v>79400</v>
       </c>
       <c r="F94" t="n">
-        <v>1330</v>
+        <v>246</v>
       </c>
       <c r="G94" t="n">
-        <v>20641600</v>
-      </c>
-      <c r="H94" t="inlineStr"/>
+        <v>19532400</v>
+      </c>
+      <c r="H94" t="n">
+        <v>-8</v>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>24200</v>
+        <v>14780</v>
       </c>
       <c r="F95" t="n">
-        <v>210</v>
+        <v>1338</v>
       </c>
       <c r="G95" t="n">
-        <v>5082000</v>
-      </c>
-      <c r="H95" t="inlineStr"/>
+        <v>19775640</v>
+      </c>
+      <c r="H95" t="n">
+        <v>33.89</v>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -3526,62 +3524,62 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>36300</v>
+        <v>195800</v>
       </c>
       <c r="F96" t="n">
-        <v>569</v>
+        <v>101.9921</v>
       </c>
       <c r="G96" t="n">
-        <v>20654700</v>
+        <v>19970062</v>
       </c>
       <c r="H96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>후성</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>093370</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>279500</v>
+        <v>14600</v>
       </c>
       <c r="F97" t="n">
-        <v>43</v>
+        <v>1367.8125</v>
       </c>
       <c r="G97" t="n">
-        <v>12018500</v>
+        <v>19970062</v>
       </c>
       <c r="H97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -3590,94 +3588,94 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>132600</v>
+        <v>36300</v>
       </c>
       <c r="F98" t="n">
-        <v>90</v>
+        <v>275.0697</v>
       </c>
       <c r="G98" t="n">
-        <v>11934000</v>
+        <v>9985031</v>
       </c>
       <c r="H98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>44600</v>
+        <v>159300</v>
       </c>
       <c r="F99" t="n">
-        <v>139</v>
+        <v>62.6807</v>
       </c>
       <c r="G99" t="n">
-        <v>6199400</v>
+        <v>9985031</v>
       </c>
       <c r="H99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>147100</v>
+        <v>147200</v>
       </c>
       <c r="F100" t="n">
-        <v>6</v>
+        <v>67</v>
       </c>
       <c r="G100" t="n">
-        <v>882600</v>
+        <v>9862400</v>
       </c>
       <c r="H100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -3686,84 +3684,86 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>33500</v>
+        <v>14540</v>
       </c>
       <c r="F101" t="n">
-        <v>8</v>
+        <v>983</v>
       </c>
       <c r="G101" t="n">
-        <v>268000</v>
+        <v>14292820</v>
       </c>
       <c r="H101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>143100</v>
+        <v>113400</v>
       </c>
       <c r="F102" t="n">
-        <v>95</v>
+        <v>167</v>
       </c>
       <c r="G102" t="n">
-        <v>13594500</v>
-      </c>
-      <c r="H102" t="inlineStr"/>
+        <v>18937800</v>
+      </c>
+      <c r="H102" t="n">
+        <v>-7.88</v>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>83800</v>
+        <v>24350</v>
       </c>
       <c r="F103" t="n">
-        <v>106</v>
+        <v>407</v>
       </c>
       <c r="G103" t="n">
-        <v>8882800</v>
+        <v>9910450</v>
       </c>
       <c r="H103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -3778,98 +3778,100 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>42300</v>
+        <v>44100</v>
       </c>
       <c r="F104" t="n">
         <v>488</v>
       </c>
       <c r="G104" t="n">
-        <v>20642400</v>
-      </c>
-      <c r="H104" t="inlineStr"/>
+        <v>21520800</v>
+      </c>
+      <c r="H104" t="n">
+        <v>4.26</v>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>81200</v>
+        <v>165700</v>
       </c>
       <c r="F105" t="n">
-        <v>135</v>
+        <v>120</v>
       </c>
       <c r="G105" t="n">
-        <v>10962000</v>
+        <v>19884000</v>
       </c>
       <c r="H105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>78600</v>
+        <v>28950</v>
       </c>
       <c r="F106" t="n">
-        <v>389</v>
+        <v>353</v>
       </c>
       <c r="G106" t="n">
-        <v>30575400</v>
+        <v>10219350</v>
       </c>
       <c r="H106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -3878,326 +3880,318 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>92500</v>
+        <v>1853000</v>
       </c>
       <c r="F107" t="n">
-        <v>106</v>
+        <v>11</v>
       </c>
       <c r="G107" t="n">
-        <v>9805000</v>
+        <v>20383000</v>
       </c>
       <c r="H107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>2026-09-04</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>25550</v>
+        <v>269000</v>
       </c>
       <c r="F108" t="n">
-        <v>1151</v>
+        <v>76</v>
       </c>
       <c r="G108" t="n">
-        <v>29408050</v>
+        <v>20444000</v>
       </c>
       <c r="H108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>대한유화</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006650</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>21800</v>
+        <v>106300</v>
       </c>
       <c r="F109" t="n">
-        <v>832</v>
+        <v>194</v>
       </c>
       <c r="G109" t="n">
-        <v>18137600</v>
+        <v>20622200</v>
       </c>
       <c r="H109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>엘앤에프</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>066970</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>32250</v>
+        <v>123100</v>
       </c>
       <c r="F110" t="n">
-        <v>878</v>
+        <v>167</v>
       </c>
       <c r="G110" t="n">
-        <v>28315500</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-5.33</v>
-      </c>
+        <v>20557700</v>
+      </c>
+      <c r="H110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>105800</v>
+        <v>1856000</v>
       </c>
       <c r="F111" t="n">
-        <v>332</v>
+        <v>23</v>
       </c>
       <c r="G111" t="n">
-        <v>35125600</v>
-      </c>
-      <c r="H111" t="n">
-        <v>17.17</v>
-      </c>
+        <v>42688000</v>
+      </c>
+      <c r="H111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>33750</v>
+        <v>49000</v>
       </c>
       <c r="F112" t="n">
-        <v>791</v>
+        <v>167</v>
       </c>
       <c r="G112" t="n">
-        <v>26696250</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.29</v>
-      </c>
+        <v>8183000</v>
+      </c>
+      <c r="H112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>SK바이오팜</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>326030</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>86300</v>
+        <v>13340</v>
       </c>
       <c r="F113" t="n">
-        <v>352</v>
+        <v>236</v>
       </c>
       <c r="G113" t="n">
-        <v>30377600</v>
+        <v>3148240</v>
       </c>
       <c r="H113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>21000</v>
+        <v>29800</v>
       </c>
       <c r="F114" t="n">
-        <v>1517</v>
+        <v>66</v>
       </c>
       <c r="G114" t="n">
-        <v>31857000</v>
-      </c>
-      <c r="H114" t="n">
-        <v>3.96</v>
-      </c>
+        <v>1966800</v>
+      </c>
+      <c r="H114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>21900</v>
+        <v>269500</v>
       </c>
       <c r="F115" t="n">
-        <v>906</v>
+        <v>118</v>
       </c>
       <c r="G115" t="n">
-        <v>19841400</v>
+        <v>31801000</v>
       </c>
       <c r="H115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>135300</v>
+        <v>330000</v>
       </c>
       <c r="F116" t="n">
-        <v>226</v>
+        <v>24</v>
       </c>
       <c r="G116" t="n">
-        <v>30577800</v>
+        <v>7920000</v>
       </c>
       <c r="H116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -4206,154 +4200,148 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>22250</v>
+        <v>35550</v>
       </c>
       <c r="F117" t="n">
-        <v>1399</v>
+        <v>581</v>
       </c>
       <c r="G117" t="n">
-        <v>31127750</v>
+        <v>20654550</v>
       </c>
       <c r="H117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>33500</v>
+        <v>574000</v>
       </c>
       <c r="F118" t="n">
-        <v>848</v>
+        <v>22</v>
       </c>
       <c r="G118" t="n">
-        <v>28408000</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-9.07</v>
-      </c>
+        <v>12628000</v>
+      </c>
+      <c r="H118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>300000</v>
+        <v>165900</v>
       </c>
       <c r="F119" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="G119" t="n">
-        <v>31200000</v>
-      </c>
-      <c r="H119" t="n">
-        <v>20.95</v>
-      </c>
+        <v>3981600</v>
+      </c>
+      <c r="H119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>003490</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>28200</v>
+        <v>91300</v>
       </c>
       <c r="F120" t="n">
-        <v>1105</v>
+        <v>45</v>
       </c>
       <c r="G120" t="n">
-        <v>31161000</v>
+        <v>4108500</v>
       </c>
       <c r="H120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>398000</v>
+        <v>224500</v>
       </c>
       <c r="F121" t="n">
-        <v>72</v>
+        <v>92</v>
       </c>
       <c r="G121" t="n">
-        <v>28656000</v>
-      </c>
-      <c r="H121" t="n">
-        <v>-6.88</v>
-      </c>
+        <v>20654000</v>
+      </c>
+      <c r="H121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4368,196 +4356,194 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>5620</v>
+        <v>6010</v>
       </c>
       <c r="F122" t="n">
-        <v>4707</v>
+        <v>3435</v>
       </c>
       <c r="G122" t="n">
-        <v>26453340</v>
-      </c>
-      <c r="H122" t="n">
-        <v>-8.220000000000001</v>
-      </c>
+        <v>20644350</v>
+      </c>
+      <c r="H122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>2026-08-27</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>126900</v>
+        <v>25800</v>
       </c>
       <c r="F123" t="n">
-        <v>246</v>
+        <v>351</v>
       </c>
       <c r="G123" t="n">
-        <v>31217400</v>
+        <v>9055800</v>
       </c>
       <c r="H123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>1671000</v>
+        <v>49150</v>
       </c>
       <c r="F124" t="n">
-        <v>44</v>
+        <v>420</v>
       </c>
       <c r="G124" t="n">
-        <v>73524000</v>
+        <v>20643000</v>
       </c>
       <c r="H124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>미래에셋생명</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>085620</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>50600</v>
+        <v>19280</v>
       </c>
       <c r="F125" t="n">
-        <v>186</v>
+        <v>1071</v>
       </c>
       <c r="G125" t="n">
-        <v>9411600</v>
+        <v>20648880</v>
       </c>
       <c r="H125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E126" t="n">
-        <v>11720</v>
+        <v>19740</v>
       </c>
       <c r="F126" t="n">
-        <v>665</v>
+        <v>523</v>
       </c>
       <c r="G126" t="n">
-        <v>7793800</v>
+        <v>10324020</v>
       </c>
       <c r="H126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>414000</v>
+        <v>25150</v>
       </c>
       <c r="F127" t="n">
-        <v>26</v>
+        <v>821</v>
       </c>
       <c r="G127" t="n">
-        <v>10764000</v>
+        <v>20648150</v>
       </c>
       <c r="H127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -4566,514 +4552,510 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>257000</v>
+        <v>153500</v>
       </c>
       <c r="F128" t="n">
-        <v>239</v>
+        <v>24</v>
       </c>
       <c r="G128" t="n">
-        <v>61423000</v>
+        <v>3684000</v>
       </c>
       <c r="H128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>33900</v>
+        <v>6240</v>
       </c>
       <c r="F129" t="n">
-        <v>292</v>
+        <v>3308</v>
       </c>
       <c r="G129" t="n">
-        <v>9898800</v>
+        <v>20641920</v>
       </c>
       <c r="H129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>515000</v>
+        <v>15520</v>
       </c>
       <c r="F130" t="n">
-        <v>17</v>
+        <v>1330</v>
       </c>
       <c r="G130" t="n">
-        <v>8755000</v>
+        <v>20641600</v>
       </c>
       <c r="H130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>141200</v>
+        <v>24200</v>
       </c>
       <c r="F131" t="n">
-        <v>81</v>
+        <v>210</v>
       </c>
       <c r="G131" t="n">
-        <v>11437200</v>
+        <v>5082000</v>
       </c>
       <c r="H131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>6320</v>
+        <v>36300</v>
       </c>
       <c r="F132" t="n">
-        <v>1396</v>
+        <v>569</v>
       </c>
       <c r="G132" t="n">
-        <v>8822720</v>
+        <v>20654700</v>
       </c>
       <c r="H132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>알테오젠</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>196170</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>90300</v>
+        <v>279500</v>
       </c>
       <c r="F133" t="n">
-        <v>332</v>
+        <v>43</v>
       </c>
       <c r="G133" t="n">
-        <v>29979600</v>
+        <v>12018500</v>
       </c>
       <c r="H133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>163100</v>
+        <v>132600</v>
       </c>
       <c r="F134" t="n">
-        <v>119</v>
+        <v>90</v>
       </c>
       <c r="G134" t="n">
-        <v>19408900</v>
-      </c>
-      <c r="H134" t="n">
-        <v>-3.2</v>
-      </c>
+        <v>11934000</v>
+      </c>
+      <c r="H134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>실리콘투</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>257720</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>37900</v>
+        <v>44600</v>
       </c>
       <c r="F135" t="n">
-        <v>163</v>
+        <v>139</v>
       </c>
       <c r="G135" t="n">
-        <v>6177700</v>
+        <v>6199400</v>
       </c>
       <c r="H135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>19990</v>
+        <v>147100</v>
       </c>
       <c r="F136" t="n">
-        <v>615</v>
+        <v>6</v>
       </c>
       <c r="G136" t="n">
-        <v>12293850</v>
+        <v>882600</v>
       </c>
       <c r="H136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>35100</v>
+        <v>33500</v>
       </c>
       <c r="F137" t="n">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="G137" t="n">
-        <v>11232000</v>
+        <v>268000</v>
       </c>
       <c r="H137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>286000</v>
+        <v>143100</v>
       </c>
       <c r="F138" t="n">
-        <v>20</v>
+        <v>95</v>
       </c>
       <c r="G138" t="n">
-        <v>5720000</v>
+        <v>13594500</v>
       </c>
       <c r="H138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>416000</v>
+        <v>83800</v>
       </c>
       <c r="F139" t="n">
-        <v>51</v>
+        <v>106</v>
       </c>
       <c r="G139" t="n">
-        <v>21216000</v>
-      </c>
-      <c r="H139" t="n">
-        <v>5.85</v>
-      </c>
+        <v>8882800</v>
+      </c>
+      <c r="H139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E140" t="n">
-        <v>49450</v>
+        <v>42300</v>
       </c>
       <c r="F140" t="n">
-        <v>153</v>
+        <v>488</v>
       </c>
       <c r="G140" t="n">
-        <v>7565850</v>
+        <v>20642400</v>
       </c>
       <c r="H140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-09</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>138000</v>
+        <v>81200</v>
       </c>
       <c r="F141" t="n">
-        <v>68</v>
+        <v>135</v>
       </c>
       <c r="G141" t="n">
-        <v>9384000</v>
+        <v>10962000</v>
       </c>
       <c r="H141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>31950</v>
+        <v>78600</v>
       </c>
       <c r="F142" t="n">
-        <v>339</v>
+        <v>389</v>
       </c>
       <c r="G142" t="n">
-        <v>10831050</v>
+        <v>30575400</v>
       </c>
       <c r="H142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>124800</v>
+        <v>92500</v>
       </c>
       <c r="F143" t="n">
-        <v>78</v>
+        <v>106</v>
       </c>
       <c r="G143" t="n">
-        <v>9734400</v>
+        <v>9805000</v>
       </c>
       <c r="H143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>한국화장품제조</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>003350</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -5082,128 +5064,130 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>10800</v>
+        <v>25550</v>
       </c>
       <c r="F144" t="n">
-        <v>1892</v>
+        <v>1151</v>
       </c>
       <c r="G144" t="n">
-        <v>20433600</v>
+        <v>29408050</v>
       </c>
       <c r="H144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>11880</v>
+        <v>21800</v>
       </c>
       <c r="F145" t="n">
-        <v>1474</v>
+        <v>832</v>
       </c>
       <c r="G145" t="n">
-        <v>17511120</v>
-      </c>
-      <c r="H145" t="n">
-        <v>-12.45</v>
-      </c>
+        <v>18137600</v>
+      </c>
+      <c r="H145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>삼성중공업</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>010140</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>20200</v>
+        <v>32250</v>
       </c>
       <c r="F146" t="n">
-        <v>1517</v>
+        <v>878</v>
       </c>
       <c r="G146" t="n">
-        <v>30643400</v>
-      </c>
-      <c r="H146" t="inlineStr"/>
+        <v>28315500</v>
+      </c>
+      <c r="H146" t="n">
+        <v>-5.33</v>
+      </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>102200</v>
+        <v>105800</v>
       </c>
       <c r="F147" t="n">
-        <v>200</v>
+        <v>332</v>
       </c>
       <c r="G147" t="n">
-        <v>20440000</v>
-      </c>
-      <c r="H147" t="inlineStr"/>
+        <v>35125600</v>
+      </c>
+      <c r="H147" t="n">
+        <v>17.17</v>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -5212,132 +5196,130 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>23450</v>
+        <v>33750</v>
       </c>
       <c r="F148" t="n">
-        <v>762</v>
+        <v>791</v>
       </c>
       <c r="G148" t="n">
-        <v>17868900</v>
+        <v>26696250</v>
       </c>
       <c r="H148" t="n">
-        <v>-10.67</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>SK바이오팜</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>326030</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>22050</v>
+        <v>86300</v>
       </c>
       <c r="F149" t="n">
-        <v>875</v>
+        <v>352</v>
       </c>
       <c r="G149" t="n">
-        <v>19293750</v>
-      </c>
-      <c r="H149" t="n">
-        <v>-3.5</v>
-      </c>
+        <v>30377600</v>
+      </c>
+      <c r="H149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>아이티센글로벌</t>
+          <t>삼성중공업</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>124500</t>
+          <t>010140</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>32550</v>
+        <v>21000</v>
       </c>
       <c r="F150" t="n">
-        <v>628</v>
+        <v>1517</v>
       </c>
       <c r="G150" t="n">
-        <v>20441400</v>
-      </c>
-      <c r="H150" t="inlineStr"/>
+        <v>31857000</v>
+      </c>
+      <c r="H150" t="n">
+        <v>3.96</v>
+      </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E151" t="n">
-        <v>99700</v>
+        <v>21900</v>
       </c>
       <c r="F151" t="n">
-        <v>180</v>
+        <v>906</v>
       </c>
       <c r="G151" t="n">
-        <v>17946000</v>
-      </c>
-      <c r="H151" t="n">
-        <v>-10.1</v>
-      </c>
+        <v>19841400</v>
+      </c>
+      <c r="H151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -5346,30 +5328,30 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1662000</v>
+        <v>135300</v>
       </c>
       <c r="F152" t="n">
-        <v>150</v>
+        <v>226</v>
       </c>
       <c r="G152" t="n">
-        <v>249300000</v>
+        <v>30577800</v>
       </c>
       <c r="H152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -5378,94 +5360,98 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>49700</v>
+        <v>22250</v>
       </c>
       <c r="F153" t="n">
-        <v>402</v>
+        <v>1399</v>
       </c>
       <c r="G153" t="n">
-        <v>19979400</v>
+        <v>31127750</v>
       </c>
       <c r="H153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>005380</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>435000</v>
+        <v>33500</v>
       </c>
       <c r="F154" t="n">
-        <v>46</v>
+        <v>848</v>
       </c>
       <c r="G154" t="n">
-        <v>20010000</v>
-      </c>
-      <c r="H154" t="inlineStr"/>
+        <v>28408000</v>
+      </c>
+      <c r="H154" t="n">
+        <v>-9.07</v>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>268500</v>
+        <v>300000</v>
       </c>
       <c r="F155" t="n">
-        <v>931</v>
+        <v>104</v>
       </c>
       <c r="G155" t="n">
-        <v>249973500</v>
-      </c>
-      <c r="H155" t="inlineStr"/>
+        <v>31200000</v>
+      </c>
+      <c r="H155" t="n">
+        <v>20.95</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>이수화학</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>005950</t>
+          <t>003490</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -5474,94 +5460,98 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>13570</v>
+        <v>28200</v>
       </c>
       <c r="F156" t="n">
-        <v>1474</v>
+        <v>1105</v>
       </c>
       <c r="G156" t="n">
-        <v>20002180</v>
+        <v>31161000</v>
       </c>
       <c r="H156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>343500</v>
+        <v>398000</v>
       </c>
       <c r="F157" t="n">
-        <v>87</v>
+        <v>72</v>
       </c>
       <c r="G157" t="n">
-        <v>29884500</v>
-      </c>
-      <c r="H157" t="inlineStr"/>
+        <v>28656000</v>
+      </c>
+      <c r="H157" t="n">
+        <v>-6.88</v>
+      </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>GS건설</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>006360</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>34150</v>
+        <v>5620</v>
       </c>
       <c r="F158" t="n">
-        <v>586</v>
+        <v>4707</v>
       </c>
       <c r="G158" t="n">
-        <v>20011900</v>
-      </c>
-      <c r="H158" t="inlineStr"/>
+        <v>26453340</v>
+      </c>
+      <c r="H158" t="n">
+        <v>-8.220000000000001</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-27</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -5570,318 +5560,318 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>488000</v>
+        <v>126900</v>
       </c>
       <c r="F159" t="n">
-        <v>41</v>
+        <v>246</v>
       </c>
       <c r="G159" t="n">
-        <v>20008000</v>
+        <v>31217400</v>
       </c>
       <c r="H159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>153600</v>
+        <v>1671000</v>
       </c>
       <c r="F160" t="n">
-        <v>130</v>
+        <v>44</v>
       </c>
       <c r="G160" t="n">
-        <v>19968000</v>
+        <v>73524000</v>
       </c>
       <c r="H160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>99800</v>
+        <v>50600</v>
       </c>
       <c r="F161" t="n">
-        <v>200</v>
+        <v>186</v>
       </c>
       <c r="G161" t="n">
-        <v>19960000</v>
+        <v>9411600</v>
       </c>
       <c r="H161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>한국화장품제조</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>003350</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E162" t="n">
-        <v>6040</v>
+        <v>11720</v>
       </c>
       <c r="F162" t="n">
-        <v>3311</v>
+        <v>665</v>
       </c>
       <c r="G162" t="n">
-        <v>19998440</v>
+        <v>7793800</v>
       </c>
       <c r="H162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>STX엔진</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>077970</t>
+          <t>005380</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E163" t="n">
-        <v>26250</v>
+        <v>414000</v>
       </c>
       <c r="F163" t="n">
-        <v>762</v>
+        <v>26</v>
       </c>
       <c r="G163" t="n">
-        <v>20002500</v>
+        <v>10764000</v>
       </c>
       <c r="H163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>22850</v>
+        <v>257000</v>
       </c>
       <c r="F164" t="n">
-        <v>875</v>
+        <v>239</v>
       </c>
       <c r="G164" t="n">
-        <v>19993750</v>
+        <v>61423000</v>
       </c>
       <c r="H164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>KB금융</t>
+          <t>GS건설</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>105560</t>
+          <t>006360</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E165" t="n">
-        <v>168500</v>
+        <v>33900</v>
       </c>
       <c r="F165" t="n">
-        <v>119</v>
+        <v>292</v>
       </c>
       <c r="G165" t="n">
-        <v>20051500</v>
+        <v>9898800</v>
       </c>
       <c r="H165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>22850</v>
+        <v>515000</v>
       </c>
       <c r="F166" t="n">
-        <v>875</v>
+        <v>17</v>
       </c>
       <c r="G166" t="n">
-        <v>19993750</v>
+        <v>8755000</v>
       </c>
       <c r="H166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>170920</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>37900</v>
+        <v>141200</v>
       </c>
       <c r="F167" t="n">
-        <v>528</v>
+        <v>81</v>
       </c>
       <c r="G167" t="n">
-        <v>20011200</v>
+        <v>11437200</v>
       </c>
       <c r="H167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>코스맥스</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>192820</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E168" t="n">
-        <v>239000</v>
+        <v>6320</v>
       </c>
       <c r="F168" t="n">
-        <v>84</v>
+        <v>1396</v>
       </c>
       <c r="G168" t="n">
-        <v>20076000</v>
+        <v>8822720</v>
       </c>
       <c r="H168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>알테오젠</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>196170</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -5890,207 +5880,1371 @@
         </is>
       </c>
       <c r="E169" t="n">
-        <v>298000</v>
+        <v>90300</v>
       </c>
       <c r="F169" t="n">
-        <v>117</v>
+        <v>332</v>
       </c>
       <c r="G169" t="n">
-        <v>34866000</v>
+        <v>29979600</v>
       </c>
       <c r="H169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>파마리서치</t>
+          <t>KB금융</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>214450</t>
+          <t>105560</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E170" t="n">
-        <v>393000</v>
+        <v>163100</v>
       </c>
       <c r="F170" t="n">
-        <v>51</v>
+        <v>119</v>
       </c>
       <c r="G170" t="n">
-        <v>20043000</v>
-      </c>
-      <c r="H170" t="inlineStr"/>
+        <v>19408900</v>
+      </c>
+      <c r="H170" t="n">
+        <v>-3.2</v>
+      </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아이티센글로벌</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>124500</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E171" t="n">
-        <v>110900</v>
+        <v>37900</v>
       </c>
       <c r="F171" t="n">
-        <v>180</v>
+        <v>163</v>
       </c>
       <c r="G171" t="n">
-        <v>19962000</v>
+        <v>6177700</v>
       </c>
       <c r="H171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>실리콘투</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>257720</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E172" t="n">
-        <v>44500</v>
+        <v>19990</v>
       </c>
       <c r="F172" t="n">
-        <v>449</v>
+        <v>615</v>
       </c>
       <c r="G172" t="n">
-        <v>19980500</v>
+        <v>12293850</v>
       </c>
       <c r="H172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>엘티씨</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>170920</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E173" t="n">
-        <v>135000</v>
+        <v>35100</v>
       </c>
       <c r="F173" t="n">
-        <v>148</v>
+        <v>320</v>
       </c>
       <c r="G173" t="n">
-        <v>19980000</v>
+        <v>11232000</v>
       </c>
       <c r="H173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>2026-08-18</t>
+          <t>2026-08-24</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>코스맥스</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>192820</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E174" t="n">
-        <v>33750</v>
+        <v>286000</v>
       </c>
       <c r="F174" t="n">
-        <v>593</v>
+        <v>20</v>
       </c>
       <c r="G174" t="n">
-        <v>20013750</v>
+        <v>5720000</v>
       </c>
       <c r="H174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>416000</v>
+      </c>
+      <c r="F175" t="n">
+        <v>51</v>
+      </c>
+      <c r="G175" t="n">
+        <v>21216000</v>
+      </c>
+      <c r="H175" t="n">
+        <v>5.85</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E176" t="n">
+        <v>49450</v>
+      </c>
+      <c r="F176" t="n">
+        <v>153</v>
+      </c>
+      <c r="G176" t="n">
+        <v>7565850</v>
+      </c>
+      <c r="H176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E177" t="n">
+        <v>138000</v>
+      </c>
+      <c r="F177" t="n">
+        <v>68</v>
+      </c>
+      <c r="G177" t="n">
+        <v>9384000</v>
+      </c>
+      <c r="H177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E178" t="n">
+        <v>31950</v>
+      </c>
+      <c r="F178" t="n">
+        <v>339</v>
+      </c>
+      <c r="G178" t="n">
+        <v>10831050</v>
+      </c>
+      <c r="H178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>HD현대에너지솔루션</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>322000</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E179" t="n">
+        <v>124800</v>
+      </c>
+      <c r="F179" t="n">
+        <v>78</v>
+      </c>
+      <c r="G179" t="n">
+        <v>9734400</v>
+      </c>
+      <c r="H179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>한국화장품제조</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>003350</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E180" t="n">
+        <v>10800</v>
+      </c>
+      <c r="F180" t="n">
+        <v>1892</v>
+      </c>
+      <c r="G180" t="n">
+        <v>20433600</v>
+      </c>
+      <c r="H180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E181" t="n">
+        <v>11880</v>
+      </c>
+      <c r="F181" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G181" t="n">
+        <v>17511120</v>
+      </c>
+      <c r="H181" t="n">
+        <v>-12.45</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>삼성중공업</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>010140</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E182" t="n">
+        <v>20200</v>
+      </c>
+      <c r="F182" t="n">
+        <v>1517</v>
+      </c>
+      <c r="G182" t="n">
+        <v>30643400</v>
+      </c>
+      <c r="H182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>비중 확대</t>
+        </is>
+      </c>
+      <c r="E183" t="n">
+        <v>102200</v>
+      </c>
+      <c r="F183" t="n">
+        <v>200</v>
+      </c>
+      <c r="G183" t="n">
+        <v>20440000</v>
+      </c>
+      <c r="H183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E184" t="n">
+        <v>23450</v>
+      </c>
+      <c r="F184" t="n">
+        <v>762</v>
+      </c>
+      <c r="G184" t="n">
+        <v>17868900</v>
+      </c>
+      <c r="H184" t="n">
+        <v>-10.67</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E185" t="n">
+        <v>22050</v>
+      </c>
+      <c r="F185" t="n">
+        <v>875</v>
+      </c>
+      <c r="G185" t="n">
+        <v>19293750</v>
+      </c>
+      <c r="H185" t="n">
+        <v>-3.5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>아이티센글로벌</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>124500</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E186" t="n">
+        <v>32550</v>
+      </c>
+      <c r="F186" t="n">
+        <v>628</v>
+      </c>
+      <c r="G186" t="n">
+        <v>20441400</v>
+      </c>
+      <c r="H186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>2026-08-21</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>편출</t>
+        </is>
+      </c>
+      <c r="E187" t="n">
+        <v>99700</v>
+      </c>
+      <c r="F187" t="n">
+        <v>180</v>
+      </c>
+      <c r="G187" t="n">
+        <v>17946000</v>
+      </c>
+      <c r="H187" t="n">
+        <v>-10.1</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="B175" t="inlineStr">
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>SK하이닉스</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>000660</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E188" t="n">
+        <v>1662000</v>
+      </c>
+      <c r="F188" t="n">
+        <v>150</v>
+      </c>
+      <c r="G188" t="n">
+        <v>249300000</v>
+      </c>
+      <c r="H188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>현대해상</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>001450</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E189" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F189" t="n">
+        <v>402</v>
+      </c>
+      <c r="G189" t="n">
+        <v>19979400</v>
+      </c>
+      <c r="H189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>005380</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E190" t="n">
+        <v>435000</v>
+      </c>
+      <c r="F190" t="n">
+        <v>46</v>
+      </c>
+      <c r="G190" t="n">
+        <v>20010000</v>
+      </c>
+      <c r="H190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>005930</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E191" t="n">
+        <v>268500</v>
+      </c>
+      <c r="F191" t="n">
+        <v>931</v>
+      </c>
+      <c r="G191" t="n">
+        <v>249973500</v>
+      </c>
+      <c r="H191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>이수화학</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>005950</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E192" t="n">
+        <v>13570</v>
+      </c>
+      <c r="F192" t="n">
+        <v>1474</v>
+      </c>
+      <c r="G192" t="n">
+        <v>20002180</v>
+      </c>
+      <c r="H192" t="inlineStr"/>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>LS</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>006260</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E193" t="n">
+        <v>343500</v>
+      </c>
+      <c r="F193" t="n">
+        <v>87</v>
+      </c>
+      <c r="G193" t="n">
+        <v>29884500</v>
+      </c>
+      <c r="H193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>006360</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E194" t="n">
+        <v>34150</v>
+      </c>
+      <c r="F194" t="n">
+        <v>586</v>
+      </c>
+      <c r="G194" t="n">
+        <v>20011900</v>
+      </c>
+      <c r="H194" t="inlineStr"/>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>삼성SDI</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>006400</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E195" t="n">
+        <v>488000</v>
+      </c>
+      <c r="F195" t="n">
+        <v>41</v>
+      </c>
+      <c r="G195" t="n">
+        <v>20008000</v>
+      </c>
+      <c r="H195" t="inlineStr"/>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>S-Oil</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>010950</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E196" t="n">
+        <v>153600</v>
+      </c>
+      <c r="F196" t="n">
+        <v>130</v>
+      </c>
+      <c r="G196" t="n">
+        <v>19968000</v>
+      </c>
+      <c r="H196" t="inlineStr"/>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>SK텔레콤</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>017670</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E197" t="n">
+        <v>99800</v>
+      </c>
+      <c r="F197" t="n">
+        <v>200</v>
+      </c>
+      <c r="G197" t="n">
+        <v>19960000</v>
+      </c>
+      <c r="H197" t="inlineStr"/>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>팬오션</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>028670</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E198" t="n">
+        <v>6040</v>
+      </c>
+      <c r="F198" t="n">
+        <v>3311</v>
+      </c>
+      <c r="G198" t="n">
+        <v>19998440</v>
+      </c>
+      <c r="H198" t="inlineStr"/>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>STX엔진</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>077970</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E199" t="n">
+        <v>26250</v>
+      </c>
+      <c r="F199" t="n">
+        <v>762</v>
+      </c>
+      <c r="G199" t="n">
+        <v>20002500</v>
+      </c>
+      <c r="H199" t="inlineStr"/>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>089890</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E200" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F200" t="n">
+        <v>875</v>
+      </c>
+      <c r="G200" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H200" t="inlineStr"/>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>KB금융</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>105560</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E201" t="n">
+        <v>168500</v>
+      </c>
+      <c r="F201" t="n">
+        <v>119</v>
+      </c>
+      <c r="G201" t="n">
+        <v>20051500</v>
+      </c>
+      <c r="H201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>159010</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E202" t="n">
+        <v>22850</v>
+      </c>
+      <c r="F202" t="n">
+        <v>875</v>
+      </c>
+      <c r="G202" t="n">
+        <v>19993750</v>
+      </c>
+      <c r="H202" t="inlineStr"/>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>170920</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E203" t="n">
+        <v>37900</v>
+      </c>
+      <c r="F203" t="n">
+        <v>528</v>
+      </c>
+      <c r="G203" t="n">
+        <v>20011200</v>
+      </c>
+      <c r="H203" t="inlineStr"/>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>코스맥스</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>192820</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E204" t="n">
+        <v>239000</v>
+      </c>
+      <c r="F204" t="n">
+        <v>84</v>
+      </c>
+      <c r="G204" t="n">
+        <v>20076000</v>
+      </c>
+      <c r="H204" t="inlineStr"/>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>알테오젠</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>196170</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E205" t="n">
+        <v>298000</v>
+      </c>
+      <c r="F205" t="n">
+        <v>117</v>
+      </c>
+      <c r="G205" t="n">
+        <v>34866000</v>
+      </c>
+      <c r="H205" t="inlineStr"/>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>파마리서치</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>214450</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E206" t="n">
+        <v>393000</v>
+      </c>
+      <c r="F206" t="n">
+        <v>51</v>
+      </c>
+      <c r="G206" t="n">
+        <v>20043000</v>
+      </c>
+      <c r="H206" t="inlineStr"/>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>222800</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E207" t="n">
+        <v>110900</v>
+      </c>
+      <c r="F207" t="n">
+        <v>180</v>
+      </c>
+      <c r="G207" t="n">
+        <v>19962000</v>
+      </c>
+      <c r="H207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>실리콘투</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>257720</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E208" t="n">
+        <v>44500</v>
+      </c>
+      <c r="F208" t="n">
+        <v>449</v>
+      </c>
+      <c r="G208" t="n">
+        <v>19980500</v>
+      </c>
+      <c r="H208" t="inlineStr"/>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>세아제강</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>306200</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E209" t="n">
+        <v>135000</v>
+      </c>
+      <c r="F209" t="n">
+        <v>148</v>
+      </c>
+      <c r="G209" t="n">
+        <v>19980000</v>
+      </c>
+      <c r="H209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>우리금융지주</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>316140</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>편입</t>
+        </is>
+      </c>
+      <c r="E210" t="n">
+        <v>33750</v>
+      </c>
+      <c r="F210" t="n">
+        <v>593</v>
+      </c>
+      <c r="G210" t="n">
+        <v>20013750</v>
+      </c>
+      <c r="H210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
         <is>
           <t>HD현대에너지솔루션</t>
         </is>
       </c>
-      <c r="C175" t="inlineStr">
+      <c r="C211" t="inlineStr">
         <is>
           <t>322000</t>
         </is>
       </c>
-      <c r="D175" t="inlineStr">
+      <c r="D211" t="inlineStr">
         <is>
           <t>편입</t>
         </is>
       </c>
-      <c r="E175" t="n">
+      <c r="E211" t="n">
         <v>124600</v>
       </c>
-      <c r="F175" t="n">
+      <c r="F211" t="n">
         <v>161</v>
       </c>
-      <c r="G175" t="n">
+      <c r="G211" t="n">
         <v>20060600</v>
       </c>
-      <c r="H175" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/downloads/troy_mp_history.xlsx
+++ b/docs/downloads/troy_mp_history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H211"/>
+  <dimension ref="A1:H216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -473,81 +473,85 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>000660</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1842000</v>
+        <v>113100</v>
       </c>
       <c r="F2" t="n">
-        <v>4.4662</v>
+        <v>185.2126</v>
       </c>
       <c r="G2" t="n">
-        <v>8226684.7</v>
-      </c>
-      <c r="H2" t="inlineStr"/>
+        <v>20947543.1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>-9.550000000000001</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>000720</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>114700</v>
+        <v>300500</v>
       </c>
       <c r="F3" t="n">
-        <v>20.0826</v>
+        <v>109.0002</v>
       </c>
       <c r="G3" t="n">
-        <v>2303471.7</v>
-      </c>
-      <c r="H3" t="inlineStr"/>
+        <v>32754558.6</v>
+      </c>
+      <c r="H3" t="n">
+        <v>-7.52</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>현대해상</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>001450</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -556,79 +560,81 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>47650</v>
+        <v>6260</v>
       </c>
       <c r="F4" t="n">
-        <v>27.6237</v>
+        <v>1755.1067</v>
       </c>
       <c r="G4" t="n">
-        <v>1316269.6</v>
+        <v>10986967.7</v>
       </c>
       <c r="H4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>알멕</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>005930</t>
+          <t>354320</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>276000</v>
+        <v>50800</v>
       </c>
       <c r="F5" t="n">
-        <v>17.0892</v>
+        <v>432.5578</v>
       </c>
       <c r="G5" t="n">
-        <v>4716632.6</v>
+        <v>21973935.4</v>
       </c>
       <c r="H5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2026-10-02</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LS</t>
+          <t>달바글로벌</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>006260</t>
+          <t>483650</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>299000</v>
+        <v>182200</v>
       </c>
       <c r="F6" t="n">
-        <v>45.123</v>
+        <v>173.4945</v>
       </c>
       <c r="G6" t="n">
-        <v>13491762.9</v>
-      </c>
-      <c r="H6" t="inlineStr"/>
+        <v>31610702.7</v>
+      </c>
+      <c r="H6" t="n">
+        <v>6.44</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -638,12 +644,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>006400</t>
+          <t>000660</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,13 +658,13 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>529000</v>
+        <v>1842000</v>
       </c>
       <c r="F7" t="n">
-        <v>2.9029</v>
+        <v>4.4662</v>
       </c>
       <c r="G7" t="n">
-        <v>1535647.8</v>
+        <v>8226684.7</v>
       </c>
       <c r="H7" t="inlineStr"/>
     </row>
@@ -670,27 +676,27 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>010950</t>
+          <t>000720</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>164900</v>
+        <v>114700</v>
       </c>
       <c r="F8" t="n">
-        <v>53.2149</v>
+        <v>20.0826</v>
       </c>
       <c r="G8" t="n">
-        <v>8775130.300000001</v>
+        <v>2303471.7</v>
       </c>
       <c r="H8" t="inlineStr"/>
     </row>
@@ -702,12 +708,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
+          <t>현대해상</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>012450</t>
+          <t>001450</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -716,13 +722,13 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1069000</v>
+        <v>47650</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5391</v>
+        <v>27.6237</v>
       </c>
       <c r="G9" t="n">
-        <v>1645336.9</v>
+        <v>1316269.6</v>
       </c>
       <c r="H9" t="inlineStr"/>
     </row>
@@ -734,12 +740,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SK텔레콤</t>
+          <t>삼성전자</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>017670</t>
+          <t>005930</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -748,13 +754,13 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>88600</v>
+        <v>276000</v>
       </c>
       <c r="F10" t="n">
-        <v>18.5704</v>
+        <v>17.0892</v>
       </c>
       <c r="G10" t="n">
-        <v>1645336.9</v>
+        <v>4716632.6</v>
       </c>
       <c r="H10" t="inlineStr"/>
     </row>
@@ -766,12 +772,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>삼성에스디에스</t>
+          <t>LS</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>018260</t>
+          <t>006260</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -780,13 +786,13 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>219000</v>
+        <v>299000</v>
       </c>
       <c r="F11" t="n">
-        <v>4.5078</v>
+        <v>45.123</v>
       </c>
       <c r="G11" t="n">
-        <v>987202.2</v>
+        <v>13491762.9</v>
       </c>
       <c r="H11" t="inlineStr"/>
     </row>
@@ -798,12 +804,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>팬오션</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>028670</t>
+          <t>006400</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -812,13 +818,13 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6250</v>
+        <v>529000</v>
       </c>
       <c r="F12" t="n">
-        <v>87.7513</v>
+        <v>2.9029</v>
       </c>
       <c r="G12" t="n">
-        <v>548445.6</v>
+        <v>1535647.8</v>
       </c>
       <c r="H12" t="inlineStr"/>
     </row>
@@ -830,27 +836,27 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>삼성생명</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>032830</t>
+          <t>010950</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>288000</v>
+        <v>164900</v>
       </c>
       <c r="F13" t="n">
-        <v>5.3321</v>
+        <v>53.2149</v>
       </c>
       <c r="G13" t="n">
-        <v>1535647.8</v>
+        <v>8775130.300000001</v>
       </c>
       <c r="H13" t="inlineStr"/>
     </row>
@@ -862,27 +868,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>에프에스티</t>
+          <t>한화에어로스페이스</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>036810</t>
+          <t>012450</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>35700</v>
+        <v>1069000</v>
       </c>
       <c r="F14" t="n">
-        <v>73.7406</v>
+        <v>1.5391</v>
       </c>
       <c r="G14" t="n">
-        <v>2632539.1</v>
+        <v>1645336.9</v>
       </c>
       <c r="H14" t="inlineStr"/>
     </row>
@@ -894,12 +900,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>SK텔레콤</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>017670</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -908,13 +914,13 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>126700</v>
+        <v>88600</v>
       </c>
       <c r="F15" t="n">
-        <v>0.8657</v>
+        <v>18.5704</v>
       </c>
       <c r="G15" t="n">
-        <v>109689.1</v>
+        <v>1645336.9</v>
       </c>
       <c r="H15" t="inlineStr"/>
     </row>
@@ -926,12 +932,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>산일전기</t>
+          <t>삼성에스디에스</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>062040</t>
+          <t>018260</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -940,13 +946,13 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>227000</v>
+        <v>219000</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4832</v>
+        <v>4.5078</v>
       </c>
       <c r="G16" t="n">
-        <v>109689.1</v>
+        <v>987202.2</v>
       </c>
       <c r="H16" t="inlineStr"/>
     </row>
@@ -958,27 +964,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>한양디지텍</t>
+          <t>팬오션</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>078350</t>
+          <t>028670</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>36000</v>
+        <v>6250</v>
       </c>
       <c r="F17" t="n">
-        <v>216.3313</v>
+        <v>87.7513</v>
       </c>
       <c r="G17" t="n">
-        <v>7787928.2</v>
+        <v>548445.6</v>
       </c>
       <c r="H17" t="inlineStr"/>
     </row>
@@ -990,27 +996,27 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>제우스</t>
+          <t>삼성생명</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>079370</t>
+          <t>032830</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>14360</v>
+        <v>288000</v>
       </c>
       <c r="F18" t="n">
-        <v>229.1556</v>
+        <v>5.3321</v>
       </c>
       <c r="G18" t="n">
-        <v>3290673.9</v>
+        <v>1535647.8</v>
       </c>
       <c r="H18" t="inlineStr"/>
     </row>
@@ -1022,27 +1028,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>한화엔진</t>
+          <t>에프에스티</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>082740</t>
+          <t>036810</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>48600</v>
+        <v>35700</v>
       </c>
       <c r="F19" t="n">
-        <v>29.3407</v>
+        <v>73.7406</v>
       </c>
       <c r="G19" t="n">
-        <v>1425958.7</v>
+        <v>2632539.1</v>
       </c>
       <c r="H19" t="inlineStr"/>
     </row>
@@ -1054,27 +1060,27 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>동국제약</t>
+          <t>한전기술</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>086450</t>
+          <t>052690</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>22900</v>
+        <v>126700</v>
       </c>
       <c r="F20" t="n">
-        <v>14.3698</v>
+        <v>0.8657</v>
       </c>
       <c r="G20" t="n">
-        <v>329067.4</v>
+        <v>109689.1</v>
       </c>
       <c r="H20" t="inlineStr"/>
     </row>
@@ -1086,27 +1092,27 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>코세스</t>
+          <t>산일전기</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>089890</t>
+          <t>062040</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>36450</v>
+        <v>227000</v>
       </c>
       <c r="F21" t="n">
-        <v>240.7443</v>
+        <v>0.4832</v>
       </c>
       <c r="G21" t="n">
-        <v>8775130.300000001</v>
+        <v>109689.1</v>
       </c>
       <c r="H21" t="inlineStr"/>
     </row>
@@ -1118,12 +1124,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>한양디지텍</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>095610</t>
+          <t>078350</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1132,13 +1138,13 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>178400</v>
+        <v>36000</v>
       </c>
       <c r="F22" t="n">
-        <v>11.0673</v>
+        <v>216.3313</v>
       </c>
       <c r="G22" t="n">
-        <v>1974404.3</v>
+        <v>7787928.2</v>
       </c>
       <c r="H22" t="inlineStr"/>
     </row>
@@ -1150,27 +1156,27 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>제우스</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>096770</t>
+          <t>079370</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>151300</v>
+        <v>14360</v>
       </c>
       <c r="F23" t="n">
-        <v>5.7998</v>
+        <v>229.1556</v>
       </c>
       <c r="G23" t="n">
-        <v>877513</v>
+        <v>3290673.9</v>
       </c>
       <c r="H23" t="inlineStr"/>
     </row>
@@ -1182,12 +1188,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>티씨머티리얼즈</t>
+          <t>한화엔진</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>125020</t>
+          <t>082740</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1196,13 +1202,13 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6250</v>
+        <v>48600</v>
       </c>
       <c r="F24" t="n">
-        <v>245.7036</v>
+        <v>29.3407</v>
       </c>
       <c r="G24" t="n">
-        <v>1535647.8</v>
+        <v>1425958.7</v>
       </c>
       <c r="H24" t="inlineStr"/>
     </row>
@@ -1214,27 +1220,27 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>비나텍</t>
+          <t>동국제약</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>126340</t>
+          <t>086450</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>94900</v>
+        <v>22900</v>
       </c>
       <c r="F25" t="n">
-        <v>231.1678</v>
+        <v>14.3698</v>
       </c>
       <c r="G25" t="n">
-        <v>21937825.9</v>
+        <v>329067.4</v>
       </c>
       <c r="H25" t="inlineStr"/>
     </row>
@@ -1246,27 +1252,27 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BNK금융지주</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>138930</t>
+          <t>089890</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>16020</v>
+        <v>36450</v>
       </c>
       <c r="F26" t="n">
-        <v>41.0821</v>
+        <v>240.7443</v>
       </c>
       <c r="G26" t="n">
-        <v>658134.8</v>
+        <v>8775130.300000001</v>
       </c>
       <c r="H26" t="inlineStr"/>
     </row>
@@ -1278,12 +1284,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>159010</t>
+          <t>095610</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1292,13 +1298,13 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>32100</v>
+        <v>178400</v>
       </c>
       <c r="F27" t="n">
-        <v>392.9673</v>
+        <v>11.0673</v>
       </c>
       <c r="G27" t="n">
-        <v>12614249.9</v>
+        <v>1974404.3</v>
       </c>
       <c r="H27" t="inlineStr"/>
     </row>
@@ -1310,27 +1316,27 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>222800</t>
+          <t>096770</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>170200</v>
+        <v>151300</v>
       </c>
       <c r="F28" t="n">
-        <v>22.5565</v>
+        <v>5.7998</v>
       </c>
       <c r="G28" t="n">
-        <v>3839119.5</v>
+        <v>877513</v>
       </c>
       <c r="H28" t="inlineStr"/>
     </row>
@@ -1342,27 +1348,27 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>티씨머티리얼즈</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>253590</t>
+          <t>125020</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>15580</v>
+        <v>6250</v>
       </c>
       <c r="F29" t="n">
-        <v>1408.0761</v>
+        <v>245.7036</v>
       </c>
       <c r="G29" t="n">
-        <v>21937825.9</v>
+        <v>1535647.8</v>
       </c>
       <c r="H29" t="inlineStr"/>
     </row>
@@ -1374,12 +1380,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>엘앤씨바이오</t>
+          <t>비나텍</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>290650</t>
+          <t>126340</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1388,10 +1394,10 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>54000</v>
+        <v>94900</v>
       </c>
       <c r="F30" t="n">
-        <v>406.256</v>
+        <v>231.1678</v>
       </c>
       <c r="G30" t="n">
         <v>21937825.9</v>
@@ -1406,12 +1412,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>세아제강</t>
+          <t>BNK금융지주</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>306200</t>
+          <t>138930</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1420,13 +1426,13 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>153700</v>
+        <v>16020</v>
       </c>
       <c r="F31" t="n">
-        <v>7.1366</v>
+        <v>41.0821</v>
       </c>
       <c r="G31" t="n">
-        <v>1096891.3</v>
+        <v>658134.8</v>
       </c>
       <c r="H31" t="inlineStr"/>
     </row>
@@ -1438,31 +1444,29 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>우리금융지주</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>316140</t>
+          <t>159010</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>33750</v>
+        <v>32100</v>
       </c>
       <c r="F32" t="n">
-        <v>572.1789</v>
+        <v>392.9673</v>
       </c>
       <c r="G32" t="n">
-        <v>19311036.7</v>
-      </c>
-      <c r="H32" t="n">
-        <v>1.98</v>
-      </c>
+        <v>12614249.9</v>
+      </c>
+      <c r="H32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1472,12 +1476,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>HD현대에너지솔루션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>322000</t>
+          <t>222800</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1486,13 +1490,13 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>139200</v>
+        <v>170200</v>
       </c>
       <c r="F33" t="n">
-        <v>9.456</v>
+        <v>22.5565</v>
       </c>
       <c r="G33" t="n">
-        <v>1316269.6</v>
+        <v>3839119.5</v>
       </c>
       <c r="H33" t="inlineStr"/>
     </row>
@@ -1504,27 +1508,27 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>RF머트리얼즈</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>327260</t>
+          <t>253590</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>53200</v>
+        <v>15580</v>
       </c>
       <c r="F34" t="n">
-        <v>12.371</v>
+        <v>1408.0761</v>
       </c>
       <c r="G34" t="n">
-        <v>658134.8</v>
+        <v>21937825.9</v>
       </c>
       <c r="H34" t="inlineStr"/>
     </row>
@@ -1536,27 +1540,27 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>DL이앤씨</t>
+          <t>엘앤씨바이오</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>375500</t>
+          <t>290650</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>비중 확대</t>
+          <t>편입</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>75700</v>
+        <v>54000</v>
       </c>
       <c r="F35" t="n">
-        <v>40.5719</v>
+        <v>406.256</v>
       </c>
       <c r="G35" t="n">
-        <v>3071295.6</v>
+        <v>21937825.9</v>
       </c>
       <c r="H35" t="inlineStr"/>
     </row>
@@ -1568,27 +1572,27 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>토모큐브</t>
+          <t>세아제강</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>475960</t>
+          <t>306200</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>34600</v>
+        <v>153700</v>
       </c>
       <c r="F36" t="n">
-        <v>345.5525</v>
+        <v>7.1366</v>
       </c>
       <c r="G36" t="n">
-        <v>11956115.1</v>
+        <v>1096891.3</v>
       </c>
       <c r="H36" t="inlineStr"/>
     </row>
@@ -1600,274 +1604,272 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>달바글로벌</t>
+          <t>우리금융지주</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>483650</t>
+          <t>316140</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>비중 축소</t>
+          <t>편출</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>183400</v>
+        <v>33750</v>
       </c>
       <c r="F37" t="n">
-        <v>110.6461</v>
+        <v>572.1789</v>
       </c>
       <c r="G37" t="n">
-        <v>20292488.9</v>
-      </c>
-      <c r="H37" t="inlineStr"/>
+        <v>19311036.7</v>
+      </c>
+      <c r="H37" t="n">
+        <v>1.98</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>한전기술</t>
+          <t>HD현대에너지솔루션</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>052690</t>
+          <t>322000</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 축소</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>125800</v>
+        <v>139200</v>
       </c>
       <c r="F38" t="n">
-        <v>171.563</v>
+        <v>9.456</v>
       </c>
       <c r="G38" t="n">
-        <v>21582624.3</v>
+        <v>1316269.6</v>
       </c>
       <c r="H38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>타이거일렉</t>
+          <t>RF머트리얼즈</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>219130</t>
+          <t>327260</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>편출</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>91800</v>
+        <v>53200</v>
       </c>
       <c r="F39" t="n">
-        <v>275.5075</v>
+        <v>12.371</v>
       </c>
       <c r="G39" t="n">
-        <v>25291590.7</v>
-      </c>
-      <c r="H39" t="n">
-        <v>21.27</v>
-      </c>
+        <v>658134.8</v>
+      </c>
+      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>2026-09-30</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>토모큐브</t>
+          <t>DL이앤씨</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>475960</t>
+          <t>375500</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>편입</t>
+          <t>비중 확대</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>34750</v>
+        <v>75700</v>
       </c>
       <c r="F40" t="n">
-        <v>912.5508</v>
+        <v>40.5719</v>
       </c>
       <c r="G40" t="n">
-        <v>31711139.3</v>
+        <v>3071295.6</v>
       </c>
       <